--- a/output/Partnerships_Tracker.xlsx
+++ b/output/Partnerships_Tracker.xlsx
@@ -231,8 +231,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tracker" displayName="Tracker" ref="A1:L46" headerRowCount="1">
-  <autoFilter ref="A1:L46"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tracker" displayName="Tracker" ref="A1:L59" headerRowCount="1">
+  <autoFilter ref="A1:L59"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Status"/>
     <tableColumn id="2" name="Country"/>
@@ -558,7 +558,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scope: partnerships that are active, or ended or last active within the past five years. Last checked 2026-09-30.</t>
+          <t>Scope: partnerships that are active, or ended or last active within the past five years. Last checked 2026-10-05.</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF(Tracker!$A$2:$A$46,A5)</f>
+        <f>COUNTIF(Tracker!$A$2:$A$59,A5)</f>
         <v/>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Tracker!$A$2:$A$46,A6)</f>
+        <f>COUNTIF(Tracker!$A$2:$A$59,A6)</f>
         <v/>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Tracker!$A$2:$A$46,A7)</f>
+        <f>COUNTIF(Tracker!$A$2:$A$59,A7)</f>
         <v/>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -670,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -757,12 +757,12 @@
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>Children's Hospital of Philadelphia (CHOP)</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
@@ -772,38 +772,38 @@
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
-          <t>Amrita Hospital, Faridabad</t>
+          <t>Saudi German Hospital Cairo (Saudi German Health)</t>
         </is>
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>Training and education</t>
+          <t>Clinical affiliation</t>
         </is>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
-          <t>CHOP cardiac volunteers provide peer training and donated patient-records software to Amrita Faridabad's pediatric heart program through the NGO Children's HeartLink.</t>
+          <t>Saudi German Hospital Cairo has been a member of the Mayo Clinic Care Network since July 2019, the first in Egypt and Africa, giving its physicians access to Mayo Clinic knowledge and expertise. The relationship was expanded group wide at a signing ceremony in Cairo in October 2025.</t>
         </is>
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019-07</t>
         </is>
       </c>
       <c r="I2" s="12" t="inlineStr"/>
       <c r="J2" s="12" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="K2" s="12" t="inlineStr">
         <is>
-          <t>Children's HeartLink article of 15 October 2024 describes the ongoing CHOP and Amrita Faridabad partnership, with a site assessment in July 2023. Delivered via a third-party NGO.</t>
+          <t>Trade Arabia, 4 October 2025, reports the expanded Mayo Clinic Care Network relationship signed at the Waldorf Astoria Cairo with a Mayo Clinic delegation present. Mayo's 15 July 2019 release (republished by KROC News) confirms membership since 2019.</t>
         </is>
       </c>
       <c r="L2" s="14" t="inlineStr">
         <is>
-          <t>Children's HeartLink, 2024-10-15</t>
+          <t>Trade Arabia, 2025-10-04</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>Cleveland Clinic</t>
+          <t>University of Texas Medical Branch (UTMB Health)</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -830,38 +830,38 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Government of Maharashtra and Arodhan Health City (Navi Mumbai International MediCity); Brookfield Asset Management is a co-signatory investor</t>
+          <t>Badya University</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>Hospital development or joint venture</t>
+          <t>Training and education</t>
         </is>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Clinic signed an MoU to be anchor institution of the planned US$1.2 billion, 250-acre Navi Mumbai International MediCity.</t>
+          <t>Academic partnership under which UTMB provides technical assistance to Badya University's schools of medicine, dentistry and physical therapy, covering curriculum and faculty development, student exchanges and joint research.</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr"/>
       <c r="J3" s="12" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K3" s="12" t="inlineStr">
         <is>
-          <t>MoU signed 10 June 2026 and reported 11 June 2026; the project is at MoU stage with no construction reported.</t>
+          <t>Badya newsroom: UTMB delegation ran a three week academic exchange on 2 to 20 February 2025; Badya students presented posters at the 2026 UTMB Research Summit (21 May 2026); a 'Clinical exchange program at UTMB' item is dated 4 August 2026. Start year from verifier research, not confirmed on a dated page.</t>
         </is>
       </c>
       <c r="L3" s="14" t="inlineStr">
         <is>
-          <t>Free Press Journal, 11 June 2026</t>
+          <t>Badya University</t>
         </is>
       </c>
     </row>
@@ -873,22 +873,22 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>Emory University (Emory Global Diabetes Research Center)</t>
+          <t>AP-HP Beaujon Hospital (with Université Paris Cité)</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>IIT Madras Shankar Center of Excellence in Diabetes Research, with AIIMS, Madras Diabetes Research Foundation and others</t>
+          <t>Theodor Bilharz Research Institute, with Cairo University Faculty of Medicine (Kasr Al Ainy)</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
@@ -898,24 +898,28 @@
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
-          <t>Emory diabetes center co-organized a 2025 Chennai expert workshop and hackathon on technology for diabetes in India, building on the CARRS research network.</t>
-        </is>
-      </c>
-      <c r="H4" s="12" t="inlineStr"/>
+          <t>Long-running cooperation agreement in gastroenterology, hepatology and endoscopy, covering joint scientific meetings, training of Egyptian physicians and researchers at Beaujon and joint research. It was renewed for the fourth time in July 2023 with Cairo University and Université Paris Cité joining.</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
       <c r="I4" s="12" t="inlineStr"/>
       <c r="J4" s="12" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="K4" s="12" t="inlineStr">
         <is>
-          <t>Emory News of 13 May 2025 reports the April 2025 joint event at IIT Madras. Emory Healthcare itself not named; academic center only.</t>
+          <t>Theodor Bilharz Research Institute news item dated 13 April 2025 describes the cooperation as ongoing, reports the higher education minister's endorsement and says the next phase will expand collaboration; the agreement was renewed on 11 July 2023. The Kasr Al Ainy French-language medical degree reported by Al-Fanar was not confirmed on a primary page and is not included.</t>
         </is>
       </c>
       <c r="L4" s="14" t="inlineStr">
         <is>
-          <t>Emory News Center, 2025-05-13</t>
+          <t>Theodor Bilharz Research Institute, 2025-04-13</t>
         </is>
       </c>
     </row>
@@ -927,53 +931,53 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>Alder Hey Children's Hospital (Alder Hey Global)</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Apollo Hospitals</t>
+          <t>Ain Shams University Hospitals</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Clinical affiliation or network membership</t>
+          <t>Training and education</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>Strategic affiliation covering nurse training and recruitment, oncology second opinions and tumor boards, CAR-T and BMT collaboration, and virtual assistant programs.</t>
+          <t>Alder Hey runs annual visiting surgical teams and training in pediatric cardiology and cardiac surgery at Ain Shams, under an MoU signed in June 2025 covering clinical training, research and academic collaboration.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I5" s="12" t="inlineStr"/>
       <c r="J5" s="12" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>Affiliation announced 29 January 2025, within 24 months of today; no later update or end notice found.</t>
+          <t>Ain Shams reports the third annual Alder Hey visiting team (18 complex pediatric heart operations) on 19 July 2026 under the cooperation protocol; Alder Hey news of 30 June 2025 reports the MoU signed by its Global Project Manager for the trust.</t>
         </is>
       </c>
       <c r="L5" s="14" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health, 2025-01-29</t>
+          <t>Alder Hey, 2025-06-30</t>
         </is>
       </c>
     </row>
@@ -985,53 +989,53 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>Johns Hopkins (University)</t>
+          <t>Barraquer Ophthalmology Centre</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Ajit Isaac Foundation, Bengaluru</t>
+          <t>Ministry of Health and Population (Memorial Institute for Ophthalmic Research)</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Training and education</t>
+          <t>Clinical affiliation</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>JHU signed an MoU to help set up rural palliative care centres in India, including caregiver training, curriculum and a research fellowship.</t>
+          <t>Memorandum of understanding covering treatment of complex eye cases in Egypt and Barcelona, training of ophthalmologists and technical staff, and joint research.</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr"/>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>Forbes India (April 2026) reports the foundation's palliative care work with Johns Hopkins continuing, the Tumkur centre opened October 2025, and a joint geriatric centre planned.</t>
+          <t>Barraquer newsroom, 26 February 2026, announces the MoU, signed for Egypt by the director of the Memorial Institute for Ophthalmic Research on behalf of the health minister.</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>Forbes India, 6 April 2026</t>
+          <t>Barraquer, 2026-02-26</t>
         </is>
       </c>
     </row>
@@ -1043,53 +1047,53 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Johns Hopkins (University)</t>
+          <t>Burjeel Holdings (Burjeel Medical City, Burjeel Cancer Institute)</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Dr. D.Y. Patil Medical College and Vidyapeeth, Pune</t>
+          <t>Ministry of Health and Population (Secretariat of Specialized Medical Centers)</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Research collaboration</t>
+          <t>Clinical affiliation</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>JHU and Dr. D.Y. Patil Medical College signed a research MoU in March 2024 and co-run TB and HIV studies in Pune.</t>
+          <t>MoU signed at Arab Health 2025 to develop a comprehensive bone marrow transplant program in Egypt, led by Burjeel Medical City with support from Burjeel Cancer Institute.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr"/>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>A March 2026 trial protocol by Johns Hopkins and D.Y. Patil Medical College authors describes their joint HATHI alcohol, TB and HIV trial now recruiting in Pune.</t>
+          <t>Gulf Today, 30 January 2025, reports the MoU signed by the head of the ministry's Secretariat of Specialized Medical Centers and Burjeel's group CEO in the presence of the health minister. Nothing newer found.</t>
         </is>
       </c>
       <c r="L7" s="14" t="inlineStr">
         <is>
-          <t>Research Square (PubMed 41928807), 25 March 2026</t>
+          <t>Gulf Today, 2025-01-30</t>
         </is>
       </c>
     </row>
@@ -1101,53 +1105,53 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>Johns Hopkins (University)</t>
+          <t>Freiburg University Cancer Center</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>IIT Bombay, Koita Centre for Digital Health</t>
+          <t>National Cancer Institute (new '500500' hospital), Sheikh Zayed</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Research collaboration</t>
+          <t>Clinical affiliation</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>JHU and IIT Bombay's Koita Centre agreed to joint digital-health research and training, co-funding seed grants through the Gupta-Klinsky India Institute.</t>
+          <t>A partnership agreement for scientific cooperation on cancer care, covering hospital equipment and operations and training, for Egypt's new 500500 cancer hospital.</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I8" s="12" t="inlineStr"/>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>IIT Bombay's January 2025 digest reports the joint JHU-KCDH grants program funding two projects, and JHU launched a 2025-26 grant cycle in December 2025.</t>
+          <t>Reported by Egypt's higher education minister at a cabinet meeting on 24 December 2024 (inside the window, so Active under the rule); single Egyptian-side source, no German-side release found. On 14 June 2026 the prime minister directed a partnership with an unnamed global operator to run the 500500 hospital, so the operating role may be unsettled.</t>
         </is>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>Johns Hopkins University, December 2025</t>
+          <t>Daily News Egypt, 2024-12-24</t>
         </is>
       </c>
     </row>
@@ -1159,37 +1163,37 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>Johns Hopkins University (School of Medicine)</t>
+          <t>Gruppo San Donato (with GKSD Group)</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Byramjee Jeejeebhoy Government Medical College and Sassoon General Hospitals, Pune (BJGMC-JHU Clinical Research Site)</t>
+          <t>Ministry of Health and Population and Health Insurance Organization (New Heliopolis Hospital)</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Research collaboration</t>
+          <t>Ownership or management</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>Long-running NIH-funded HIV and TB clinical research site in Pune, part of the ACTG and IMPAACT trial networks since 2008.</t>
+          <t>Agreement signed with Egypt's Health Insurance Organization to manage the New Heliopolis Hospital for 15 years, with the contract starting in 2027 once construction is complete. In September 2026 the health minister met San Donato and GKSD and raised the planned capacity from 424 to 495 beds.</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="I9" s="12" t="inlineStr"/>
@@ -1200,12 +1204,12 @@
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>A September 2026 paper lists the BJGMC-Johns Hopkins University Clinical Research Site as an affiliation, reporting on a joint Pune cohort running from 2023 to the present.</t>
+          <t>Signed 30 March 2026 at EGYPS (Italpress, LaPresse). Daily News Egypt, 28 September 2026, reports the minister's meeting with San Donato, GKSD and Eni on accelerating the hospital. A 1 September 2026 report says the ministry is reviewing a concession proposal for the hospital, naming no party, so the contract may not be final.</t>
         </is>
       </c>
       <c r="L9" s="14" t="inlineStr">
         <is>
-          <t>Journal of the International AIDS Society (PubMed 42764545), 1 September 2026</t>
+          <t>Italpress, 2026-03-31</t>
         </is>
       </c>
     </row>
@@ -1217,53 +1221,53 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>MD Anderson Cancer Center</t>
+          <t>Gustave Roussy (Gustave Roussy International)</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Tata Memorial Centre, Mumbai</t>
+          <t>Gustave Roussy International Egypt (former Dar Al-Salam Hermel Oncology Hospital), with the Egyptian government and Elevate P.E.</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Research collaboration</t>
+          <t>Clinical affiliation</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>MD Anderson and Tata Memorial have a sister-institution agreement from October 2003 supporting clinical trials, faculty exchange and joint programs.</t>
+          <t>Gustave Roussy licensed its brand to a Cairo cancer center (the former Dar Al-Salam Hermel Oncology Hospital) that opened in April 2025, in partnership with the Egyptian government and Elevate P.E., with training of Egyptian staff. The Universal Health Insurance Authority signed a services agreement with the center in May 2025.</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>2003-10</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr"/>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>In December 2024 MD Anderson and Tata Memorial announced a joint session at the SACT cell therapy summit in Navi Mumbai, 6 to 9 March 2025.</t>
+          <t>Gustave Roussy news page published 9 April 2025 confirms the brand licensing agreement and opening; Amwal Al Ghad reports the UHIA services agreement signed 28 May 2025. Nothing newer found.</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>OncoDaily, 4 December 2024</t>
+          <t>Gustave Roussy, 2025-04-09</t>
         </is>
       </c>
     </row>
@@ -1275,32 +1279,32 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>University of Oxford</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>AIIMS New Delhi (Departments of Pathology and Nephrology)</t>
+          <t>National Cancer Institute (new '500500' hospital), Cairo University</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>Training and education</t>
+          <t>Research collaboration</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>AIIMS and Mayo Clinic jointly organised a two-day continuing education update in kidney diseases and transplant in Delhi.</t>
+          <t>Memorandum of understanding to develop gene therapy for cancer at the new 500500 National Cancer Institute hospital.</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
@@ -1316,155 +1320,155 @@
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>The AIIMS-Mayo Clinic Update in Kidney Diseases and Transplant was held 7 to 8 December 2024 with Mayo faculty; no later edition was found.</t>
+          <t>Reported by the higher education minister at the cabinet meeting of 24 December 2024 alongside the Freiburg agreement (inside the window, so Active under the rule); single Egyptian-side source, no Oxford-side release or later evidence found.</t>
         </is>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
-          <t>Event website, 7-8 December 2024</t>
+          <t>Daily News Egypt, 2024-12-24</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>Active</t>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Great Ormond Street Hospital for Children NHS Foundation Trust</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Adani Group (Adani Health City, Ahmedabad and Mumbai; planned Kolkata campus)</t>
+          <t>Ain Shams University Hospitals (Children's Hospital)</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Consulting or management</t>
+          <t>Training and education</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>Mayo Clinic Global Consulting advises Adani on planned 1,000-bed Adani Health City campuses in Ahmedabad and Mumbai; a Kolkata campus was reported in 2026.</t>
+          <t>Five year program funded by the CIB Foundation in intensive care, hematology and oncology, with visiting GOSH consultants, a clinical education program and observerships in London.</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2020-08</t>
         </is>
       </c>
       <c r="I12" s="12" t="inlineStr"/>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>A July 2026 report says Adani's third health city, in Kolkata, will be built in technical collaboration with Mayo Clinic; Mayo has not commented publicly.</t>
+          <t>Contract signed August 2020 (GOV.UK). Ain Shams reported a GOSH delegation visit 'activating the partnership' on 8 December 2021. The five year term would have run to about 2025; no later evidence found.</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>Digital Health News, 6 July 2026</t>
+          <t>GOV.UK, 2020-08-19</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Active</t>
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Royal Brompton and Harefield Hospitals (Guy's and St Thomas' NHS Foundation Trust)</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Lilavati Hospital, GIFT City, Gujarat</t>
+          <t>Ain Shams University Hospitals (Cardiovascular Diseases and Surgery Hospital)</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Consulting or management</t>
+          <t>Clinical affiliation</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>Mayo Clinic Global Consulting advises Lilavati's new GIFT City hospital, which opened its first phase in 2026, on clinical practice and patient safety.</t>
+          <t>Cooperation protocol signed in November 2021 to build an aortic surgery center at Ain Shams, with visiting British surgical teams, clinical systems development, education and research. A second protocol in June 2022, with Essentia Trending, covers development of the Ain Shams Oncology Center.</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2021-11</t>
         </is>
       </c>
       <c r="I13" s="12" t="inlineStr"/>
       <c r="J13" s="12" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>An April 2026 report on the GIFT City hospital's first phase opening says Lilavati has partnered with Mayo Clinic for training and technology transfer.</t>
+          <t>Ain Shams news: protocol 15 November 2021; oncology protocol 16 June 2022; a Royal Brompton aortic team visit announced for 13 to 18 January 2024 (news of 4 January 2024). Nothing newer found.</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
-          <t>The Indian Practitioner, 22 April 2026</t>
+          <t>Ain Shams University, 2021-11-15</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Active</t>
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>University of Hertfordshire</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Lilavati Hospital, Mumbai</t>
+          <t>Cleopatra Hospitals Group</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -1474,28 +1478,28 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>Mayo ran a Nursing Excellence Training Program for 120 Lilavati nurses and is collaborating on a planned 300-bed cancer institute in Mumbai.</t>
+          <t>MoU on clinical pharmacy, pharmaceutical care, IT, training and research.</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr"/>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>Lilavati's news page records its promoter meeting Mayo Clinic leaders at Lilavati Hospital Mumbai on 23 September 2025, after the March 2025 nurse training.</t>
+          <t>Cleopatra press release of 12 July 2023; nothing newer found. Signed with the university's Cairo branch.</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>Lilavati Hospital, 23 September 2025</t>
+          <t>Cleopatra Hospitals Group, 2023-07-12</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1516,7 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Children's Hospital of Philadelphia (CHOP)</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -1522,38 +1526,38 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Ramaiah Memorial Hospital, Bengaluru</t>
+          <t>Amrita Hospital, Faridabad</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>Clinical affiliation or network membership</t>
+          <t>Training and education</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Ten-year exclusive collaboration from 2024 on centers of excellence, quality, technology and joint review of complex cases.</t>
+          <t>CHOP cardiac volunteers provide peer training and donated patient-records software to Amrita Faridabad's pediatric heart program through the NGO Children's HeartLink.</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr"/>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>Ramaiah's press release of 28 September 2026 states the hospital is affiliated with Mount Sinai International, New York; original deal signed July 2024.</t>
+          <t>Children's HeartLink article of 15 October 2024 describes the ongoing CHOP and Amrita Faridabad partnership, with a site assessment in July 2023. Delivered via a third-party NGO.</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>Business Standard, 28 September 2026</t>
+          <t>Children's HeartLink, 2024-10-15</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1574,7 @@
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>Rutgers Robert Wood Johnson Medical School (Rutgers Health)</t>
+          <t>Cleveland Clinic</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -1580,38 +1584,38 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Govind Ballabh Pant Institute of Postgraduate Medical Education and Research (GIPMER), New Delhi</t>
+          <t>Government of Maharashtra and Arodhan Health City (Navi Mumbai International MediCity); Brookfield Asset Management is a co-signatory investor</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>Research collaboration</t>
+          <t>Hospital development or joint venture</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>MOU between the RWJMS cardiovascular division and GIPMER for cardiovascular research, AI, digital health, biobanking and clinical trials.</t>
+          <t>Cleveland Clinic signed an MoU to be anchor institution of the planned US$1.2 billion, 250-acre Navi Mumbai International MediCity.</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr"/>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>MOU signed in September 2025 during the New Jersey governor's mission to India; announcement is within 24 months.</t>
+          <t>MoU signed 10 June 2026 and reported 11 June 2026; the project is at MoU stage with no construction reported.</t>
         </is>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>Insider NJ, 2025-09-19</t>
+          <t>Free Press Journal, 11 June 2026</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1632,7 @@
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Emory University (Emory Global Diabetes Research Center)</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -1638,38 +1642,34 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>National Cancer Grid (NCG) India, including Tata Memorial network centres</t>
+          <t>IIT Madras Shankar Center of Excellence in Diabetes Research, with AIIMS, Madras Diabetes Research Foundation and others</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>Training and education</t>
+          <t>Research collaboration</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Stanford quality improvement training and mentoring helped build EQuIP India, a national cancer care quality improvement program run by the National Cancer Grid.</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
+          <t>Emory diabetes center co-organized a 2025 Chennai expert workshop and hackathon on technology for diabetes in India, building on the CARRS research network.</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr"/>
       <c r="I17" s="12" t="inlineStr"/>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>Stanford Global Health post of 18 April 2025 reports EQuIP India spreading across India and thanks Stanford partners; program started 2017.</t>
+          <t>Emory News of 13 May 2025 reports the April 2025 joint event at IIT Madras. Emory Healthcare itself not named; academic center only.</t>
         </is>
       </c>
       <c r="L17" s="14" t="inlineStr">
         <is>
-          <t>Stanford Global Health, 2025-04-18</t>
+          <t>Emory News Center, 2025-05-13</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>Stanford Medicine (Emergency Medicine International, Center for Innovation in Global Health)</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -1696,38 +1696,38 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Emergency Management and Research Institute (EMRI), India</t>
+          <t>Apollo Hospitals</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>Research collaboration</t>
+          <t>Clinical affiliation or network membership</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>Long-running collaboration on emergency medical services systems and research between Stanford emergency medicine faculty and India's EMRI ambulance network.</t>
+          <t>Strategic affiliation covering nurse training and recruitment, oncology second opinions and tumor boards, CAR-T and BMT collaboration, and virtual assistant programs.</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr"/>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>Stanford page of 17 June 2025 describes EMRI leaders visiting Stanford in spring 2025 and collaborating with faculty for decades. Start year not stated.</t>
+          <t>Affiliation announced 29 January 2025, within 24 months of today; no later update or end notice found.</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>Stanford Global Health, 2025-06-17</t>
+          <t>Hackensack Meridian Health, 2025-01-29</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>Thomas Jefferson University / Jefferson Health (Jefferson India Center)</t>
+          <t>Johns Hopkins (University)</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1754,20 +1754,24 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>KLE Academy of Higher Education and Research (J N Medical College, Belagavi); LV Prasad Eye Institute, Hyderabad (listed by Jefferson, no recent dated activity)</t>
+          <t>Ajit Isaac Foundation, Bengaluru</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Research collaboration</t>
+          <t>Training and education</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>Jefferson India Center runs maternal and child health and eye research with KLE and LV Prasad Eye Institute.</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr"/>
+          <t>JHU signed an MoU to help set up rural palliative care centres in India, including caregiver training, curriculum and a research fellowship.</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
       <c r="I19" s="12" t="inlineStr"/>
       <c r="J19" s="12" t="inlineStr">
         <is>
@@ -1776,12 +1780,12 @@
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>KLE and Jefferson co-authored an April 2026 RAPIDIRON trial paper, and Jefferson's March 2026 Global Jefferson Day featured the Jefferson India Center with a KLE keynote.</t>
+          <t>Forbes India (April 2026) reports the foundation's palliative care work with Johns Hopkins continuing, the Tumkur centre opened October 2025, and a joint geriatric centre planned.</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>Journal of Maternal-Fetal and Neonatal Medicine (PubMed 42045095), 27 April 2026</t>
+          <t>Forbes India, 6 April 2026</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1802,7 @@
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>Johns Hopkins (University)</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -1808,7 +1812,7 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>All India Institute of Medical Sciences, New Delhi</t>
+          <t>Dr. D.Y. Patil Medical College and Vidyapeeth, Pune</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -1818,28 +1822,28 @@
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>UCLA's GRACE program and AIIMS are implementing quantitative blood loss measurement to reduce postpartum hemorrhage, with phase 1 training completed.</t>
+          <t>JHU and Dr. D.Y. Patil Medical College signed a research MoU in March 2024 and co-run TB and HIV studies in Pune.</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr"/>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>UCLA's page says phase 1 at AIIMS trained 52 staff; the dated Summer 2025 newsletter reports a 2025-26 seed grant for the same QBL project.</t>
+          <t>A March 2026 trial protocol by Johns Hopkins and D.Y. Patil Medical College authors describes their joint HATHI alcohol, TB and HIV trial now recruiting in Pune.</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>UCLA Health, Summer 2025</t>
+          <t>Research Square (PubMed 41928807), 25 March 2026</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1860,7 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>Johns Hopkins (University)</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1866,22 +1870,22 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Federation of Obstetric and Gynaecological Societies of India (FOGSI) and SAFOG</t>
+          <t>IIT Bombay, Koita Centre for Digital Health</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>Training and education</t>
+          <t>Research collaboration</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>UCLA OB/GYN holds virtual guideline discussions and simulation exchanges with FOGSI and the South Asian federation.</t>
+          <t>JHU and IIT Bombay's Koita Centre agreed to joint digital-health research and training, co-funding seed grants through the Gupta-Klinsky India Institute.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>2020-01</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="I21" s="12" t="inlineStr"/>
@@ -1892,12 +1896,12 @@
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>A UCLA Health article of 8 December 2025 describes these virtual exchanges with FOGSI as results of ongoing global programs; start date not given.</t>
+          <t>IIT Bombay's January 2025 digest reports the joint JHU-KCDH grants program funding two projects, and JHU launched a 2025-26 grant cycle in December 2025.</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>UCLA Health, 8 December 2025</t>
+          <t>Johns Hopkins University, December 2025</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1918,7 @@
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>Johns Hopkins University (School of Medicine)</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
@@ -1924,38 +1928,38 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Narendra Modi Medical College, Ahmedabad</t>
+          <t>Byramjee Jeejeebhoy Government Medical College and Sassoon General Hospitals, Pune (BJGMC-JHU Clinical Research Site)</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>Training and education</t>
+          <t>Research collaboration</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>UCLA OB/GYN runs a resident and faculty exchange with Narendra Modi Medical College, with joint academic seminars.</t>
+          <t>Long-running NIH-funded HIV and TB clinical research site in Pune, part of the ACTG and IMPAACT trial networks since 2008.</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr"/>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>UCLA OB/GYN's page and Summer 2025 newsletter describe the exchange continuing, with the first joint lecture held in summer 2025.</t>
+          <t>A September 2026 paper lists the BJGMC-Johns Hopkins University Clinical Research Site as an affiliation, reporting on a joint Pune cohort running from 2023 to the present.</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>UCLA Health, Summer 2025</t>
+          <t>Journal of the International AIDS Society (PubMed 42764545), 1 September 2026</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1976,7 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>University of Alabama at Birmingham (Heersink School of Medicine)</t>
+          <t>MD Anderson Cancer Center</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -1982,38 +1986,38 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Pravara Institute of Medical Sciences (Loni) and Bharati Vidyapeeth Medical College (Pune)</t>
+          <t>Tata Memorial Centre, Mumbai</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>Training and education</t>
+          <t>Research collaboration</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>MOU for faculty and student exchange, training and joint research with two Maharashtra medical institutions.</t>
+          <t>MD Anderson and Tata Memorial have a sister-institution agreement from October 2003 supporting clinical trials, faculty exchange and joint programs.</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2003-10</t>
         </is>
       </c>
       <c r="I23" s="12" t="inlineStr"/>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>UAB news item of 29 July 2025 reports the signed MOU and faculty visits and workshops already held.</t>
+          <t>In December 2024 MD Anderson and Tata Memorial announced a joint session at the SACT cell therapy summit in Navi Mumbai, 6 to 9 March 2025.</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>UAB Medicine, 2025-07-29</t>
+          <t>OncoDaily, 4 December 2024</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2034,7 @@
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>University of California San Francisco (Francis I. Proctor Foundation)</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -2040,34 +2044,38 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Aravind Eye Care System, Madurai</t>
+          <t>AIIMS New Delhi (Departments of Pathology and Nephrology)</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>Research collaboration</t>
+          <t>Training and education</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>Long-standing joint clinical trials in corneal infection with Aravind, including SCUT II (2025) and REAGIR (follow-up published 2026).</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="inlineStr"/>
+          <t>AIIMS and Mayo Clinic jointly organised a two-day continuing education update in kidney diseases and transplant in Delhi.</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
       <c r="I24" s="12" t="inlineStr"/>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>JAMA Ophthalmology published 12-month results of the REAGIR trial, run at Aravind hospitals with the UCSF Proctor Foundation, in August 2026.</t>
+          <t>The AIIMS-Mayo Clinic Update in Kidney Diseases and Transplant was held 7 to 8 December 2024 with Mayo faculty; no later edition was found.</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>JAMA Ophthalmology (PubMed 42348235), 1 August 2026</t>
+          <t>Event website, 7-8 December 2024</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2092,7 @@
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>University of Iowa (Carver College of Medicine, Ophthalmology)</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -2094,38 +2102,38 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Dr. Shroff's Charity Eye Hospital, New Delhi</t>
+          <t>Adani Group (Adani Health City, Ahmedabad and Mumbai; planned Kolkata campus)</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>Training and education</t>
+          <t>Consulting or management</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>MoU signed in early 2024 for trainee and faculty exchange and joint research in ophthalmology.</t>
+          <t>Mayo Clinic Global Consulting advises Adani on planned 1,000-bed Adani Health City campuses in Ahmedabad and Mumbai; a Kolkata campus was reported in 2026.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="I25" s="12" t="inlineStr"/>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>A February 2025 Iowa Lions Eye Bank article reports a University of Iowa ophthalmologist visiting Shroff's in November 2024 and training its fellows in DMEK surgery.</t>
+          <t>A July 2026 report says Adani's third health city, in Kolkata, will be built in technical collaboration with Mayo Clinic; Mayo has not commented publicly.</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>Iowa Lions Eye Bank, 1 February 2025</t>
+          <t>Digital Health News, 6 July 2026</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2150,7 @@
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>University of Michigan Medical School / Michigan Medicine</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -2152,34 +2160,38 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>AIIMS Jammu</t>
+          <t>Lilavati Hospital, GIFT City, Gujarat</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>Training and education</t>
+          <t>Consulting or management</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>Michigan faculty co-led two international academic events at AIIMS Jammu in late 2025 on critical care of the injured and lung cancer precision oncology.</t>
-        </is>
-      </c>
-      <c r="H26" s="12" t="inlineStr"/>
+          <t>Mayo Clinic Global Consulting advises Lilavati's new GIFT City hospital, which opened its first phase in 2026, on clinical practice and patient safety.</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
       <c r="I26" s="12" t="inlineStr"/>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>Collegehai report of 14 November 2025 says AIIMS Jammu ran the conferences in collaboration with the University of Michigan. Formal agreement terms not seen.</t>
+          <t>An April 2026 report on the GIFT City hospital's first phase opening says Lilavati has partnered with Mayo Clinic for training and technology transfer.</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>CollegeHai, 2025-11-14</t>
+          <t>The Indian Practitioner, 22 April 2026</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2208,7 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Madison Department of Ophthalmology and Visual Sciences (UW Health)</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -2206,7 +2218,7 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Dr. Shroff's Charity Eye Hospital, New Delhi</t>
+          <t>Lilavati Hospital, Mumbai</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -2216,28 +2228,28 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Annual resident and faculty clinical and research rotation at Shroff's Charity Eye Hospital, marking a decade of partnership in 2025.</t>
+          <t>Mayo ran a Nursing Excellence Training Program for 120 Lilavati nurses and is collaborating on a planned 300-bed cancer institute in Mumbai.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr"/>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>Department post of 28 February 2025 reports a rotation held 31 January to 15 February 2025 and a decade of partnership.</t>
+          <t>Lilavati's news page records its promoter meeting Mayo Clinic leaders at Lilavati Hospital Mumbai on 23 September 2025, after the March 2025 nurse training.</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>UW-Madison Ophthalmology, 2025-02-28</t>
+          <t>Lilavati Hospital, 23 September 2025</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2266,7 @@
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>Weill Cornell Medicine (Center for Global Health)</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
@@ -2264,22 +2276,22 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Byramjee Jeejeebhoy Government Medical College and Sassoon Hospital, Pune; Deep Griha Society</t>
+          <t>Ramaiah Memorial Hospital, Bengaluru</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>Research collaboration</t>
+          <t>Clinical affiliation or network membership</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>Joint research and training in Pune on tuberculosis in pregnancy, HIV, gestational diabetes and maternal depression since 2009.</t>
+          <t>Ten-year exclusive collaboration from 2024 on centers of excellence, quality, technology and joint review of complex cases.</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr"/>
@@ -2290,12 +2302,12 @@
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>A September 2026 paper by Weill Cornell and BJ Government Medical College authors uses their joint Pune pregnancy cohort, PRAGATHi, which runs from 2023 to the present.</t>
+          <t>Ramaiah's press release of 28 September 2026 states the hospital is affiliated with Mount Sinai International, New York; original deal signed July 2024.</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>Journal of the International AIDS Society (PubMed 42764545), 1 September 2026</t>
+          <t>Business Standard, 28 September 2026</t>
         </is>
       </c>
     </row>
@@ -2312,44 +2324,48 @@
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>Cambridge University Hospitals NHS Foundation Trust (with Cambridge Global Health Partnerships)</t>
+          <t>Rutgers Robert Wood Johnson Medical School (Rutgers Health)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Himalayan Hospital (Dehradun) and Ganga Prem Hospice, Rishikesh, via Rama Foundation</t>
+          <t>Govind Ballabh Pant Institute of Postgraduate Medical Education and Research (GIPMER), New Delhi</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>Training and education</t>
+          <t>Research collaboration</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Uttarakhand-Cambridge Health Partnership: volunteer NHS nurses and allied health staff co-deliver palliative and cancer care training in Uttarakhand.</t>
-        </is>
-      </c>
-      <c r="H29" s="12" t="inlineStr"/>
+          <t>MOU between the RWJMS cardiovascular division and GIPMER for cardiovascular research, AI, digital health, biobanking and clinical trials.</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
       <c r="I29" s="12" t="inlineStr"/>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>CUH team visited Rishikesh and Dehradun in August 2025; Rama Foundation links with CUH staff are described as running about 15 years.</t>
+          <t>MOU signed in September 2025 during the New Jersey governor's mission to India; announcement is within 24 months.</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>Cambridge University Hospitals NHS Foundation Trust, 6 August 2025</t>
+          <t>Insider NJ, 2025-09-19</t>
         </is>
       </c>
     </row>
@@ -2366,48 +2382,48 @@
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>Juntendo University (Tokyo)</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Saint Hardyal Educational and Orphans' Welfare Society (SHEOWS), Delhi</t>
+          <t>National Cancer Grid (NCG) India, including Tata Memorial network centres</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>Research collaboration</t>
+          <t>Training and education</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>MoU for dementia and geriatric research, academic exchange and advisory support for a planned geriatric hospital and research centre.</t>
+          <t>Stanford quality improvement training and mentoring helped build EQuIP India, a national cancer care quality improvement program run by the National Cancer Grid.</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr"/>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>MoU signed in Tokyo and announced 10 August 2026; Indian partner is a nonprofit elder care society.</t>
+          <t>Stanford Global Health post of 18 April 2025 reports EQuIP India spreading across India and thanks Stanford partners; program started 2017.</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>The Wire (PTI), 2026-08-10</t>
+          <t>Stanford Global Health, 2025-04-18</t>
         </is>
       </c>
     </row>
@@ -2424,48 +2440,48 @@
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>King's College London and Guy's and St Thomas' NHS Foundation Trust</t>
+          <t>Stanford Medicine (Emergency Medicine International, Center for Innovation in Global Health)</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>P. D. Hinduja Hospital and Medical Research Centre, Mumbai (National Health &amp; Education Society)</t>
+          <t>Emergency Management and Research Institute (EMRI), India</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>Training and education</t>
+          <t>Research collaboration</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Hinduja-King's Health Partners Academy delivering clinical and nursing leadership training, research capacity building and funded PhD and MSc scholarships for Indian students.</t>
+          <t>Long-running collaboration on emergency medical services systems and research between Stanford emergency medicine faculty and India's EMRI ambulance network.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="I31" s="12" t="inlineStr"/>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>Nursing leadership course began May 2025; first scholars began October 2025 and 2026-27 scholarship calls opened in May 2026.</t>
+          <t>Stanford page of 17 June 2025 describes EMRI leaders visiting Stanford in spring 2025 and collaborating with faculty for decades. Start year not stated.</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>Free Press Journal, 2026-05-22</t>
+          <t>Stanford Global Health, 2025-06-17</t>
         </is>
       </c>
     </row>
@@ -2482,17 +2498,17 @@
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>Monash University (Faculty of Information Technology)</t>
+          <t>Thomas Jefferson University / Jefferson Health (Jefferson India Center)</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Apollo Hospitals and The Apollo University</t>
+          <t>KLE Academy of Higher Education and Research (J N Medical College, Belagavi); LV Prasad Eye Institute, Hyderabad (listed by Jefferson, no recent dated activity)</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -2502,28 +2518,24 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>MoUs on health AI research and education, including access to de-identified Apollo patient data and joint certification programmes.</t>
-        </is>
-      </c>
-      <c r="H32" s="12" t="inlineStr">
-        <is>
-          <t>2023-12</t>
-        </is>
-      </c>
+          <t>Jefferson India Center runs maternal and child health and eye research with KLE and LV Prasad Eye Institute.</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr"/>
       <c r="I32" s="12" t="inlineStr"/>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>University MoU signed December 2023; a further Apollo Hospitals data partnership was reported November 2024, within 24 months. No later news found.</t>
+          <t>KLE and Jefferson co-authored an April 2026 RAPIDIRON trial paper, and Jefferson's March 2026 Global Jefferson Day featured the Jefferson India Center with a KLE keynote.</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>Digital Health News, 2024-11-29</t>
+          <t>Journal of Maternal-Fetal and Neonatal Medicine (PubMed 42045095), 27 April 2026</t>
         </is>
       </c>
     </row>
@@ -2540,48 +2552,48 @@
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>SingHealth</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Athulya Senior Care, Chennai</t>
+          <t>All India Institute of Medical Sciences, New Delhi</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>Training and education</t>
+          <t>Research collaboration</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>MoU to explore collaboration in senior care services, professional training, research and knowledge exchange with annual joint programmes planned.</t>
+          <t>UCLA's GRACE program and AIIMS are implementing quantitative blood loss measurement to reduce postpartum hemorrhage, with phase 1 training completed.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="I33" s="12" t="inlineStr"/>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>MoU announced April 2026, within 24 months; Indian partner is an assisted-living provider rather than a hospital.</t>
+          <t>UCLA's page says phase 1 at AIIMS trained 52 staff; the dated Summer 2025 newsletter reports a 2025-26 seed grant for the same QBL project.</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>VOH Network, 2026-04-29</t>
+          <t>UCLA Health, Summer 2025</t>
         </is>
       </c>
     </row>
@@ -2598,48 +2610,48 @@
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>University College London</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>AIIMS New Delhi and IIT Delhi</t>
+          <t>Federation of Obstetric and Gynaecological Societies of India (FOGSI) and SAFOG</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>Research collaboration</t>
+          <t>Training and education</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>Trilateral agreement to advance medical technology research and innovation using shared industry connections.</t>
+          <t>UCLA OB/GYN holds virtual guideline discussions and simulation exchanges with FOGSI and the South Asian federation.</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2020-01</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr"/>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>UCL announced in November 2025 the first seven jointly funded UCL-AIIMS-IIT Delhi medtech research projects under the November 2024 agreement.</t>
+          <t>A UCLA Health article of 8 December 2025 describes these virtual exchanges with FOGSI as results of ongoing global programs; start date not given.</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>University College London, November 2025</t>
+          <t>UCLA Health, 8 December 2025</t>
         </is>
       </c>
     </row>
@@ -2656,48 +2668,48 @@
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>University of Leicester and University Hospitals of Leicester NHS Trust</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Apollo Hospitals and The Apollo University</t>
+          <t>Narendra Modi Medical College, Ahmedabad</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>Research collaboration</t>
+          <t>Training and education</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>Centre for Digital Health and Precision Medicine with hubs at Chittoor and Glenfield Hospital Leicester, focused on cardiovascular, emergency medicine and multimorbidity research.</t>
+          <t>UCLA OB/GYN runs a resident and faculty exchange with Narendra Modi Medical College, with joint academic seminars.</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I35" s="12" t="inlineStr"/>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>Centre launched January 2025 and held its first major joint conference on 14 and 15 July 2026.</t>
+          <t>UCLA OB/GYN's page and Summer 2025 newsletter describe the exchange continuing, with the first joint lecture held in summer 2025.</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>Indian Pharma Post, 2026-07-16</t>
+          <t>UCLA Health, Summer 2025</t>
         </is>
       </c>
     </row>
@@ -2714,17 +2726,17 @@
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>University of Leicester, University Hospitals of Leicester NHS Trust and BAPIO Training Academy</t>
+          <t>University of Alabama at Birmingham (Heersink School of Medicine)</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Apollo Health Resources (Apollo Hospitals)</t>
+          <t>Pravara Institute of Medical Sciences (Loni) and Bharati Vidyapeeth Medical College (Pune)</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -2734,28 +2746,28 @@
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>2+2 postgraduate residency: two years of training at Apollo Hospitals in India, then two years supervised residency in NHS hospitals.</t>
+          <t>MOU for faculty and student exchange, training and joint research with two Maharashtra medical institutions.</t>
         </is>
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="I36" s="12" t="inlineStr"/>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>Programme announced October 2025; Leicester-Apollo partnership was still described as ongoing at the July 2026 joint conference.</t>
+          <t>UAB news item of 29 July 2025 reports the signed MOU and faculty visits and workshops already held.</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>Indian Pharma Post, 2026-07-16</t>
+          <t>UAB Medicine, 2025-07-29</t>
         </is>
       </c>
     </row>
@@ -2772,17 +2784,17 @@
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>University of Liverpool</t>
+          <t>University of California San Francisco (Francis I. Proctor Foundation)</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Saveetha Institute of Medical and Technical Sciences (SIMATS), Chennai</t>
+          <t>Aravind Eye Care System, Madurai</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
@@ -2792,35 +2804,31 @@
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>Five-year MoU in health and life sciences covering joint research, student exchange and academic events, including a medical student summer school.</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
+          <t>Long-standing joint clinical trials in corneal infection with Aravind, including SCUT II (2025) and REAGIR (follow-up published 2026).</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr"/>
       <c r="I37" s="12" t="inlineStr"/>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>MoU signed in Chennai with the British Deputy High Commission present; announced July 2025, within 24 months, with a five-year term.</t>
+          <t>JAMA Ophthalmology published 12-month results of the REAGIR trial, run at Aravind hospitals with the UCSF Proctor Foundation, in August 2026.</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>University of Liverpool, 2025-07-14</t>
+          <t>JAMA Ophthalmology (PubMed 42348235), 1 August 2026</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t>Unclear</t>
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
@@ -2830,7 +2838,7 @@
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>Cleveland Clinic</t>
+          <t>University of Iowa (Carver College of Medicine, Ophthalmology)</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
@@ -2840,45 +2848,45 @@
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Group</t>
+          <t>Dr. Shroff's Charity Eye Hospital, New Delhi</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>Telemedicine or second opinion</t>
+          <t>Training and education</t>
         </is>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>Apollo doctors can request international second opinions from The Clinic by Cleveland Clinic, Cleveland Clinic's virtual second-opinion arm.</t>
+          <t>MoU signed in early 2024 for trainee and faculty exchange and joint research in ophthalmology.</t>
         </is>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr"/>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>Launched January 2022 per Indian press; no source found confirming the service running after that, and no source reporting an end.</t>
+          <t>A February 2025 Iowa Lions Eye Bank article reports a University of Iowa ophthalmologist visiting Shroff's in November 2024 and training its fellows in DMEK surgery.</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>Telangana Today, January 2022</t>
+          <t>Iowa Lions Eye Bank, 1 February 2025</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>Unclear</t>
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
@@ -2888,7 +2896,7 @@
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>Johns Hopkins (University)</t>
+          <t>University of Michigan Medical School / Michigan Medicine</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -2898,7 +2906,7 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>College of Nursing, Christian Medical College Vellore</t>
+          <t>AIIMS Jammu</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
@@ -2908,35 +2916,31 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>The Johns Hopkins School of Nursing and CMC Vellore's College of Nursing signed an MoU for joint research, faculty and student exchange.</t>
-        </is>
-      </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
+          <t>Michigan faculty co-led two international academic events at AIIMS Jammu in late 2025 on critical care of the injured and lung cancer precision oncology.</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr"/>
       <c r="I39" s="12" t="inlineStr"/>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>A joint JHU-CMC nursing paper published October 2024 reviews their partnership, but it reports only the 2021 webinar series; no current joint activity found.</t>
+          <t>Collegehai report of 14 November 2025 says AIIMS Jammu ran the conferences in collaboration with the University of Michigan. Formal agreement terms not seen.</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>Journal of Psychiatric and Mental Health Nursing (PubMed 39361448), 3 October 2024</t>
+          <t>CollegeHai, 2025-11-14</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t>Unclear</t>
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="B40" s="12" t="inlineStr">
@@ -2946,7 +2950,7 @@
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>University of Wisconsin-Madison Department of Ophthalmology and Visual Sciences (UW Health)</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
@@ -2956,22 +2960,22 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>AIG Hospitals, Hyderabad</t>
+          <t>Dr. Shroff's Charity Eye Hospital, New Delhi</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>Clinical affiliation or network membership</t>
+          <t>Training and education</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>AIG Hospitals joined the Mayo Clinic Care Network in 2019 as the first Indian member, with eConsults and eBoards.</t>
+          <t>Annual resident and faculty clinical and research rotation at Shroff's Charity Eye Hospital, marking a decade of partnership in 2025.</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr"/>
@@ -2982,19 +2986,19 @@
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>Joined October 2019; the only later source, a February 2025 news report, cites 2023 Mayo filings listing an unnamed Indian member, not current AIG activity.</t>
+          <t>Department post of 28 February 2025 reports a rotation held 31 January to 15 February 2025 and a decade of partnership.</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>Post Bulletin, 11 February 2025</t>
+          <t>UW-Madison Ophthalmology, 2025-02-28</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>Unclear</t>
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
@@ -3004,7 +3008,7 @@
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering</t>
+          <t>Weill Cornell Medicine (Center for Global Health)</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -3014,45 +3018,45 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>iCliniq, Chennai (MSKCC India)</t>
+          <t>Byramjee Jeejeebhoy Government Medical College and Sassoon Hospital, Pune; Deep Griha Society</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>Telemedicine or second opinion</t>
+          <t>Research collaboration</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>MSK launched MSKCC India with iCliniq in August 2021 to give Indian patients remote second opinions, plus education and research access.</t>
+          <t>Joint research and training in Pune on tuberculosis in pregnancy, HIV, gestational diabetes and maternal depression since 2009.</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="I41" s="12" t="inlineStr"/>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>Launched 2 August 2021; iCliniq's MSK India pages now return HTTP 410 (removed) and no source after 2021 shows the service running or ended.</t>
+          <t>A September 2026 paper by Weill Cornell and BJ Government Medical College authors uses their joint Pune pregnancy cohort, PRAGATHi, which runs from 2023 to the present.</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>PR Newswire, 2 August 2021</t>
+          <t>Journal of the International AIDS Society (PubMed 42764545), 1 September 2026</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>Unclear</t>
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
@@ -3062,55 +3066,51 @@
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>Northwell Health (Center for Global Health)</t>
+          <t>Cambridge University Hospitals NHS Foundation Trust (with Cambridge Global Health Partnerships)</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Christian Medical College (CMC) Vellore</t>
+          <t>Himalayan Hospital (Dehradun) and Ganga Prem Hospice, Rishikesh, via Rama Foundation</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>Clinical affiliation or network membership</t>
+          <t>Training and education</t>
         </is>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>Five-year MOU for medical student and resident exchange and development of both systems' clinical services.</t>
-        </is>
-      </c>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>2023-03</t>
-        </is>
-      </c>
+          <t>Uttarakhand-Cambridge Health Partnership: volunteer NHS nurses and allied health staff co-deliver palliative and cancer care training in Uttarakhand.</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr"/>
       <c r="I42" s="12" t="inlineStr"/>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>MOU signed 24 March 2023 for five years, so term runs to about 2028, but no dated source from October 2024 onward was found. Northwell page blocked.</t>
+          <t>CUH team visited Rishikesh and Dehradun in August 2025; Rama Foundation links with CUH staff are described as running about 15 years.</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>Northwell Health, 2023-03</t>
+          <t>Cambridge University Hospitals NHS Foundation Trust, 6 August 2025</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>Unclear</t>
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
@@ -3120,17 +3120,17 @@
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>LMU Klinikum (University Hospital Munich)</t>
+          <t>Juntendo University (Tokyo)</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>AIIMS New Delhi</t>
+          <t>Saint Hardyal Educational and Orphans' Welfare Society (SHEOWS), Delhi</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
@@ -3140,35 +3140,35 @@
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>Non-binding MoU to explore joint research, faculty and student exchange, and multicentre clinical trials.</t>
+          <t>MoU for dementia and geriatric research, academic exchange and advisory support for a planned geriatric hospital and research centre.</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="I43" s="12" t="inlineStr"/>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>Signed September 2023; specific projects were left to separate agreements, and no later activity was found.</t>
+          <t>MoU signed in Tokyo and announced 10 August 2026; Indian partner is a nonprofit elder care society.</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>Careers360, 2023-09-16</t>
+          <t>The Wire (PTI), 2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
-        <is>
-          <t>Unclear</t>
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>University of Bolton Institute of Medicine (now University of Greater Manchester Medical School)</t>
+          <t>King's College London and Guy's and St Thomas' NHS Foundation Trust</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
@@ -3188,160 +3188,914 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>AIIMS New Delhi</t>
+          <t>P. D. Hinduja Hospital and Medical Research Centre, Mumbai (National Health &amp; Education Society)</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>Research collaboration</t>
+          <t>Training and education</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>MoU on medical research, innovation, education, staff and student exchange and collaborative degree programmes.</t>
+          <t>Hinduja-King's Health Partners Academy delivering clinical and nursing leadership training, research capacity building and funded PhD and MSc scholarships for Indian students.</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr"/>
       <c r="J44" s="12" t="inlineStr">
         <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="K44" s="12" t="inlineStr">
+        <is>
+          <t>Nursing leadership course began May 2025; first scholars began October 2025 and 2026-27 scholarship calls opened in May 2026.</t>
+        </is>
+      </c>
+      <c r="L44" s="14" t="inlineStr">
+        <is>
+          <t>Free Press Journal, 2026-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>Monash University (Faculty of Information Technology)</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals and The Apollo University</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>MoUs on health AI research and education, including access to de-identified Apollo patient data and joint certification programmes.</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="inlineStr"/>
+      <c r="J45" s="12" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="K45" s="12" t="inlineStr">
+        <is>
+          <t>University MoU signed December 2023; a further Apollo Hospitals data partnership was reported November 2024, within 24 months. No later news found.</t>
+        </is>
+      </c>
+      <c r="L45" s="14" t="inlineStr">
+        <is>
+          <t>Digital Health News, 2024-11-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>SingHealth</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>Athulya Senior Care, Chennai</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>MoU to explore collaboration in senior care services, professional training, research and knowledge exchange with annual joint programmes planned.</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="inlineStr"/>
+      <c r="J46" s="12" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="K46" s="12" t="inlineStr">
+        <is>
+          <t>MoU announced April 2026, within 24 months; Indian partner is an assisted-living provider rather than a hospital.</t>
+        </is>
+      </c>
+      <c r="L46" s="14" t="inlineStr">
+        <is>
+          <t>VOH Network, 2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>University College London</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>AIIMS New Delhi and IIT Delhi</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>Trilateral agreement to advance medical technology research and innovation using shared industry connections.</t>
+        </is>
+      </c>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="I47" s="12" t="inlineStr"/>
+      <c r="J47" s="12" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="K47" s="12" t="inlineStr">
+        <is>
+          <t>UCL announced in November 2025 the first seven jointly funded UCL-AIIMS-IIT Delhi medtech research projects under the November 2024 agreement.</t>
+        </is>
+      </c>
+      <c r="L47" s="14" t="inlineStr">
+        <is>
+          <t>University College London, November 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>University of Leicester and University Hospitals of Leicester NHS Trust</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals and The Apollo University</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>Centre for Digital Health and Precision Medicine with hubs at Chittoor and Glenfield Hospital Leicester, focused on cardiovascular, emergency medicine and multimorbidity research.</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr"/>
+      <c r="J48" s="12" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="K48" s="12" t="inlineStr">
+        <is>
+          <t>Centre launched January 2025 and held its first major joint conference on 14 and 15 July 2026.</t>
+        </is>
+      </c>
+      <c r="L48" s="14" t="inlineStr">
+        <is>
+          <t>Indian Pharma Post, 2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>University of Leicester, University Hospitals of Leicester NHS Trust and BAPIO Training Academy</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>Apollo Health Resources (Apollo Hospitals)</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>2+2 postgraduate residency: two years of training at Apollo Hospitals in India, then two years supervised residency in NHS hospitals.</t>
+        </is>
+      </c>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="I49" s="12" t="inlineStr"/>
+      <c r="J49" s="12" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="K49" s="12" t="inlineStr">
+        <is>
+          <t>Programme announced October 2025; Leicester-Apollo partnership was still described as ongoing at the July 2026 joint conference.</t>
+        </is>
+      </c>
+      <c r="L49" s="14" t="inlineStr">
+        <is>
+          <t>Indian Pharma Post, 2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>University of Liverpool</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>Saveetha Institute of Medical and Technical Sciences (SIMATS), Chennai</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>Five-year MoU in health and life sciences covering joint research, student exchange and academic events, including a medical student summer school.</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr"/>
+      <c r="J50" s="12" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="K50" s="12" t="inlineStr">
+        <is>
+          <t>MoU signed in Chennai with the British Deputy High Commission present; announced July 2025, within 24 months, with a five-year term.</t>
+        </is>
+      </c>
+      <c r="L50" s="14" t="inlineStr">
+        <is>
+          <t>University of Liverpool, 2025-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t>Cleveland Clinic</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals Group</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>Telemedicine or second opinion</t>
+        </is>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>Apollo doctors can request international second opinions from The Clinic by Cleveland Clinic, Cleveland Clinic's virtual second-opinion arm.</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="I51" s="12" t="inlineStr"/>
+      <c r="J51" s="12" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="K51" s="12" t="inlineStr">
+        <is>
+          <t>Launched January 2022 per Indian press; no source found confirming the service running after that, and no source reporting an end.</t>
+        </is>
+      </c>
+      <c r="L51" s="14" t="inlineStr">
+        <is>
+          <t>Telangana Today, January 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>Johns Hopkins (University)</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
+        <is>
+          <t>College of Nursing, Christian Medical College Vellore</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>The Johns Hopkins School of Nursing and CMC Vellore's College of Nursing signed an MoU for joint research, faculty and student exchange.</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I52" s="12" t="inlineStr"/>
+      <c r="J52" s="12" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="K52" s="12" t="inlineStr">
+        <is>
+          <t>A joint JHU-CMC nursing paper published October 2024 reviews their partnership, but it reports only the 2021 webinar series; no current joint activity found.</t>
+        </is>
+      </c>
+      <c r="L52" s="14" t="inlineStr">
+        <is>
+          <t>Journal of Psychiatric and Mental Health Nursing (PubMed 39361448), 3 October 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>AIG Hospitals, Hyderabad</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>Clinical affiliation or network membership</t>
+        </is>
+      </c>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>AIG Hospitals joined the Mayo Clinic Care Network in 2019 as the first Indian member, with eConsults and eBoards.</t>
+        </is>
+      </c>
+      <c r="H53" s="12" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="I53" s="12" t="inlineStr"/>
+      <c r="J53" s="12" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="K53" s="12" t="inlineStr">
+        <is>
+          <t>Joined October 2019; the only later source, a February 2025 news report, cites 2023 Mayo filings listing an unnamed Indian member, not current AIG activity.</t>
+        </is>
+      </c>
+      <c r="L53" s="14" t="inlineStr">
+        <is>
+          <t>Post Bulletin, 11 February 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>Memorial Sloan Kettering</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
+        <is>
+          <t>iCliniq, Chennai (MSKCC India)</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>Telemedicine or second opinion</t>
+        </is>
+      </c>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>MSK launched MSKCC India with iCliniq in August 2021 to give Indian patients remote second opinions, plus education and research access.</t>
+        </is>
+      </c>
+      <c r="H54" s="12" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="I54" s="12" t="inlineStr"/>
+      <c r="J54" s="12" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="K54" s="12" t="inlineStr">
+        <is>
+          <t>Launched 2 August 2021; iCliniq's MSK India pages now return HTTP 410 (removed) and no source after 2021 shows the service running or ended.</t>
+        </is>
+      </c>
+      <c r="L54" s="14" t="inlineStr">
+        <is>
+          <t>PR Newswire, 2 August 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>Northwell Health (Center for Global Health)</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>Christian Medical College (CMC) Vellore</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>Clinical affiliation or network membership</t>
+        </is>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>Five-year MOU for medical student and resident exchange and development of both systems' clinical services.</t>
+        </is>
+      </c>
+      <c r="H55" s="12" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="I55" s="12" t="inlineStr"/>
+      <c r="J55" s="12" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="K55" s="12" t="inlineStr">
+        <is>
+          <t>MOU signed 24 March 2023 for five years, so term runs to about 2028, but no dated source from October 2024 onward was found. Northwell page blocked.</t>
+        </is>
+      </c>
+      <c r="L55" s="14" t="inlineStr">
+        <is>
+          <t>Northwell Health, 2023-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>LMU Klinikum (University Hospital Munich)</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>AIIMS New Delhi</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>Non-binding MoU to explore joint research, faculty and student exchange, and multicentre clinical trials.</t>
+        </is>
+      </c>
+      <c r="H56" s="12" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="I56" s="12" t="inlineStr"/>
+      <c r="J56" s="12" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="K56" s="12" t="inlineStr">
+        <is>
+          <t>Signed September 2023; specific projects were left to separate agreements, and no later activity was found.</t>
+        </is>
+      </c>
+      <c r="L56" s="14" t="inlineStr">
+        <is>
+          <t>Careers360, 2023-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>University of Bolton Institute of Medicine (now University of Greater Manchester Medical School)</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>AIIMS New Delhi</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>MoU on medical research, innovation, education, staff and student exchange and collaborative degree programmes.</t>
+        </is>
+      </c>
+      <c r="H57" s="12" t="inlineStr">
+        <is>
           <t>2024-05</t>
         </is>
       </c>
-      <c r="K44" s="12" t="inlineStr">
+      <c r="I57" s="12" t="inlineStr"/>
+      <c r="J57" s="12" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="K57" s="12" t="inlineStr">
         <is>
           <t>Signed virtually in May 2024; announcement is over 24 months old and no later activity was found.</t>
         </is>
       </c>
-      <c r="L44" s="14" t="inlineStr">
+      <c r="L57" s="14" t="inlineStr">
         <is>
           <t>All India Radio News, 2024-05-15</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="16" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="16" t="inlineStr">
         <is>
           <t>Ended</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="C45" s="13" t="inlineStr">
+      <c r="C58" s="13" t="inlineStr">
         <is>
           <t>Johns Hopkins (Medicine International)</t>
         </is>
       </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="D58" s="12" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E58" s="12" t="inlineStr">
         <is>
           <t>HCL Healthcare</t>
         </is>
       </c>
-      <c r="F45" s="12" t="inlineStr">
+      <c r="F58" s="12" t="inlineStr">
         <is>
           <t>Consulting or management</t>
         </is>
       </c>
-      <c r="G45" s="12" t="inlineStr">
+      <c r="G58" s="12" t="inlineStr">
         <is>
           <t>Johns Hopkins Medicine International signed a 10-year affiliation in February 2014 covering clinical programs, training and quality advice for HCL's clinics.</t>
         </is>
       </c>
-      <c r="H45" s="12" t="inlineStr">
+      <c r="H58" s="12" t="inlineStr">
         <is>
           <t>2014-02</t>
         </is>
       </c>
-      <c r="I45" s="12" t="inlineStr">
+      <c r="I58" s="12" t="inlineStr">
         <is>
           <t>2024-02</t>
         </is>
       </c>
-      <c r="J45" s="12" t="inlineStr">
+      <c r="J58" s="12" t="inlineStr">
         <is>
           <t>2014-02</t>
         </is>
       </c>
-      <c r="K45" s="12" t="inlineStr">
+      <c r="K58" s="12" t="inlineStr">
         <is>
           <t>JHMI signed a 10-year affiliation in February 2014; the term expired about February 2024 and no renewal or later activity was found.</t>
         </is>
       </c>
-      <c r="L45" s="14" t="inlineStr">
+      <c r="L58" s="14" t="inlineStr">
         <is>
           <t>Domain-b, 6 February 2014</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="16" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="16" t="inlineStr">
         <is>
           <t>Ended</t>
         </is>
       </c>
-      <c r="B46" s="12" t="inlineStr">
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="C46" s="13" t="inlineStr">
+      <c r="C59" s="13" t="inlineStr">
         <is>
           <t>MD Anderson Cancer Center</t>
         </is>
       </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="D59" s="12" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E59" s="12" t="inlineStr">
         <is>
           <t>Tata Memorial Hospital, Mumbai (Project ECHO Palliative Care Africa II)</t>
         </is>
       </c>
-      <c r="F46" s="12" t="inlineStr">
+      <c r="F59" s="12" t="inlineStr">
         <is>
           <t>Training and education</t>
         </is>
       </c>
-      <c r="G46" s="12" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t>Tata Memorial took part in MD Anderson's Project ECHO videoconference network for palliative care in Africa and India.</t>
         </is>
       </c>
-      <c r="H46" s="12" t="inlineStr">
+      <c r="H59" s="12" t="inlineStr">
         <is>
           <t>2023-05</t>
         </is>
       </c>
-      <c r="I46" s="12" t="inlineStr">
+      <c r="I59" s="12" t="inlineStr">
         <is>
           <t>2025-01</t>
         </is>
       </c>
-      <c r="J46" s="12" t="inlineStr">
+      <c r="J59" s="12" t="inlineStr">
         <is>
           <t>2025-01</t>
         </is>
       </c>
-      <c r="K46" s="12" t="inlineStr">
+      <c r="K59" s="12" t="inlineStr">
         <is>
           <t>MD Anderson's program page gives the ECHO-PACA schedule as May 2023 to January 2025 and still lists Tata Memorial; no extension was found.</t>
         </is>
       </c>
-      <c r="L46" s="14" t="inlineStr">
+      <c r="L59" s="14" t="inlineStr">
         <is>
           <t>MD Anderson Cancer Center, undated</t>
         </is>
@@ -3394,10 +4148,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId46"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId59"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3408,7 +4175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3448,1043 +4215,1039 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Children's Hospital of Philadelphia (CHOP)</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Amrita Hospital, Faridabad</t>
+          <t>Saudi German Hospital Cairo (Saudi German Health)</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Children's HeartLink From Philadelphia to Faridabad, This Hospital Partnership Is Transforming Heart Care for Children in India</t>
+          <t>Trade Arabia Saudi German Health boosts relationship with Mayo Clinic</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>https://childrensheartlink.org/from-philadelphia-to-faridabad-this-hospital-partnership-is-transforming-heart-care-for-children-in-india/</t>
+          <t>https://tradearabia.com/News/328805/Saudi-German-Health-boosts-relationship-with-Mayo-Clinic</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Cleveland Clinic</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Government of Maharashtra and Arodhan Health City (Navi Mumbai International MediCity); Brookfield Asset Management is a co-signatory investor</t>
+          <t>Saudi German Hospital Cairo (Saudi German Health)</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Kalpesh Mhamunkar Maharashtra Signs MoU With Cleveland Clinic And Brookfield For Navi Mumbai International MediCity, India's First Global-Scale Healthcare Hub</t>
+          <t>Mayo Clinic News Network Saudi German Health strengthens relationship with Mayo Clinic, becoming largest group of Mayo Clinic Care Network members in the region</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>11 June 2026</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-signs-mou-with-cleveland-clinic-and-brookfield-for-navi-mumbai-international-medicity-indias-first-global-scale-healthcare-hub</t>
+          <t>https://newsnetwork.mayoclinic.org/discussion/saudi-german-health-strengthens-relationship-with-mayo-clinic-becoming-largest-group-of-mayo-clinic-care-network-members-in-the-region/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Emory University (Emory Global Diabetes Research Center)</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>IIT Madras Shankar Center of Excellence in Diabetes Research, with AIIMS, Madras Diabetes Research Foundation and others</t>
+          <t>Saudi German Hospital Cairo (Saudi German Health)</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Myra C. Nwafor Emory students propose innovative solutions to diabetes care in India</t>
+          <t>Mayo Clinic News Network Saudi German Hospital Cairo joins Mayo Clinic Care Network</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2019-07-15</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>https://news.emory.edu/stories/2025/05/hs_diabetes_care_india_13-05-2025/story.html</t>
+          <t>https://newsnetwork.mayoclinic.org/discussion/saudi-german-hospital-cairo-joins-mayo-clinic-care-network/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Apollo Hospitals</t>
+          <t>Saudi German Hospital Cairo (Saudi German Health)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health Hackensack Meridian Health and Apollo Hospitals Bridge Continents to Advance Healthcare Innovation and Delivery</t>
+          <t>Andy Brownell Egyptian Hospital Joins Mayo Clinic Care Network</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2019-07-15</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>https://www.hackensackmeridianhealth.org/en/news/2025/01/29/hmh-and-apollo-hospitals-bridge-continents-to-advance-healthcare</t>
+          <t>https://krocnews.com/egyptian-hospital-joins-mayo-clinic-care-network/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>University of Texas Medical Branch (UTMB Health)</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Apollo Hospitals</t>
+          <t>Badya University</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>BW Online Bureau Apollo Hospitals &amp; Hackensack Meridian Health Forge Strategic Affiliation</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>2025-01-31</t>
-        </is>
-      </c>
+          <t>Badya University Academic Partnership</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>https://www.bwhealthcareworld.com/article/apollo-hospitals-hackensack-meridian-health-forge-strategic-affiliation-546583</t>
+          <t>https://www.badyauni.edu.eg/about-badya-university/academic-partnership/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins (University)</t>
+          <t>University of Texas Medical Branch (UTMB Health)</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Ajit Isaac Foundation, Bengaluru</t>
+          <t>Badya University</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Forbes India From beginning to end of life: Ajit and Sarah Isaac fill in the blanks</t>
+          <t>Badya University UTMB Delegation Engages in Three-Week Academic Exchange with Badya University</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>6 April 2026</t>
+          <t>2025-02-23</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>https://www.forbesindia.com/article/leadership/from-beginning-to-end-of-life-ajit-and-sarah-isaac-fill-in-the-blanks/2992863/1</t>
+          <t>https://www.badyauni.edu.eg/utmb-delegation-engages-in-three-week-academic-exchange-with-badya-university/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins (University)</t>
+          <t>University of Texas Medical Branch (UTMB Health)</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Ajit Isaac Foundation, Bengaluru</t>
+          <t>Badya University</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Devdiscourse Global Partnership Pioneers Palliative Care in Underserved India</t>
+          <t>Badya University Presentation of research posters at the 2026 UTMB Research Summit in Galveston, Texas</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>November 2024</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/health/3165425-global-partnership-pioneers-palliative-care-in-underserved-india</t>
+          <t>https://www.badyauni.edu.eg/presentation-of-research-posters-at-the-2026-utmb-research-summit-in-galveston-texas/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins (University)</t>
+          <t>University of Texas Medical Branch (UTMB Health)</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Ajit Isaac Foundation, Bengaluru</t>
+          <t>Badya University</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>IndiaMedToday Johns Hopkins University signs MoU with Ajit Isaac Foundation</t>
+          <t>Badya University Badya University Takes Confident Steps Toward Leadership in Medical Education (news listing incl. 'Clinical exchange program at UTMB', 4 August 2026)</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>November 2024</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>https://indiamedtoday.com/johns-hopkins-university-signs-mou-with-ajit-isaac-foundation/</t>
+          <t>https://www.badyauni.edu.eg/?p=1534</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins (University)</t>
+          <t>AP-HP Beaujon Hospital (with Université Paris Cité)</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Dr. D.Y. Patil Medical College and Vidyapeeth, Pune</t>
+          <t>Theodor Bilharz Research Institute, with Cairo University Faculty of Medicine (Kasr Al Ainy)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>HATHI study authors (Johns Hopkins University; Dr. D.Y. Patil Medical College, Hospital and Research Centre; BJGMC and others) Hybrid trial for Alcohol reduction among people with TB and HIV in India (HATHI): Protocol for a Hybrid Type 1 Effectiveness-Implementation Randomized Controlled Trial</t>
+          <t>Theodor Bilharz Research Institute Sustainable Academic and Research Cooperation with Beaujon Hospital, with the Participation of Cairo University and Université Paris Cité</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>25 March 2026</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/41928807/</t>
+          <t>https://www.tbri.sci.eg/en/institute-news/sustainable-academic-and-research-cooperation-with-beaujon-hospital</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins (University)</t>
+          <t>Alder Hey Children's Hospital (Alder Hey Global)</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Dr. D.Y. Patil Medical College and Vidyapeeth, Pune</t>
+          <t>Ain Shams University Hospitals</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Medical Dialogues Dr DY Patil Medical College, Johns Hopkins University join hands for Collaborative Research</t>
+          <t>Alder Hey Children's Hospital Alder Hey and Ain Shams University sign official partnership</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>13 March 2024</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/education/medical-colleges/dr-dy-patil-medical-college-johns-hopkins-university-join-hands-for-collaborative-research-125812</t>
+          <t>https://www.alderhey.nhs.uk/?p=112799</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins (University)</t>
+          <t>Alder Hey Children's Hospital (Alder Hey Global)</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Dr. D.Y. Patil Medical College and Vidyapeeth, Pune</t>
+          <t>Ain Shams University Hospitals</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Gupta-Klinsky India Institute, Johns Hopkins University Partnership Meetings</t>
+          <t>Ain Shams University Unprecedented Medical Achievement: 18 Complex Pediatric Heart Surgeries Successfully Performed at Ain Shams University Hospitals in Collaboration with British Experts</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>undated</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>https://indiainstitute.jhu.edu/events-2025/past-events/events-2024/jhu-india-trip-2024/partnership-meetings/</t>
+          <t>https://www.asu.edu.eg/10235/news</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins (University)</t>
+          <t>Barraquer Ophthalmology Centre</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>IIT Bombay, Koita Centre for Digital Health</t>
+          <t>Ministry of Health and Population (Memorial Institute for Ophthalmic Research)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Gupta-Klinsky India Institute News from GKII 2025 (launch of 2025-26 GKII-KCDH Data Science and AI Breakthrough Research Grants)</t>
+          <t>Barraquer We signed a collaboration agreement with the Ministry of Health and Population of Egypt</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>December 2025</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>https://indiainstitute.jhu.edu/news/news-2025/news-from-gkii-2025/</t>
+          <t>https://www.barraquer.com/en/news/we-signed-collaboration-agreement-ministry-health-population-egypt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins (University)</t>
+          <t>Burjeel Holdings (Burjeel Medical City, Burjeel Cancer Institute)</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>IIT Bombay, Koita Centre for Digital Health</t>
+          <t>Ministry of Health and Population (Secretariat of Specialized Medical Centers)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Koita Centre for Digital Health KCDH Digest: achievements between January and December 2024</t>
+          <t>Gulf Today Egypt's Health Ministry, Burjeel Holdings collaborate to develop advanced BMT program</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>January 2025</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>https://www.kcdh.iitb.ac.in/site/newsletter-document/a6abea01-50ce-11f0-9b5b-fbbec49cc3fb.pdf</t>
+          <t>https://gulftoday.ae/business/2025/01/30/egypts-health-ministry-burjeel-holdings-collaborate-to-develop-advanced-bmt-program</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins (University)</t>
+          <t>Freiburg University Cancer Center</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>IIT Bombay, Koita Centre for Digital Health</t>
+          <t>National Cancer Institute (new '500500' hospital), Sheikh Zayed</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Gupta-Klinsky India Institute, Johns Hopkins University Collaboration Agreement with IIT Bombay and Roundtable Discussion Shine a Spotlight on Digital Health</t>
+          <t>Daily News Egypt '500500' Hospital project to enhance cancer care, says Egyptian PM</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>undated</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>https://indiainstitute.jhu.edu/news/news-2025/news-from-gkii/collaboration-agreement-with-iit-bombay-and-roundtable-discussion-shine-a-spotlight-on-digital-health</t>
+          <t>https://www.dailynewsegypt.com/2024/12/24/500500-hospital-project-to-enhance-cancer-care-says-egyptian-pm/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins (University)</t>
+          <t>Freiburg University Cancer Center</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>IIT Bombay, Koita Centre for Digital Health</t>
+          <t>National Cancer Institute (new '500500' hospital), Sheikh Zayed</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Gupta-Klinsky India Institute, Johns Hopkins University GKII X KCDH Breakthrough Grants on Digital Health (2024)</t>
+          <t>Safia Hamdi Prime Minister: partnership with a global operator to run the 500500 hospital (Arabic)</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>https://indiainstitute.jhu.edu/?p=4857</t>
+          <t>https://almalnews.com/2119185/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins University (School of Medicine)</t>
+          <t>Gruppo San Donato (with GKSD Group)</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Byramjee Jeejeebhoy Government Medical College and Sassoon General Hospitals, Pune (BJGMC-JHU Clinical Research Site)</t>
+          <t>Ministry of Health and Population and Health Insurance Organization (New Heliopolis Hospital)</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>BJGMC, Weill Cornell Medicine and Johns Hopkins authors Dolutegravir Is Associated With Lower Odds of Gestational Diabetes Compared to Other Antiretroviral Therapy Regimens Among Pregnant Women in India: A Cross-Sectional Analysis</t>
+          <t>Italpress GKSD and Gruppo San Donato sign agreement to manage new hospital in Egypt</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>1 September 2026</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42764545/</t>
+          <t>https://www.italpress.com/?p=665165</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins University (School of Medicine)</t>
+          <t>Gruppo San Donato (with GKSD Group)</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Byramjee Jeejeebhoy Government Medical College and Sassoon General Hospitals, Pune (BJGMC-JHU Clinical Research Site)</t>
+          <t>Ministry of Health and Population and Health Insurance Organization (New Heliopolis Hospital)</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>BJGMC, Weill Cornell Medicine, Johns Hopkins and Columbia authors Impact of maternal HIV infection on the gut microbiome and metabolome of mothers and infants: the PRACHITi cohort in Pune, India</t>
+          <t>LaPresse Il Gruppo San Donato gestirà per 15 anni un nuovo ospedale al Cairo</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>23 February 2026</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/41730922/</t>
+          <t>https://www.lapresse.it/salute/sanita/2026/03/31/il-gruppo-san-donato-gestira-per-15-anni-nuovo-ospedale-al-cairo/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins University (School of Medicine)</t>
+          <t>Gruppo San Donato (with GKSD Group)</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Byramjee Jeejeebhoy Government Medical College and Sassoon General Hospitals, Pune (BJGMC-JHU Clinical Research Site)</t>
+          <t>Ministry of Health and Population and Health Insurance Organization (New Heliopolis Hospital)</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins University BJGMC (India): BJGMC-JHU CRS</t>
+          <t>Daily News Egypt Health ministry accelerates New Heliopolis Hospital project, raises capacity to 495 beds</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>undated</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>http://jhubi-ctu.jhu.edu/our-sites/bjgmc-india</t>
+          <t>https://www.dailynewsegypt.com/2026/09/28/health-ministry-accelerates-new-heliopolis-hospital-project-raises-capacity-to-495-beds/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>MD Anderson Cancer Center</t>
+          <t>Gruppo San Donato (with GKSD Group)</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Tata Memorial Centre, Mumbai</t>
+          <t>Ministry of Health and Population and Health Insurance Organization (New Heliopolis Hospital)</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>OncoDaily Joint session by MD Anderson Cancer Center and Tata Memorial Centre at SACT 2025 Summit</t>
+          <t>Daily News Egypt Health Ministry reviews concession to operate New Heliopolis Hospital</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>4 December 2024</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>https://oncodaily.com/blog/md-anderson-cancer-center-197733</t>
+          <t>https://www.dailynewsegypt.com/2026/09/01/health-ministry-reviews-concession-to-operate-new-heliopolis-hospital/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>MD Anderson Cancer Center</t>
+          <t>Gustave Roussy (Gustave Roussy International)</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Tata Memorial Centre, Mumbai</t>
+          <t>Gustave Roussy International Egypt (former Dar Al-Salam Hermel Oncology Hospital), with the Egyptian government and Elevate P.E.</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>India Herald MD Anderson Cancer Center signs sister institution accord with Tata Memorial</t>
+          <t>Gustave Roussy Opening of the First Gustave Roussy-Branded Facility in Egypt</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>17 October 2003</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>https://india-herald.com/md-anderson-cancer-center-signs-sister-institution-accord-with-tata-memoria-p305-19.htm</t>
+          <t>https://www.gustaveroussy.fr/en/news-opening-first-gustave-roussy-branded-facility-egypt</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Gustave Roussy (Gustave Roussy International)</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>AIIMS New Delhi (Departments of Pathology and Nephrology)</t>
+          <t>Gustave Roussy International Egypt (former Dar Al-Salam Hermel Oncology Hospital), with the Egyptian government and Elevate P.E.</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AIIMS New Delhi AIIMS Mayo Clinic Update in Kidney Diseases and Transplant 2024</t>
+          <t>Amwal Al Ghad Egypt's UHIA signs oncology care deal with Gustave Roussy</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>7-8 December 2024</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>https://aiimsmayoclinicupdate2024.com/</t>
+          <t>https://en.amwalalghad.com/?p=203380</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>University of Oxford</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Adani Group (Adani Health City, Ahmedabad and Mumbai; planned Kolkata campus)</t>
+          <t>National Cancer Institute (new '500500' hospital), Cairo University</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Digital Health News Adani Group to Set Up INR 2,500 Crore Health City in West Bengal with Mayo Clinic Collaboration</t>
+          <t>Daily News Egypt '500500' Hospital project to enhance cancer care, says Egyptian PM</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>6 July 2026</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>https://www.digitalhealthnews.com/adani-group-to-invest-inr-2-500-cr-in-health-city-project-in-west-bengal</t>
+          <t>https://www.dailynewsegypt.com/2024/12/24/500500-hospital-project-to-enhance-cancer-care-says-egyptian-pm/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Great Ormond Street Hospital for Children NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Adani Group (Adani Health City, Ahmedabad and Mumbai; planned Kolkata campus)</t>
+          <t>Ain Shams University Hospitals (Children's Hospital)</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Adani Group Adani to Partner Mayo Clinic to Establish Affordable World Class Healthcare Facilities</t>
+          <t>British Embassy Cairo GOSH Hospital signs a five-year contract with Ain Shams University Hospital</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>10 February 2025</t>
+          <t>2020-08-19</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>https://www.adani.com/newsroom/media-releases/adani-to-partner-mayo-clinic-to-establish-affordable-world-class-healthcare-facilities</t>
+          <t>https://www.gov.uk/government/news/gosh-hospital-signs-a-five-year-contract-with-ain-shams-university-hospital</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Great Ormond Street Hospital for Children NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Adani Group (Adani Health City, Ahmedabad and Mumbai; planned Kolkata campus)</t>
+          <t>Ain Shams University Hospitals (Children's Hospital)</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Post Bulletin Billionaire to partner with Mayo Clinic on India hospitals</t>
+          <t>Ain Shams University Activating the partnership between Ain Shams University Hospitals and GOSH British Hospital</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>11 February 2025</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>https://www.postbulletin.com/business/billionaire-to-partner-with-mayo-clinic-on-india-hospitals</t>
+          <t>https://www.asu.edu.eg/3337/news</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Royal Brompton and Harefield Hospitals (Guy's and St Thomas' NHS Foundation Trust)</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Lilavati Hospital, GIFT City, Gujarat</t>
+          <t>Ain Shams University Hospitals (Cardiovascular Diseases and Surgery Hospital)</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>The Indian Practitioner Lilavati Expands Globally and Domestically with Mauritius, GIFT City Projects</t>
+          <t>Ain Shams University A cooperation protocol between Ain Shams University Hospitals, Royal Brompton and Harefield Hospitals</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>22 April 2026</t>
+          <t>2021-11-15</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>https://theindianpractitioner.com/lilavati-expands-globally-and-domestically-with-mauritius-gift-city-projects/</t>
+          <t>https://www.asu.edu.eg/3150/news</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Royal Brompton and Harefield Hospitals (Guy's and St Thomas' NHS Foundation Trust)</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Lilavati Hospital, GIFT City, Gujarat</t>
+          <t>Ain Shams University Hospitals (Cardiovascular Diseases and Surgery Hospital)</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Lilavati Hospital News and Media</t>
+          <t>Ain Shams University A cooperation protocol between Ain Shams University Hospitals, Guy's Hospital, St. Thomas Hospital, NHS and Essentia Trending Limited</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>23 September 2025</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>https://www.lilavati-hospital.com/news-and-media.php</t>
+          <t>https://www.asu.edu.eg/4427/news</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Royal Brompton and Harefield Hospitals (Guy's and St Thomas' NHS Foundation Trust)</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Lilavati Hospital, GIFT City, Gujarat</t>
+          <t>Ain Shams University Hospitals (Cardiovascular Diseases and Surgery Hospital)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Press Trust of India Lilavati Hospital, Mayo Clinic to establish 300-bed cancer institute in Mumbai</t>
+          <t>Ain Shams University The British Royal Brompton crew arrives at the Heart Academy on January 13</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>24 January 2025</t>
+          <t>2024-01-04</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>https://medicalbuyer.co.in/lilavati-hospital-mayo-clinic-to-establish-300-bed-cancer-institute-in-mumbai/</t>
+          <t>https://www.asu.edu.eg/7191/news</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>University of Hertfordshire</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Lilavati Hospital, GIFT City, Gujarat</t>
+          <t>Cleopatra Hospitals Group</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>VMPL Lilavati Hospital in Gift City, Gujarat has engaged with Mayo Clinic Global Consulting to enhance the patient care standards</t>
+          <t>Cleopatra Hospitals Group Cleopatra Hospitals Group signs MoU with the University of Hertfordshire</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>20 March 2024</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/content/press-releases-ani/lilavati-hospital-in-gift-city-gujarat-has-engaged-with-mayo-clinic-global-consulting-to-enhance-the-patient-care-standards-124032000688_1.html</t>
+          <t>https://cleopatrahospitals.com/en/media-center/cleopatra-hospitals-group-is-proud-to-announce-the-signing-of-a-memorandum-of-understanding-mou-with-the-university-of-hertfordshire</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Children's Hospital of Philadelphia (CHOP)</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Lilavati Hospital, Mumbai</t>
+          <t>Amrita Hospital, Faridabad</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Lilavati Hospital News and Media</t>
+          <t>Children's HeartLink From Philadelphia to Faridabad, This Hospital Partnership Is Transforming Heart Care for Children in India</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>23 September 2025</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>https://www.lilavati-hospital.com/news-and-media.php</t>
+          <t>https://childrensheartlink.org/from-philadelphia-to-faridabad-this-hospital-partnership-is-transforming-heart-care-for-children-in-india/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Cleveland Clinic</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Lilavati Hospital, Mumbai</t>
+          <t>Government of Maharashtra and Arodhan Health City (Navi Mumbai International MediCity); Brookfield Asset Management is a co-signatory investor</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Kajal Rajput Mayo Clinic, Lilavati Hospital complete India's first Nursing Excellence Training Program</t>
+          <t>Kalpesh Mhamunkar Maharashtra Signs MoU With Cleveland Clinic And Brookfield For Navi Mumbai International MediCity, India's First Global-Scale Healthcare Hub</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>29 March 2025</t>
+          <t>11 June 2026</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/health/hospital-diagnostics/mayo-clinic-lilavati-hospital-complete-indias-first-nursing-excellence-training-program-145698</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-signs-mou-with-cleveland-clinic-and-brookfield-for-navi-mumbai-international-medicity-indias-first-global-scale-healthcare-hub</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Emory University (Emory Global Diabetes Research Center)</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Lilavati Hospital, Mumbai</t>
+          <t>IIT Madras Shankar Center of Excellence in Diabetes Research, with AIIMS, Madras Diabetes Research Foundation and others</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Press Trust of India Lilavati Hospital, Mayo Clinic to establish 300-bed cancer institute in Mumbai</t>
+          <t>Myra C. Nwafor Emory students propose innovative solutions to diabetes care in India</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>24 January 2025</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>https://medicalbuyer.co.in/lilavati-hospital-mayo-clinic-to-establish-300-bed-cancer-institute-in-mumbai/</t>
+          <t>https://news.emory.edu/stories/2025/05/hs_diabetes_care_india_13-05-2025/story.html</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Ramaiah Memorial Hospital, Bengaluru</t>
+          <t>Apollo Hospitals</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>ANI Ramaiah Memorial Hospital Brings 700+ Citizens Together to Put Heart Health in Motion</t>
+          <t>Hackensack Meridian Health Hackensack Meridian Health and Apollo Hospitals Bridge Continents to Advance Healthcare Innovation and Delivery</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/content/press-releases-ani/ramaiah-memorial-hospital-brings-700-citizens-together-to-put-heart-health-in-motion-126092801082_1.html</t>
+          <t>https://www.hackensackmeridianhealth.org/en/news/2025/01/29/hmh-and-apollo-hospitals-bridge-continents-to-advance-healthcare</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Ramaiah Memorial Hospital, Bengaluru</t>
+          <t>Apollo Hospitals</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System Ramaiah Memorial Hospital Signs Long Term Collaboration Agreement with the Mount Sinai Health System in New York</t>
+          <t>BW Online Bureau Apollo Hospitals &amp; Hackensack Meridian Health Forge Strategic Affiliation</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>12 July 2024</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/news/ramaiah-memorial-hospital-signs-long-143000744.html</t>
+          <t>https://www.bwhealthcareworld.com/article/apollo-hospitals-hackensack-meridian-health-forge-strategic-affiliation-546583</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Johns Hopkins (University)</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Ramaiah Memorial Hospital, Bengaluru</t>
+          <t>Ajit Isaac Foundation, Bengaluru</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Deccan Herald Ramaiah Memorial inks 10-year partnership with Mount Sinai Health System of New York</t>
+          <t>Forbes India From beginning to end of life: Ajit and Sarah Isaac fill in the blanks</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>13 July 2024</t>
+          <t>6 April 2026</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/karnataka/bengaluru/ramaiah-memorial-inks-10-year-partnership-with-mount-sinai-health-system-of-new-york-3103995</t>
+          <t>https://www.forbesindia.com/article/leadership/from-beginning-to-end-of-life-ajit-and-sarah-isaac-fill-in-the-blanks/2992863/1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Rutgers Robert Wood Johnson Medical School (Rutgers Health)</t>
+          <t>Johns Hopkins (University)</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Govind Ballabh Pant Institute of Postgraduate Medical Education and Research (GIPMER), New Delhi</t>
+          <t>Ajit Isaac Foundation, Bengaluru</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Choose New Jersey Governor Murphy Celebrates Signing of MOUs Between New Jersey and Indian Universities, Hospitals to Advance Cardiovascular Research and Innovation</t>
+          <t>Devdiscourse Global Partnership Pioneers Palliative Care in Underserved India</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>November 2024</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>https://www.insidernj.com/press-release/governor-murphy-celebrates-signing-of-mous-between-new-jersey-and-indian-universities-hospitals-to-advance-cardiovascular-research-and-innovation/</t>
+          <t>https://www.devdiscourse.com/article/health/3165425-global-partnership-pioneers-palliative-care-in-underserved-india</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Johns Hopkins (University)</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>National Cancer Grid (NCG) India, including Tata Memorial network centres</t>
+          <t>Ajit Isaac Foundation, Bengaluru</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Jake Mickelsen Learn how a quality improvement program is improving care for cancer patients across India</t>
+          <t>IndiaMedToday Johns Hopkins University signs MoU with Ajit Isaac Foundation</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>November 2024</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>https://globalhealth.stanford.edu/bidirectional-partnerships/9912.html/</t>
+          <t>https://indiamedtoday.com/johns-hopkins-university-signs-mou-with-ajit-isaac-foundation/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Johns Hopkins (University)</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>National Cancer Grid (NCG) India, including Tata Memorial network centres</t>
+          <t>Dr. D.Y. Patil Medical College and Vidyapeeth, Pune</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Jamie Hansen Getting Better at Getting Better: A Stanford-India partnership sparks a movement in improving palliative care</t>
+          <t>HATHI study authors (Johns Hopkins University; Dr. D.Y. Patil Medical College, Hospital and Research Centre; BJGMC and others) Hybrid trial for Alcohol reduction among people with TB and HIV in India (HATHI): Protocol for a Hybrid Type 1 Effectiveness-Implementation Randomized Controlled Trial</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>2022-04-18</t>
+          <t>25 March 2026</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>https://globalhealth.stanford.edu/beyond-stanford/getting-better-at-getting-better-a-stanford-india-partnership-sparks-a-movement-in-improving-palliative-care.html/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41928807/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Stanford Medicine (Emergency Medicine International, Center for Innovation in Global Health)</t>
+          <t>Johns Hopkins (University)</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Emergency Management and Research Institute (EMRI), India</t>
+          <t>Dr. D.Y. Patil Medical College and Vidyapeeth, Pune</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Stanford Center for Innovation in Global Health Longtime global emergency medicine collaborators from India's Emergency Management and Research Institute visit Stanford</t>
+          <t>Medical Dialogues Dr DY Patil Medical College, Johns Hopkins University join hands for Collaborative Research</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>13 March 2024</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>https://globalhealth.stanford.edu/bidirectional-parnterships/longtime-global-emergency-medicine-collaborators-from-indias-emergency-management-and-research-institute-visit-stanford.html/</t>
+          <t>https://medicaldialogues.in/news/education/medical-colleges/dr-dy-patil-medical-college-johns-hopkins-university-join-hands-for-collaborative-research-125812</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Stanford Medicine (Emergency Medicine International, Center for Innovation in Global Health)</t>
+          <t>Johns Hopkins (University)</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Emergency Management and Research Institute (EMRI), India</t>
+          <t>Dr. D.Y. Patil Medical College and Vidyapeeth, Pune</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>EMRI Green Health Services Partnerships</t>
+          <t>Gupta-Klinsky India Institute, Johns Hopkins University Partnership Meetings</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -4494,78 +5257,78 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>https://www.emri.in/partnerships-3/</t>
+          <t>https://indiainstitute.jhu.edu/events-2025/past-events/events-2024/jhu-india-trip-2024/partnership-meetings/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Thomas Jefferson University / Jefferson Health (Jefferson India Center)</t>
+          <t>Johns Hopkins (University)</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>KLE Academy of Higher Education and Research (J N Medical College, Belagavi); LV Prasad Eye Institute, Hyderabad (listed by Jefferson, no recent dated activity)</t>
+          <t>IIT Bombay, Koita Centre for Digital Health</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>KLE J N Medical College and Thomas Jefferson University authors Response of reticulocyte and red blood cell indices to single-dose intravenous iron in pregnant women with moderate iron deficiency anemia: secondary analysis of the RAPIDIRON trial</t>
+          <t>Gupta-Klinsky India Institute News from GKII 2025 (launch of 2025-26 GKII-KCDH Data Science and AI Breakthrough Research Grants)</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>27 April 2026</t>
+          <t>December 2025</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42045095/</t>
+          <t>https://indiainstitute.jhu.edu/news/news-2025/news-from-gkii-2025/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Thomas Jefferson University / Jefferson Health (Jefferson India Center)</t>
+          <t>Johns Hopkins (University)</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>KLE Academy of Higher Education and Research (J N Medical College, Belagavi); LV Prasad Eye Institute, Hyderabad (listed by Jefferson, no recent dated activity)</t>
+          <t>IIT Bombay, Koita Centre for Digital Health</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Thomas Jefferson University Office of Global Affairs Global Jefferson Day 2026: Optimizing Global Health Outcomes: Jefferson India Center</t>
+          <t>Koita Centre for Digital Health KCDH Digest: achievements between January and December 2024</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>26 March 2026</t>
+          <t>January 2025</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>https://global.jefferson.edu/global-jefferson-day.html</t>
+          <t>https://www.kcdh.iitb.ac.in/site/newsletter-document/a6abea01-50ce-11f0-9b5b-fbbec49cc3fb.pdf</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Thomas Jefferson University / Jefferson Health (Jefferson India Center)</t>
+          <t>Johns Hopkins (University)</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>KLE Academy of Higher Education and Research (J N Medical College, Belagavi); LV Prasad Eye Institute, Hyderabad (listed by Jefferson, no recent dated activity)</t>
+          <t>IIT Bombay, Koita Centre for Digital Health</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Jefferson Office of International Services Jefferson India Center</t>
+          <t>Gupta-Klinsky India Institute, Johns Hopkins University Collaboration Agreement with IIT Bombay and Roundtable Discussion Shine a Spotlight on Digital Health</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -4575,888 +5338,888 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>https://global.jefferson.edu/jeffersons-global-centers/jefferson-india-center.html</t>
+          <t>https://indiainstitute.jhu.edu/news/news-2025/news-from-gkii/collaboration-agreement-with-iit-bombay-and-roundtable-discussion-shine-a-spotlight-on-digital-health</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>Johns Hopkins (University)</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>All India Institute of Medical Sciences, New Delhi</t>
+          <t>IIT Bombay, Koita Centre for Digital Health</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>UCLA Health Department of Obstetrics and Gynecology Newsletter Summer 2025: New and Noteworthy</t>
+          <t>Gupta-Klinsky India Institute, Johns Hopkins University GKII X KCDH Breakthrough Grants on Digital Health (2024)</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Summer 2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>https://www.uclahealth.org/departments/obgyn/about-us/news/newsletter-summer-2025/new-and-noteworthy</t>
+          <t>https://indiainstitute.jhu.edu/?p=4857</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>Johns Hopkins University (School of Medicine)</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>All India Institute of Medical Sciences, New Delhi</t>
+          <t>Byramjee Jeejeebhoy Government Medical College and Sassoon General Hospitals, Pune (BJGMC-JHU Clinical Research Site)</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>UCLA Health Department of Obstetrics and Gynecology UCLA-India Global Health Exchange in OB/GYN</t>
+          <t>BJGMC, Weill Cornell Medicine and Johns Hopkins authors Dolutegravir Is Associated With Lower Odds of Gestational Diabetes Compared to Other Antiretroviral Therapy Regimens Among Pregnant Women in India: A Cross-Sectional Analysis</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>undated</t>
+          <t>1 September 2026</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>https://www.uclahealth.org/departments/obgyn/about-us/global-reproductive-health-alliance-collaborative-engagement/ucla-india-global-health-exchange-obgyn</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42764545/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>Johns Hopkins University (School of Medicine)</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Federation of Obstetric and Gynaecological Societies of India (FOGSI) and SAFOG</t>
+          <t>Byramjee Jeejeebhoy Government Medical College and Sassoon General Hospitals, Pune (BJGMC-JHU Clinical Research Site)</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>UCLA Health UCLA OB/GYN global health initiatives spark learning, innovation and training</t>
+          <t>BJGMC, Weill Cornell Medicine, Johns Hopkins and Columbia authors Impact of maternal HIV infection on the gut microbiome and metabolome of mothers and infants: the PRACHITi cohort in Pune, India</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>8 December 2025</t>
+          <t>23 February 2026</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>https://www.uclahealth.org/news/article/ucla-obgyn-global-health-initiatives-spark-learning</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41730922/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>Johns Hopkins University (School of Medicine)</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Narendra Modi Medical College, Ahmedabad</t>
+          <t>Byramjee Jeejeebhoy Government Medical College and Sassoon General Hospitals, Pune (BJGMC-JHU Clinical Research Site)</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>UCLA Health Department of Obstetrics and Gynecology New and Noteworthy</t>
+          <t>Johns Hopkins University BJGMC (India): BJGMC-JHU CRS</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Summer 2025</t>
+          <t>undated</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>https://www.uclahealth.org/departments/obgyn/about-us/news/newsletter-summer-2025/new-and-noteworthy</t>
+          <t>http://jhubi-ctu.jhu.edu/our-sites/bjgmc-india</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>MD Anderson Cancer Center</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Narendra Modi Medical College, Ahmedabad</t>
+          <t>Tata Memorial Centre, Mumbai</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>UCLA Health Department of Obstetrics and Gynecology UCLA-India Global Health Exchange in OB/GYN</t>
+          <t>OncoDaily Joint session by MD Anderson Cancer Center and Tata Memorial Centre at SACT 2025 Summit</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>undated</t>
+          <t>4 December 2024</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>https://www.uclahealth.org/departments/obgyn/about-us/global-reproductive-health-alliance-collaborative-engagement/ucla-india-global-health-exchange-obgyn</t>
+          <t>https://oncodaily.com/blog/md-anderson-cancer-center-197733</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>University of Alabama at Birmingham (Heersink School of Medicine)</t>
+          <t>MD Anderson Cancer Center</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Pravara Institute of Medical Sciences (Loni) and Bharati Vidyapeeth Medical College (Pune)</t>
+          <t>Tata Memorial Centre, Mumbai</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Shawna Masters New UAB-India partnership aims to enhance global health training</t>
+          <t>India Herald MD Anderson Cancer Center signs sister institution accord with Tata Memorial</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>17 October 2003</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>https://www.uab.edu/medicine/news/global-health/new-uab-india-partnership-aims-to-enhance-global-health-training</t>
+          <t>https://india-herald.com/md-anderson-cancer-center-signs-sister-institution-accord-with-tata-memoria-p305-19.htm</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>University of California San Francisco (Francis I. Proctor Foundation)</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Aravind Eye Care System, Madurai</t>
+          <t>AIIMS New Delhi (Departments of Pathology and Nephrology)</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>REAGIR trial authors (Aravind Eye Hospital; Francis I. Proctor Foundation, UCSF and others) Rose Bengal Electromagnetic Activation With Green Light for Infection Reduction: Follow-Up of a Randomized Clinical Trial</t>
+          <t>AIIMS New Delhi AIIMS Mayo Clinic Update in Kidney Diseases and Transplant 2024</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>1 August 2026</t>
+          <t>7-8 December 2024</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42348235/</t>
+          <t>https://aiimsmayoclinicupdate2024.com/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>University of California San Francisco (Francis I. Proctor Foundation)</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Aravind Eye Care System, Madurai</t>
+          <t>Adani Group (Adani Health City, Ahmedabad and Mumbai; planned Kolkata campus)</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>SCUT II Study authors (not verified) Steroids and Cross-Linking for Ulcer Treatment: The SCUT II Randomized Clinical Trial</t>
+          <t>Digital Health News Adani Group to Set Up INR 2,500 Crore Health City in West Bengal with Mayo Clinic Collaboration</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>6 July 2026</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>https://jamanetwork.com/journals/jamaophthalmology/fullarticle/2836544</t>
+          <t>https://www.digitalhealthnews.com/adani-group-to-invest-inr-2-500-cr-in-health-city-project-in-west-bengal</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>University of Iowa (Carver College of Medicine, Ophthalmology)</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Dr. Shroff's Charity Eye Hospital, New Delhi</t>
+          <t>Adani Group (Adani Health City, Ahmedabad and Mumbai; planned Kolkata campus)</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Iowa Lions Eye Bank Iowa Lions Eye Bank Shares Expertise with Corneal Specialists in India</t>
+          <t>Adani Group Adani to Partner Mayo Clinic to Establish Affordable World Class Healthcare Facilities</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>1 February 2025</t>
+          <t>10 February 2025</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>https://iowalionseyebank.org/news/2025/02/iowa-lions-eye-bank-shares-expertise-corneal-specialists-india</t>
+          <t>https://www.adani.com/newsroom/media-releases/adani-to-partner-mayo-clinic-to-establish-affordable-world-class-healthcare-facilities</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>University of Iowa (Carver College of Medicine, Ophthalmology)</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Dr. Shroff's Charity Eye Hospital, New Delhi</t>
+          <t>Adani Group (Adani Health City, Ahmedabad and Mumbai; planned Kolkata campus)</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>University of Iowa International Programs Forging paths in global ophthalmology: University of Iowa partners with charity eye hospital in India</t>
+          <t>Post Bulletin Billionaire to partner with Mayo Clinic on India hospitals</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>11 February 2025</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>https://international.uiowa.edu/node/15891</t>
+          <t>https://www.postbulletin.com/business/billionaire-to-partner-with-mayo-clinic-on-india-hospitals</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>University of Michigan Medical School / Michigan Medicine</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>AIIMS Jammu</t>
+          <t>Lilavati Hospital, GIFT City, Gujarat</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Tanya Verma AIIMS Jammu and University of Michigan Collaborate for Twin International Conferences</t>
+          <t>The Indian Practitioner Lilavati Expands Globally and Domestically with Mauritius, GIFT City Projects</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>22 April 2026</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>https://collegehai.com/news/aiims-jammu-university-of-michigan-international-conferences</t>
+          <t>https://theindianpractitioner.com/lilavati-expands-globally-and-domestically-with-mauritius-gift-city-projects/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Madison Department of Ophthalmology and Visual Sciences (UW Health)</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Dr. Shroff's Charity Eye Hospital, New Delhi</t>
+          <t>Lilavati Hospital, GIFT City, Gujarat</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>UW Department of Ophthalmology and Visual Sciences DOVS Celebrates a Decade of Partnership with Colleagues in India</t>
+          <t>Lilavati Hospital News and Media</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>23 September 2025</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>https://www.ophth.wisc.edu/blog/2025/02/28/india_rotation_2025</t>
+          <t>https://www.lilavati-hospital.com/news-and-media.php</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Weill Cornell Medicine (Center for Global Health)</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Byramjee Jeejeebhoy Government Medical College and Sassoon Hospital, Pune; Deep Griha Society</t>
+          <t>Lilavati Hospital, GIFT City, Gujarat</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>BJGMC, Weill Cornell Medicine and Johns Hopkins authors Dolutegravir Is Associated With Lower Odds of Gestational Diabetes Compared to Other Antiretroviral Therapy Regimens Among Pregnant Women in India: A Cross-Sectional Analysis</t>
+          <t>Press Trust of India Lilavati Hospital, Mayo Clinic to establish 300-bed cancer institute in Mumbai</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>1 September 2026</t>
+          <t>24 January 2025</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42764545/</t>
+          <t>https://medicalbuyer.co.in/lilavati-hospital-mayo-clinic-to-establish-300-bed-cancer-institute-in-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Weill Cornell Medicine (Center for Global Health)</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Byramjee Jeejeebhoy Government Medical College and Sassoon Hospital, Pune; Deep Griha Society</t>
+          <t>Lilavati Hospital, GIFT City, Gujarat</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>BJGMC, Weill Cornell Medicine, Johns Hopkins and Columbia authors Impact of maternal HIV infection on the gut microbiome and metabolome of mothers and infants: the PRACHITi cohort in Pune, India</t>
+          <t>VMPL Lilavati Hospital in Gift City, Gujarat has engaged with Mayo Clinic Global Consulting to enhance the patient care standards</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>23 February 2026</t>
+          <t>20 March 2024</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/41730922/</t>
+          <t>https://www.business-standard.com/content/press-releases-ani/lilavati-hospital-in-gift-city-gujarat-has-engaged-with-mayo-clinic-global-consulting-to-enhance-the-patient-care-standards-124032000688_1.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Weill Cornell Medicine (Center for Global Health)</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Byramjee Jeejeebhoy Government Medical College and Sassoon Hospital, Pune; Deep Griha Society</t>
+          <t>Lilavati Hospital, Mumbai</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Weill Cornell Center for Global Health Pune, India</t>
+          <t>Lilavati Hospital News and Media</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>undated</t>
+          <t>23 September 2025</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>https://globalhealth.weill.cornell.edu/major-initiatives/pune-india</t>
+          <t>https://www.lilavati-hospital.com/news-and-media.php</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Cambridge University Hospitals NHS Foundation Trust (with Cambridge Global Health Partnerships)</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Himalayan Hospital (Dehradun) and Ganga Prem Hospice, Rishikesh, via Rama Foundation</t>
+          <t>Lilavati Hospital, Mumbai</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Cambridge University Hospitals Health team prepare for India mission</t>
+          <t>Kajal Rajput Mayo Clinic, Lilavati Hospital complete India's first Nursing Excellence Training Program</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>6 August 2025</t>
+          <t>29 March 2025</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>https://www.cuh.nhs.uk/news/health-team-prepare-for-india-mission/</t>
+          <t>https://medicaldialogues.in/news/health/hospital-diagnostics/mayo-clinic-lilavati-hospital-complete-indias-first-nursing-excellence-training-program-145698</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Cambridge University Hospitals NHS Foundation Trust (with Cambridge Global Health Partnerships)</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Himalayan Hospital (Dehradun) and Ganga Prem Hospice, Rishikesh, via Rama Foundation</t>
+          <t>Lilavati Hospital, Mumbai</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Mike Scialom Cambridge healthcare professionals head to northern India for partnership visit</t>
+          <t>Press Trust of India Lilavati Hospital, Mayo Clinic to establish 300-bed cancer institute in Mumbai</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>24 January 2025</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>https://www.cambridgeindependent.co.uk/news/cambridge-healthcare-professionals-head-to-northern-india-fo-9429740/</t>
+          <t>https://medicalbuyer.co.in/lilavati-hospital-mayo-clinic-to-establish-300-bed-cancer-institute-in-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Juntendo University (Tokyo)</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Saint Hardyal Educational and Orphans' Welfare Society (SHEOWS), Delhi</t>
+          <t>Ramaiah Memorial Hospital, Bengaluru</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>PTI SHEOWS and Juntendo University, Tokyo Sign MoU to Advance Geriatric Care and Research Collaboration Between India and Japan</t>
+          <t>ANI Ramaiah Memorial Hospital Brings 700+ Citizens Together to Put Heart Health in Motion</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>https://m.thewire.in/article/ptiprnews/sheows-and-juntendo-university-tokyo-sign-mou-to-advance-geriatric-care-and-research-collaboration-between-india-and-japan/amp</t>
+          <t>https://www.business-standard.com/amp/content/press-releases-ani/ramaiah-memorial-hospital-brings-700-citizens-together-to-put-heart-health-in-motion-126092801082_1.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>King's College London and Guy's and St Thomas' NHS Foundation Trust</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>P. D. Hinduja Hospital and Medical Research Centre, Mumbai (National Health &amp; Education Society)</t>
+          <t>Ramaiah Memorial Hospital, Bengaluru</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Amit Srivastava Hinduja Foundation Offers MSc And PhD Scholarships For Indian Students At King's College London For 2026-27</t>
+          <t>Mount Sinai Health System Ramaiah Memorial Hospital Signs Long Term Collaboration Agreement with the Mount Sinai Health System in New York</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>12 July 2024</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/hinduja-foundation-offers-msc-and-phd-scholarships-for-indian-students-at-kings-college-london-for-202627</t>
+          <t>https://finance.yahoo.com/news/ramaiah-memorial-hospital-signs-long-143000744.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>King's College London and Guy's and St Thomas' NHS Foundation Trust</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>P. D. Hinduja Hospital and Medical Research Centre, Mumbai (National Health &amp; Education Society)</t>
+          <t>Ramaiah Memorial Hospital, Bengaluru</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Pharmautility P. D. Hinduja Hospital and King's College London Collaborate and Commence Their First Training Program for Nurses</t>
+          <t>Deccan Herald Ramaiah Memorial inks 10-year partnership with Mount Sinai Health System of New York</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>13 July 2024</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>https://pharmautility.com/p-d-hinduja-hospital-and-kings-college-london-collaborate-and-commence-their-first-training-program-for-nurses/</t>
+          <t>https://www.deccanherald.com/india/karnataka/bengaluru/ramaiah-memorial-inks-10-year-partnership-with-mount-sinai-health-system-of-new-york-3103995</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>King's College London and Guy's and St Thomas' NHS Foundation Trust</t>
+          <t>Rutgers Robert Wood Johnson Medical School (Rutgers Health)</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>P. D. Hinduja Hospital and Medical Research Centre, Mumbai (National Health &amp; Education Society)</t>
+          <t>Govind Ballabh Pant Institute of Postgraduate Medical Education and Research (GIPMER), New Delhi</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>King's College London New partnership to improve healthcare outcomes in India and the UK</t>
+          <t>Choose New Jersey Governor Murphy Celebrates Signing of MOUs Between New Jersey and Indian Universities, Hospitals to Advance Cardiovascular Research and Innovation</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>https://www.kcl.ac.uk/news/new-partnership-to-improve-healthcare-outcomes-in-india-and-the-uk</t>
+          <t>https://www.insidernj.com/press-release/governor-murphy-celebrates-signing-of-mous-between-new-jersey-and-indian-universities-hospitals-to-advance-cardiovascular-research-and-innovation/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Monash University (Faculty of Information Technology)</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Apollo Hospitals and The Apollo University</t>
+          <t>National Cancer Grid (NCG) India, including Tata Memorial network centres</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Health News Monash University Partners with Apollo Hospitals for Digital Health Research</t>
+          <t>Jake Mickelsen Learn how a quality improvement program is improving care for cancer patients across India</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>https://www.digitalhealthnews.com/monash-university-partners-with-apollo-hospitals-for-digital-health-research</t>
+          <t>https://globalhealth.stanford.edu/bidirectional-partnerships/9912.html/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Monash University (Faculty of Information Technology)</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Apollo Hospitals and The Apollo University</t>
+          <t>National Cancer Grid (NCG) India, including Tata Memorial network centres</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Dylan Bushell-Embling Monash partners with Apollo University on health AI research</t>
+          <t>Jamie Hansen Getting Better at Getting Better: A Stanford-India partnership sparks a movement in improving palliative care</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2022-04-18</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>https://www.govtechreview.com.au/content/gov-digital/news/monash-partners-with-apollo-university-on-health-ai-research-652623324</t>
+          <t>https://globalhealth.stanford.edu/beyond-stanford/getting-better-at-getting-better-a-stanford-india-partnership-sparks-a-movement-in-improving-palliative-care.html/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>SingHealth</t>
+          <t>Stanford Medicine (Emergency Medicine International, Center for Innovation in Global Health)</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Athulya Senior Care, Chennai</t>
+          <t>Emergency Management and Research Institute (EMRI), India</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Team VOH Athulya Senior Care Inks Landmark MoU with SingHealth to Advance Senior Care, Training, and Research Collaboration</t>
+          <t>Stanford Center for Innovation in Global Health Longtime global emergency medicine collaborators from India's Emergency Management and Research Institute visit Stanford</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>https://vohnetwork.com/news/hospitals-providers/athulya-senior-care-inks-landmark-mou-with-singhealth-to-advance-senior-care-training-and-research-collaboration</t>
+          <t>https://globalhealth.stanford.edu/bidirectional-parnterships/longtime-global-emergency-medicine-collaborators-from-indias-emergency-management-and-research-institute-visit-stanford.html/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>University College London</t>
+          <t>Stanford Medicine (Emergency Medicine International, Center for Innovation in Global Health)</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>AIIMS New Delhi and IIT Delhi</t>
+          <t>Emergency Management and Research Institute (EMRI), India</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>University College London Inaugural recipients of UCL-AIIMS-IITD trilateral seed funds revealed</t>
+          <t>EMRI Green Health Services Partnerships</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>November 2025</t>
+          <t>undated</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>https://www.ucl.ac.uk/global/news/2025/nov/inaugural-recipients-ucl-aiims-iitd-trilateral-seed-funds-revealed</t>
+          <t>https://www.emri.in/partnerships-3/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>University College London</t>
+          <t>Thomas Jefferson University / Jefferson Health (Jefferson India Center)</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>AIIMS New Delhi and IIT Delhi</t>
+          <t>KLE Academy of Higher Education and Research (J N Medical College, Belagavi); LV Prasad Eye Institute, Hyderabad (listed by Jefferson, no recent dated activity)</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Sanket Koul UCL inks trilateral pact with AIIMS, IIT-D to scale up medtech innovation</t>
+          <t>KLE J N Medical College and Thomas Jefferson University authors Response of reticulocyte and red blood cell indices to single-dose intravenous iron in pregnant women with moderate iron deficiency anemia: secondary analysis of the RAPIDIRON trial</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>27 April 2026</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/ucl-inks-trilateral-pact-with-aiims-iit-d-to-scale-up-medtech-innovation-124112201280_1.html</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42045095/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>University of Leicester and University Hospitals of Leicester NHS Trust</t>
+          <t>Thomas Jefferson University / Jefferson Health (Jefferson India Center)</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Apollo Hospitals and The Apollo University</t>
+          <t>KLE Academy of Higher Education and Research (J N Medical College, Belagavi); LV Prasad Eye Institute, Hyderabad (listed by Jefferson, no recent dated activity)</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>IPP Bureau University of Leicester, Apollo showcase AI-driven healthcare research to strengthen UK-India collaboration</t>
+          <t>Thomas Jefferson University Office of Global Affairs Global Jefferson Day 2026: Optimizing Global Health Outcomes: Jefferson India Center</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>26 March 2026</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/hospitals/university-of-leicester-apollo-showcase-ai-driven-healthcare-research-to-strengthen-uk-india-collaboration-20937</t>
+          <t>https://global.jefferson.edu/global-jefferson-day.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>University of Leicester and University Hospitals of Leicester NHS Trust</t>
+          <t>Thomas Jefferson University / Jefferson Health (Jefferson India Center)</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Apollo Hospitals and The Apollo University</t>
+          <t>KLE Academy of Higher Education and Research (J N Medical College, Belagavi); LV Prasad Eye Institute, Hyderabad (listed by Jefferson, no recent dated activity)</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>University of Leicester University of Leicester and The Apollo University launch global research centre for digital health and precision medicine</t>
+          <t>Jefferson Office of International Services Jefferson India Center</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>undated</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>https://le.ac.uk/news/2025/january/apollo-launch</t>
+          <t>https://global.jefferson.edu/jeffersons-global-centers/jefferson-india-center.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>University of Leicester, University Hospitals of Leicester NHS Trust and BAPIO Training Academy</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Apollo Health Resources (Apollo Hospitals)</t>
+          <t>All India Institute of Medical Sciences, New Delhi</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>IPP Bureau University of Leicester, Apollo showcase AI-driven healthcare research to strengthen UK-India collaboration</t>
+          <t>UCLA Health Department of Obstetrics and Gynecology Newsletter Summer 2025: New and Noteworthy</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/hospitals/university-of-leicester-apollo-showcase-ai-driven-healthcare-research-to-strengthen-uk-india-collaboration-20937</t>
+          <t>https://www.uclahealth.org/departments/obgyn/about-us/news/newsletter-summer-2025/new-and-noteworthy</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>University of Leicester, University Hospitals of Leicester NHS Trust and BAPIO Training Academy</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Apollo Health Resources (Apollo Hospitals)</t>
+          <t>All India Institute of Medical Sciences, New Delhi</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>University of Leicester Trainee doctors in India to bolster their clinical skills with the NHS thanks to landmark initiative</t>
+          <t>UCLA Health Department of Obstetrics and Gynecology UCLA-India Global Health Exchange in OB/GYN</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>undated</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>https://le.ac.uk/news/2025/october/trainee-doctors-india-clinical-skills-nhs-landmark-initiative</t>
+          <t>https://www.uclahealth.org/departments/obgyn/about-us/global-reproductive-health-alliance-collaborative-engagement/ucla-india-global-health-exchange-obgyn</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>University of Liverpool</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Saveetha Institute of Medical and Technical Sciences (SIMATS), Chennai</t>
+          <t>Federation of Obstetric and Gynaecological Societies of India (FOGSI) and SAFOG</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>University of Liverpool New partnerships build on Liverpool-India research and education ties</t>
+          <t>UCLA Health UCLA OB/GYN global health initiatives spark learning, innovation and training</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>8 December 2025</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>https://news.liverpool.ac.uk/2025/07/14/new-partnerships-further-strengthen-liverpool-india-research-and-education-ties/</t>
+          <t>https://www.uclahealth.org/news/article/ucla-obgyn-global-health-initiatives-spark-learning</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Cleveland Clinic</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Group</t>
+          <t>Narendra Modi Medical College, Ahmedabad</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Telangana Today Apollo Hospitals launches International second opinion services for patients</t>
+          <t>UCLA Health Department of Obstetrics and Gynecology New and Noteworthy</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>January 2022</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>https://telanganatoday.com/apollo-hospitals-launches-international-second-opinion-services-for-patients</t>
+          <t>https://www.uclahealth.org/departments/obgyn/about-us/news/newsletter-summer-2025/new-and-noteworthy</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Cleveland Clinic</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Group</t>
+          <t>Narendra Modi Medical College, Ahmedabad</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>HHM Global Apollo Hospitals collaborates with Cleveland Clinic to offer international second opinion services to patients</t>
+          <t>UCLA Health Department of Obstetrics and Gynecology UCLA-India Global Health Exchange in OB/GYN</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -5466,356 +6229,1112 @@
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>https://www.hhmglobal.com/knowledge-bank/news/apollo-hospitals-collaborates-with-cleveland-clinic-to-offer-international-second-opinion-services-to-patients</t>
+          <t>https://www.uclahealth.org/departments/obgyn/about-us/global-reproductive-health-alliance-collaborative-engagement/ucla-india-global-health-exchange-obgyn</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins (University)</t>
+          <t>University of Alabama at Birmingham (Heersink School of Medicine)</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>College of Nursing, Christian Medical College Vellore</t>
+          <t>Pravara Institute of Medical Sciences (Loni) and Bharati Vidyapeeth Medical College (Pune)</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins School of Nursing and CMC Vellore College of Nursing authors Leveraging a Global Partnership to Address COVID-19-Related Mental Health Challenges</t>
+          <t>Shawna Masters New UAB-India partnership aims to enhance global health training</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>3 October 2024</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/10.1111/jpm.13115</t>
+          <t>https://www.uab.edu/medicine/news/global-health/new-uab-india-partnership-aims-to-enhance-global-health-training</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins (University)</t>
+          <t>University of California San Francisco (Francis I. Proctor Foundation)</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>College of Nursing, Christian Medical College Vellore</t>
+          <t>Aravind Eye Care System, Madurai</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins School of Nursing From Baltimore to Vellore, India: Global Support for Nurses Struggling with COVID-Related Mental Health</t>
+          <t>REAGIR trial authors (Aravind Eye Hospital; Francis I. Proctor Foundation, UCSF and others) Rose Bengal Electromagnetic Activation With Green Light for Infection Reduction: Follow-Up of a Randomized Clinical Trial</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>August 2021</t>
+          <t>1 August 2026</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>https://nursing.jhu.edu/magazine/articles/2021/08/from-baltimore-to-vellore-india-global-support-for-nurses-struggling-with-covid-related-mental-health/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42348235/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins (University)</t>
+          <t>University of California San Francisco (Francis I. Proctor Foundation)</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>College of Nursing, Christian Medical College Vellore</t>
+          <t>Aravind Eye Care System, Madurai</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>College of Nursing, CMC Vellore Collaboration</t>
+          <t>SCUT II Study authors (not verified) Steroids and Cross-Linking for Ulcer Treatment: The SCUT II Randomized Clinical Trial</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>undated</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>https://concmc.org/collaboration/</t>
+          <t>https://jamanetwork.com/journals/jamaophthalmology/fullarticle/2836544</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>University of Iowa (Carver College of Medicine, Ophthalmology)</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>AIG Hospitals, Hyderabad</t>
+          <t>Dr. Shroff's Charity Eye Hospital, New Delhi</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Post Bulletin Billionaire to partner with Mayo Clinic on India hospitals</t>
+          <t>Iowa Lions Eye Bank Iowa Lions Eye Bank Shares Expertise with Corneal Specialists in India</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>11 February 2025</t>
+          <t>1 February 2025</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>https://www.postbulletin.com/business/billionaire-to-partner-with-mayo-clinic-on-india-hospitals</t>
+          <t>https://iowalionseyebank.org/news/2025/02/iowa-lions-eye-bank-shares-expertise-corneal-specialists-india</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>University of Iowa (Carver College of Medicine, Ophthalmology)</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>AIG Hospitals, Hyderabad</t>
+          <t>Dr. Shroff's Charity Eye Hospital, New Delhi</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic AIG Hospitals in India joins Mayo Clinic Care Network</t>
+          <t>University of Iowa International Programs Forging paths in global ophthalmology: University of Iowa partners with charity eye hospital in India</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>24 October 2019</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>https://www.newswise.com/articles/aig-hospitals-in-india-joins-mayo-clinic-care-network</t>
+          <t>https://international.uiowa.edu/node/15891</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering</t>
+          <t>University of Michigan Medical School / Michigan Medicine</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>iCliniq, Chennai (MSKCC India)</t>
+          <t>AIIMS Jammu</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center Memorial Sloan Kettering Cancer Center Launches MSKCC India to Expand Access to World-Renowned Oncologists, Cancer Care, Research, and Education</t>
+          <t>Tanya Verma AIIMS Jammu and University of Michigan Collaborate for Twin International Conferences</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>2 August 2021</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/memorial-sloan-kettering-cancer-center-launches-mskcc-india-to-expand-access-to-world-renowned-oncologists-cancer-care-research-and-education-301345795.html</t>
+          <t>https://collegehai.com/news/aiims-jammu-university-of-michigan-international-conferences</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering</t>
+          <t>University of Wisconsin-Madison Department of Ophthalmology and Visual Sciences (UW Health)</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>iCliniq, Chennai (MSKCC India)</t>
+          <t>Dr. Shroff's Charity Eye Hospital, New Delhi</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>iCliniq Frequently Asked Question: MSK India</t>
+          <t>UW Department of Ophthalmology and Visual Sciences DOVS Celebrates a Decade of Partnership with Colleagues in India</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>undated</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>https://mskcc.icliniq.com/mskcc-india-services/mskcc-patient-faqs</t>
+          <t>https://www.ophth.wisc.edu/blog/2025/02/28/india_rotation_2025</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Northwell Health (Center for Global Health)</t>
+          <t>Weill Cornell Medicine (Center for Global Health)</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Christian Medical College (CMC) Vellore</t>
+          <t>Byramjee Jeejeebhoy Government Medical College and Sassoon Hospital, Pune; Deep Griha Society</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Northwell Health Northwell Health signs five-year strategic agreement with Indian health system, CMC Vellore</t>
+          <t>BJGMC, Weill Cornell Medicine and Johns Hopkins authors Dolutegravir Is Associated With Lower Odds of Gestational Diabetes Compared to Other Antiretroviral Therapy Regimens Among Pregnant Women in India: A Cross-Sectional Analysis</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>1 September 2026</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>https://www.northwell.edu/news/the-latest/northwell-signs-5-year-strategic-agreement-india-s-cmc-vellore</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42764545/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>LMU Klinikum (University Hospital Munich)</t>
+          <t>Weill Cornell Medicine (Center for Global Health)</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>AIIMS New Delhi</t>
+          <t>Byramjee Jeejeebhoy Government Medical College and Sassoon Hospital, Pune; Deep Griha Society</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Press Trust of India AIIMS Delhi, Munich-based university sign agreement for research in medicine, life sciences</t>
+          <t>BJGMC, Weill Cornell Medicine, Johns Hopkins and Columbia authors Impact of maternal HIV infection on the gut microbiome and metabolome of mothers and infants: the PRACHITi cohort in Pune, India</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>23 February 2026</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/aiims-delhi-munich-based-university-sign-non-binding-mou-for-collaborative-endeavours/amp</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41730922/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>University of Bolton Institute of Medicine (now University of Greater Manchester Medical School)</t>
+          <t>Weill Cornell Medicine (Center for Global Health)</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>AIIMS New Delhi</t>
+          <t>Byramjee Jeejeebhoy Government Medical College and Sassoon Hospital, Pune; Deep Griha Society</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>News Services Division AIIMS New Delhi signed MoU with University of Bolton Institute of Medicine</t>
+          <t>Weill Cornell Center for Global Health Pune, India</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>undated</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>https://newsonair.gov.in/aiims-new-delhi-signed-mou-with-university-of-bolton-institute-of-medicine</t>
+          <t>https://globalhealth.weill.cornell.edu/major-initiatives/pune-india</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins (Medicine International)</t>
+          <t>Cambridge University Hospitals NHS Foundation Trust (with Cambridge Global Health Partnerships)</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>HCL Healthcare</t>
+          <t>Himalayan Hospital (Dehradun) and Ganga Prem Hospice, Rishikesh, via Rama Foundation</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Domain-b HCL enters healthcare with HCL Avitas</t>
+          <t>Cambridge University Hospitals Health team prepare for India mission</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>6 February 2014</t>
+          <t>6 August 2025</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>https://www.domain-b.com/companies-organisations/firms-companies/hcl-enters-healthcare-with-hcl-avitas</t>
+          <t>https://www.cuh.nhs.uk/news/health-team-prepare-for-india-mission/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins (Medicine International)</t>
+          <t>Cambridge University Hospitals NHS Foundation Trust (with Cambridge Global Health Partnerships)</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>HCL Healthcare</t>
+          <t>Himalayan Hospital (Dehradun) and Ganga Prem Hospice, Rishikesh, via Rama Foundation</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins Medicine International HCL Healthcare</t>
+          <t>Mike Scialom Cambridge healthcare professionals head to northern India for partnership visit</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>undated</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>https://www.hopkinsmedicine.org/international/health-care-consulting/asia-pacific/hcl-healthcare</t>
+          <t>https://www.cambridgeindependent.co.uk/news/cambridge-healthcare-professionals-head-to-northern-india-fo-9429740/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
+          <t>Juntendo University (Tokyo)</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Saint Hardyal Educational and Orphans' Welfare Society (SHEOWS), Delhi</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>PTI SHEOWS and Juntendo University, Tokyo Sign MoU to Advance Geriatric Care and Research Collaboration Between India and Japan</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>https://m.thewire.in/article/ptiprnews/sheows-and-juntendo-university-tokyo-sign-mou-to-advance-geriatric-care-and-research-collaboration-between-india-and-japan/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>King's College London and Guy's and St Thomas' NHS Foundation Trust</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>P. D. Hinduja Hospital and Medical Research Centre, Mumbai (National Health &amp; Education Society)</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Amit Srivastava Hinduja Foundation Offers MSc And PhD Scholarships For Indian Students At King's College London For 2026-27</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/education/hinduja-foundation-offers-msc-and-phd-scholarships-for-indian-students-at-kings-college-london-for-202627</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>King's College London and Guy's and St Thomas' NHS Foundation Trust</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>P. D. Hinduja Hospital and Medical Research Centre, Mumbai (National Health &amp; Education Society)</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Pharmautility P. D. Hinduja Hospital and King's College London Collaborate and Commence Their First Training Program for Nurses</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>https://pharmautility.com/p-d-hinduja-hospital-and-kings-college-london-collaborate-and-commence-their-first-training-program-for-nurses/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>King's College London and Guy's and St Thomas' NHS Foundation Trust</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>P. D. Hinduja Hospital and Medical Research Centre, Mumbai (National Health &amp; Education Society)</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>King's College London New partnership to improve healthcare outcomes in India and the UK</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/news/new-partnership-to-improve-healthcare-outcomes-in-india-and-the-uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Monash University (Faculty of Information Technology)</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals and The Apollo University</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Health News Monash University Partners with Apollo Hospitals for Digital Health Research</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digitalhealthnews.com/monash-university-partners-with-apollo-hospitals-for-digital-health-research</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>Monash University (Faculty of Information Technology)</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals and The Apollo University</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Dylan Bushell-Embling Monash partners with Apollo University on health AI research</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>https://www.govtechreview.com.au/content/gov-digital/news/monash-partners-with-apollo-university-on-health-ai-research-652623324</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>SingHealth</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Athulya Senior Care, Chennai</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Team VOH Athulya Senior Care Inks Landmark MoU with SingHealth to Advance Senior Care, Training, and Research Collaboration</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>https://vohnetwork.com/news/hospitals-providers/athulya-senior-care-inks-landmark-mou-with-singhealth-to-advance-senior-care-training-and-research-collaboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>University College London</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>AIIMS New Delhi and IIT Delhi</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>University College London Inaugural recipients of UCL-AIIMS-IITD trilateral seed funds revealed</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>November 2025</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/global/news/2025/nov/inaugural-recipients-ucl-aiims-iitd-trilateral-seed-funds-revealed</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>University College London</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>AIIMS New Delhi and IIT Delhi</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Sanket Koul UCL inks trilateral pact with AIIMS, IIT-D to scale up medtech innovation</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/india-news/ucl-inks-trilateral-pact-with-aiims-iit-d-to-scale-up-medtech-innovation-124112201280_1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>University of Leicester and University Hospitals of Leicester NHS Trust</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals and The Apollo University</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>IPP Bureau University of Leicester, Apollo showcase AI-driven healthcare research to strengthen UK-India collaboration</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>https://www.indianpharmapost.com/hospitals/university-of-leicester-apollo-showcase-ai-driven-healthcare-research-to-strengthen-uk-india-collaboration-20937</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>University of Leicester and University Hospitals of Leicester NHS Trust</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals and The Apollo University</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>University of Leicester University of Leicester and The Apollo University launch global research centre for digital health and precision medicine</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>https://le.ac.uk/news/2025/january/apollo-launch</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>University of Leicester, University Hospitals of Leicester NHS Trust and BAPIO Training Academy</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>Apollo Health Resources (Apollo Hospitals)</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>IPP Bureau University of Leicester, Apollo showcase AI-driven healthcare research to strengthen UK-India collaboration</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>https://www.indianpharmapost.com/hospitals/university-of-leicester-apollo-showcase-ai-driven-healthcare-research-to-strengthen-uk-india-collaboration-20937</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>University of Leicester, University Hospitals of Leicester NHS Trust and BAPIO Training Academy</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>Apollo Health Resources (Apollo Hospitals)</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>University of Leicester Trainee doctors in India to bolster their clinical skills with the NHS thanks to landmark initiative</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>https://le.ac.uk/news/2025/october/trainee-doctors-india-clinical-skills-nhs-landmark-initiative</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>University of Liverpool</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>Saveetha Institute of Medical and Technical Sciences (SIMATS), Chennai</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>University of Liverpool New partnerships build on Liverpool-India research and education ties</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>https://news.liverpool.ac.uk/2025/07/14/new-partnerships-further-strengthen-liverpool-india-research-and-education-ties/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Clinic</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals Group</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Telangana Today Apollo Hospitals launches International second opinion services for patients</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>January 2022</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>https://telanganatoday.com/apollo-hospitals-launches-international-second-opinion-services-for-patients</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Clinic</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals Group</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>HHM Global Apollo Hospitals collaborates with Cleveland Clinic to offer international second opinion services to patients</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>undated</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hhmglobal.com/knowledge-bank/news/apollo-hospitals-collaborates-with-cleveland-clinic-to-offer-international-second-opinion-services-to-patients</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>Johns Hopkins (University)</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>College of Nursing, Christian Medical College Vellore</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Johns Hopkins School of Nursing and CMC Vellore College of Nursing authors Leveraging a Global Partnership to Address COVID-19-Related Mental Health Challenges</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>3 October 2024</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>https://onlinelibrary.wiley.com/doi/10.1111/jpm.13115</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>Johns Hopkins (University)</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>College of Nursing, Christian Medical College Vellore</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>Johns Hopkins School of Nursing From Baltimore to Vellore, India: Global Support for Nurses Struggling with COVID-Related Mental Health</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>August 2021</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>https://nursing.jhu.edu/magazine/articles/2021/08/from-baltimore-to-vellore-india-global-support-for-nurses-struggling-with-covid-related-mental-health/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Johns Hopkins (University)</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>College of Nursing, Christian Medical College Vellore</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>College of Nursing, CMC Vellore Collaboration</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>undated</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>https://concmc.org/collaboration/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>AIG Hospitals, Hyderabad</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>Post Bulletin Billionaire to partner with Mayo Clinic on India hospitals</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>11 February 2025</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>https://www.postbulletin.com/business/billionaire-to-partner-with-mayo-clinic-on-india-hospitals</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>AIG Hospitals, Hyderabad</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>Mayo Clinic AIG Hospitals in India joins Mayo Clinic Care Network</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>24 October 2019</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>https://www.newswise.com/articles/aig-hospitals-in-india-joins-mayo-clinic-care-network</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>Memorial Sloan Kettering</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>iCliniq, Chennai (MSKCC India)</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>Memorial Sloan Kettering Cancer Center Memorial Sloan Kettering Cancer Center Launches MSKCC India to Expand Access to World-Renowned Oncologists, Cancer Care, Research, and Education</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>2 August 2021</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/memorial-sloan-kettering-cancer-center-launches-mskcc-india-to-expand-access-to-world-renowned-oncologists-cancer-care-research-and-education-301345795.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>Memorial Sloan Kettering</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>iCliniq, Chennai (MSKCC India)</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>iCliniq Frequently Asked Question: MSK India</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>undated</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>https://mskcc.icliniq.com/mskcc-india-services/mskcc-patient-faqs</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>Northwell Health (Center for Global Health)</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>Christian Medical College (CMC) Vellore</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>Northwell Health Northwell Health signs five-year strategic agreement with Indian health system, CMC Vellore</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>https://www.northwell.edu/news/the-latest/northwell-signs-5-year-strategic-agreement-india-s-cmc-vellore</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>LMU Klinikum (University Hospital Munich)</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>AIIMS New Delhi</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Press Trust of India AIIMS Delhi, Munich-based university sign agreement for research in medicine, life sciences</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>https://news.careers360.com/aiims-delhi-munich-based-university-sign-non-binding-mou-for-collaborative-endeavours/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>University of Bolton Institute of Medicine (now University of Greater Manchester Medical School)</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>AIIMS New Delhi</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>News Services Division AIIMS New Delhi signed MoU with University of Bolton Institute of Medicine</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>https://newsonair.gov.in/aiims-new-delhi-signed-mou-with-university-of-bolton-institute-of-medicine</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>Johns Hopkins (Medicine International)</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>HCL Healthcare</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>Domain-b HCL enters healthcare with HCL Avitas</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>6 February 2014</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>https://www.domain-b.com/companies-organisations/firms-companies/hcl-enters-healthcare-with-hcl-avitas</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>Johns Hopkins (Medicine International)</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>HCL Healthcare</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>Johns Hopkins Medicine International HCL Healthcare</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>undated</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hopkinsmedicine.org/international/health-care-consulting/asia-pacific/hcl-healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
           <t>MD Anderson Cancer Center</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B117" s="5" t="inlineStr">
         <is>
           <t>Tata Memorial Hospital, Mumbai (Project ECHO Palliative Care Africa II)</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C117" s="5" t="inlineStr">
         <is>
           <t>The University of Texas MD Anderson Cancer Center Project ECHO: Palliative Care Africa (PACA) II</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D117" s="5" t="inlineStr">
         <is>
           <t>undated</t>
         </is>
       </c>
-      <c r="E89" s="5" t="inlineStr">
+      <c r="E117" s="5" t="inlineStr">
         <is>
           <t>https://www.mdanderson.org/education-training/outreach-programs/project-echo/programs/palliative-care-africa.html</t>
         </is>
@@ -5911,6 +7430,34 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId116"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Partnerships_Tracker.xlsx
+++ b/output/Partnerships_Tracker.xlsx
@@ -231,8 +231,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tracker" displayName="Tracker" ref="A1:L59" headerRowCount="1">
-  <autoFilter ref="A1:L59"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tracker" displayName="Tracker" ref="A1:L96" headerRowCount="1">
+  <autoFilter ref="A1:L96"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Status"/>
     <tableColumn id="2" name="Country"/>
@@ -558,7 +558,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scope: partnerships that are active, or ended or last active within the past five years. Last checked 2026-10-05.</t>
+          <t>Scope: partnerships that are active, or ended or last active within the past five years. Last checked 2026-10-07.</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF(Tracker!$A$2:$A$59,A5)</f>
+        <f>COUNTIF(Tracker!$A$2:$A$96,A5)</f>
         <v/>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Tracker!$A$2:$A$59,A6)</f>
+        <f>COUNTIF(Tracker!$A$2:$A$96,A6)</f>
         <v/>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Tracker!$A$2:$A$59,A7)</f>
+        <f>COUNTIF(Tracker!$A$2:$A$96,A7)</f>
         <v/>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -670,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4098,6 +4098,2140 @@
       <c r="L59" s="14" t="inlineStr">
         <is>
           <t>MD Anderson Cancer Center, undated</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>Cedars-Sinai</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="inlineStr">
+        <is>
+          <t>Eka Hospital Group</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G60" s="12" t="inlineStr">
+        <is>
+          <t>Cedars-Sinai and Eka Hospital Group signed a three-year memorandum of understanding in August 2022, starting with advisory services in emergency medicine and trauma care. Under the agreement, two Cedars-Sinai emergency nurses led a two-week teaching mission for nurses from Eka's seven hospitals in Jakarta.</t>
+        </is>
+      </c>
+      <c r="H60" s="12" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="I60" s="12" t="inlineStr"/>
+      <c r="J60" s="12" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="K60" s="12" t="inlineStr">
+        <is>
+          <t>Cedars-Sinai's story dated 20 December 2024 (date in the page's own data) reports the two nurses had recently returned from the teaching mission at Eka under the 2022 agreement. The three-year term nominally ran to about August 2025 and no renewal was found.</t>
+        </is>
+      </c>
+      <c r="L60" s="14" t="inlineStr">
+        <is>
+          <t>Cedars-Sinai, 2022-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>Harvard Medical School</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t>Universitas Harkat Negeri and CISDI (Primary Healthcare Impact Lab)</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G61" s="12" t="inlineStr">
+        <is>
+          <t>Harvard Medical School co-founded the Primary Healthcare Impact Lab with CISDI, Universitas Harkat Negeri and PT Tamaris Hidro, launched in Jakarta on 7 May 2026. The lab works on primary care service delivery, research and leadership education in Kota Tegal, Kabupaten Tegal and Brebes, and Harvard Medical School supports the university's medical curriculum.</t>
+        </is>
+      </c>
+      <c r="H61" s="12" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="I61" s="12" t="inlineStr"/>
+      <c r="J61" s="12" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="K61" s="12" t="inlineStr">
+        <is>
+          <t>Suara.com reports the launch at BRIN in Jakarta on 7 May 2026, and CISDI's own page names Harvard Medical School as a founding partner working in Tegal and Brebes. Neither source names Brigham and Women's Hospital.</t>
+        </is>
+      </c>
+      <c r="L61" s="14" t="inlineStr">
+        <is>
+          <t>Suara.com, 2026-05-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>MD Anderson Cancer Center</t>
+        </is>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="inlineStr">
+        <is>
+          <t>Indonesian Ministry of Health and RS Kanker Dharmais</t>
+        </is>
+      </c>
+      <c r="F62" s="12" t="inlineStr">
+        <is>
+          <t>Government agreement</t>
+        </is>
+      </c>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>MD Anderson signed a memorandum of understanding with the Ministry of Health in February 2023 covering service comparison, training, research support and cancer data management, with Dharmais as implementing hospital. It runs Project NOTRE, a breast cancer ECHO telementoring program with Dharmais.</t>
+        </is>
+      </c>
+      <c r="H62" s="12" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="I62" s="12" t="inlineStr"/>
+      <c r="J62" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="K62" s="12" t="inlineStr">
+        <is>
+          <t>MD Anderson's ECHO program listing for Project NOTRE with Dharmais is dated 20 June 2025 for a session on 14 June 2025.</t>
+        </is>
+      </c>
+      <c r="L62" s="14" t="inlineStr">
+        <is>
+          <t>WHO Global Breast Cancer Initiative Community, 2025-06-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="inlineStr">
+        <is>
+          <t>MD Anderson Cancer Center</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
+        <is>
+          <t>MRCCC Siloam Semanggi (Siloam Hospitals)</t>
+        </is>
+      </c>
+      <c r="F63" s="12" t="inlineStr">
+        <is>
+          <t>Advisory and consulting</t>
+        </is>
+      </c>
+      <c r="G63" s="12" t="inlineStr">
+        <is>
+          <t>MD Anderson provides strategic and clinical advisory support to MRCCC Siloam Semanggi from January 2026 to January 2027. It covers multidisciplinary care, patient navigation, quality assurance and breast and lung cancer programs.</t>
+        </is>
+      </c>
+      <c r="H63" s="12" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="I63" s="12" t="inlineStr"/>
+      <c r="J63" s="12" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="K63" s="12" t="inlineStr">
+        <is>
+          <t>Kontan, 31 March 2026, reports the advisory collaboration running January 2026 to January 2027, based on an MRCCC release.</t>
+        </is>
+      </c>
+      <c r="L63" s="14" t="inlineStr">
+        <is>
+          <t>Kontan, 2026-03-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="inlineStr">
+        <is>
+          <t>IHC Rumah Sakit Pusat Pertamina (RSPP)</t>
+        </is>
+      </c>
+      <c r="F64" s="12" t="inlineStr">
+        <is>
+          <t>Clinical affiliation</t>
+        </is>
+      </c>
+      <c r="G64" s="12" t="inlineStr">
+        <is>
+          <t>RSPP is the first Indonesian member of the Mayo Clinic Care Network, with access to eConsults, eTumor boards and Mayo health care consulting projects. RSPP physicians also visit Mayo Clinic campuses for knowledge exchange.</t>
+        </is>
+      </c>
+      <c r="H64" s="12" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="I64" s="12" t="inlineStr"/>
+      <c r="J64" s="12" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="K64" s="12" t="inlineStr">
+        <is>
+          <t>RSPP's own newsroom on 4 December 2024 describes an RSPP endocrinologist visiting Mayo Clinic Florida through the Care Network membership. Mayo announced the membership on 26 January 2023.</t>
+        </is>
+      </c>
+      <c r="L64" s="14" t="inlineStr">
+        <is>
+          <t>RS Pusat Pertamina, 2024-12-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>St. Jude Children's Research Hospital</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
+        <is>
+          <t>RSUPN Dr. Cipto Mangunkusumo (RSCM) and Indonesian Ministry of Health</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G65" s="12" t="inlineStr">
+        <is>
+          <t>St. Jude Global has worked with Indonesia's pediatric oncology community for over 15 years and supports the Ministry of Health in drafting a national pediatric cancer control plan. Its Asia Pacific team visited RSCM in April 2026 to review services and exchange knowledge.</t>
+        </is>
+      </c>
+      <c r="H65" s="12" t="inlineStr"/>
+      <c r="I65" s="12" t="inlineStr"/>
+      <c r="J65" s="12" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="K65" s="12" t="inlineStr">
+        <is>
+          <t>The Ministry of Health hospital directorate reported on 8 April 2026 a St. Jude Global Asia Pacific visit to RSCM on 7 April 2026 to strengthen childhood cancer collaboration.</t>
+        </is>
+      </c>
+      <c r="L65" s="14" t="inlineStr">
+        <is>
+          <t>Kemenkes, 2026-04-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals</t>
+        </is>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="inlineStr">
+        <is>
+          <t>Mayapada Healthcare Group (Mayapada Hospital)</t>
+        </is>
+      </c>
+      <c r="F66" s="12" t="inlineStr">
+        <is>
+          <t>Clinical affiliation</t>
+        </is>
+      </c>
+      <c r="G66" s="12" t="inlineStr">
+        <is>
+          <t>Apollo and Mayapada signed an MoU in New Delhi in January 2025 covering medical education, case proctorship, nurse and doctor training in India, and technology for the planned Mayapada Apollo Batam International Hospital. Two further MoUs in January 2026 added AI based preventive health and emergency nursing training.</t>
+        </is>
+      </c>
+      <c r="H66" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I66" s="12" t="inlineStr"/>
+      <c r="J66" s="12" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="K66" s="12" t="inlineStr">
+        <is>
+          <t>Detik (20 January 2026) and JawaPos report the Apollo leadership visit to Batam and Jakarta on 7 to 9 January 2026 and two new MoUs signed on 8 January 2026 at Mayapada Hospital Jakarta Selatan.</t>
+        </is>
+      </c>
+      <c r="L66" s="14" t="inlineStr">
+        <is>
+          <t>JawaPos, 2026-01-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C67" s="13" t="inlineStr">
+        <is>
+          <t>Asia OneHealthcare (A1Health, formerly Columbia Asia Healthcare)</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
+        <is>
+          <t>RS Premier Jatinegara, Bintaro and Surabaya and Columbia Asia hospitals</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>Ownership or management</t>
+        </is>
+      </c>
+      <c r="G67" s="12" t="inlineStr">
+        <is>
+          <t>Malaysia based hospital group A1Health owns and operates nine hospitals in Indonesia, including in Jakarta, Surabaya, Banten, Medan and Semarang. They include the three RS Premier hospitals it gained by buying Ramsay Sime Darby Health Care, which closed in 2024.</t>
+        </is>
+      </c>
+      <c r="H67" s="12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I67" s="12" t="inlineStr"/>
+      <c r="J67" s="12" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="K67" s="12" t="inlineStr">
+        <is>
+          <t>The Edge Malaysia (2 February 2026) reports A1Health has nine hospitals in Indonesia; The Edge (6 September 2024) reports the rename and the completed acquisition of Ramsay Sime Darby Health Care.</t>
+        </is>
+      </c>
+      <c r="L67" s="14" t="inlineStr">
+        <is>
+          <t>The Edge Malaysia, 2026-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="inlineStr">
+        <is>
+          <t>Chung Shan Medical University (Taiwan)</t>
+        </is>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="inlineStr">
+        <is>
+          <t>Universitas Indonesia</t>
+        </is>
+      </c>
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G68" s="12" t="inlineStr">
+        <is>
+          <t>CSMU and Universitas Indonesia signed an MoU in August 2025 on faculty and student exchange, joint curriculum, research and clinical training, building on dental medicine exchanges with UI's Faculty of Dentistry since 2017.</t>
+        </is>
+      </c>
+      <c r="H68" s="12" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="I68" s="12" t="inlineStr"/>
+      <c r="J68" s="12" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="K68" s="12" t="inlineStr">
+        <is>
+          <t>CSMU's press page dated 8 August 2025 reports the MoU signed by both presidents.</t>
+        </is>
+      </c>
+      <c r="L68" s="14" t="inlineStr">
+        <is>
+          <t>Chung Shan Medical University, 2025-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>Hong Kong Asia Medical Group (HKAMG)</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t>Bali International Hospital (PT Pertamedika Bali Hospital, IHC)</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>Clinical affiliation</t>
+        </is>
+      </c>
+      <c r="G69" s="12" t="inlineStr">
+        <is>
+          <t>HKAMG, a private cardiovascular hospital group whose flagship is Wuhan Asia Heart Hospital, provides cardiology and clinical expertise to Bali International Hospital. Its specialists took part in the hospital's first TAVI procedures in March 2026, which HKAMG funded.</t>
+        </is>
+      </c>
+      <c r="H69" s="12" t="inlineStr"/>
+      <c r="I69" s="12" t="inlineStr"/>
+      <c r="J69" s="12" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="K69" s="12" t="inlineStr">
+        <is>
+          <t>ANTARA (9 March 2026) reports that the first TAVI procedures at Bali International Hospital on 7 March 2026 were supported by HKAMG, quoting HKAMG's CEO; BIH named HKAMG a partner on 25 April 2025.</t>
+        </is>
+      </c>
+      <c r="L69" s="14" t="inlineStr">
+        <is>
+          <t>ANTARA, 2026-03-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>Icon Group (Icon Cancer Centre)</t>
+        </is>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
+        <is>
+          <t>Bali International Hospital (PT Pertamina Bina Medika IHC)</t>
+        </is>
+      </c>
+      <c r="F70" s="12" t="inlineStr">
+        <is>
+          <t>Ownership or management</t>
+        </is>
+      </c>
+      <c r="G70" s="12" t="inlineStr">
+        <is>
+          <t>Icon Cancer Centre operates the radiation oncology and cancer service inside Bali International Hospital in the Sanur special economic zone, with its own international doctors, the first allowed to practice in Indonesia. It treated its first patient on 7 May 2025.</t>
+        </is>
+      </c>
+      <c r="H70" s="12" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="I70" s="12" t="inlineStr"/>
+      <c r="J70" s="12" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="K70" s="12" t="inlineStr">
+        <is>
+          <t>Icon Group's release of 26 March 2026 reports the launch of the first stereotactic radiotherapy service and the first brachytherapy treatment at Icon Cancer Centre, Bali International Hospital.</t>
+        </is>
+      </c>
+      <c r="L70" s="14" t="inlineStr">
+        <is>
+          <t>Icon Group, 2026-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C71" s="13" t="inlineStr">
+        <is>
+          <t>International University of Health and Welfare (IUHW)</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>Ministry of Health (Kemenkes)</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G71" s="12" t="inlineStr">
+        <is>
+          <t>The Ministry of Health and IUHW signed an MoU in April 2026 on postgraduate clinical training and specialist development, academic exchange and technical help from Japanese experts.</t>
+        </is>
+      </c>
+      <c r="H71" s="12" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="I71" s="12" t="inlineStr"/>
+      <c r="J71" s="12" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="K71" s="12" t="inlineStr">
+        <is>
+          <t>The Ministry of Health reports the MoU signed on 13 April 2026 by its Secretary General, Kunta Wibawa Dasa Nugraha, and IUHW President Yasuhiro Suzuki, witnessed by the health minister.</t>
+        </is>
+      </c>
+      <c r="L71" s="14" t="inlineStr">
+        <is>
+          <t>Kementerian Kesehatan RI, 2026-04-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>Monash Health</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>RS Otak Dr. Drs. M. Hatta Bukittinggi (RSOMH, Ministry of Health brain hospital)</t>
+        </is>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>Monash Health and the national brain hospital in Bukittinggi signed an MoU in November 2024 and hold knowledge sharing sessions and clinical case reviews on multidisciplinary stroke rehabilitation. In September 2026 they discussed a wider joint program.</t>
+        </is>
+      </c>
+      <c r="H72" s="12" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="I72" s="12" t="inlineStr"/>
+      <c r="J72" s="12" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K72" s="12" t="inlineStr">
+        <is>
+          <t>The Health Ministry's hospital directorate reports a 22 July 2026 stroke rehabilitation session under the November 2024 MoU, and meetings on 24 and 28 September 2026.</t>
+        </is>
+      </c>
+      <c r="L72" s="14" t="inlineStr">
+        <is>
+          <t>Ditjen Kesehatan Lanjutan, Kemenkes, 2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>National Center for Global Health and Medicine (NCGM) and Kobe University</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>Universitas Airlangga (Institute of Tropical Disease and RS Universitas Airlangga)</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t>Japanese institutions work with Universitas Airlangga on infectious disease research through the J-GRID program, running since 2007 and renewed in 2015. A delegation visit to Unair Hospital in February 2025 explored widening it.</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="I73" s="12" t="inlineStr"/>
+      <c r="J73" s="12" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="K73" s="12" t="inlineStr">
+        <is>
+          <t>Unair News (20 February 2025) reports the 19 February 2025 visit of NCGM and Kobe University staff and the hospital director describing continued J-GRID research collaboration.</t>
+        </is>
+      </c>
+      <c r="L73" s="14" t="inlineStr">
+        <is>
+          <t>Universitas Airlangga, 2025-02-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C74" s="13" t="inlineStr">
+        <is>
+          <t>Ramathibodi Hospital, Mahidol University</t>
+        </is>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
+        <is>
+          <t>Faculty of Medicine Universitas Indonesia and RSCM</t>
+        </is>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <t>Ramathibodi and FMUI-RSCM signed an MoU in May 2025 for clinical training and academic cooperation, with an initial focus on urology and endoscopic surgical education.</t>
+        </is>
+      </c>
+      <c r="H74" s="12" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="I74" s="12" t="inlineStr"/>
+      <c r="J74" s="12" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="K74" s="12" t="inlineStr">
+        <is>
+          <t>Ramathibodi's international office reports the MoU signing on 21 May 2025 at the Faculty of Medicine Ramathibodi Hospital.</t>
+        </is>
+      </c>
+      <c r="L74" s="14" t="inlineStr">
+        <is>
+          <t>Ramathibodi Hospital, Mahidol University, 2025-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C75" s="13" t="inlineStr">
+        <is>
+          <t>Sapporo Cardio Vascular Clinic</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>Bali International Hospital (PT Pertamedika Bali Hospital, IHC)</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr">
+        <is>
+          <t>Clinical affiliation</t>
+        </is>
+      </c>
+      <c r="G75" s="12" t="inlineStr">
+        <is>
+          <t>Sapporo Cardio Vascular Clinic provides cardiology expertise to Bali International Hospital and introduced itself in Indonesia with the hospital's first TAVI procedures in March 2026. A Sapporo cardiovascular center also hosts Indonesian cardiologists on Ministry of Health fellowships.</t>
+        </is>
+      </c>
+      <c r="H75" s="12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I75" s="12" t="inlineStr"/>
+      <c r="J75" s="12" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="K75" s="12" t="inlineStr">
+        <is>
+          <t>Investor Daily (17 March 2026) reports two TAVI procedures on 7 March 2026 at Bali International Hospital, performed by an SCVC interventional cardiologist with HKAMG specialists, introducing SCVC's presence in Indonesia through its collaboration with the hospital. BIH named the clinic a cardiology partner on 25 April 2025.</t>
+        </is>
+      </c>
+      <c r="L75" s="14" t="inlineStr">
+        <is>
+          <t>investor.id, 2026-03-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C76" s="13" t="inlineStr">
+        <is>
+          <t>Seoul National University Hospital (SNUH)</t>
+        </is>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="inlineStr">
+        <is>
+          <t>Faculty of Medicine Universitas Indonesia and RSUPN Dr. Cipto Mangunkusumo (RSCM)</t>
+        </is>
+      </c>
+      <c r="F76" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G76" s="12" t="inlineStr">
+        <is>
+          <t>SNUH, Universitas Indonesia and RSCM signed an MoU in July 2024 covering joint research, academic exchange, online education and staff and student exchange. SNUH's urology department signed a five-year implementation agreement with FMUI and RSCM on 13 January 2025.</t>
+        </is>
+      </c>
+      <c r="H76" s="12" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="I76" s="12" t="inlineStr"/>
+      <c r="J76" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="K76" s="12" t="inlineStr">
+        <is>
+          <t>Medipharm Health (4 February 2025) reports the implementation agreement signed on 13 January 2025 as a follow-up to the July 2024 MoU.</t>
+        </is>
+      </c>
+      <c r="L76" s="14" t="inlineStr">
+        <is>
+          <t>Medipharm Health News, 2025-02-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C77" s="13" t="inlineStr">
+        <is>
+          <t>Seoul National University Hospital (SNUH)</t>
+        </is>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>RSUP Fatmawati (Ministry of Health hospital)</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>Clinical affiliation</t>
+        </is>
+      </c>
+      <c r="G77" s="12" t="inlineStr">
+        <is>
+          <t>Fatmawati and SNUH signed an MoU in March 2023, witnessed by the health minister, to build liver, kidney and orthopedic transplant capacity. Fatmawati's living donor liver transplant program is being developed with SNUH to build the skills of its medical staff.</t>
+        </is>
+      </c>
+      <c r="H77" s="12" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="I77" s="12" t="inlineStr"/>
+      <c r="J77" s="12" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="K77" s="12" t="inlineStr">
+        <is>
+          <t>The Health Ministry's release of 10 April 2026 on Fatmawati's third liver transplant (9 April 2026) says the program is developed through cooperation with SNUH.</t>
+        </is>
+      </c>
+      <c r="L77" s="14" t="inlineStr">
+        <is>
+          <t>Kementerian Kesehatan RI, 2026-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>SingHealth</t>
+        </is>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia Healthcare Corporation (PT Pertamina Bina Medika) and Bali International Hospital</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G78" s="12" t="inlineStr">
+        <is>
+          <t>SingHealth and IHC signed an MoU in April 2024 on sharing clinical practice, hospital management, staff training and nursing transformation, aimed at supporting Bali International Hospital, where SingHealth is the academic partner for continuing medical education.</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="I78" s="12" t="inlineStr"/>
+      <c r="J78" s="12" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="K78" s="12" t="inlineStr">
+        <is>
+          <t>Bali International Hospital's press release of 25 April 2025 names SingHealth as its academic partner for continuing medical education and clinical advancement.</t>
+        </is>
+      </c>
+      <c r="L78" s="14" t="inlineStr">
+        <is>
+          <t>Bali.com, 2025-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>SingHealth Duke-NUS Global Health Institute (SingHealth and Duke-NUS Medical School)</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>Universitas Sumatera Utara (Faculty of Medicine)</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G79" s="12" t="inlineStr">
+        <is>
+          <t>SingHealth and the National University of Singapore (Duke-NUS) signed a partnership with USU in July 2023 on global health research, education and capacity building. The institute and USU's medical faculty ran a joint international summer course in July 2025.</t>
+        </is>
+      </c>
+      <c r="H79" s="12" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="I79" s="12" t="inlineStr"/>
+      <c r="J79" s="12" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="K79" s="12" t="inlineStr">
+        <is>
+          <t>USU reports the summer course with the SingHealth Duke-NUS Global Health Institute opened on 21 July 2025; USU's 8 August 2023 news item reports the partnership.</t>
+        </is>
+      </c>
+      <c r="L79" s="14" t="inlineStr">
+        <is>
+          <t>Universitas Sumatera Utara, 2025-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>Sun Medical Center (Sun Healthcare International)</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
+        <is>
+          <t>RSUP Prof. Dr. I.G.N.G. Ngoerah</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>Clinical affiliation</t>
+        </is>
+      </c>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>Ngoerah hospital and Korea's Sun Medical Hospital signed an MoU in March 2023, witnessed by the health minister, to support health tourism in Bali. The health minister opened the Ngoerah Sun Wellness and Aesthetic Center, run in collaboration with Sun Healthcare International, on 3 October 2024.</t>
+        </is>
+      </c>
+      <c r="H80" s="12" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="I80" s="12" t="inlineStr"/>
+      <c r="J80" s="12" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="K80" s="12" t="inlineStr">
+        <is>
+          <t>Liputan6 (5 October 2024) reports the opening of the Ngoerah Sun Wellness and Aesthetic Center on 3 October 2024 in collaboration with Sun Healthcare International of South Korea.</t>
+        </is>
+      </c>
+      <c r="L80" s="14" t="inlineStr">
+        <is>
+          <t>Liputan6, 2024-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C81" s="13" t="inlineStr">
+        <is>
+          <t>Taipei Veterans General Hospital</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>DKH Hospitals Group</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="inlineStr">
+        <is>
+          <t>Clinical affiliation</t>
+        </is>
+      </c>
+      <c r="G81" s="12" t="inlineStr">
+        <is>
+          <t>TVGH and DKH Hospitals Group signed a two year MoU in May 2025 covering exchange of medical staff, research and clinical trials, telehealth, training and international patient referrals.</t>
+        </is>
+      </c>
+      <c r="H81" s="12" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="I81" s="12" t="inlineStr"/>
+      <c r="J81" s="12" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="K81" s="12" t="inlineStr">
+        <is>
+          <t>Antara, 23 May 2025, reports the MoU signed in Bogor on 23 May 2025, running two years with an option to extend.</t>
+        </is>
+      </c>
+      <c r="L81" s="14" t="inlineStr">
+        <is>
+          <t>Antara, 2025-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C82" s="13" t="inlineStr">
+        <is>
+          <t>Tokushukai Medical Group</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
+        <is>
+          <t>RSJPD Harapan Kita (National Heart Center) and Ministry of Health</t>
+        </is>
+      </c>
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>Clinical affiliation</t>
+        </is>
+      </c>
+      <c r="G82" s="12" t="inlineStr">
+        <is>
+          <t>Tokushukai has worked with Harapan Kita since 2004, exchanging doctors and knowledge, and signed a December 2023 agreement for a new cardiac building that the Health Ministry describes as a grant of about Rp 1 trillion. The building is planned as a center for cardiovascular education and international collaboration.</t>
+        </is>
+      </c>
+      <c r="H82" s="12" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="I82" s="12" t="inlineStr"/>
+      <c r="J82" s="12" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="K82" s="12" t="inlineStr">
+        <is>
+          <t>The Health Ministry reports the topping off ceremony for the Harapan Kita-Tokushukai Building on 15 April 2026, attended by the health minister, with a Da Vinci surgical robot due in November 2026.</t>
+        </is>
+      </c>
+      <c r="L82" s="14" t="inlineStr">
+        <is>
+          <t>Kementerian Kesehatan RI, 2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C83" s="13" t="inlineStr">
+        <is>
+          <t>Wuhan Asia Heart Hospital</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>Ministry of Health (Kemenkes)</t>
+        </is>
+      </c>
+      <c r="F83" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G83" s="12" t="inlineStr">
+        <is>
+          <t>Under a Ministry of Health fellowship program funded by LPDP, Indonesian cardiologists train in cardiac intervention for 12 months at Wuhan Asia Heart Hospital, the flagship of Hong Kong Asia Medical Group.</t>
+        </is>
+      </c>
+      <c r="H83" s="12" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="I83" s="12" t="inlineStr"/>
+      <c r="J83" s="12" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="K83" s="12" t="inlineStr">
+        <is>
+          <t>The Health Ministry's release of 12 November 2024 reports six of 13 cardiology fellows placed at Wuhan Asia Heart Hospital for 12 months.</t>
+        </is>
+      </c>
+      <c r="L83" s="14" t="inlineStr">
+        <is>
+          <t>Kementerian Kesehatan RI, 2024-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C84" s="13" t="inlineStr">
+        <is>
+          <t>Zhongda Hospital (Southeast University)</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t>Ministry of Health (Kemenkes)</t>
+        </is>
+      </c>
+      <c r="F84" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G84" s="12" t="inlineStr">
+        <is>
+          <t>Zhongda Hospital is one of the named host hospitals for the Ministry of Health's one-year interventional cardiology and neurology fellowships.</t>
+        </is>
+      </c>
+      <c r="H84" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="I84" s="12" t="inlineStr"/>
+      <c r="J84" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="K84" s="12" t="inlineStr">
+        <is>
+          <t>The Health Ministry's release of 6 January 2025 names Zhongda Hospital among the hosts for 27 fellows.</t>
+        </is>
+      </c>
+      <c r="L84" s="14" t="inlineStr">
+        <is>
+          <t>Kementerian Kesehatan RI, 2025-01-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C85" s="13" t="inlineStr">
+        <is>
+          <t>Zhongshan Hospital (Fudan University)</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t>Ministry of Health (Kemenkes)</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G85" s="12" t="inlineStr">
+        <is>
+          <t>Under a Ministry of Health cardiology fellowship program funded by LPDP, Indonesian cardiologists train in cardiac intervention for 12 months at Fudan University Zhongshan Hospital. The ministry signed a cooperation agreement with the hospital in June 2024.</t>
+        </is>
+      </c>
+      <c r="H85" s="12" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="I85" s="12" t="inlineStr"/>
+      <c r="J85" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="K85" s="12" t="inlineStr">
+        <is>
+          <t>The Health Ministry reports seven of 13 cardiology fellows placed at Zhongshan Hospital in November 2024, and names the hospital among hosts for a further 27 fellows sent on 6 January 2025.</t>
+        </is>
+      </c>
+      <c r="L85" s="14" t="inlineStr">
+        <is>
+          <t>Kementerian Kesehatan RI, 2025-01-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B86" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C86" s="13" t="inlineStr">
+        <is>
+          <t>Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="inlineStr">
+        <is>
+          <t>Bali International Hospital (Indonesia Healthcare Corporation)</t>
+        </is>
+      </c>
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>Advisory and consulting</t>
+        </is>
+      </c>
+      <c r="G86" s="12" t="inlineStr">
+        <is>
+          <t>Mayo Clinic Global Consulting advised on the planning and design of Bali International Hospital in the Sanur special economic zone. Mayo has said it acts only as a consultant and clinical knowledge partner and does not run the hospital.</t>
+        </is>
+      </c>
+      <c r="H86" s="12" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="I86" s="12" t="inlineStr"/>
+      <c r="J86" s="12" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="K86" s="12" t="inlineStr">
+        <is>
+          <t>The latest dated source found is the Jakarta Post of 17 March 2023, quoting a Mayo executive that Mayo is only a consultant. Bali International Hospital did not list Mayo among its international partners in its 25 April 2025 partner announcement, and no 2024 to 2026 evidence of continued advisory work was found.</t>
+        </is>
+      </c>
+      <c r="L86" s="14" t="inlineStr">
+        <is>
+          <t>The Jakarta Post, 2023-03-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C87" s="13" t="inlineStr">
+        <is>
+          <t>UCLA Health</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>RS Jantung dan Pembuluh Darah Harapan Kita</t>
+        </is>
+      </c>
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>Advisory and consulting</t>
+        </is>
+      </c>
+      <c r="G87" s="12" t="inlineStr">
+        <is>
+          <t>UCLA Health worked with Harapan Kita on developing Indonesia's first heart transplant program, as the Ministry of Health reported when the hospital's new building opened in November 2022.</t>
+        </is>
+      </c>
+      <c r="H87" s="12" t="inlineStr"/>
+      <c r="I87" s="12" t="inlineStr"/>
+      <c r="J87" s="12" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="K87" s="12" t="inlineStr">
+        <is>
+          <t>The Ministry of Health release of the new Harapan Kita building launch in November 2022 names UCLA Health as a partner for heart transplant services. No newer dated evidence was found.</t>
+        </is>
+      </c>
+      <c r="L87" s="14" t="inlineStr">
+        <is>
+          <t>Kemenkes, 2022-11-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C88" s="13" t="inlineStr">
+        <is>
+          <t>Asan Medical Center</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t>Siloam Hospitals Group</t>
+        </is>
+      </c>
+      <c r="F88" s="12" t="inlineStr">
+        <is>
+          <t>Clinical affiliation</t>
+        </is>
+      </c>
+      <c r="G88" s="12" t="inlineStr">
+        <is>
+          <t>Siloam and Asan Medical Center signed an MoU in November 2023 to develop clinical capability, with joint patient care, referrals and exchange of medical staff and researchers.</t>
+        </is>
+      </c>
+      <c r="H88" s="12" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="I88" s="12" t="inlineStr"/>
+      <c r="J88" s="12" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="K88" s="12" t="inlineStr">
+        <is>
+          <t>Kompas TV reports the MoU press conference held on 2 November 2023, attended by Ministry of Health officials. No newer dated evidence was found.</t>
+        </is>
+      </c>
+      <c r="L88" s="14" t="inlineStr">
+        <is>
+          <t>Kompas TV, 2023-11-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C89" s="13" t="inlineStr">
+        <is>
+          <t>Icon Group (Icon Cancer Centre, Singapore)</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t>RS Universitas Airlangga (RSUA)</t>
+        </is>
+      </c>
+      <c r="F89" s="12" t="inlineStr">
+        <is>
+          <t>Clinical affiliation</t>
+        </is>
+      </c>
+      <c r="G89" s="12" t="inlineStr">
+        <is>
+          <t>Airlangga University Hospital and Icon Cancer Centre signed an agreement for medical exchange in cancer service, education and research in April 2023.</t>
+        </is>
+      </c>
+      <c r="H89" s="12" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="I89" s="12" t="inlineStr"/>
+      <c r="J89" s="12" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="K89" s="12" t="inlineStr">
+        <is>
+          <t>BioSpectrum Asia reports the signing on 10 April 2023; no newer dated activity was found.</t>
+        </is>
+      </c>
+      <c r="L89" s="14" t="inlineStr">
+        <is>
+          <t>BioSpectrum Asia, 2023-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C90" s="13" t="inlineStr">
+        <is>
+          <t>National Center for Global Health and Medicine (NCGM)</t>
+        </is>
+      </c>
+      <c r="D90" s="12" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="inlineStr">
+        <is>
+          <t>Siloam Hospitals Group</t>
+        </is>
+      </c>
+      <c r="F90" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G90" s="12" t="inlineStr">
+        <is>
+          <t>NCGM and Siloam signed an MoU on clinical research cooperation in August 2022 and held a joint seminar to launch Siloam's new Clinical Research Department.</t>
+        </is>
+      </c>
+      <c r="H90" s="12" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="I90" s="12" t="inlineStr"/>
+      <c r="J90" s="12" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="K90" s="12" t="inlineStr">
+        <is>
+          <t>NCGM's news release of 7 October 2022 reports the MoU concluded on 13 August 2022; nothing newer was found.</t>
+        </is>
+      </c>
+      <c r="L90" s="14" t="inlineStr">
+        <is>
+          <t>NCGM, 2022-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C91" s="13" t="inlineStr">
+        <is>
+          <t>Peking Union Medical College Hospital</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>Ministry of Health (Kemenkes)</t>
+        </is>
+      </c>
+      <c r="F91" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G91" s="12" t="inlineStr">
+        <is>
+          <t>The Ministry of Health signed a cooperation agreement with PUMCH during its June 2024 China visit, alongside other Chinese hospitals.</t>
+        </is>
+      </c>
+      <c r="H91" s="12" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="I91" s="12" t="inlineStr"/>
+      <c r="J91" s="12" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="K91" s="12" t="inlineStr">
+        <is>
+          <t>Ministry of Health release dated 11 June 2024 names PUMCH among agreements signed. Content of the agreement is not detailed and nothing newer was found.</t>
+        </is>
+      </c>
+      <c r="L91" s="14" t="inlineStr">
+        <is>
+          <t>Ministry of Health, 2024-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B92" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C92" s="13" t="inlineStr">
+        <is>
+          <t>Rizhao Xinyi Hospital (Rizhao Heart Hospital)</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="inlineStr">
+        <is>
+          <t>Ministry of Health (Kemenkes)</t>
+        </is>
+      </c>
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
+        <is>
+          <t>A June 2024 letter of intent provides for sending Indonesian cardiovascular doctors, nurses and technicians to Rizhao for training over five years.</t>
+        </is>
+      </c>
+      <c r="H92" s="12" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="I92" s="12" t="inlineStr"/>
+      <c r="J92" s="12" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="K92" s="12" t="inlineStr">
+        <is>
+          <t>Ministry of Health release dated 11 June 2024. No newer dated evidence found.</t>
+        </is>
+      </c>
+      <c r="L92" s="14" t="inlineStr">
+        <is>
+          <t>Ministry of Health, 2024-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C93" s="13" t="inlineStr">
+        <is>
+          <t>Royal Brompton and Harefield Hospitals (Guy's and St Thomas' NHS Foundation Trust)</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>Mandaya Royal Hospital Puri</t>
+        </is>
+      </c>
+      <c r="F93" s="12" t="inlineStr">
+        <is>
+          <t>Telehealth and second opinion</t>
+        </is>
+      </c>
+      <c r="G93" s="12" t="inlineStr">
+        <is>
+          <t>A November 2020 MoU gave Mandaya patients second opinions and teleconsultations with Royal Brompton clinicians, plus remote training and joint cardiorespiratory service development. A pediatric cardiac centre was launched with the partner in May 2023.</t>
+        </is>
+      </c>
+      <c r="H93" s="12" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="I93" s="12" t="inlineStr"/>
+      <c r="J93" s="12" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="K93" s="12" t="inlineStr">
+        <is>
+          <t>Mandaya's May 2023 inauguration of a pediatric cardiac centre with Royal Brompton and Harefield is the latest dated evidence found; nothing from October 2024 onward.</t>
+        </is>
+      </c>
+      <c r="L93" s="14" t="inlineStr">
+        <is>
+          <t>Mandaya Hospital Group, 2020-12-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C94" s="13" t="inlineStr">
+        <is>
+          <t>UMC Utrecht</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t>RS Jantung dan Pembuluh Darah Harapan Kita</t>
+        </is>
+      </c>
+      <c r="F94" s="12" t="inlineStr">
+        <is>
+          <t>Clinical affiliation</t>
+        </is>
+      </c>
+      <c r="G94" s="12" t="inlineStr">
+        <is>
+          <t>The Health Ministry reported that Harapan Kita works with UMC Utrecht to develop heart failure services, alongside UCLA Health for heart transplantation.</t>
+        </is>
+      </c>
+      <c r="H94" s="12" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="I94" s="12" t="inlineStr"/>
+      <c r="J94" s="12" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="K94" s="12" t="inlineStr">
+        <is>
+          <t>The Health Ministry's release of 9 November 2022 on the new Harapan Kita building names UMC Utrecht; no newer dated evidence was found.</t>
+        </is>
+      </c>
+      <c r="L94" s="14" t="inlineStr">
+        <is>
+          <t>Kementerian Kesehatan RI, 2022-11-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>Ended</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C95" s="13" t="inlineStr">
+        <is>
+          <t>KPJ Healthcare</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t>RS Medika BSD</t>
+        </is>
+      </c>
+      <c r="F95" s="12" t="inlineStr">
+        <is>
+          <t>Ownership or management</t>
+        </is>
+      </c>
+      <c r="G95" s="12" t="inlineStr">
+        <is>
+          <t>KPJ Healthcare managed RS Medika BSD until Columbia Asia acquired the hospital in September 2023 and renamed it RS Columbia Asia BSD.</t>
+        </is>
+      </c>
+      <c r="H95" s="12" t="inlineStr"/>
+      <c r="I95" s="12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="J95" s="12" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="K95" s="12" t="inlineStr">
+        <is>
+          <t>Warta Ekonomi (2 October 2023) reports that RS Columbia Asia BSD resulted from the acquisition of RS Medika BSD, previously managed by KPJ Healthcare Group Malaysia; Kontan reports the acquisition on 19 September 2023.</t>
+        </is>
+      </c>
+      <c r="L95" s="14" t="inlineStr">
+        <is>
+          <t>Warta Ekonomi, 2023-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>Ended</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C96" s="13" t="inlineStr">
+        <is>
+          <t>Ramsay Health Care</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="inlineStr">
+        <is>
+          <t>RS Premier Jatinegara, Bintaro and Surabaya</t>
+        </is>
+      </c>
+      <c r="F96" s="12" t="inlineStr">
+        <is>
+          <t>Ownership or management</t>
+        </is>
+      </c>
+      <c r="G96" s="12" t="inlineStr">
+        <is>
+          <t>Ramsay Health Care co-owned the three RS Premier hospitals through Ramsay Sime Darby Health Care, its 50:50 joint venture with Sime Darby, until the venture was sold to Columbia Asia (now A1Health).</t>
+        </is>
+      </c>
+      <c r="H96" s="12" t="inlineStr"/>
+      <c r="I96" s="12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="J96" s="12" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="K96" s="12" t="inlineStr">
+        <is>
+          <t>The Edge (6 September 2024) reports that Columbia Asia had recently completed the purchase of Ramsay Sime Darby Health Care, which operated three hospitals in Indonesia, from Sime Darby and its Australian partner.</t>
+        </is>
+      </c>
+      <c r="L96" s="14" t="inlineStr">
+        <is>
+          <t>The Edge Malaysia, 2024-09-06</t>
         </is>
       </c>
     </row>
@@ -4161,10 +6295,47 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId95"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId59"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId96"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4175,7 +6346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E117"/>
+  <dimension ref="A1:E187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7337,6 +9508,1888 @@
       <c r="E117" s="5" t="inlineStr">
         <is>
           <t>https://www.mdanderson.org/education-training/outreach-programs/project-echo/programs/palliative-care-africa.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>Cedars-Sinai</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>Eka Hospital Group</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>Cedars-Sinai Cedars-Sinai International Launches Presence in Indonesia</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cedars-sinai.org/blog/cedars-sinai-launches-collaboration-in-indonesia.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>Cedars-Sinai</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>Eka Hospital Group</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>Kompas Eka Hospital Group Jalin Kerja Sama dengan Cedars-Sinai Hospital</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>2022-08-25</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>https://biz.kompas.com/read/2022/08/25/121418528/eka-hospital-group-jalin-kerja-sama-dengan-cedars-sinai-hospital</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>Cedars-Sinai</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>Eka Hospital Group</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>Cedars-Sinai Staff Nurses Share Expertise with International EKA Hospital Group</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cedars-sinai.org/international-stories/nurses-share-expertise-with-international-eka-hospital-group.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>Harvard Medical School</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>Universitas Harkat Negeri and CISDI (Primary Healthcare Impact Lab)</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>Bangun Santoso, Suara.com UHN dan CISDI Gandeng Harvard Medical School, Bangun Pusat Riset Kesehatan Primer di RI</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>https://www.suara.com/news/2026/05/07/202619/uhn-dan-cisdi-gandeng-harvard-medical-school-bangun-pusat-riset-kesehatan-primer-di-ri</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>Harvard Medical School</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>Universitas Harkat Negeri and CISDI (Primary Healthcare Impact Lab)</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>CISDI Primary Healthcare IMPACT Lab</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr"/>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>https://cisdi.org/en/our-works/phcimpactlab</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>MD Anderson Cancer Center</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>Indonesian Ministry of Health and RS Kanker Dharmais</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>MD Anderson Cancer Center Project NOTRE (Indonesia Breast Cancer ECHO)</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>https://knowledge-action-portal.com/en/content/project-notre-indonesia-breast-cancer-echo-jun-14-2025-0300-pm-eest</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>MD Anderson Cancer Center</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>Indonesian Ministry of Health and RS Kanker Dharmais</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>MD Anderson Cancer Center MD Anderson announces new collaboration in Indonesia to reduce global cancer burden</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>2023-02-03</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mdanderson.org/newsroom/md-anderson-announces-new-collaboration-in-indonesia.h00-159616278.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>MD Anderson Cancer Center</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>Indonesian Ministry of Health and RS Kanker Dharmais</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>Kementerian Kesehatan RI Kemenkes dan MD Anderson Cancer Center Jalin Kerja Sama Atasi Kanker</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>2023-02-03</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kemkes.go.id/eng/kemenkes-dan-md-anderson-cancer-center-jalin-kerja-sama-atasi-kanker</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>MD Anderson Cancer Center</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>MRCCC Siloam Semanggi (Siloam Hospitals)</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>Kontan Kesenjangan Layanan Kanker di Indonesia, MRCCC Siloam Menggandeng MD Anderson</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>https://industri.kontan.co.id/news/kesenjangan-layanan-kanker-di-indonesia-mrccc-siloam-menggandeng-md-anderson</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>IHC Rumah Sakit Pusat Pertamina (RSPP)</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>RS Pusat Pertamina Learning from the Best: IHC RSPP Endocrinologist Gains Insights into Innovative Medical Practices firsthand at Mayo Clinic's campus in Jacksonville, Florida</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>https://rspp.co.id/artikel-detail-597-Learning-from-the-Best-IHC-RSPP-Endocrinologist-Gains-Insights-into-Innovative-Medical-Practices-firsthand-at-Mayo-Clinic’s-campus-in-Jacksonville,-Florida-.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>IHC Rumah Sakit Pusat Pertamina (RSPP)</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>Mayo Clinic News Network IHC Rumah Sakit Pusat Pertamina in Indonesia joins Mayo Clinic Care Network</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>2023-01-26</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>https://newsnetwork.mayoclinic.org/discussion/ihc-rumah-sakit-pusat-pertamina-in-indonesia-joins-mayo-clinic-care-network</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>IHC Rumah Sakit Pusat Pertamina (RSPP)</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>RS Pusat Pertamina RSPP Gains Insight from Mayo Clinic for Outpatient Chemotherapy Unit</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>https://rspp.co.id/artikel-detail-210-Rumah-Sakit-Pusat-Pertamina-(RSPP)-Gains-Insight-from-Mayo-Clinic-for-Outpatient-Chemotherapy-Unit-.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>St. Jude Children's Research Hospital</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>RSUPN Dr. Cipto Mangunkusumo (RSCM) and Indonesian Ministry of Health</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>Kementerian Kesehatan RI (Ditjen Kesehatan Lanjutan) RSUPN Dr Cipto Mangunkusumo Mendapat Kunjungan dari St Jude Global Asia Pacific Regional Untuk Perkuat Kolaborasi Kanker Anak</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>https://keslan.kemkes.go.id/view_foto/554</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>St. Jude Children's Research Hospital</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>RSUPN Dr. Cipto Mangunkusumo (RSCM) and Indonesian Ministry of Health</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>St. Jude Children's Research Hospital St. Jude Global and Indonesian stakeholders unite for first-ever national childhood cancer policy planning</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>https://stjude.org/research/progress/2024/st-jude-global-and-indonesian-stakeholders-unite-for-first-ever-national-childhood-cancer-policy-planning.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>Mayapada Healthcare Group (Mayapada Hospital)</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>JawaPos Perkuat kolaborasi lintas negara, Mayapada Healthcare yakin bisa kurangi orang berobat ke luar negeri</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>https://www.jawapos.com/kesehatan/2601230030/perkuat-kolaborasi-lintas-negara-mayapada-healthcare-yakin-bisa-kurangi-orang-berobat-ke-luar-negeri</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>Mayapada Healthcare Group (Mayapada Hospital)</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>Detik Health Kolaborasi Klinis Mayapada Healthcare &amp; Apollo Hospitals India Kian Matang</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>https://health.detik.com/berita-detikhealth/d-8316666/kolaborasi-klinis-mayapada-healthcare-apollo-hospitals-india-kian-matang</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>Mayapada Healthcare Group (Mayapada Hospital)</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>Investortrust Mayapada Healthcare Partners with India's Apollo Hospitals to Curb Medical Tourism</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>https://investortrust.id/business/54719/mayapada-healthcare-partners-with-indias-apollo-hospitals-to-curb-medical-tourism</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>Asia OneHealthcare (A1Health, formerly Columbia Asia Healthcare)</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>RS Premier Jatinegara, Bintaro and Surabaya and Columbia Asia hospitals</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>The Edge Malaysia Weekly Bankers court A1Health for possible IPO</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>https://theedgemalaysia.com/node/791491</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>Asia OneHealthcare (A1Health, formerly Columbia Asia Healthcare)</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>RS Premier Jatinegara, Bintaro and Surabaya and Columbia Asia hospitals</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>The Edge Malaysia Columbia Asia Healthcare renamed Asia OneHealthcare (A1Health) after consolidating assets in Malaysia, Indonesia and Vietnam</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>https://theedgemalaysia.com/node/725855</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>Asia OneHealthcare (A1Health, formerly Columbia Asia Healthcare)</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>RS Premier Jatinegara, Bintaro and Surabaya and Columbia Asia hospitals</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>Vina Elvira, Kontan Rumah Sakit Internasional Columbia Asia Resmi Akuisisi RS Medika BSD</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>https://industri.kontan.co.id/news/rumah-sakit-internasional-columbia-asia-resmi-akuisisi-rs-medika-bsd</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>Chung Shan Medical University (Taiwan)</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>Universitas Indonesia</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>CSMU Chung Shan Medical University Signs MOU with Universitas Indonesia to Advance Comprehensive Collaboration</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>https://pr.csmu.edu.tw/p/16-1024-71677.php?Lang=zh-tw</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>Hong Kong Asia Medical Group (HKAMG)</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>Bali International Hospital (PT Pertamedika Bali Hospital, IHC)</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>Ni Putu Putri Muliantari, ANTARA Akhirnya ada prosedur TAVI di KEK Sanur untuk tangani kasus jantung</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>https://bali.antaranews.com/berita/400683/akhirnya-ada-prosedur-tavi-di-kek-sanur-untuk-tangani-kasus-jantung</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>Hong Kong Asia Medical Group (HKAMG)</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>Bali International Hospital (PT Pertamedika Bali Hospital, IHC)</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>Bali International Hospital (press release) Bali International Hospital Hosts Meet &amp; Greet with Global Medical Partners</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>https://bali.com/news/press-releases/bali-international-hospital-hosts-meet-greet-with-global-medical-partners</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>Hong Kong Asia Medical Group (HKAMG)</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>Bali International Hospital (PT Pertamedika Bali Hospital, IHC)</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>International Finance Corporation Asia Heart project (Hong Kong Asia Medical Holding and Wuhan Asia Heart Hospital)</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr"/>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>https://disclosures.ifc.org/project-detail/SII/33623/asia-heart-project</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>Icon Group (Icon Cancer Centre)</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>Bali International Hospital (PT Pertamina Bina Medika IHC)</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>Icon Writers Icon Cancer Centre at Bali International Hospital marks regional first with advanced radiotherapy cancer treatments</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>https://icongroup.global/?p=18098</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>Icon Group (Icon Cancer Centre)</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>Bali International Hospital (PT Pertamina Bina Medika IHC)</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>Icon Writers Icon Cancer Centre Bali treats first patient</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>https://icongroup.global/en/news/2025-05-07/icon-cancer-centre-bali-treats-first-patient/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>Icon Group (Icon Cancer Centre)</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>Bali International Hospital (PT Pertamina Bina Medika IHC)</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>Icon Group Icon Group, Bali International Hospital partnership to deliver exceptional cancer care</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>https://icongroup.global/en/news/2025-03-04/icon-group-and-bali-international-hospital/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>International University of Health and Welfare (IUHW)</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>Ministry of Health (Kemenkes)</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>Ministry of Health of Indonesia Kemenkes dan IUHW Jepang Kerja Sama Perkuat Pendidikan Dokter Spesialis</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>https://kemkes.go.id/id/kemenkes-dan-iuhw-jepang-kerja-sama-perkuat-pendidikan-dokter-spesialis</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>International University of Health and Welfare (IUHW)</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>Ministry of Health (Kemenkes)</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>RRI Indonesia and Japan Expand Cooperation in Specialist Medical Education</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>https://rri.co.id/en/education/2332993/indonesia-and-japan-expand-cooperation-in-specialist-medical-education</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>Monash Health</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>RS Otak Dr. Drs. M. Hatta Bukittinggi (RSOMH, Ministry of Health brain hospital)</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>Humas RSOMH Bukittinggi RSOMH Bukittinggi dan Monash Health Perkuat Kolaborasi Pengembangan Rehabilitasi Stroke</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>https://keslan.kemkes.go.id/read/4058/rsomh-bukittinggi-dan-monash-health-perkuat-kolaborasi-pengembangan-rehabilitasi-stroke</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>Monash Health</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>RS Otak Dr. Drs. M. Hatta Bukittinggi (RSOMH, Ministry of Health brain hospital)</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>Humas RSOMH Bukittinggi RSOMH Bukittinggi Dukung Rencana Program Kerja Sama Bersama Monash Health</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>https://keslan.kemkes.go.id/read/4358/rsomh-bukittinggi-dukung-rencana-program-kerja-sama-bersama-monash-health</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>National Center for Global Health and Medicine (NCGM) and Kobe University</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>Universitas Airlangga (Institute of Tropical Disease and RS Universitas Airlangga)</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>UNAIR News Japanese delegation visits UNAIR Hospital to strengthen research and innovation collaboration</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>https://unair.ac.id/en/japanese-delegation-visits-unair-hospital-to-strengthen-research-and-innovation-collaboration/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>Ramathibodi Hospital, Mahidol University</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>Faculty of Medicine Universitas Indonesia and RSCM</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>Ramathibodi International Office Ramathibodi Hospital and Universitas Indonesia Strengthen Medical Ties with MOU Signing</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>https://www.rama.mahidol.ac.th/international/news/event/22052025-1111</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>Sapporo Cardio Vascular Clinic</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>Bali International Hospital (PT Pertamedika Bali Hospital, IHC)</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>Mardiana Makmun, Investor Daily Teknologi TAVI Tangani Penyakit Katup Jantung</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>https://investor.id/lifestyle/432385/teknologi-tavi-tangani-penyakit-katup-jantung</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>Sapporo Cardio Vascular Clinic</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>Bali International Hospital (PT Pertamedika Bali Hospital, IHC)</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>Bali International Hospital (press release) Bali International Hospital Hosts Meet &amp; Greet with Global Medical Partners</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>https://bali.com/news/press-releases/bali-international-hospital-hosts-meet-greet-with-global-medical-partners</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>Sapporo Cardio Vascular Clinic</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>Bali International Hospital (PT Pertamedika Bali Hospital, IHC)</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>Ministry of Health of Indonesia Atasi Kekurangan Dokter Spesialis, Kemenkes Berangkatkan 27 Dokter Belajar ke RRT dan Jepang</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>2025-01-06</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>https://kemkes.go.id/eng/atasi-kekurangan-dokter-spesialis-kemenkes-berangkatkan-27-dokter-belajar-ke-rrt-dan-jepang</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>Seoul National University Hospital (SNUH)</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>Faculty of Medicine Universitas Indonesia and RSUPN Dr. Cipto Mangunkusumo (RSCM)</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>Noh Jae-young, Medipharm Health 서울대병원-인도네시아 의대-RSCM 병원 간 AOI 체결</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>2025-02-04</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>https://medipharmhealth.co.kr/news/article.html?no=105006</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>Seoul National University Hospital (SNUH)</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>RSUP Fatmawati (Ministry of Health hospital)</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>Ministry of Health of Indonesia Lakukan Transplantasi Hati Ketiga RSUP Fatmawati Perkuat Kemandirian Layanan Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kemkes.go.id/eng/lakukan-transplantasi-hati-ketiga-rsup-fatmawati-perkuat-kemandirian-layanan-dalam-negeri</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>Seoul National University Hospital (SNUH)</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>RSUP Fatmawati (Ministry of Health hospital)</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>Ministry of Health of Indonesia Kerja Sama Indonesia-Korea Dukung Implementasi Transformasi Kesehatan</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="inlineStr">
+        <is>
+          <t>2023-03-27</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kemkes.go.id/eng/kerja-sama-indonesia-korea-dukung-implementasi-transformasi-kesehatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>SingHealth</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>Indonesia Healthcare Corporation (PT Pertamina Bina Medika) and Bali International Hospital</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>Bali International Hospital (press release) Bali International Hospital Hosts Meet &amp; Greet with Global Medical Partners</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>https://bali.com/news/press-releases/bali-international-hospital-hosts-meet-greet-with-global-medical-partners</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>SingHealth</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>Indonesia Healthcare Corporation (PT Pertamina Bina Medika) and Bali International Hospital</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>Indonesia Business Post IHC, Singhealth seals deal collaboration to improve patient care</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>https://indonesiabusinesspost.com/1823/Politics/ihc-singhealth-seals-deal-collaboration-to-improve-patient-care</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>SingHealth</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>Indonesia Healthcare Corporation (PT Pertamina Bina Medika) and Bali International Hospital</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>Pertamina Pertamina Bina Medika IHC and SingHealth collaborate to enhance healthcare services</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>https://pertamina.com/en/news-room/news-release/pertamina-bina-medika-ihc-and-singhealth-collaborate-to-enhance-healthcare-services</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>SingHealth Duke-NUS Global Health Institute (SingHealth and Duke-NUS Medical School)</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>Universitas Sumatera Utara (Faculty of Medicine)</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>Universitas Sumatera Utara Collaboration between the Faculty of Medicine, Universitas Sumatera Utara (USU) and SingHealth Duke-NUS Global Health Institute on the 2025 Summer Course</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>https://www.usu.ac.id/en/news/collaboration-between-the-faculty-of-medicine-universitas-sumatera-utara-usu-and-singhealth-duke-nus-global-health-institute-on-the-2025-summer-course</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>SingHealth Duke-NUS Global Health Institute (SingHealth and Duke-NUS Medical School)</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>Universitas Sumatera Utara (Faculty of Medicine)</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>Universitas Sumatera Utara USU-Duke NUS Global Health Strengthen Partnerships</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>https://www.usu.ac.id/en/news/usu-duke-nus-global-health-strengthen-partnerships</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>Sun Medical Center (Sun Healthcare International)</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>RSUP Prof. Dr. I.G.N.G. Ngoerah</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>Benedikta Desideria, Liputan6 Dorong Wisata Medis Bali, Menkes Budi: Jangan Pilih yang Kuratif tapi Wellness</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/health/read/5731675/dorong-wisata-medis-bali-menkes-budi-jangan-pilih-yang-kuratif-tapi-wellness</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>Sun Medical Center (Sun Healthcare International)</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>RSUP Prof. Dr. I.G.N.G. Ngoerah</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>Ministry of Health of Indonesia Kerja Sama Indonesia-Korea Dukung Implementasi Transformasi Kesehatan</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>2023-03-27</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kemkes.go.id/eng/kerja-sama-indonesia-korea-dukung-implementasi-transformasi-kesehatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>Taipei Veterans General Hospital</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>DKH Hospitals Group</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>Antara DKH Hospitals dan TVGH teken MoU tingkatkan layanan kesehatan di RI</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/4853713/dkh-hospitals-dan-tvgh-teken-mou-tingkatkan-layanan-kesehatan-di-ri</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>Tokushukai Medical Group</t>
+        </is>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>RSJPD Harapan Kita (National Heart Center) and Ministry of Health</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="inlineStr">
+        <is>
+          <t>Ministry of Health of Indonesia Perkuat Layanan Jantung Berkelas Dunia di Indonesia, Gedung Baru RS Harkit Resmi Topping Off</t>
+        </is>
+      </c>
+      <c r="D165" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kemkes.go.id/eng/perkuat-layanan-jantung-berkelas-dunia-di-indonesia-gedung-baru-rs-harkit-resmi-topping-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="inlineStr">
+        <is>
+          <t>Tokushukai Medical Group</t>
+        </is>
+      </c>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>RSJPD Harapan Kita (National Heart Center) and Ministry of Health</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>Antara Indonesia, Japan back Harapan Kita as Asia's biggest cardiac hub</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="inlineStr">
+        <is>
+          <t>https://en.antaranews.com/news/412388/indonesia-japan-back-harapan-kita-as-asias-biggest-cardiac-hub</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>Tokushukai Medical Group</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>RSJPD Harapan Kita (National Heart Center) and Ministry of Health</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>SSEK SSEK Acts for Tokushukai Medical Corporation Group in Major Cooperation Project in Indonesian Health Sector</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>2023-12-11</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>https://ssek.com/blog/ssek-acts-for-tokushukai-medical-corporation-group-in-major-cooperation-project-in-indonesian-health-sector/?lang=id</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t>Wuhan Asia Heart Hospital</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>Ministry of Health (Kemenkes)</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>Ministry of Health of Indonesia Perkuat Layanan Jantung Nasional: 13 Dokter Spesialis Jantung Indonesia Berguru ke Tiongkok</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="inlineStr">
+        <is>
+          <t>https://kemkes.go.id/id/perkuat-layanan-jantung-nasional-13-dokter-spesialis-jantung-indonesia-berguru-ke-tiongkok</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>Zhongda Hospital (Southeast University)</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>Ministry of Health (Kemenkes)</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>Ministry of Health of Indonesia Atasi Kekurangan Dokter Spesialis, Kemenkes Berangkatkan 27 Dokter Belajar ke RRT dan Jepang</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>2025-01-06</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="inlineStr">
+        <is>
+          <t>https://kemkes.go.id/eng/atasi-kekurangan-dokter-spesialis-kemenkes-berangkatkan-27-dokter-belajar-ke-rrt-dan-jepang</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="inlineStr">
+        <is>
+          <t>Zhongshan Hospital (Fudan University)</t>
+        </is>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>Ministry of Health (Kemenkes)</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>Ministry of Health of Indonesia Atasi Kekurangan Dokter Spesialis, Kemenkes Berangkatkan 27 Dokter Belajar ke RRT dan Jepang</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>2025-01-06</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="inlineStr">
+        <is>
+          <t>https://kemkes.go.id/eng/atasi-kekurangan-dokter-spesialis-kemenkes-berangkatkan-27-dokter-belajar-ke-rrt-dan-jepang</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>Zhongshan Hospital (Fudan University)</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>Ministry of Health (Kemenkes)</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>Ministry of Health of Indonesia Perkuat Layanan Jantung Nasional: 13 Dokter Spesialis Jantung Indonesia Berguru ke Tiongkok</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="inlineStr">
+        <is>
+          <t>https://kemkes.go.id/id/perkuat-layanan-jantung-nasional-13-dokter-spesialis-jantung-indonesia-berguru-ke-tiongkok</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="inlineStr">
+        <is>
+          <t>Zhongshan Hospital (Fudan University)</t>
+        </is>
+      </c>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
+          <t>Ministry of Health (Kemenkes)</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>Kemenkes Kemenkes RI dan RS Rizhao Xinyi Kerja Sama Pelatihan Dokter Kardiovaskular</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kemkes.go.id/eng/kemenkes-ri-dan-rs-rizhao-xinyi-kerja-sama-pelatihan-dokter-kardiovaskular</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t>Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
+          <t>Bali International Hospital (Indonesia Healthcare Corporation)</t>
+        </is>
+      </c>
+      <c r="C173" s="5" t="inlineStr">
+        <is>
+          <t>The Jakarta Post Mayo Clinic only acting as consultant for Bali International Hospital, executive says</t>
+        </is>
+      </c>
+      <c r="D173" s="5" t="inlineStr">
+        <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thejakartapost.com/business/2023/03/17/mayo-clinic-only-acting-as-consultant-for-bali-international-hospital-executive-says</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>Bali International Hospital (Indonesia Healthcare Corporation)</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>Becker's Hospital Review Mayo Clinic to advise on building, operating hospital in Indonesia</t>
+        </is>
+      </c>
+      <c r="D174" s="5" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="inlineStr">
+        <is>
+          <t>https://www.beckershospitalreview.com/capital/mayo-clinic-to-help-build-operate-hospital-in-indonesia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t>Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>Bali International Hospital (Indonesia Healthcare Corporation)</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="inlineStr">
+        <is>
+          <t>Bali International Hospital (press release) Bali International Hospital Hosts Meet &amp; Greet with Global Medical Partners</t>
+        </is>
+      </c>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="inlineStr">
+        <is>
+          <t>https://bali.com/news/press-releases/bali-international-hospital-hosts-meet-greet-with-global-medical-partners</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t>UCLA Health</t>
+        </is>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>RS Jantung dan Pembuluh Darah Harapan Kita</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>Kementerian Kesehatan RI Wujudkan Transformasi Layanan Rujukan, RS Jantung Harapan Kita jadi RS Pertama Transplantasi Jantung di Indonesia</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>2022-11-09</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="inlineStr">
+        <is>
+          <t>https://kemkes.go.id/eng/wujudkan-transformasi-layanan-rujukan-rs-jantung-harapan-kita-jadi-rs-pertama-transplantasi-jantung-di-indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>Asan Medical Center</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>Siloam Hospitals Group</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>Adv Team Grup RS Siloam Jalin Kerja Sama dengan Asan Medical Center Korea Selatan</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>2023-11-03</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kompas.tv/advertorial/457691/grup-rs-siloam-jalin-kerja-sama-dengan-asan-medical-center-korea-selatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
+          <t>Icon Group (Icon Cancer Centre, Singapore)</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
+        <is>
+          <t>RS Universitas Airlangga (RSUA)</t>
+        </is>
+      </c>
+      <c r="C178" s="5" t="inlineStr">
+        <is>
+          <t>BioSpectrum Asia Airlangga University Hospital signs MoU with Singapore's Icon Cancer Center</t>
+        </is>
+      </c>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>2023-04-10</t>
+        </is>
+      </c>
+      <c r="E178" s="5" t="inlineStr">
+        <is>
+          <t>https://www.biospectrumasia.com/news/54/22260/airlangga-university-hospital-signs-mou-with-singapores-icon-cancer-center.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
+          <t>National Center for Global Health and Medicine (NCGM)</t>
+        </is>
+      </c>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>Siloam Hospitals Group</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="inlineStr">
+        <is>
+          <t>National Center for Global Health and Medicine The National Center for Global Health and Medicine and the Siloam Hospitals Group have signed a Memorandum of Understanding (MoU) for clinical research cooperation</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ncgm.go.jp/en/news/FY2022/20221007.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="inlineStr">
+        <is>
+          <t>Peking Union Medical College Hospital</t>
+        </is>
+      </c>
+      <c r="B180" s="5" t="inlineStr">
+        <is>
+          <t>Ministry of Health (Kemenkes)</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>Kemenkes Kemenkes RI dan RS Rizhao Xinyi Kerja Sama Pelatihan Dokter Kardiovaskular</t>
+        </is>
+      </c>
+      <c r="D180" s="5" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="E180" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kemkes.go.id/eng/kemenkes-ri-dan-rs-rizhao-xinyi-kerja-sama-pelatihan-dokter-kardiovaskular</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>Rizhao Xinyi Hospital (Rizhao Heart Hospital)</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>Ministry of Health (Kemenkes)</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>Kemenkes Kemenkes RI dan RS Rizhao Xinyi Kerja Sama Pelatihan Dokter Kardiovaskular</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kemkes.go.id/eng/kemenkes-ri-dan-rs-rizhao-xinyi-kerja-sama-pelatihan-dokter-kardiovaskular</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="inlineStr">
+        <is>
+          <t>Royal Brompton and Harefield Hospitals (Guy's and St Thomas' NHS Foundation Trust)</t>
+        </is>
+      </c>
+      <c r="B182" s="5" t="inlineStr">
+        <is>
+          <t>Mandaya Royal Hospital Puri</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>Mandaya Hospital Group Mandaya Royal Hospital Puri and London's Royal Brompton &amp; Harefield Hospitals Announce Strategic Partnership</t>
+        </is>
+      </c>
+      <c r="D182" s="5" t="inlineStr">
+        <is>
+          <t>2020-12-19</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="inlineStr">
+        <is>
+          <t>https://mandayahospitalgroup.com/?p=11304</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>Royal Brompton and Harefield Hospitals (Guy's and St Thomas' NHS Foundation Trust)</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>Mandaya Royal Hospital Puri</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>RM.id Gandeng Royal Brompton, Mandaya Hospital resmikan pusat jantung anak</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>2023-05-22</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="inlineStr">
+        <is>
+          <t>https://rm.id/baca-berita/life-style/172779/gandeng-royal-brompton-mandaya-hospital-resmikan-pusat-jantung-anak</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="inlineStr">
+        <is>
+          <t>UMC Utrecht</t>
+        </is>
+      </c>
+      <c r="B184" s="5" t="inlineStr">
+        <is>
+          <t>RS Jantung dan Pembuluh Darah Harapan Kita</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="inlineStr">
+        <is>
+          <t>Ministry of Health of Indonesia Wujudkan Transformasi Layanan Rujukan, RS Jantung Harapan Kita jadi RS Pertama Transplantasi Jantung di Indonesia</t>
+        </is>
+      </c>
+      <c r="D184" s="5" t="inlineStr">
+        <is>
+          <t>2022-11-09</t>
+        </is>
+      </c>
+      <c r="E184" s="5" t="inlineStr">
+        <is>
+          <t>https://kemkes.go.id/eng/wujudkan-transformasi-layanan-rujukan-rs-jantung-harapan-kita-jadi-rs-pertama-transplantasi-jantung-di-indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>KPJ Healthcare</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>RS Medika BSD</t>
+        </is>
+      </c>
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>Warta Ekonomi Ekspansi Besar-besaran, RS Columbia Asia Buka Dua Rumah Sakit dalam Seminggu</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="inlineStr">
+        <is>
+          <t>https://wartaekonomi.co.id/read515939/ekspansi-besar-besaran-rs-columbia-asia-buka-dua-rumah-sakit-dalam-seminggu</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>KPJ Healthcare</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
+        <is>
+          <t>RS Medika BSD</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>Vina Elvira, Kontan Rumah Sakit Internasional Columbia Asia Resmi Akuisisi RS Medika BSD</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="E186" s="5" t="inlineStr">
+        <is>
+          <t>https://industri.kontan.co.id/news/rumah-sakit-internasional-columbia-asia-resmi-akuisisi-rs-medika-bsd</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>Ramsay Health Care</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
+        <is>
+          <t>RS Premier Jatinegara, Bintaro and Surabaya</t>
+        </is>
+      </c>
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>The Edge Malaysia Columbia Asia Healthcare renamed Asia OneHealthcare (A1Health) after consolidating assets in Malaysia, Indonesia and Vietnam</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="inlineStr">
+        <is>
+          <t>https://theedgemalaysia.com/node/725855</t>
         </is>
       </c>
     </row>
@@ -7458,6 +11511,76 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId186"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Partnerships_Tracker.xlsx
+++ b/output/Partnerships_Tracker.xlsx
@@ -847,7 +847,7 @@
       <c r="I3" s="12" t="inlineStr"/>
       <c r="J3" s="12" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="K3" s="12" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="L3" s="14" t="inlineStr">
         <is>
-          <t>Epworth HealthCare (SmartRecruiters), undated; fellowship commences February 2026</t>
+          <t>Epworth HealthCare (SmartRecruiters), 2025-11-05</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>A faculty level memorandum of understanding signed in September 2023 on academic exchange sits under a wider university partnership, with a student placement agreement and a joint community placement in Hokkaido in July 2025.</t>
+          <t>A faculty level memorandum of understanding signed in September 2023 on academic exchange sits under a wider university partnership, with a student placement agreement and a joint community placement in Hokkaido in July 2025. Borderline: a university partnership with no hospital party.</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>A new memorandum of understanding signed on 2 September 2026 renews a longstanding partnership, with five priority areas including flagship research, joint doctoral education and staff and student mobility, with medicine named as a focus.</t>
+          <t>A new memorandum of understanding signed in Mumbai on 2 September 2026 renews a longstanding university partnership across five priority areas, including flagship research, joint doctoral education and staff and student mobility; MAHE cites its teaching hospitals and clinical networks as part of the collaboration. Borderline: a university-to-university agreement.</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr"/>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>St Vincent's Hospital Melbourne newsroom reports the signing during a visit by Sichuan delegates (page undated in fetch); BioMelbourne Network dated the report 10 April 2025.</t>
+          <t>St Vincent's Hospital Melbourne newsroom reports the signing during a visit by Sichuan delegates (page undated in fetch); Hospital Management reported the signing on 7 April 2025.</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>SickKids announced IPCHiP on 25 February 2021 naming 'the Murdoch Children's Research Institute with The Royal Children's Hospital (Melbourne)' as a member (read). The University of Toronto McLaughlin Centre release of 27 February 2025 (read) reports the partnership's progress. Already used as evidence for the Boston Children's record; SickKids is a co-equal foreign member and was left out.</t>
+          <t>SickKids announced IPCHiP on 25 February 2021, naming the Murdoch Children's Research Institute with The Royal Children's Hospital as a founding member. A University of Toronto McLaughlin Centre release of 27 February 2025 reports the partnership's progress in npj Genomic Medicine.</t>
         </is>
       </c>
       <c r="L17" s="14" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>A July 2026 memorandum of understanding sets a framework for research, education and innovation between the two health innovation programmes, building on the Biodesign link.</t>
+          <t>A July 2026 memorandum of understanding sets a framework for research, education and innovation between the two health innovation programmes, building on the Biodesign link. Borderline: a university partnership with no hospital party.</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>West China Hospital news post (fetched) reports the signing on 9 April during a visit by UQ's Deputy Vice-Chancellor. The post carries no year; it cites UQ's 2025 QS, ARWU and THE rankings, which places it in April 2025 (the 2025 THE ranking was published October 2024), so the year is inferred.</t>
+          <t>West China Hospital news post published 18 April 2025 reports the signing on 9 April 2025 and the unveiling of a sister laboratory with UQ's Institute for Molecular Bioscience.</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>West China Hospital, 2025-04</t>
+          <t>West China Hospital, 2025-04-18</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>St Vincent's Hospital Sydney newsroom item dated 13 December 2023 (read) announces the selection. No Mayo-side release, terms or later dated activity was found. Borderline because it is a reference-laboratory service arrangement, but it is a named institutional arrangement announced by the Australian hospital; the draft excluded it as a commercial lab contract.</t>
+          <t>St Vincent's Hospital Sydney newsroom item dated 13 December 2023 announces that SydPath selected Mayo Clinic Laboratories as its reference laboratory. No Mayo-side release, terms or later dated activity was found.</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       <c r="I24" s="12" t="inlineStr"/>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>Monash and Victorian Government releases of March 2023 report the signing, with $200,000 from Victoria for cardiovascular work. Monash Health newsroom item of 5 July 2023 reports the ARC Innovation Centre partnership. No dated activity found after July 2023.</t>
+          <t>Monash and Victorian Government releases of March 2023 report the signing, with $200,000 from Victoria for cardiovascular work. Peter Mac reported the partnership's ARC innovation program in June 2023; no dated activity was found after that.</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
@@ -7872,7 +7872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E243"/>
+  <dimension ref="A1:E244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>undated; fellowship commences February 2026</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>undated; fellowship commences February 2025</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>BioMelbourne Network MoU signed between St Vincent's Hospital Melbourne and Sichuan Provincial People's Hospital enhances research collaboration with China</t>
+          <t>Hospital Management St Vincent's Melbourne and Sichuan Provincial People's Hospital sign MoU</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>7 April 2025</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -9267,22 +9267,22 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>NSW Health (New South Wales Government)</t>
+          <t>Monash University (with Monash Health and the Victorian Government)</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>NSW Health Win for health and medical research in NSW with international partnership</t>
+          <t>Peter MacCallum Cancer Centre Partnership to put innovation on an upward ARC</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>2023-02-17</t>
+          <t>June 2023</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>https://www.health.nsw.gov.au/news/Pages/20230217_01.aspx</t>
+          <t>https://petermac.org/about-us/news-and-events/news/details/partnership-to-put-innovation-on-an-upward-arc</t>
         </is>
       </c>
     </row>
@@ -9299,17 +9299,17 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Sheba Medical Center Memorandum of Understanding with New South Wales Government will bring innovative healthcare to Australia</t>
+          <t>NSW Health Win for health and medical research in NSW with international partnership</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>2023-02-17</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>https://sheba-global.com/memorandum-of-understanding-with-new-south-wales-government-will-bring-innovative-healthcare-to-australia/</t>
+          <t>https://www.health.nsw.gov.au/news/Pages/20230217_01.aspx</t>
         </is>
       </c>
     </row>
@@ -9321,22 +9321,22 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Peter MacCallum Cancer Centre (with Australian Friends of Sheba)</t>
+          <t>NSW Health (New South Wales Government)</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Peter MacCallum Cancer Centre MOU spurs collaboration between leading Australian and Israeli cancer centres</t>
+          <t>Sheba Medical Center Memorandum of Understanding with New South Wales Government will bring innovative healthcare to Australia</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>2022-05-20</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>https://petermac.org/about-us/news-and-events/news/details/mou-spurs-collaboration-between-leading-australian-israeli-cancer-centres</t>
+          <t>https://sheba-global.com/memorandum-of-understanding-with-new-south-wales-government-will-bring-innovative-healthcare-to-australia/</t>
         </is>
       </c>
     </row>
@@ -9353,17 +9353,17 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Israel Trade and Economic Office Australia Sheba Medical Center signs agreement with Australian cancer center</t>
+          <t>Peter MacCallum Cancer Centre MOU spurs collaboration between leading Australian and Israeli cancer centres</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>https://israeltrade.org.au/2022/05/25/sheba-medical-center-signs-agreement-with-australian-cancer-center/</t>
+          <t>https://petermac.org/about-us/news-and-events/news/details/mou-spurs-collaboration-between-leading-australian-israeli-cancer-centres</t>
         </is>
       </c>
     </row>
@@ -9380,71 +9380,71 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Peter MacCallum Cancer Centre Partnership to put innovation on an upward ARC</t>
+          <t>Israel Trade and Economic Office Australia Sheba Medical Center signs agreement with Australian cancer center</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>https://petermac.org/about-us/news-and-events/news/details/partnership-to-put-innovation-on-an-upward-arc</t>
+          <t>https://israeltrade.org.au/2022/05/25/sheba-medical-center-signs-agreement-with-australian-cancer-center/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Siriraj Hospital, Faculty of Medicine, Mahidol University</t>
+          <t>Sheba Medical Center</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>University of Sydney (Faculty of Medicine and Health)</t>
+          <t>Peter MacCallum Cancer Centre (with Australian Friends of Sheba)</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Siriraj Hospital, Mahidol University MOU Signing Ceremony Between Siriraj and University of Sydney</t>
+          <t>Peter MacCallum Cancer Centre Partnership to put innovation on an upward ARC</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>https://www2.si.mahidol.ac.th/en/news-events/mou-signing-ceremony-between-siriraj-and-university-of-sydney/</t>
+          <t>https://petermac.org/about-us/news-and-events/news/details/partnership-to-put-innovation-on-an-upward-arc</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Siriraj Hospital, Faculty of Medicine, Mahidol University</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Saudi German Hospital Cairo (Saudi German Health)</t>
+          <t>University of Sydney (Faculty of Medicine and Health)</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Trade Arabia Saudi German Health boosts relationship with Mayo Clinic</t>
+          <t>Siriraj Hospital, Mahidol University MOU Signing Ceremony Between Siriraj and University of Sydney</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>https://tradearabia.com/News/328805/Saudi-German-Health-boosts-relationship-with-Mayo-Clinic</t>
+          <t>https://www2.si.mahidol.ac.th/en/news-events/mou-signing-ceremony-between-siriraj-and-university-of-sydney/</t>
         </is>
       </c>
     </row>
@@ -9461,17 +9461,17 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic News Network Saudi German Health strengthens relationship with Mayo Clinic, becoming largest group of Mayo Clinic Care Network members in the region</t>
+          <t>Trade Arabia Saudi German Health boosts relationship with Mayo Clinic</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>https://newsnetwork.mayoclinic.org/discussion/saudi-german-health-strengthens-relationship-with-mayo-clinic-becoming-largest-group-of-mayo-clinic-care-network-members-in-the-region/</t>
+          <t>https://tradearabia.com/News/328805/Saudi-German-Health-boosts-relationship-with-Mayo-Clinic</t>
         </is>
       </c>
     </row>
@@ -9488,17 +9488,17 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic News Network Saudi German Hospital Cairo joins Mayo Clinic Care Network</t>
+          <t>Mayo Clinic News Network Saudi German Health strengthens relationship with Mayo Clinic, becoming largest group of Mayo Clinic Care Network members in the region</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>2019-07-15</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>https://newsnetwork.mayoclinic.org/discussion/saudi-german-hospital-cairo-joins-mayo-clinic-care-network/</t>
+          <t>https://newsnetwork.mayoclinic.org/discussion/saudi-german-health-strengthens-relationship-with-mayo-clinic-becoming-largest-group-of-mayo-clinic-care-network-members-in-the-region/</t>
         </is>
       </c>
     </row>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Andy Brownell Egyptian Hospital Joins Mayo Clinic Care Network</t>
+          <t>Mayo Clinic News Network Saudi German Hospital Cairo joins Mayo Clinic Care Network</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -9525,30 +9525,34 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>https://krocnews.com/egyptian-hospital-joins-mayo-clinic-care-network/</t>
+          <t>https://newsnetwork.mayoclinic.org/discussion/saudi-german-hospital-cairo-joins-mayo-clinic-care-network/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>University of Texas Medical Branch (UTMB Health)</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Badya University</t>
+          <t>Saudi German Hospital Cairo (Saudi German Health)</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Badya University Academic Partnership</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr"/>
+          <t>Andy Brownell Egyptian Hospital Joins Mayo Clinic Care Network</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>2019-07-15</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>https://www.badyauni.edu.eg/about-badya-university/academic-partnership/</t>
+          <t>https://krocnews.com/egyptian-hospital-joins-mayo-clinic-care-network/</t>
         </is>
       </c>
     </row>
@@ -9565,17 +9569,13 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Badya University UTMB Delegation Engages in Three-Week Academic Exchange with Badya University</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>2025-02-23</t>
-        </is>
-      </c>
+          <t>Badya University Academic Partnership</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr"/>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>https://www.badyauni.edu.eg/utmb-delegation-engages-in-three-week-academic-exchange-with-badya-university/</t>
+          <t>https://www.badyauni.edu.eg/about-badya-university/academic-partnership/</t>
         </is>
       </c>
     </row>
@@ -9592,17 +9592,17 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Badya University Presentation of research posters at the 2026 UTMB Research Summit in Galveston, Texas</t>
+          <t>Badya University UTMB Delegation Engages in Three-Week Academic Exchange with Badya University</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-02-23</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>https://www.badyauni.edu.eg/presentation-of-research-posters-at-the-2026-utmb-research-summit-in-galveston-texas/</t>
+          <t>https://www.badyauni.edu.eg/utmb-delegation-engages-in-three-week-academic-exchange-with-badya-university/</t>
         </is>
       </c>
     </row>
@@ -9619,71 +9619,71 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Badya University Badya University Takes Confident Steps Toward Leadership in Medical Education (news listing incl. 'Clinical exchange program at UTMB', 4 August 2026)</t>
+          <t>Badya University Presentation of research posters at the 2026 UTMB Research Summit in Galveston, Texas</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>https://www.badyauni.edu.eg/?p=1534</t>
+          <t>https://www.badyauni.edu.eg/presentation-of-research-posters-at-the-2026-utmb-research-summit-in-galveston-texas/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>AP-HP Beaujon Hospital (with Université Paris Cité)</t>
+          <t>University of Texas Medical Branch (UTMB Health)</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Theodor Bilharz Research Institute, with Cairo University Faculty of Medicine (Kasr Al Ainy)</t>
+          <t>Badya University</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Theodor Bilharz Research Institute Sustainable Academic and Research Cooperation with Beaujon Hospital, with the Participation of Cairo University and Université Paris Cité</t>
+          <t>Badya University Badya University Takes Confident Steps Toward Leadership in Medical Education (news listing incl. 'Clinical exchange program at UTMB', 4 August 2026)</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>https://www.tbri.sci.eg/en/institute-news/sustainable-academic-and-research-cooperation-with-beaujon-hospital</t>
+          <t>https://www.badyauni.edu.eg/?p=1534</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Alder Hey Children's Hospital (Alder Hey Global)</t>
+          <t>AP-HP Beaujon Hospital (with Université Paris Cité)</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Ain Shams University Hospitals</t>
+          <t>Theodor Bilharz Research Institute, with Cairo University Faculty of Medicine (Kasr Al Ainy)</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Alder Hey Children's Hospital Alder Hey and Ain Shams University sign official partnership</t>
+          <t>Theodor Bilharz Research Institute Sustainable Academic and Research Cooperation with Beaujon Hospital, with the Participation of Cairo University and Université Paris Cité</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>https://www.alderhey.nhs.uk/?p=112799</t>
+          <t>https://www.tbri.sci.eg/en/institute-news/sustainable-academic-and-research-cooperation-with-beaujon-hospital</t>
         </is>
       </c>
     </row>
@@ -9700,98 +9700,98 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Ain Shams University Unprecedented Medical Achievement: 18 Complex Pediatric Heart Surgeries Successfully Performed at Ain Shams University Hospitals in Collaboration with British Experts</t>
+          <t>Alder Hey Children's Hospital Alder Hey and Ain Shams University sign official partnership</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>https://www.asu.edu.eg/10235/news</t>
+          <t>https://www.alderhey.nhs.uk/?p=112799</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Barraquer Ophthalmology Centre</t>
+          <t>Alder Hey Children's Hospital (Alder Hey Global)</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Ministry of Health and Population (Memorial Institute for Ophthalmic Research)</t>
+          <t>Ain Shams University Hospitals</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Barraquer We signed a collaboration agreement with the Ministry of Health and Population of Egypt</t>
+          <t>Ain Shams University Unprecedented Medical Achievement: 18 Complex Pediatric Heart Surgeries Successfully Performed at Ain Shams University Hospitals in Collaboration with British Experts</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>https://www.barraquer.com/en/news/we-signed-collaboration-agreement-ministry-health-population-egypt</t>
+          <t>https://www.asu.edu.eg/10235/news</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Burjeel Holdings (Burjeel Medical City, Burjeel Cancer Institute)</t>
+          <t>Barraquer Ophthalmology Centre</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Ministry of Health and Population (Secretariat of Specialized Medical Centers)</t>
+          <t>Ministry of Health and Population (Memorial Institute for Ophthalmic Research)</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Gulf Today Egypt's Health Ministry, Burjeel Holdings collaborate to develop advanced BMT program</t>
+          <t>Barraquer We signed a collaboration agreement with the Ministry of Health and Population of Egypt</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>https://gulftoday.ae/business/2025/01/30/egypts-health-ministry-burjeel-holdings-collaborate-to-develop-advanced-bmt-program</t>
+          <t>https://www.barraquer.com/en/news/we-signed-collaboration-agreement-ministry-health-population-egypt</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Freiburg University Cancer Center</t>
+          <t>Burjeel Holdings (Burjeel Medical City, Burjeel Cancer Institute)</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>National Cancer Institute (new '500500' hospital), Sheikh Zayed</t>
+          <t>Ministry of Health and Population (Secretariat of Specialized Medical Centers)</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Daily News Egypt '500500' Hospital project to enhance cancer care, says Egyptian PM</t>
+          <t>Gulf Today Egypt's Health Ministry, Burjeel Holdings collaborate to develop advanced BMT program</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>2024-12-24</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>https://www.dailynewsegypt.com/2024/12/24/500500-hospital-project-to-enhance-cancer-care-says-egyptian-pm/</t>
+          <t>https://gulftoday.ae/business/2025/01/30/egypts-health-ministry-burjeel-holdings-collaborate-to-develop-advanced-bmt-program</t>
         </is>
       </c>
     </row>
@@ -9808,44 +9808,44 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Safia Hamdi Prime Minister: partnership with a global operator to run the 500500 hospital (Arabic)</t>
+          <t>Daily News Egypt '500500' Hospital project to enhance cancer care, says Egyptian PM</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>https://almalnews.com/2119185/</t>
+          <t>https://www.dailynewsegypt.com/2024/12/24/500500-hospital-project-to-enhance-cancer-care-says-egyptian-pm/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Gruppo San Donato (with GKSD Group)</t>
+          <t>Freiburg University Cancer Center</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Ministry of Health and Population and Health Insurance Organization (New Heliopolis Hospital)</t>
+          <t>National Cancer Institute (new '500500' hospital), Sheikh Zayed</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Italpress GKSD and Gruppo San Donato sign agreement to manage new hospital in Egypt</t>
+          <t>Safia Hamdi Prime Minister: partnership with a global operator to run the 500500 hospital (Arabic)</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>https://www.italpress.com/?p=665165</t>
+          <t>https://almalnews.com/2119185/</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>LaPresse Il Gruppo San Donato gestirà per 15 anni un nuovo ospedale al Cairo</t>
+          <t>Italpress GKSD and Gruppo San Donato sign agreement to manage new hospital in Egypt</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>https://www.lapresse.it/salute/sanita/2026/03/31/il-gruppo-san-donato-gestira-per-15-anni-nuovo-ospedale-al-cairo/</t>
+          <t>https://www.italpress.com/?p=665165</t>
         </is>
       </c>
     </row>
@@ -9889,17 +9889,17 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Daily News Egypt Health ministry accelerates New Heliopolis Hospital project, raises capacity to 495 beds</t>
+          <t>LaPresse Il Gruppo San Donato gestirà per 15 anni un nuovo ospedale al Cairo</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>https://www.dailynewsegypt.com/2026/09/28/health-ministry-accelerates-new-heliopolis-hospital-project-raises-capacity-to-495-beds/</t>
+          <t>https://www.lapresse.it/salute/sanita/2026/03/31/il-gruppo-san-donato-gestira-per-15-anni-nuovo-ospedale-al-cairo/</t>
         </is>
       </c>
     </row>
@@ -9916,44 +9916,44 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Daily News Egypt Health Ministry reviews concession to operate New Heliopolis Hospital</t>
+          <t>Daily News Egypt Health ministry accelerates New Heliopolis Hospital project, raises capacity to 495 beds</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>https://www.dailynewsegypt.com/2026/09/01/health-ministry-reviews-concession-to-operate-new-heliopolis-hospital/</t>
+          <t>https://www.dailynewsegypt.com/2026/09/28/health-ministry-accelerates-new-heliopolis-hospital-project-raises-capacity-to-495-beds/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Gustave Roussy (Gustave Roussy International)</t>
+          <t>Gruppo San Donato (with GKSD Group)</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Gustave Roussy International Egypt (former Dar Al-Salam Hermel Oncology Hospital), with the Egyptian government and Elevate P.E.</t>
+          <t>Ministry of Health and Population and Health Insurance Organization (New Heliopolis Hospital)</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Gustave Roussy Opening of the First Gustave Roussy-Branded Facility in Egypt</t>
+          <t>Daily News Egypt Health Ministry reviews concession to operate New Heliopolis Hospital</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>https://www.gustaveroussy.fr/en/news-opening-first-gustave-roussy-branded-facility-egypt</t>
+          <t>https://www.dailynewsegypt.com/2026/09/01/health-ministry-reviews-concession-to-operate-new-heliopolis-hospital/</t>
         </is>
       </c>
     </row>
@@ -9970,71 +9970,71 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Amwal Al Ghad Egypt's UHIA signs oncology care deal with Gustave Roussy</t>
+          <t>Gustave Roussy Opening of the First Gustave Roussy-Branded Facility in Egypt</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>https://en.amwalalghad.com/?p=203380</t>
+          <t>https://www.gustaveroussy.fr/en/news-opening-first-gustave-roussy-branded-facility-egypt</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>University of Oxford</t>
+          <t>Gustave Roussy (Gustave Roussy International)</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>National Cancer Institute (new '500500' hospital), Cairo University</t>
+          <t>Gustave Roussy International Egypt (former Dar Al-Salam Hermel Oncology Hospital), with the Egyptian government and Elevate P.E.</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Daily News Egypt '500500' Hospital project to enhance cancer care, says Egyptian PM</t>
+          <t>Amwal Al Ghad Egypt's UHIA signs oncology care deal with Gustave Roussy</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>2024-12-24</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>https://www.dailynewsegypt.com/2024/12/24/500500-hospital-project-to-enhance-cancer-care-says-egyptian-pm/</t>
+          <t>https://en.amwalalghad.com/?p=203380</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Great Ormond Street Hospital for Children NHS Foundation Trust</t>
+          <t>University of Oxford</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Ain Shams University Hospitals (Children's Hospital)</t>
+          <t>National Cancer Institute (new '500500' hospital), Cairo University</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>British Embassy Cairo GOSH Hospital signs a five-year contract with Ain Shams University Hospital</t>
+          <t>Daily News Egypt '500500' Hospital project to enhance cancer care, says Egyptian PM</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>2020-08-19</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/news/gosh-hospital-signs-a-five-year-contract-with-ain-shams-university-hospital</t>
+          <t>https://www.dailynewsegypt.com/2024/12/24/500500-hospital-project-to-enhance-cancer-care-says-egyptian-pm/</t>
         </is>
       </c>
     </row>
@@ -10051,44 +10051,44 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Ain Shams University Activating the partnership between Ain Shams University Hospitals and GOSH British Hospital</t>
+          <t>British Embassy Cairo GOSH Hospital signs a five-year contract with Ain Shams University Hospital</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2020-08-19</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>https://www.asu.edu.eg/3337/news</t>
+          <t>https://www.gov.uk/government/news/gosh-hospital-signs-a-five-year-contract-with-ain-shams-university-hospital</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Royal Brompton and Harefield Hospitals (Guy's and St Thomas' NHS Foundation Trust)</t>
+          <t>Great Ormond Street Hospital for Children NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Ain Shams University Hospitals (Cardiovascular Diseases and Surgery Hospital)</t>
+          <t>Ain Shams University Hospitals (Children's Hospital)</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Ain Shams University A cooperation protocol between Ain Shams University Hospitals, Royal Brompton and Harefield Hospitals</t>
+          <t>Ain Shams University Activating the partnership between Ain Shams University Hospitals and GOSH British Hospital</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>2021-11-15</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>https://www.asu.edu.eg/3150/news</t>
+          <t>https://www.asu.edu.eg/3337/news</t>
         </is>
       </c>
     </row>
@@ -10105,17 +10105,17 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Ain Shams University A cooperation protocol between Ain Shams University Hospitals, Guy's Hospital, St. Thomas Hospital, NHS and Essentia Trending Limited</t>
+          <t>Ain Shams University A cooperation protocol between Ain Shams University Hospitals, Royal Brompton and Harefield Hospitals</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2021-11-15</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>https://www.asu.edu.eg/4427/news</t>
+          <t>https://www.asu.edu.eg/3150/news</t>
         </is>
       </c>
     </row>
@@ -10132,152 +10132,152 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Ain Shams University The British Royal Brompton crew arrives at the Heart Academy on January 13</t>
+          <t>Ain Shams University A cooperation protocol between Ain Shams University Hospitals, Guy's Hospital, St. Thomas Hospital, NHS and Essentia Trending Limited</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>2024-01-04</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>https://www.asu.edu.eg/7191/news</t>
+          <t>https://www.asu.edu.eg/4427/news</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>University of Hertfordshire</t>
+          <t>Royal Brompton and Harefield Hospitals (Guy's and St Thomas' NHS Foundation Trust)</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Cleopatra Hospitals Group</t>
+          <t>Ain Shams University Hospitals (Cardiovascular Diseases and Surgery Hospital)</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Cleopatra Hospitals Group Cleopatra Hospitals Group signs MoU with the University of Hertfordshire</t>
+          <t>Ain Shams University The British Royal Brompton crew arrives at the Heart Academy on January 13</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
+          <t>2024-01-04</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>https://cleopatrahospitals.com/en/media-center/cleopatra-hospitals-group-is-proud-to-announce-the-signing-of-a-memorandum-of-understanding-mou-with-the-university-of-hertfordshire</t>
+          <t>https://www.asu.edu.eg/7191/news</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Children's Hospital of Philadelphia (CHOP)</t>
+          <t>University of Hertfordshire</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Amrita Hospital, Faridabad</t>
+          <t>Cleopatra Hospitals Group</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Children's HeartLink From Philadelphia to Faridabad, This Hospital Partnership Is Transforming Heart Care for Children in India</t>
+          <t>Cleopatra Hospitals Group Cleopatra Hospitals Group signs MoU with the University of Hertfordshire</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>https://childrensheartlink.org/from-philadelphia-to-faridabad-this-hospital-partnership-is-transforming-heart-care-for-children-in-india/</t>
+          <t>https://cleopatrahospitals.com/en/media-center/cleopatra-hospitals-group-is-proud-to-announce-the-signing-of-a-memorandum-of-understanding-mou-with-the-university-of-hertfordshire</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Cleveland Clinic</t>
+          <t>Children's Hospital of Philadelphia (CHOP)</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Government of Maharashtra and Arodhan Health City (Navi Mumbai International MediCity); Brookfield Asset Management is a co-signatory investor</t>
+          <t>Amrita Hospital, Faridabad</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Kalpesh Mhamunkar Maharashtra Signs MoU With Cleveland Clinic And Brookfield For Navi Mumbai International MediCity, India's First Global-Scale Healthcare Hub</t>
+          <t>Children's HeartLink From Philadelphia to Faridabad, This Hospital Partnership Is Transforming Heart Care for Children in India</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>11 June 2026</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-signs-mou-with-cleveland-clinic-and-brookfield-for-navi-mumbai-international-medicity-indias-first-global-scale-healthcare-hub</t>
+          <t>https://childrensheartlink.org/from-philadelphia-to-faridabad-this-hospital-partnership-is-transforming-heart-care-for-children-in-india/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Emory University (Emory Global Diabetes Research Center)</t>
+          <t>Cleveland Clinic</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>IIT Madras Shankar Center of Excellence in Diabetes Research, with AIIMS, Madras Diabetes Research Foundation and others</t>
+          <t>Government of Maharashtra and Arodhan Health City (Navi Mumbai International MediCity); Brookfield Asset Management is a co-signatory investor</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Myra C. Nwafor Emory students propose innovative solutions to diabetes care in India</t>
+          <t>Kalpesh Mhamunkar Maharashtra Signs MoU With Cleveland Clinic And Brookfield For Navi Mumbai International MediCity, India's First Global-Scale Healthcare Hub</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>11 June 2026</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>https://news.emory.edu/stories/2025/05/hs_diabetes_care_india_13-05-2025/story.html</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-signs-mou-with-cleveland-clinic-and-brookfield-for-navi-mumbai-international-medicity-indias-first-global-scale-healthcare-hub</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>Emory University (Emory Global Diabetes Research Center)</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Apollo Hospitals</t>
+          <t>IIT Madras Shankar Center of Excellence in Diabetes Research, with AIIMS, Madras Diabetes Research Foundation and others</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health Hackensack Meridian Health and Apollo Hospitals Bridge Continents to Advance Healthcare Innovation and Delivery</t>
+          <t>Myra C. Nwafor Emory students propose innovative solutions to diabetes care in India</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>https://www.hackensackmeridianhealth.org/en/news/2025/01/29/hmh-and-apollo-hospitals-bridge-continents-to-advance-healthcare</t>
+          <t>https://news.emory.edu/stories/2025/05/hs_diabetes_care_india_13-05-2025/story.html</t>
         </is>
       </c>
     </row>
@@ -10294,44 +10294,44 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>BW Online Bureau Apollo Hospitals &amp; Hackensack Meridian Health Forge Strategic Affiliation</t>
+          <t>Hackensack Meridian Health Hackensack Meridian Health and Apollo Hospitals Bridge Continents to Advance Healthcare Innovation and Delivery</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>https://www.bwhealthcareworld.com/article/apollo-hospitals-hackensack-meridian-health-forge-strategic-affiliation-546583</t>
+          <t>https://www.hackensackmeridianhealth.org/en/news/2025/01/29/hmh-and-apollo-hospitals-bridge-continents-to-advance-healthcare</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins (University)</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Ajit Isaac Foundation, Bengaluru</t>
+          <t>Apollo Hospitals</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Forbes India From beginning to end of life: Ajit and Sarah Isaac fill in the blanks</t>
+          <t>BW Online Bureau Apollo Hospitals &amp; Hackensack Meridian Health Forge Strategic Affiliation</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>6 April 2026</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>https://www.forbesindia.com/article/leadership/from-beginning-to-end-of-life-ajit-and-sarah-isaac-fill-in-the-blanks/2992863/1</t>
+          <t>https://www.bwhealthcareworld.com/article/apollo-hospitals-hackensack-meridian-health-forge-strategic-affiliation-546583</t>
         </is>
       </c>
     </row>
@@ -10348,17 +10348,17 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Devdiscourse Global Partnership Pioneers Palliative Care in Underserved India</t>
+          <t>Forbes India From beginning to end of life: Ajit and Sarah Isaac fill in the blanks</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>November 2024</t>
+          <t>6 April 2026</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/health/3165425-global-partnership-pioneers-palliative-care-in-underserved-india</t>
+          <t>https://www.forbesindia.com/article/leadership/from-beginning-to-end-of-life-ajit-and-sarah-isaac-fill-in-the-blanks/2992863/1</t>
         </is>
       </c>
     </row>
@@ -10375,7 +10375,7 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>IndiaMedToday Johns Hopkins University signs MoU with Ajit Isaac Foundation</t>
+          <t>Devdiscourse Global Partnership Pioneers Palliative Care in Underserved India</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>https://indiamedtoday.com/johns-hopkins-university-signs-mou-with-ajit-isaac-foundation/</t>
+          <t>https://www.devdiscourse.com/article/health/3165425-global-partnership-pioneers-palliative-care-in-underserved-india</t>
         </is>
       </c>
     </row>
@@ -10397,22 +10397,22 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Dr. D.Y. Patil Medical College and Vidyapeeth, Pune</t>
+          <t>Ajit Isaac Foundation, Bengaluru</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>HATHI study authors (Johns Hopkins University; Dr. D.Y. Patil Medical College, Hospital and Research Centre; BJGMC and others) Hybrid trial for Alcohol reduction among people with TB and HIV in India (HATHI): Protocol for a Hybrid Type 1 Effectiveness-Implementation Randomized Controlled Trial</t>
+          <t>IndiaMedToday Johns Hopkins University signs MoU with Ajit Isaac Foundation</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>25 March 2026</t>
+          <t>November 2024</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/41928807/</t>
+          <t>https://indiamedtoday.com/johns-hopkins-university-signs-mou-with-ajit-isaac-foundation/</t>
         </is>
       </c>
     </row>
@@ -10429,17 +10429,17 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Medical Dialogues Dr DY Patil Medical College, Johns Hopkins University join hands for Collaborative Research</t>
+          <t>HATHI study authors (Johns Hopkins University; Dr. D.Y. Patil Medical College, Hospital and Research Centre; BJGMC and others) Hybrid trial for Alcohol reduction among people with TB and HIV in India (HATHI): Protocol for a Hybrid Type 1 Effectiveness-Implementation Randomized Controlled Trial</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>13 March 2024</t>
+          <t>25 March 2026</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/education/medical-colleges/dr-dy-patil-medical-college-johns-hopkins-university-join-hands-for-collaborative-research-125812</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41928807/</t>
         </is>
       </c>
     </row>
@@ -10456,17 +10456,17 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Gupta-Klinsky India Institute, Johns Hopkins University Partnership Meetings</t>
+          <t>Medical Dialogues Dr DY Patil Medical College, Johns Hopkins University join hands for Collaborative Research</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>undated</t>
+          <t>13 March 2024</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>https://indiainstitute.jhu.edu/events-2025/past-events/events-2024/jhu-india-trip-2024/partnership-meetings/</t>
+          <t>https://medicaldialogues.in/news/education/medical-colleges/dr-dy-patil-medical-college-johns-hopkins-university-join-hands-for-collaborative-research-125812</t>
         </is>
       </c>
     </row>
@@ -10478,22 +10478,22 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>IIT Bombay, Koita Centre for Digital Health</t>
+          <t>Dr. D.Y. Patil Medical College and Vidyapeeth, Pune</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Gupta-Klinsky India Institute News from GKII 2025 (launch of 2025-26 GKII-KCDH Data Science and AI Breakthrough Research Grants)</t>
+          <t>Gupta-Klinsky India Institute, Johns Hopkins University Partnership Meetings</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>December 2025</t>
+          <t>undated</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>https://indiainstitute.jhu.edu/news/news-2025/news-from-gkii-2025/</t>
+          <t>https://indiainstitute.jhu.edu/events-2025/past-events/events-2024/jhu-india-trip-2024/partnership-meetings/</t>
         </is>
       </c>
     </row>
@@ -10510,17 +10510,17 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Koita Centre for Digital Health KCDH Digest: achievements between January and December 2024</t>
+          <t>Gupta-Klinsky India Institute News from GKII 2025 (launch of 2025-26 GKII-KCDH Data Science and AI Breakthrough Research Grants)</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>January 2025</t>
+          <t>December 2025</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>https://www.kcdh.iitb.ac.in/site/newsletter-document/a6abea01-50ce-11f0-9b5b-fbbec49cc3fb.pdf</t>
+          <t>https://indiainstitute.jhu.edu/news/news-2025/news-from-gkii-2025/</t>
         </is>
       </c>
     </row>
@@ -10537,17 +10537,17 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Gupta-Klinsky India Institute, Johns Hopkins University Collaboration Agreement with IIT Bombay and Roundtable Discussion Shine a Spotlight on Digital Health</t>
+          <t>Koita Centre for Digital Health KCDH Digest: achievements between January and December 2024</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>undated</t>
+          <t>January 2025</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>https://indiainstitute.jhu.edu/news/news-2025/news-from-gkii/collaboration-agreement-with-iit-bombay-and-roundtable-discussion-shine-a-spotlight-on-digital-health</t>
+          <t>https://www.kcdh.iitb.ac.in/site/newsletter-document/a6abea01-50ce-11f0-9b5b-fbbec49cc3fb.pdf</t>
         </is>
       </c>
     </row>
@@ -10564,44 +10564,44 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Gupta-Klinsky India Institute, Johns Hopkins University GKII X KCDH Breakthrough Grants on Digital Health (2024)</t>
+          <t>Gupta-Klinsky India Institute, Johns Hopkins University Collaboration Agreement with IIT Bombay and Roundtable Discussion Shine a Spotlight on Digital Health</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>undated</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>https://indiainstitute.jhu.edu/?p=4857</t>
+          <t>https://indiainstitute.jhu.edu/news/news-2025/news-from-gkii/collaboration-agreement-with-iit-bombay-and-roundtable-discussion-shine-a-spotlight-on-digital-health</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins University (School of Medicine)</t>
+          <t>Johns Hopkins (University)</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>Byramjee Jeejeebhoy Government Medical College and Sassoon General Hospitals, Pune (BJGMC-JHU Clinical Research Site)</t>
+          <t>IIT Bombay, Koita Centre for Digital Health</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>BJGMC, Weill Cornell Medicine and Johns Hopkins authors Dolutegravir Is Associated With Lower Odds of Gestational Diabetes Compared to Other Antiretroviral Therapy Regimens Among Pregnant Women in India: A Cross-Sectional Analysis</t>
+          <t>Gupta-Klinsky India Institute, Johns Hopkins University GKII X KCDH Breakthrough Grants on Digital Health (2024)</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>1 September 2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42764545/</t>
+          <t>https://indiainstitute.jhu.edu/?p=4857</t>
         </is>
       </c>
     </row>
@@ -10618,17 +10618,17 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>BJGMC, Weill Cornell Medicine, Johns Hopkins and Columbia authors Impact of maternal HIV infection on the gut microbiome and metabolome of mothers and infants: the PRACHITi cohort in Pune, India</t>
+          <t>BJGMC, Weill Cornell Medicine and Johns Hopkins authors Dolutegravir Is Associated With Lower Odds of Gestational Diabetes Compared to Other Antiretroviral Therapy Regimens Among Pregnant Women in India: A Cross-Sectional Analysis</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>23 February 2026</t>
+          <t>1 September 2026</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/41730922/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42764545/</t>
         </is>
       </c>
     </row>
@@ -10645,44 +10645,44 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins University BJGMC (India): BJGMC-JHU CRS</t>
+          <t>BJGMC, Weill Cornell Medicine, Johns Hopkins and Columbia authors Impact of maternal HIV infection on the gut microbiome and metabolome of mothers and infants: the PRACHITi cohort in Pune, India</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>undated</t>
+          <t>23 February 2026</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>http://jhubi-ctu.jhu.edu/our-sites/bjgmc-india</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41730922/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>MD Anderson Cancer Center</t>
+          <t>Johns Hopkins University (School of Medicine)</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Tata Memorial Centre, Mumbai</t>
+          <t>Byramjee Jeejeebhoy Government Medical College and Sassoon General Hospitals, Pune (BJGMC-JHU Clinical Research Site)</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>OncoDaily Joint session by MD Anderson Cancer Center and Tata Memorial Centre at SACT 2025 Summit</t>
+          <t>Johns Hopkins University BJGMC (India): BJGMC-JHU CRS</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>4 December 2024</t>
+          <t>undated</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>https://oncodaily.com/blog/md-anderson-cancer-center-197733</t>
+          <t>http://jhubi-ctu.jhu.edu/our-sites/bjgmc-india</t>
         </is>
       </c>
     </row>
@@ -10699,44 +10699,44 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>India Herald MD Anderson Cancer Center signs sister institution accord with Tata Memorial</t>
+          <t>OncoDaily Joint session by MD Anderson Cancer Center and Tata Memorial Centre at SACT 2025 Summit</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>17 October 2003</t>
+          <t>4 December 2024</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>https://india-herald.com/md-anderson-cancer-center-signs-sister-institution-accord-with-tata-memoria-p305-19.htm</t>
+          <t>https://oncodaily.com/blog/md-anderson-cancer-center-197733</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>MD Anderson Cancer Center</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>AIIMS New Delhi (Departments of Pathology and Nephrology)</t>
+          <t>Tata Memorial Centre, Mumbai</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>AIIMS New Delhi AIIMS Mayo Clinic Update in Kidney Diseases and Transplant 2024</t>
+          <t>India Herald MD Anderson Cancer Center signs sister institution accord with Tata Memorial</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>7-8 December 2024</t>
+          <t>17 October 2003</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>https://aiimsmayoclinicupdate2024.com/</t>
+          <t>https://india-herald.com/md-anderson-cancer-center-signs-sister-institution-accord-with-tata-memoria-p305-19.htm</t>
         </is>
       </c>
     </row>
@@ -10748,22 +10748,22 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>Adani Group (Adani Health City, Ahmedabad and Mumbai; planned Kolkata campus)</t>
+          <t>AIIMS New Delhi (Departments of Pathology and Nephrology)</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Digital Health News Adani Group to Set Up INR 2,500 Crore Health City in West Bengal with Mayo Clinic Collaboration</t>
+          <t>AIIMS New Delhi AIIMS Mayo Clinic Update in Kidney Diseases and Transplant 2024</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>6 July 2026</t>
+          <t>7-8 December 2024</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>https://www.digitalhealthnews.com/adani-group-to-invest-inr-2-500-cr-in-health-city-project-in-west-bengal</t>
+          <t>https://aiimsmayoclinicupdate2024.com/</t>
         </is>
       </c>
     </row>
@@ -10780,17 +10780,17 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Adani Group Adani to Partner Mayo Clinic to Establish Affordable World Class Healthcare Facilities</t>
+          <t>Digital Health News Adani Group to Set Up INR 2,500 Crore Health City in West Bengal with Mayo Clinic Collaboration</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>10 February 2025</t>
+          <t>6 July 2026</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>https://www.adani.com/newsroom/media-releases/adani-to-partner-mayo-clinic-to-establish-affordable-world-class-healthcare-facilities</t>
+          <t>https://www.digitalhealthnews.com/adani-group-to-invest-inr-2-500-cr-in-health-city-project-in-west-bengal</t>
         </is>
       </c>
     </row>
@@ -10807,17 +10807,17 @@
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Post Bulletin Billionaire to partner with Mayo Clinic on India hospitals</t>
+          <t>Adani Group Adani to Partner Mayo Clinic to Establish Affordable World Class Healthcare Facilities</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>11 February 2025</t>
+          <t>10 February 2025</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>https://www.postbulletin.com/business/billionaire-to-partner-with-mayo-clinic-on-india-hospitals</t>
+          <t>https://www.adani.com/newsroom/media-releases/adani-to-partner-mayo-clinic-to-establish-affordable-world-class-healthcare-facilities</t>
         </is>
       </c>
     </row>
@@ -10829,22 +10829,22 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>Lilavati Hospital, GIFT City, Gujarat</t>
+          <t>Adani Group (Adani Health City, Ahmedabad and Mumbai; planned Kolkata campus)</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>The Indian Practitioner Lilavati Expands Globally and Domestically with Mauritius, GIFT City Projects</t>
+          <t>Post Bulletin Billionaire to partner with Mayo Clinic on India hospitals</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>22 April 2026</t>
+          <t>11 February 2025</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>https://theindianpractitioner.com/lilavati-expands-globally-and-domestically-with-mauritius-gift-city-projects/</t>
+          <t>https://www.postbulletin.com/business/billionaire-to-partner-with-mayo-clinic-on-india-hospitals</t>
         </is>
       </c>
     </row>
@@ -10861,17 +10861,17 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Lilavati Hospital News and Media</t>
+          <t>The Indian Practitioner Lilavati Expands Globally and Domestically with Mauritius, GIFT City Projects</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>23 September 2025</t>
+          <t>22 April 2026</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>https://www.lilavati-hospital.com/news-and-media.php</t>
+          <t>https://theindianpractitioner.com/lilavati-expands-globally-and-domestically-with-mauritius-gift-city-projects/</t>
         </is>
       </c>
     </row>
@@ -10888,17 +10888,17 @@
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Press Trust of India Lilavati Hospital, Mayo Clinic to establish 300-bed cancer institute in Mumbai</t>
+          <t>Lilavati Hospital News and Media</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>24 January 2025</t>
+          <t>23 September 2025</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>https://medicalbuyer.co.in/lilavati-hospital-mayo-clinic-to-establish-300-bed-cancer-institute-in-mumbai/</t>
+          <t>https://www.lilavati-hospital.com/news-and-media.php</t>
         </is>
       </c>
     </row>
@@ -10915,17 +10915,17 @@
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>VMPL Lilavati Hospital in Gift City, Gujarat has engaged with Mayo Clinic Global Consulting to enhance the patient care standards</t>
+          <t>Press Trust of India Lilavati Hospital, Mayo Clinic to establish 300-bed cancer institute in Mumbai</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>20 March 2024</t>
+          <t>24 January 2025</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/content/press-releases-ani/lilavati-hospital-in-gift-city-gujarat-has-engaged-with-mayo-clinic-global-consulting-to-enhance-the-patient-care-standards-124032000688_1.html</t>
+          <t>https://medicalbuyer.co.in/lilavati-hospital-mayo-clinic-to-establish-300-bed-cancer-institute-in-mumbai/</t>
         </is>
       </c>
     </row>
@@ -10937,22 +10937,22 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Lilavati Hospital, Mumbai</t>
+          <t>Lilavati Hospital, GIFT City, Gujarat</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Lilavati Hospital News and Media</t>
+          <t>VMPL Lilavati Hospital in Gift City, Gujarat has engaged with Mayo Clinic Global Consulting to enhance the patient care standards</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>23 September 2025</t>
+          <t>20 March 2024</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>https://www.lilavati-hospital.com/news-and-media.php</t>
+          <t>https://www.business-standard.com/content/press-releases-ani/lilavati-hospital-in-gift-city-gujarat-has-engaged-with-mayo-clinic-global-consulting-to-enhance-the-patient-care-standards-124032000688_1.html</t>
         </is>
       </c>
     </row>
@@ -10969,17 +10969,17 @@
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Kajal Rajput Mayo Clinic, Lilavati Hospital complete India's first Nursing Excellence Training Program</t>
+          <t>Lilavati Hospital News and Media</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>29 March 2025</t>
+          <t>23 September 2025</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/health/hospital-diagnostics/mayo-clinic-lilavati-hospital-complete-indias-first-nursing-excellence-training-program-145698</t>
+          <t>https://www.lilavati-hospital.com/news-and-media.php</t>
         </is>
       </c>
     </row>
@@ -10996,44 +10996,44 @@
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Press Trust of India Lilavati Hospital, Mayo Clinic to establish 300-bed cancer institute in Mumbai</t>
+          <t>Kajal Rajput Mayo Clinic, Lilavati Hospital complete India's first Nursing Excellence Training Program</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>24 January 2025</t>
+          <t>29 March 2025</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>https://medicalbuyer.co.in/lilavati-hospital-mayo-clinic-to-establish-300-bed-cancer-institute-in-mumbai/</t>
+          <t>https://medicaldialogues.in/news/health/hospital-diagnostics/mayo-clinic-lilavati-hospital-complete-indias-first-nursing-excellence-training-program-145698</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>Ramaiah Memorial Hospital, Bengaluru</t>
+          <t>Lilavati Hospital, Mumbai</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>ANI Ramaiah Memorial Hospital Brings 700+ Citizens Together to Put Heart Health in Motion</t>
+          <t>Press Trust of India Lilavati Hospital, Mayo Clinic to establish 300-bed cancer institute in Mumbai</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>28 September 2026</t>
+          <t>24 January 2025</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/content/press-releases-ani/ramaiah-memorial-hospital-brings-700-citizens-together-to-put-heart-health-in-motion-126092801082_1.html</t>
+          <t>https://medicalbuyer.co.in/lilavati-hospital-mayo-clinic-to-establish-300-bed-cancer-institute-in-mumbai/</t>
         </is>
       </c>
     </row>
@@ -11050,17 +11050,17 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System Ramaiah Memorial Hospital Signs Long Term Collaboration Agreement with the Mount Sinai Health System in New York</t>
+          <t>ANI Ramaiah Memorial Hospital Brings 700+ Citizens Together to Put Heart Health in Motion</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>12 July 2024</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/news/ramaiah-memorial-hospital-signs-long-143000744.html</t>
+          <t>https://www.business-standard.com/amp/content/press-releases-ani/ramaiah-memorial-hospital-brings-700-citizens-together-to-put-heart-health-in-motion-126092801082_1.html</t>
         </is>
       </c>
     </row>
@@ -11077,71 +11077,71 @@
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>Deccan Herald Ramaiah Memorial inks 10-year partnership with Mount Sinai Health System of New York</t>
+          <t>Mount Sinai Health System Ramaiah Memorial Hospital Signs Long Term Collaboration Agreement with the Mount Sinai Health System in New York</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>13 July 2024</t>
+          <t>12 July 2024</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/karnataka/bengaluru/ramaiah-memorial-inks-10-year-partnership-with-mount-sinai-health-system-of-new-york-3103995</t>
+          <t>https://finance.yahoo.com/news/ramaiah-memorial-hospital-signs-long-143000744.html</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Rutgers Robert Wood Johnson Medical School (Rutgers Health)</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>Govind Ballabh Pant Institute of Postgraduate Medical Education and Research (GIPMER), New Delhi</t>
+          <t>Ramaiah Memorial Hospital, Bengaluru</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>Choose New Jersey Governor Murphy Celebrates Signing of MOUs Between New Jersey and Indian Universities, Hospitals to Advance Cardiovascular Research and Innovation</t>
+          <t>Deccan Herald Ramaiah Memorial inks 10-year partnership with Mount Sinai Health System of New York</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>13 July 2024</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>https://www.insidernj.com/press-release/governor-murphy-celebrates-signing-of-mous-between-new-jersey-and-indian-universities-hospitals-to-advance-cardiovascular-research-and-innovation/</t>
+          <t>https://www.deccanherald.com/india/karnataka/bengaluru/ramaiah-memorial-inks-10-year-partnership-with-mount-sinai-health-system-of-new-york-3103995</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Rutgers Robert Wood Johnson Medical School (Rutgers Health)</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>National Cancer Grid (NCG) India, including Tata Memorial network centres</t>
+          <t>Govind Ballabh Pant Institute of Postgraduate Medical Education and Research (GIPMER), New Delhi</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>Jake Mickelsen Learn how a quality improvement program is improving care for cancer patients across India</t>
+          <t>Choose New Jersey Governor Murphy Celebrates Signing of MOUs Between New Jersey and Indian Universities, Hospitals to Advance Cardiovascular Research and Innovation</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>https://globalhealth.stanford.edu/bidirectional-partnerships/9912.html/</t>
+          <t>https://www.insidernj.com/press-release/governor-murphy-celebrates-signing-of-mous-between-new-jersey-and-indian-universities-hospitals-to-advance-cardiovascular-research-and-innovation/</t>
         </is>
       </c>
     </row>
@@ -11158,44 +11158,44 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>Jamie Hansen Getting Better at Getting Better: A Stanford-India partnership sparks a movement in improving palliative care</t>
+          <t>Jake Mickelsen Learn how a quality improvement program is improving care for cancer patients across India</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>2022-04-18</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>https://globalhealth.stanford.edu/beyond-stanford/getting-better-at-getting-better-a-stanford-india-partnership-sparks-a-movement-in-improving-palliative-care.html/</t>
+          <t>https://globalhealth.stanford.edu/bidirectional-partnerships/9912.html/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>Stanford Medicine (Emergency Medicine International, Center for Innovation in Global Health)</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Emergency Management and Research Institute (EMRI), India</t>
+          <t>National Cancer Grid (NCG) India, including Tata Memorial network centres</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>Stanford Center for Innovation in Global Health Longtime global emergency medicine collaborators from India's Emergency Management and Research Institute visit Stanford</t>
+          <t>Jamie Hansen Getting Better at Getting Better: A Stanford-India partnership sparks a movement in improving palliative care</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2022-04-18</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>https://globalhealth.stanford.edu/bidirectional-parnterships/longtime-global-emergency-medicine-collaborators-from-indias-emergency-management-and-research-institute-visit-stanford.html/</t>
+          <t>https://globalhealth.stanford.edu/beyond-stanford/getting-better-at-getting-better-a-stanford-india-partnership-sparks-a-movement-in-improving-palliative-care.html/</t>
         </is>
       </c>
     </row>
@@ -11212,44 +11212,44 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>EMRI Green Health Services Partnerships</t>
+          <t>Stanford Center for Innovation in Global Health Longtime global emergency medicine collaborators from India's Emergency Management and Research Institute visit Stanford</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>undated</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>https://www.emri.in/partnerships-3/</t>
+          <t>https://globalhealth.stanford.edu/bidirectional-parnterships/longtime-global-emergency-medicine-collaborators-from-indias-emergency-management-and-research-institute-visit-stanford.html/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>Thomas Jefferson University / Jefferson Health (Jefferson India Center)</t>
+          <t>Stanford Medicine (Emergency Medicine International, Center for Innovation in Global Health)</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>KLE Academy of Higher Education and Research (J N Medical College, Belagavi); LV Prasad Eye Institute, Hyderabad (listed by Jefferson, no recent dated activity)</t>
+          <t>Emergency Management and Research Institute (EMRI), India</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>KLE J N Medical College and Thomas Jefferson University authors Response of reticulocyte and red blood cell indices to single-dose intravenous iron in pregnant women with moderate iron deficiency anemia: secondary analysis of the RAPIDIRON trial</t>
+          <t>EMRI Green Health Services Partnerships</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>27 April 2026</t>
+          <t>undated</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42045095/</t>
+          <t>https://www.emri.in/partnerships-3/</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>Thomas Jefferson University Office of Global Affairs Global Jefferson Day 2026: Optimizing Global Health Outcomes: Jefferson India Center</t>
+          <t>KLE J N Medical College and Thomas Jefferson University authors Response of reticulocyte and red blood cell indices to single-dose intravenous iron in pregnant women with moderate iron deficiency anemia: secondary analysis of the RAPIDIRON trial</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>26 March 2026</t>
+          <t>27 April 2026</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>https://global.jefferson.edu/global-jefferson-day.html</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42045095/</t>
         </is>
       </c>
     </row>
@@ -11293,44 +11293,44 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>Jefferson Office of International Services Jefferson India Center</t>
+          <t>Thomas Jefferson University Office of Global Affairs Global Jefferson Day 2026: Optimizing Global Health Outcomes: Jefferson India Center</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>undated</t>
+          <t>26 March 2026</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>https://global.jefferson.edu/jeffersons-global-centers/jefferson-india-center.html</t>
+          <t>https://global.jefferson.edu/global-jefferson-day.html</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>Thomas Jefferson University / Jefferson Health (Jefferson India Center)</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>All India Institute of Medical Sciences, New Delhi</t>
+          <t>KLE Academy of Higher Education and Research (J N Medical College, Belagavi); LV Prasad Eye Institute, Hyderabad (listed by Jefferson, no recent dated activity)</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>UCLA Health Department of Obstetrics and Gynecology Newsletter Summer 2025: New and Noteworthy</t>
+          <t>Jefferson Office of International Services Jefferson India Center</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Summer 2025</t>
+          <t>undated</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>https://www.uclahealth.org/departments/obgyn/about-us/news/newsletter-summer-2025/new-and-noteworthy</t>
+          <t>https://global.jefferson.edu/jeffersons-global-centers/jefferson-india-center.html</t>
         </is>
       </c>
     </row>
@@ -11347,17 +11347,17 @@
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>UCLA Health Department of Obstetrics and Gynecology UCLA-India Global Health Exchange in OB/GYN</t>
+          <t>UCLA Health Department of Obstetrics and Gynecology Newsletter Summer 2025: New and Noteworthy</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>undated</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>https://www.uclahealth.org/departments/obgyn/about-us/global-reproductive-health-alliance-collaborative-engagement/ucla-india-global-health-exchange-obgyn</t>
+          <t>https://www.uclahealth.org/departments/obgyn/about-us/news/newsletter-summer-2025/new-and-noteworthy</t>
         </is>
       </c>
     </row>
@@ -11369,22 +11369,22 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>Federation of Obstetric and Gynaecological Societies of India (FOGSI) and SAFOG</t>
+          <t>All India Institute of Medical Sciences, New Delhi</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>UCLA Health UCLA OB/GYN global health initiatives spark learning, innovation and training</t>
+          <t>UCLA Health Department of Obstetrics and Gynecology UCLA-India Global Health Exchange in OB/GYN</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>8 December 2025</t>
+          <t>undated</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>https://www.uclahealth.org/news/article/ucla-obgyn-global-health-initiatives-spark-learning</t>
+          <t>https://www.uclahealth.org/departments/obgyn/about-us/global-reproductive-health-alliance-collaborative-engagement/ucla-india-global-health-exchange-obgyn</t>
         </is>
       </c>
     </row>
@@ -11396,22 +11396,22 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>Narendra Modi Medical College, Ahmedabad</t>
+          <t>Federation of Obstetric and Gynaecological Societies of India (FOGSI) and SAFOG</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>UCLA Health Department of Obstetrics and Gynecology New and Noteworthy</t>
+          <t>UCLA Health UCLA OB/GYN global health initiatives spark learning, innovation and training</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Summer 2025</t>
+          <t>8 December 2025</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>https://www.uclahealth.org/departments/obgyn/about-us/news/newsletter-summer-2025/new-and-noteworthy</t>
+          <t>https://www.uclahealth.org/news/article/ucla-obgyn-global-health-initiatives-spark-learning</t>
         </is>
       </c>
     </row>
@@ -11428,71 +11428,71 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>UCLA Health Department of Obstetrics and Gynecology UCLA-India Global Health Exchange in OB/GYN</t>
+          <t>UCLA Health Department of Obstetrics and Gynecology New and Noteworthy</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>undated</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>https://www.uclahealth.org/departments/obgyn/about-us/global-reproductive-health-alliance-collaborative-engagement/ucla-india-global-health-exchange-obgyn</t>
+          <t>https://www.uclahealth.org/departments/obgyn/about-us/news/newsletter-summer-2025/new-and-noteworthy</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>University of Alabama at Birmingham (Heersink School of Medicine)</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Pravara Institute of Medical Sciences (Loni) and Bharati Vidyapeeth Medical College (Pune)</t>
+          <t>Narendra Modi Medical College, Ahmedabad</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>Shawna Masters New UAB-India partnership aims to enhance global health training</t>
+          <t>UCLA Health Department of Obstetrics and Gynecology UCLA-India Global Health Exchange in OB/GYN</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>undated</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>https://www.uab.edu/medicine/news/global-health/new-uab-india-partnership-aims-to-enhance-global-health-training</t>
+          <t>https://www.uclahealth.org/departments/obgyn/about-us/global-reproductive-health-alliance-collaborative-engagement/ucla-india-global-health-exchange-obgyn</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>University of California San Francisco (Francis I. Proctor Foundation)</t>
+          <t>University of Alabama at Birmingham (Heersink School of Medicine)</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>Aravind Eye Care System, Madurai</t>
+          <t>Pravara Institute of Medical Sciences (Loni) and Bharati Vidyapeeth Medical College (Pune)</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>REAGIR trial authors (Aravind Eye Hospital; Francis I. Proctor Foundation, UCSF and others) Rose Bengal Electromagnetic Activation With Green Light for Infection Reduction: Follow-Up of a Randomized Clinical Trial</t>
+          <t>Shawna Masters New UAB-India partnership aims to enhance global health training</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>1 August 2026</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42348235/</t>
+          <t>https://www.uab.edu/medicine/news/global-health/new-uab-india-partnership-aims-to-enhance-global-health-training</t>
         </is>
       </c>
     </row>
@@ -11509,44 +11509,44 @@
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>SCUT II Study authors (not verified) Steroids and Cross-Linking for Ulcer Treatment: The SCUT II Randomized Clinical Trial</t>
+          <t>REAGIR trial authors (Aravind Eye Hospital; Francis I. Proctor Foundation, UCSF and others) Rose Bengal Electromagnetic Activation With Green Light for Infection Reduction: Follow-Up of a Randomized Clinical Trial</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>1 August 2026</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>https://jamanetwork.com/journals/jamaophthalmology/fullarticle/2836544</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42348235/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>University of Iowa (Carver College of Medicine, Ophthalmology)</t>
+          <t>University of California San Francisco (Francis I. Proctor Foundation)</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Dr. Shroff's Charity Eye Hospital, New Delhi</t>
+          <t>Aravind Eye Care System, Madurai</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>Iowa Lions Eye Bank Iowa Lions Eye Bank Shares Expertise with Corneal Specialists in India</t>
+          <t>SCUT II Study authors (not verified) Steroids and Cross-Linking for Ulcer Treatment: The SCUT II Randomized Clinical Trial</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>1 February 2025</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>https://iowalionseyebank.org/news/2025/02/iowa-lions-eye-bank-shares-expertise-corneal-specialists-india</t>
+          <t>https://jamanetwork.com/journals/jamaophthalmology/fullarticle/2836544</t>
         </is>
       </c>
     </row>
@@ -11563,98 +11563,98 @@
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>University of Iowa International Programs Forging paths in global ophthalmology: University of Iowa partners with charity eye hospital in India</t>
+          <t>Iowa Lions Eye Bank Iowa Lions Eye Bank Shares Expertise with Corneal Specialists in India</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>1 February 2025</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>https://international.uiowa.edu/node/15891</t>
+          <t>https://iowalionseyebank.org/news/2025/02/iowa-lions-eye-bank-shares-expertise-corneal-specialists-india</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>University of Michigan Medical School / Michigan Medicine</t>
+          <t>University of Iowa (Carver College of Medicine, Ophthalmology)</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>AIIMS Jammu</t>
+          <t>Dr. Shroff's Charity Eye Hospital, New Delhi</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>Tanya Verma AIIMS Jammu and University of Michigan Collaborate for Twin International Conferences</t>
+          <t>University of Iowa International Programs Forging paths in global ophthalmology: University of Iowa partners with charity eye hospital in India</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>https://collegehai.com/news/aiims-jammu-university-of-michigan-international-conferences</t>
+          <t>https://international.uiowa.edu/node/15891</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Madison Department of Ophthalmology and Visual Sciences (UW Health)</t>
+          <t>University of Michigan Medical School / Michigan Medicine</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Dr. Shroff's Charity Eye Hospital, New Delhi</t>
+          <t>AIIMS Jammu</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>UW Department of Ophthalmology and Visual Sciences DOVS Celebrates a Decade of Partnership with Colleagues in India</t>
+          <t>Tanya Verma AIIMS Jammu and University of Michigan Collaborate for Twin International Conferences</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>https://www.ophth.wisc.edu/blog/2025/02/28/india_rotation_2025</t>
+          <t>https://collegehai.com/news/aiims-jammu-university-of-michigan-international-conferences</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Weill Cornell Medicine (Center for Global Health)</t>
+          <t>University of Wisconsin-Madison Department of Ophthalmology and Visual Sciences (UW Health)</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>Byramjee Jeejeebhoy Government Medical College and Sassoon Hospital, Pune; Deep Griha Society</t>
+          <t>Dr. Shroff's Charity Eye Hospital, New Delhi</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>BJGMC, Weill Cornell Medicine and Johns Hopkins authors Dolutegravir Is Associated With Lower Odds of Gestational Diabetes Compared to Other Antiretroviral Therapy Regimens Among Pregnant Women in India: A Cross-Sectional Analysis</t>
+          <t>UW Department of Ophthalmology and Visual Sciences DOVS Celebrates a Decade of Partnership with Colleagues in India</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>1 September 2026</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42764545/</t>
+          <t>https://www.ophth.wisc.edu/blog/2025/02/28/india_rotation_2025</t>
         </is>
       </c>
     </row>
@@ -11671,17 +11671,17 @@
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>BJGMC, Weill Cornell Medicine, Johns Hopkins and Columbia authors Impact of maternal HIV infection on the gut microbiome and metabolome of mothers and infants: the PRACHITi cohort in Pune, India</t>
+          <t>BJGMC, Weill Cornell Medicine and Johns Hopkins authors Dolutegravir Is Associated With Lower Odds of Gestational Diabetes Compared to Other Antiretroviral Therapy Regimens Among Pregnant Women in India: A Cross-Sectional Analysis</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>23 February 2026</t>
+          <t>1 September 2026</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/41730922/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42764545/</t>
         </is>
       </c>
     </row>
@@ -11698,44 +11698,44 @@
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>Weill Cornell Center for Global Health Pune, India</t>
+          <t>BJGMC, Weill Cornell Medicine, Johns Hopkins and Columbia authors Impact of maternal HIV infection on the gut microbiome and metabolome of mothers and infants: the PRACHITi cohort in Pune, India</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>undated</t>
+          <t>23 February 2026</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>https://globalhealth.weill.cornell.edu/major-initiatives/pune-india</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41730922/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>Cambridge University Hospitals NHS Foundation Trust (with Cambridge Global Health Partnerships)</t>
+          <t>Weill Cornell Medicine (Center for Global Health)</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>Himalayan Hospital (Dehradun) and Ganga Prem Hospice, Rishikesh, via Rama Foundation</t>
+          <t>Byramjee Jeejeebhoy Government Medical College and Sassoon Hospital, Pune; Deep Griha Society</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>Cambridge University Hospitals Health team prepare for India mission</t>
+          <t>Weill Cornell Center for Global Health Pune, India</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>6 August 2025</t>
+          <t>undated</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>https://www.cuh.nhs.uk/news/health-team-prepare-for-india-mission/</t>
+          <t>https://globalhealth.weill.cornell.edu/major-initiatives/pune-india</t>
         </is>
       </c>
     </row>
@@ -11752,71 +11752,71 @@
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>Mike Scialom Cambridge healthcare professionals head to northern India for partnership visit</t>
+          <t>Cambridge University Hospitals Health team prepare for India mission</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>6 August 2025</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>https://www.cambridgeindependent.co.uk/news/cambridge-healthcare-professionals-head-to-northern-india-fo-9429740/</t>
+          <t>https://www.cuh.nhs.uk/news/health-team-prepare-for-india-mission/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Juntendo University (Tokyo)</t>
+          <t>Cambridge University Hospitals NHS Foundation Trust (with Cambridge Global Health Partnerships)</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>Saint Hardyal Educational and Orphans' Welfare Society (SHEOWS), Delhi</t>
+          <t>Himalayan Hospital (Dehradun) and Ganga Prem Hospice, Rishikesh, via Rama Foundation</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>PTI SHEOWS and Juntendo University, Tokyo Sign MoU to Advance Geriatric Care and Research Collaboration Between India and Japan</t>
+          <t>Mike Scialom Cambridge healthcare professionals head to northern India for partnership visit</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>https://m.thewire.in/article/ptiprnews/sheows-and-juntendo-university-tokyo-sign-mou-to-advance-geriatric-care-and-research-collaboration-between-india-and-japan/amp</t>
+          <t>https://www.cambridgeindependent.co.uk/news/cambridge-healthcare-professionals-head-to-northern-india-fo-9429740/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>King's College London and Guy's and St Thomas' NHS Foundation Trust</t>
+          <t>Juntendo University (Tokyo)</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>P. D. Hinduja Hospital and Medical Research Centre, Mumbai (National Health &amp; Education Society)</t>
+          <t>Saint Hardyal Educational and Orphans' Welfare Society (SHEOWS), Delhi</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>Amit Srivastava Hinduja Foundation Offers MSc And PhD Scholarships For Indian Students At King's College London For 2026-27</t>
+          <t>PTI SHEOWS and Juntendo University, Tokyo Sign MoU to Advance Geriatric Care and Research Collaboration Between India and Japan</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/hinduja-foundation-offers-msc-and-phd-scholarships-for-indian-students-at-kings-college-london-for-202627</t>
+          <t>https://m.thewire.in/article/ptiprnews/sheows-and-juntendo-university-tokyo-sign-mou-to-advance-geriatric-care-and-research-collaboration-between-india-and-japan/amp</t>
         </is>
       </c>
     </row>
@@ -11833,17 +11833,17 @@
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>Pharmautility P. D. Hinduja Hospital and King's College London Collaborate and Commence Their First Training Program for Nurses</t>
+          <t>Amit Srivastava Hinduja Foundation Offers MSc And PhD Scholarships For Indian Students At King's College London For 2026-27</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>https://pharmautility.com/p-d-hinduja-hospital-and-kings-college-london-collaborate-and-commence-their-first-training-program-for-nurses/</t>
+          <t>https://www.freepressjournal.in/education/hinduja-foundation-offers-msc-and-phd-scholarships-for-indian-students-at-kings-college-london-for-202627</t>
         </is>
       </c>
     </row>
@@ -11860,44 +11860,44 @@
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>King's College London New partnership to improve healthcare outcomes in India and the UK</t>
+          <t>Pharmautility P. D. Hinduja Hospital and King's College London Collaborate and Commence Their First Training Program for Nurses</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>https://www.kcl.ac.uk/news/new-partnership-to-improve-healthcare-outcomes-in-india-and-the-uk</t>
+          <t>https://pharmautility.com/p-d-hinduja-hospital-and-kings-college-london-collaborate-and-commence-their-first-training-program-for-nurses/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>Monash University (Faculty of Information Technology)</t>
+          <t>King's College London and Guy's and St Thomas' NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>Apollo Hospitals and The Apollo University</t>
+          <t>P. D. Hinduja Hospital and Medical Research Centre, Mumbai (National Health &amp; Education Society)</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>Health News Monash University Partners with Apollo Hospitals for Digital Health Research</t>
+          <t>King's College London New partnership to improve healthcare outcomes in India and the UK</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>https://www.digitalhealthnews.com/monash-university-partners-with-apollo-hospitals-for-digital-health-research</t>
+          <t>https://www.kcl.ac.uk/news/new-partnership-to-improve-healthcare-outcomes-in-india-and-the-uk</t>
         </is>
       </c>
     </row>
@@ -11914,71 +11914,71 @@
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>Dylan Bushell-Embling Monash partners with Apollo University on health AI research</t>
+          <t>Health News Monash University Partners with Apollo Hospitals for Digital Health Research</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>https://www.govtechreview.com.au/content/gov-digital/news/monash-partners-with-apollo-university-on-health-ai-research-652623324</t>
+          <t>https://www.digitalhealthnews.com/monash-university-partners-with-apollo-hospitals-for-digital-health-research</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>SingHealth</t>
+          <t>Monash University (Faculty of Information Technology)</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>Athulya Senior Care, Chennai</t>
+          <t>Apollo Hospitals and The Apollo University</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>Team VOH Athulya Senior Care Inks Landmark MoU with SingHealth to Advance Senior Care, Training, and Research Collaboration</t>
+          <t>Dylan Bushell-Embling Monash partners with Apollo University on health AI research</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>https://vohnetwork.com/news/hospitals-providers/athulya-senior-care-inks-landmark-mou-with-singhealth-to-advance-senior-care-training-and-research-collaboration</t>
+          <t>https://www.govtechreview.com.au/content/gov-digital/news/monash-partners-with-apollo-university-on-health-ai-research-652623324</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>University College London</t>
+          <t>SingHealth</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>AIIMS New Delhi and IIT Delhi</t>
+          <t>Athulya Senior Care, Chennai</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>University College London Inaugural recipients of UCL-AIIMS-IITD trilateral seed funds revealed</t>
+          <t>Team VOH Athulya Senior Care Inks Landmark MoU with SingHealth to Advance Senior Care, Training, and Research Collaboration</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>November 2025</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>https://www.ucl.ac.uk/global/news/2025/nov/inaugural-recipients-ucl-aiims-iitd-trilateral-seed-funds-revealed</t>
+          <t>https://vohnetwork.com/news/hospitals-providers/athulya-senior-care-inks-landmark-mou-with-singhealth-to-advance-senior-care-training-and-research-collaboration</t>
         </is>
       </c>
     </row>
@@ -11995,44 +11995,44 @@
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>Sanket Koul UCL inks trilateral pact with AIIMS, IIT-D to scale up medtech innovation</t>
+          <t>University College London Inaugural recipients of UCL-AIIMS-IITD trilateral seed funds revealed</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>November 2025</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/ucl-inks-trilateral-pact-with-aiims-iit-d-to-scale-up-medtech-innovation-124112201280_1.html</t>
+          <t>https://www.ucl.ac.uk/global/news/2025/nov/inaugural-recipients-ucl-aiims-iitd-trilateral-seed-funds-revealed</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>University of Leicester and University Hospitals of Leicester NHS Trust</t>
+          <t>University College London</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>Apollo Hospitals and The Apollo University</t>
+          <t>AIIMS New Delhi and IIT Delhi</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>IPP Bureau University of Leicester, Apollo showcase AI-driven healthcare research to strengthen UK-India collaboration</t>
+          <t>Sanket Koul UCL inks trilateral pact with AIIMS, IIT-D to scale up medtech innovation</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/hospitals/university-of-leicester-apollo-showcase-ai-driven-healthcare-research-to-strengthen-uk-india-collaboration-20937</t>
+          <t>https://www.business-standard.com/india-news/ucl-inks-trilateral-pact-with-aiims-iit-d-to-scale-up-medtech-innovation-124112201280_1.html</t>
         </is>
       </c>
     </row>
@@ -12049,44 +12049,44 @@
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>University of Leicester University of Leicester and The Apollo University launch global research centre for digital health and precision medicine</t>
+          <t>IPP Bureau University of Leicester, Apollo showcase AI-driven healthcare research to strengthen UK-India collaboration</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>https://le.ac.uk/news/2025/january/apollo-launch</t>
+          <t>https://www.indianpharmapost.com/hospitals/university-of-leicester-apollo-showcase-ai-driven-healthcare-research-to-strengthen-uk-india-collaboration-20937</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>University of Leicester, University Hospitals of Leicester NHS Trust and BAPIO Training Academy</t>
+          <t>University of Leicester and University Hospitals of Leicester NHS Trust</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>Apollo Health Resources (Apollo Hospitals)</t>
+          <t>Apollo Hospitals and The Apollo University</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>IPP Bureau University of Leicester, Apollo showcase AI-driven healthcare research to strengthen UK-India collaboration</t>
+          <t>University of Leicester University of Leicester and The Apollo University launch global research centre for digital health and precision medicine</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/hospitals/university-of-leicester-apollo-showcase-ai-driven-healthcare-research-to-strengthen-uk-india-collaboration-20937</t>
+          <t>https://le.ac.uk/news/2025/january/apollo-launch</t>
         </is>
       </c>
     </row>
@@ -12103,71 +12103,71 @@
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>University of Leicester Trainee doctors in India to bolster their clinical skills with the NHS thanks to landmark initiative</t>
+          <t>IPP Bureau University of Leicester, Apollo showcase AI-driven healthcare research to strengthen UK-India collaboration</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>https://le.ac.uk/news/2025/october/trainee-doctors-india-clinical-skills-nhs-landmark-initiative</t>
+          <t>https://www.indianpharmapost.com/hospitals/university-of-leicester-apollo-showcase-ai-driven-healthcare-research-to-strengthen-uk-india-collaboration-20937</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>University of Liverpool</t>
+          <t>University of Leicester, University Hospitals of Leicester NHS Trust and BAPIO Training Academy</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>Saveetha Institute of Medical and Technical Sciences (SIMATS), Chennai</t>
+          <t>Apollo Health Resources (Apollo Hospitals)</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>University of Liverpool New partnerships build on Liverpool-India research and education ties</t>
+          <t>University of Leicester Trainee doctors in India to bolster their clinical skills with the NHS thanks to landmark initiative</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>https://news.liverpool.ac.uk/2025/07/14/new-partnerships-further-strengthen-liverpool-india-research-and-education-ties/</t>
+          <t>https://le.ac.uk/news/2025/october/trainee-doctors-india-clinical-skills-nhs-landmark-initiative</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>Cleveland Clinic</t>
+          <t>University of Liverpool</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Group</t>
+          <t>Saveetha Institute of Medical and Technical Sciences (SIMATS), Chennai</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>Telangana Today Apollo Hospitals launches International second opinion services for patients</t>
+          <t>University of Liverpool New partnerships build on Liverpool-India research and education ties</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>January 2022</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>https://telanganatoday.com/apollo-hospitals-launches-international-second-opinion-services-for-patients</t>
+          <t>https://news.liverpool.ac.uk/2025/07/14/new-partnerships-further-strengthen-liverpool-india-research-and-education-ties/</t>
         </is>
       </c>
     </row>
@@ -12184,44 +12184,44 @@
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>HHM Global Apollo Hospitals collaborates with Cleveland Clinic to offer international second opinion services to patients</t>
+          <t>Telangana Today Apollo Hospitals launches International second opinion services for patients</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>undated</t>
+          <t>January 2022</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>https://www.hhmglobal.com/knowledge-bank/news/apollo-hospitals-collaborates-with-cleveland-clinic-to-offer-international-second-opinion-services-to-patients</t>
+          <t>https://telanganatoday.com/apollo-hospitals-launches-international-second-opinion-services-for-patients</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins (University)</t>
+          <t>Cleveland Clinic</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>College of Nursing, Christian Medical College Vellore</t>
+          <t>Apollo Hospitals Group</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins School of Nursing and CMC Vellore College of Nursing authors Leveraging a Global Partnership to Address COVID-19-Related Mental Health Challenges</t>
+          <t>HHM Global Apollo Hospitals collaborates with Cleveland Clinic to offer international second opinion services to patients</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>3 October 2024</t>
+          <t>undated</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/10.1111/jpm.13115</t>
+          <t>https://www.hhmglobal.com/knowledge-bank/news/apollo-hospitals-collaborates-with-cleveland-clinic-to-offer-international-second-opinion-services-to-patients</t>
         </is>
       </c>
     </row>
@@ -12238,17 +12238,17 @@
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins School of Nursing From Baltimore to Vellore, India: Global Support for Nurses Struggling with COVID-Related Mental Health</t>
+          <t>Johns Hopkins School of Nursing and CMC Vellore College of Nursing authors Leveraging a Global Partnership to Address COVID-19-Related Mental Health Challenges</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>August 2021</t>
+          <t>3 October 2024</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>https://nursing.jhu.edu/magazine/articles/2021/08/from-baltimore-to-vellore-india-global-support-for-nurses-struggling-with-covid-related-mental-health/</t>
+          <t>https://onlinelibrary.wiley.com/doi/10.1111/jpm.13115</t>
         </is>
       </c>
     </row>
@@ -12265,44 +12265,44 @@
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>College of Nursing, CMC Vellore Collaboration</t>
+          <t>Johns Hopkins School of Nursing From Baltimore to Vellore, India: Global Support for Nurses Struggling with COVID-Related Mental Health</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>undated</t>
+          <t>August 2021</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>https://concmc.org/collaboration/</t>
+          <t>https://nursing.jhu.edu/magazine/articles/2021/08/from-baltimore-to-vellore-india-global-support-for-nurses-struggling-with-covid-related-mental-health/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Johns Hopkins (University)</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>AIG Hospitals, Hyderabad</t>
+          <t>College of Nursing, Christian Medical College Vellore</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>Post Bulletin Billionaire to partner with Mayo Clinic on India hospitals</t>
+          <t>College of Nursing, CMC Vellore Collaboration</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>11 February 2025</t>
+          <t>undated</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>https://www.postbulletin.com/business/billionaire-to-partner-with-mayo-clinic-on-india-hospitals</t>
+          <t>https://concmc.org/collaboration/</t>
         </is>
       </c>
     </row>
@@ -12319,44 +12319,44 @@
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic AIG Hospitals in India joins Mayo Clinic Care Network</t>
+          <t>Post Bulletin Billionaire to partner with Mayo Clinic on India hospitals</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>24 October 2019</t>
+          <t>11 February 2025</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>https://www.newswise.com/articles/aig-hospitals-in-india-joins-mayo-clinic-care-network</t>
+          <t>https://www.postbulletin.com/business/billionaire-to-partner-with-mayo-clinic-on-india-hospitals</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>iCliniq, Chennai (MSKCC India)</t>
+          <t>AIG Hospitals, Hyderabad</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center Memorial Sloan Kettering Cancer Center Launches MSKCC India to Expand Access to World-Renowned Oncologists, Cancer Care, Research, and Education</t>
+          <t>Mayo Clinic AIG Hospitals in India joins Mayo Clinic Care Network</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>2 August 2021</t>
+          <t>24 October 2019</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/memorial-sloan-kettering-cancer-center-launches-mskcc-india-to-expand-access-to-world-renowned-oncologists-cancer-care-research-and-education-301345795.html</t>
+          <t>https://www.newswise.com/articles/aig-hospitals-in-india-joins-mayo-clinic-care-network</t>
         </is>
       </c>
     </row>
@@ -12373,78 +12373,78 @@
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>iCliniq Frequently Asked Question: MSK India</t>
+          <t>Memorial Sloan Kettering Cancer Center Memorial Sloan Kettering Cancer Center Launches MSKCC India to Expand Access to World-Renowned Oncologists, Cancer Care, Research, and Education</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>undated</t>
+          <t>2 August 2021</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>https://mskcc.icliniq.com/mskcc-india-services/mskcc-patient-faqs</t>
+          <t>https://www.prnewswire.com/news-releases/memorial-sloan-kettering-cancer-center-launches-mskcc-india-to-expand-access-to-world-renowned-oncologists-cancer-care-research-and-education-301345795.html</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>Northwell Health (Center for Global Health)</t>
+          <t>Memorial Sloan Kettering</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>Christian Medical College (CMC) Vellore</t>
+          <t>iCliniq, Chennai (MSKCC India)</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>Northwell Health Northwell Health signs five-year strategic agreement with Indian health system, CMC Vellore</t>
+          <t>iCliniq Frequently Asked Question: MSK India</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>undated</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>https://www.northwell.edu/news/the-latest/northwell-signs-5-year-strategic-agreement-india-s-cmc-vellore</t>
+          <t>https://mskcc.icliniq.com/mskcc-india-services/mskcc-patient-faqs</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>LMU Klinikum (University Hospital Munich)</t>
+          <t>Northwell Health (Center for Global Health)</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>AIIMS New Delhi</t>
+          <t>Christian Medical College (CMC) Vellore</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>Press Trust of India AIIMS Delhi, Munich-based university sign agreement for research in medicine, life sciences</t>
+          <t>Northwell Health Northwell Health signs five-year strategic agreement with Indian health system, CMC Vellore</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/aiims-delhi-munich-based-university-sign-non-binding-mou-for-collaborative-endeavours/amp</t>
+          <t>https://www.northwell.edu/news/the-latest/northwell-signs-5-year-strategic-agreement-india-s-cmc-vellore</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>University of Bolton Institute of Medicine (now University of Greater Manchester Medical School)</t>
+          <t>LMU Klinikum (University Hospital Munich)</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
@@ -12454,44 +12454,44 @@
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>News Services Division AIIMS New Delhi signed MoU with University of Bolton Institute of Medicine</t>
+          <t>Press Trust of India AIIMS Delhi, Munich-based university sign agreement for research in medicine, life sciences</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>https://newsonair.gov.in/aiims-new-delhi-signed-mou-with-university-of-bolton-institute-of-medicine</t>
+          <t>https://news.careers360.com/aiims-delhi-munich-based-university-sign-non-binding-mou-for-collaborative-endeavours/amp</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins (Medicine International)</t>
+          <t>University of Bolton Institute of Medicine (now University of Greater Manchester Medical School)</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>HCL Healthcare</t>
+          <t>AIIMS New Delhi</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>Domain-b HCL enters healthcare with HCL Avitas</t>
+          <t>News Services Division AIIMS New Delhi signed MoU with University of Bolton Institute of Medicine</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>6 February 2014</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>https://www.domain-b.com/companies-organisations/firms-companies/hcl-enters-healthcare-with-hcl-avitas</t>
+          <t>https://newsonair.gov.in/aiims-new-delhi-signed-mou-with-university-of-bolton-institute-of-medicine</t>
         </is>
       </c>
     </row>
@@ -12508,34 +12508,34 @@
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins Medicine International HCL Healthcare</t>
+          <t>Domain-b HCL enters healthcare with HCL Avitas</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>undated</t>
+          <t>6 February 2014</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>https://www.hopkinsmedicine.org/international/health-care-consulting/asia-pacific/hcl-healthcare</t>
+          <t>https://www.domain-b.com/companies-organisations/firms-companies/hcl-enters-healthcare-with-hcl-avitas</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>MD Anderson Cancer Center</t>
+          <t>Johns Hopkins (Medicine International)</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>Tata Memorial Hospital, Mumbai (Project ECHO Palliative Care Africa II)</t>
+          <t>HCL Healthcare</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>The University of Texas MD Anderson Cancer Center Project ECHO: Palliative Care Africa (PACA) II</t>
+          <t>Johns Hopkins Medicine International HCL Healthcare</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
@@ -12545,34 +12545,34 @@
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>https://www.mdanderson.org/education-training/outreach-programs/project-echo/programs/palliative-care-africa.html</t>
+          <t>https://www.hopkinsmedicine.org/international/health-care-consulting/asia-pacific/hcl-healthcare</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>Cedars-Sinai</t>
+          <t>MD Anderson Cancer Center</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>Eka Hospital Group</t>
+          <t>Tata Memorial Hospital, Mumbai (Project ECHO Palliative Care Africa II)</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>Cedars-Sinai Cedars-Sinai International Launches Presence in Indonesia</t>
+          <t>The University of Texas MD Anderson Cancer Center Project ECHO: Palliative Care Africa (PACA) II</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>undated</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>https://www.cedars-sinai.org/blog/cedars-sinai-launches-collaboration-in-indonesia.html</t>
+          <t>https://www.mdanderson.org/education-training/outreach-programs/project-echo/programs/palliative-care-africa.html</t>
         </is>
       </c>
     </row>
@@ -12589,17 +12589,17 @@
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>Kompas Eka Hospital Group Jalin Kerja Sama dengan Cedars-Sinai Hospital</t>
+          <t>Cedars-Sinai Cedars-Sinai International Launches Presence in Indonesia</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>https://biz.kompas.com/read/2022/08/25/121418528/eka-hospital-group-jalin-kerja-sama-dengan-cedars-sinai-hospital</t>
+          <t>https://www.cedars-sinai.org/blog/cedars-sinai-launches-collaboration-in-indonesia.html</t>
         </is>
       </c>
     </row>
@@ -12616,44 +12616,44 @@
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>Cedars-Sinai Staff Nurses Share Expertise with International EKA Hospital Group</t>
+          <t>Kompas Eka Hospital Group Jalin Kerja Sama dengan Cedars-Sinai Hospital</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>https://www.cedars-sinai.org/international-stories/nurses-share-expertise-with-international-eka-hospital-group.html</t>
+          <t>https://biz.kompas.com/read/2022/08/25/121418528/eka-hospital-group-jalin-kerja-sama-dengan-cedars-sinai-hospital</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>Harvard Medical School</t>
+          <t>Cedars-Sinai</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>Universitas Harkat Negeri and CISDI (Primary Healthcare Impact Lab)</t>
+          <t>Eka Hospital Group</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>Bangun Santoso, Suara.com UHN dan CISDI Gandeng Harvard Medical School, Bangun Pusat Riset Kesehatan Primer di RI</t>
+          <t>Cedars-Sinai Staff Nurses Share Expertise with International EKA Hospital Group</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>https://www.suara.com/news/2026/05/07/202619/uhn-dan-cisdi-gandeng-harvard-medical-school-bangun-pusat-riset-kesehatan-primer-di-ri</t>
+          <t>https://www.cedars-sinai.org/international-stories/nurses-share-expertise-with-international-eka-hospital-group.html</t>
         </is>
       </c>
     </row>
@@ -12670,40 +12670,40 @@
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>CISDI Primary Healthcare IMPACT Lab</t>
-        </is>
-      </c>
-      <c r="D178" s="5" t="inlineStr"/>
+          <t>Bangun Santoso, Suara.com UHN dan CISDI Gandeng Harvard Medical School, Bangun Pusat Riset Kesehatan Primer di RI</t>
+        </is>
+      </c>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>https://cisdi.org/en/our-works/phcimpactlab</t>
+          <t>https://www.suara.com/news/2026/05/07/202619/uhn-dan-cisdi-gandeng-harvard-medical-school-bangun-pusat-riset-kesehatan-primer-di-ri</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>MD Anderson Cancer Center</t>
+          <t>Harvard Medical School</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>Indonesian Ministry of Health and RS Kanker Dharmais</t>
+          <t>Universitas Harkat Negeri and CISDI (Primary Healthcare Impact Lab)</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>MD Anderson Cancer Center Project NOTRE (Indonesia Breast Cancer ECHO)</t>
-        </is>
-      </c>
-      <c r="D179" s="5" t="inlineStr">
-        <is>
-          <t>2025-06-20</t>
-        </is>
-      </c>
+          <t>CISDI Primary Healthcare IMPACT Lab</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="inlineStr"/>
       <c r="E179" s="5" t="inlineStr">
         <is>
-          <t>https://knowledge-action-portal.com/en/content/project-notre-indonesia-breast-cancer-echo-jun-14-2025-0300-pm-eest</t>
+          <t>https://cisdi.org/en/our-works/phcimpactlab</t>
         </is>
       </c>
     </row>
@@ -12720,17 +12720,17 @@
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>MD Anderson Cancer Center MD Anderson announces new collaboration in Indonesia to reduce global cancer burden</t>
+          <t>MD Anderson Cancer Center Project NOTRE (Indonesia Breast Cancer ECHO)</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>2023-02-03</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>https://www.mdanderson.org/newsroom/md-anderson-announces-new-collaboration-in-indonesia.h00-159616278.html</t>
+          <t>https://knowledge-action-portal.com/en/content/project-notre-indonesia-breast-cancer-echo-jun-14-2025-0300-pm-eest</t>
         </is>
       </c>
     </row>
@@ -12747,7 +12747,7 @@
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>Kementerian Kesehatan RI Kemenkes dan MD Anderson Cancer Center Jalin Kerja Sama Atasi Kanker</t>
+          <t>MD Anderson Cancer Center MD Anderson announces new collaboration in Indonesia to reduce global cancer burden</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
@@ -12757,7 +12757,7 @@
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>https://www.kemkes.go.id/eng/kemenkes-dan-md-anderson-cancer-center-jalin-kerja-sama-atasi-kanker</t>
+          <t>https://www.mdanderson.org/newsroom/md-anderson-announces-new-collaboration-in-indonesia.h00-159616278.html</t>
         </is>
       </c>
     </row>
@@ -12769,49 +12769,49 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>MRCCC Siloam Semanggi (Siloam Hospitals)</t>
+          <t>Indonesian Ministry of Health and RS Kanker Dharmais</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>Kontan Kesenjangan Layanan Kanker di Indonesia, MRCCC Siloam Menggandeng MD Anderson</t>
+          <t>Kementerian Kesehatan RI Kemenkes dan MD Anderson Cancer Center Jalin Kerja Sama Atasi Kanker</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2023-02-03</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>https://industri.kontan.co.id/news/kesenjangan-layanan-kanker-di-indonesia-mrccc-siloam-menggandeng-md-anderson</t>
+          <t>https://www.kemkes.go.id/eng/kemenkes-dan-md-anderson-cancer-center-jalin-kerja-sama-atasi-kanker</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>MD Anderson Cancer Center</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>IHC Rumah Sakit Pusat Pertamina (RSPP)</t>
+          <t>MRCCC Siloam Semanggi (Siloam Hospitals)</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>RS Pusat Pertamina Learning from the Best: IHC RSPP Endocrinologist Gains Insights into Innovative Medical Practices firsthand at Mayo Clinic's campus in Jacksonville, Florida</t>
+          <t>Kontan Kesenjangan Layanan Kanker di Indonesia, MRCCC Siloam Menggandeng MD Anderson</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>https://rspp.co.id/artikel-detail-597-Learning-from-the-Best-IHC-RSPP-Endocrinologist-Gains-Insights-into-Innovative-Medical-Practices-firsthand-at-Mayo-Clinic’s-campus-in-Jacksonville,-Florida-.html</t>
+          <t>https://industri.kontan.co.id/news/kesenjangan-layanan-kanker-di-indonesia-mrccc-siloam-menggandeng-md-anderson</t>
         </is>
       </c>
     </row>
@@ -12828,17 +12828,17 @@
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic News Network IHC Rumah Sakit Pusat Pertamina in Indonesia joins Mayo Clinic Care Network</t>
+          <t>RS Pusat Pertamina Learning from the Best: IHC RSPP Endocrinologist Gains Insights into Innovative Medical Practices firsthand at Mayo Clinic's campus in Jacksonville, Florida</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>https://newsnetwork.mayoclinic.org/discussion/ihc-rumah-sakit-pusat-pertamina-in-indonesia-joins-mayo-clinic-care-network</t>
+          <t>https://rspp.co.id/artikel-detail-597-Learning-from-the-Best-IHC-RSPP-Endocrinologist-Gains-Insights-into-Innovative-Medical-Practices-firsthand-at-Mayo-Clinic’s-campus-in-Jacksonville,-Florida-.html</t>
         </is>
       </c>
     </row>
@@ -12855,44 +12855,44 @@
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>RS Pusat Pertamina RSPP Gains Insight from Mayo Clinic for Outpatient Chemotherapy Unit</t>
+          <t>Mayo Clinic News Network IHC Rumah Sakit Pusat Pertamina in Indonesia joins Mayo Clinic Care Network</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2023-01-26</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
         <is>
-          <t>https://rspp.co.id/artikel-detail-210-Rumah-Sakit-Pusat-Pertamina-(RSPP)-Gains-Insight-from-Mayo-Clinic-for-Outpatient-Chemotherapy-Unit-.html</t>
+          <t>https://newsnetwork.mayoclinic.org/discussion/ihc-rumah-sakit-pusat-pertamina-in-indonesia-joins-mayo-clinic-care-network</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>RSUPN Dr. Cipto Mangunkusumo (RSCM) and Indonesian Ministry of Health</t>
+          <t>IHC Rumah Sakit Pusat Pertamina (RSPP)</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>Kementerian Kesehatan RI (Ditjen Kesehatan Lanjutan) RSUPN Dr Cipto Mangunkusumo Mendapat Kunjungan dari St Jude Global Asia Pacific Regional Untuk Perkuat Kolaborasi Kanker Anak</t>
+          <t>RS Pusat Pertamina RSPP Gains Insight from Mayo Clinic for Outpatient Chemotherapy Unit</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>https://keslan.kemkes.go.id/view_foto/554</t>
+          <t>https://rspp.co.id/artikel-detail-210-Rumah-Sakit-Pusat-Pertamina-(RSPP)-Gains-Insight-from-Mayo-Clinic-for-Outpatient-Chemotherapy-Unit-.html</t>
         </is>
       </c>
     </row>
@@ -12909,44 +12909,44 @@
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital St. Jude Global and Indonesian stakeholders unite for first-ever national childhood cancer policy planning</t>
+          <t>Kementerian Kesehatan RI (Ditjen Kesehatan Lanjutan) RSUPN Dr Cipto Mangunkusumo Mendapat Kunjungan dari St Jude Global Asia Pacific Regional Untuk Perkuat Kolaborasi Kanker Anak</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>https://stjude.org/research/progress/2024/st-jude-global-and-indonesian-stakeholders-unite-for-first-ever-national-childhood-cancer-policy-planning.html</t>
+          <t>https://keslan.kemkes.go.id/view_foto/554</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
         <is>
-          <t>Apollo Hospitals</t>
+          <t>St. Jude Children's Research Hospital</t>
         </is>
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>Mayapada Healthcare Group (Mayapada Hospital)</t>
+          <t>RSUPN Dr. Cipto Mangunkusumo (RSCM) and Indonesian Ministry of Health</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>JawaPos Perkuat kolaborasi lintas negara, Mayapada Healthcare yakin bisa kurangi orang berobat ke luar negeri</t>
+          <t>St. Jude Children's Research Hospital St. Jude Global and Indonesian stakeholders unite for first-ever national childhood cancer policy planning</t>
         </is>
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>https://www.jawapos.com/kesehatan/2601230030/perkuat-kolaborasi-lintas-negara-mayapada-healthcare-yakin-bisa-kurangi-orang-berobat-ke-luar-negeri</t>
+          <t>https://stjude.org/research/progress/2024/st-jude-global-and-indonesian-stakeholders-unite-for-first-ever-national-childhood-cancer-policy-planning.html</t>
         </is>
       </c>
     </row>
@@ -12963,17 +12963,17 @@
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>Detik Health Kolaborasi Klinis Mayapada Healthcare &amp; Apollo Hospitals India Kian Matang</t>
+          <t>JawaPos Perkuat kolaborasi lintas negara, Mayapada Healthcare yakin bisa kurangi orang berobat ke luar negeri</t>
         </is>
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>https://health.detik.com/berita-detikhealth/d-8316666/kolaborasi-klinis-mayapada-healthcare-apollo-hospitals-india-kian-matang</t>
+          <t>https://www.jawapos.com/kesehatan/2601230030/perkuat-kolaborasi-lintas-negara-mayapada-healthcare-yakin-bisa-kurangi-orang-berobat-ke-luar-negeri</t>
         </is>
       </c>
     </row>
@@ -12990,44 +12990,44 @@
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>Investortrust Mayapada Healthcare Partners with India's Apollo Hospitals to Curb Medical Tourism</t>
+          <t>Detik Health Kolaborasi Klinis Mayapada Healthcare &amp; Apollo Hospitals India Kian Matang</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>https://investortrust.id/business/54719/mayapada-healthcare-partners-with-indias-apollo-hospitals-to-curb-medical-tourism</t>
+          <t>https://health.detik.com/berita-detikhealth/d-8316666/kolaborasi-klinis-mayapada-healthcare-apollo-hospitals-india-kian-matang</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>Asia OneHealthcare (A1Health, formerly Columbia Asia Healthcare)</t>
+          <t>Apollo Hospitals</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>RS Premier Jatinegara, Bintaro and Surabaya and Columbia Asia hospitals</t>
+          <t>Mayapada Healthcare Group (Mayapada Hospital)</t>
         </is>
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>The Edge Malaysia Weekly Bankers court A1Health for possible IPO</t>
+          <t>Investortrust Mayapada Healthcare Partners with India's Apollo Hospitals to Curb Medical Tourism</t>
         </is>
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E191" s="5" t="inlineStr">
         <is>
-          <t>https://theedgemalaysia.com/node/791491</t>
+          <t>https://investortrust.id/business/54719/mayapada-healthcare-partners-with-indias-apollo-hospitals-to-curb-medical-tourism</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>The Edge Malaysia Columbia Asia Healthcare renamed Asia OneHealthcare (A1Health) after consolidating assets in Malaysia, Indonesia and Vietnam</t>
+          <t>The Edge Malaysia Weekly Bankers court A1Health for possible IPO</t>
         </is>
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>https://theedgemalaysia.com/node/725855</t>
+          <t>https://theedgemalaysia.com/node/791491</t>
         </is>
       </c>
     </row>
@@ -13071,71 +13071,71 @@
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>Vina Elvira, Kontan Rumah Sakit Internasional Columbia Asia Resmi Akuisisi RS Medika BSD</t>
+          <t>The Edge Malaysia Columbia Asia Healthcare renamed Asia OneHealthcare (A1Health) after consolidating assets in Malaysia, Indonesia and Vietnam</t>
         </is>
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="E193" s="5" t="inlineStr">
         <is>
-          <t>https://industri.kontan.co.id/news/rumah-sakit-internasional-columbia-asia-resmi-akuisisi-rs-medika-bsd</t>
+          <t>https://theedgemalaysia.com/node/725855</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
         <is>
-          <t>Chung Shan Medical University (Taiwan)</t>
+          <t>Asia OneHealthcare (A1Health, formerly Columbia Asia Healthcare)</t>
         </is>
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>Universitas Indonesia</t>
+          <t>RS Premier Jatinegara, Bintaro and Surabaya and Columbia Asia hospitals</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>CSMU Chung Shan Medical University Signs MOU with Universitas Indonesia to Advance Comprehensive Collaboration</t>
+          <t>Vina Elvira, Kontan Rumah Sakit Internasional Columbia Asia Resmi Akuisisi RS Medika BSD</t>
         </is>
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>https://pr.csmu.edu.tw/p/16-1024-71677.php?Lang=zh-tw</t>
+          <t>https://industri.kontan.co.id/news/rumah-sakit-internasional-columbia-asia-resmi-akuisisi-rs-medika-bsd</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>Hong Kong Asia Medical Group (HKAMG)</t>
+          <t>Chung Shan Medical University (Taiwan)</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>Bali International Hospital (PT Pertamedika Bali Hospital, IHC)</t>
+          <t>Universitas Indonesia</t>
         </is>
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>Ni Putu Putri Muliantari, ANTARA Akhirnya ada prosedur TAVI di KEK Sanur untuk tangani kasus jantung</t>
+          <t>CSMU Chung Shan Medical University Signs MOU with Universitas Indonesia to Advance Comprehensive Collaboration</t>
         </is>
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="E195" s="5" t="inlineStr">
         <is>
-          <t>https://bali.antaranews.com/berita/400683/akhirnya-ada-prosedur-tavi-di-kek-sanur-untuk-tangani-kasus-jantung</t>
+          <t>https://pr.csmu.edu.tw/p/16-1024-71677.php?Lang=zh-tw</t>
         </is>
       </c>
     </row>
@@ -13152,17 +13152,17 @@
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>Bali International Hospital (press release) Bali International Hospital Hosts Meet &amp; Greet with Global Medical Partners</t>
+          <t>Ni Putu Putri Muliantari, ANTARA Akhirnya ada prosedur TAVI di KEK Sanur untuk tangani kasus jantung</t>
         </is>
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>https://bali.com/news/press-releases/bali-international-hospital-hosts-meet-greet-with-global-medical-partners</t>
+          <t>https://bali.antaranews.com/berita/400683/akhirnya-ada-prosedur-tavi-di-kek-sanur-untuk-tangani-kasus-jantung</t>
         </is>
       </c>
     </row>
@@ -13179,40 +13179,40 @@
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>International Finance Corporation Asia Heart project (Hong Kong Asia Medical Holding and Wuhan Asia Heart Hospital)</t>
-        </is>
-      </c>
-      <c r="D197" s="5" t="inlineStr"/>
+          <t>Bali International Hospital (press release) Bali International Hospital Hosts Meet &amp; Greet with Global Medical Partners</t>
+        </is>
+      </c>
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
       <c r="E197" s="5" t="inlineStr">
         <is>
-          <t>https://disclosures.ifc.org/project-detail/SII/33623/asia-heart-project</t>
+          <t>https://bali.com/news/press-releases/bali-international-hospital-hosts-meet-greet-with-global-medical-partners</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
         <is>
-          <t>Icon Group (Icon Cancer Centre)</t>
+          <t>Hong Kong Asia Medical Group (HKAMG)</t>
         </is>
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>Bali International Hospital (PT Pertamina Bina Medika IHC)</t>
+          <t>Bali International Hospital (PT Pertamedika Bali Hospital, IHC)</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>Icon Writers Icon Cancer Centre at Bali International Hospital marks regional first with advanced radiotherapy cancer treatments</t>
-        </is>
-      </c>
-      <c r="D198" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
+          <t>International Finance Corporation Asia Heart project (Hong Kong Asia Medical Holding and Wuhan Asia Heart Hospital)</t>
+        </is>
+      </c>
+      <c r="D198" s="5" t="inlineStr"/>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>https://icongroup.global/?p=18098</t>
+          <t>https://disclosures.ifc.org/project-detail/SII/33623/asia-heart-project</t>
         </is>
       </c>
     </row>
@@ -13229,17 +13229,17 @@
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>Icon Writers Icon Cancer Centre Bali treats first patient</t>
+          <t>Icon Writers Icon Cancer Centre at Bali International Hospital marks regional first with advanced radiotherapy cancer treatments</t>
         </is>
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
         <is>
-          <t>https://icongroup.global/en/news/2025-05-07/icon-cancer-centre-bali-treats-first-patient/</t>
+          <t>https://icongroup.global/?p=18098</t>
         </is>
       </c>
     </row>
@@ -13256,44 +13256,44 @@
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>Icon Group Icon Group, Bali International Hospital partnership to deliver exceptional cancer care</t>
+          <t>Icon Writers Icon Cancer Centre Bali treats first patient</t>
         </is>
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>https://icongroup.global/en/news/2025-03-04/icon-group-and-bali-international-hospital/</t>
+          <t>https://icongroup.global/en/news/2025-05-07/icon-cancer-centre-bali-treats-first-patient/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>International University of Health and Welfare (IUHW)</t>
+          <t>Icon Group (Icon Cancer Centre)</t>
         </is>
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>Ministry of Health (Kemenkes)</t>
+          <t>Bali International Hospital (PT Pertamina Bina Medika IHC)</t>
         </is>
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>Ministry of Health of Indonesia Kemenkes dan IUHW Jepang Kerja Sama Perkuat Pendidikan Dokter Spesialis</t>
+          <t>Icon Group Icon Group, Bali International Hospital partnership to deliver exceptional cancer care</t>
         </is>
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
         <is>
-          <t>https://kemkes.go.id/id/kemenkes-dan-iuhw-jepang-kerja-sama-perkuat-pendidikan-dokter-spesialis</t>
+          <t>https://icongroup.global/en/news/2025-03-04/icon-group-and-bali-international-hospital/</t>
         </is>
       </c>
     </row>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>RRI Indonesia and Japan Expand Cooperation in Specialist Medical Education</t>
+          <t>Ministry of Health of Indonesia Kemenkes dan IUHW Jepang Kerja Sama Perkuat Pendidikan Dokter Spesialis</t>
         </is>
       </c>
       <c r="D202" s="5" t="inlineStr">
@@ -13320,34 +13320,34 @@
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>https://rri.co.id/en/education/2332993/indonesia-and-japan-expand-cooperation-in-specialist-medical-education</t>
+          <t>https://kemkes.go.id/id/kemenkes-dan-iuhw-jepang-kerja-sama-perkuat-pendidikan-dokter-spesialis</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
         <is>
-          <t>Monash Health</t>
+          <t>International University of Health and Welfare (IUHW)</t>
         </is>
       </c>
       <c r="B203" s="5" t="inlineStr">
         <is>
-          <t>RS Otak Dr. Drs. M. Hatta Bukittinggi (RSOMH, Ministry of Health brain hospital)</t>
+          <t>Ministry of Health (Kemenkes)</t>
         </is>
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>Humas RSOMH Bukittinggi RSOMH Bukittinggi dan Monash Health Perkuat Kolaborasi Pengembangan Rehabilitasi Stroke</t>
+          <t>RRI Indonesia and Japan Expand Cooperation in Specialist Medical Education</t>
         </is>
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
         <is>
-          <t>https://keslan.kemkes.go.id/read/4058/rsomh-bukittinggi-dan-monash-health-perkuat-kolaborasi-pengembangan-rehabilitasi-stroke</t>
+          <t>https://rri.co.id/en/education/2332993/indonesia-and-japan-expand-cooperation-in-specialist-medical-education</t>
         </is>
       </c>
     </row>
@@ -13364,98 +13364,98 @@
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>Humas RSOMH Bukittinggi RSOMH Bukittinggi Dukung Rencana Program Kerja Sama Bersama Monash Health</t>
+          <t>Humas RSOMH Bukittinggi RSOMH Bukittinggi dan Monash Health Perkuat Kolaborasi Pengembangan Rehabilitasi Stroke</t>
         </is>
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>https://keslan.kemkes.go.id/read/4358/rsomh-bukittinggi-dukung-rencana-program-kerja-sama-bersama-monash-health</t>
+          <t>https://keslan.kemkes.go.id/read/4058/rsomh-bukittinggi-dan-monash-health-perkuat-kolaborasi-pengembangan-rehabilitasi-stroke</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
         <is>
-          <t>National Center for Global Health and Medicine (NCGM) and Kobe University</t>
+          <t>Monash Health</t>
         </is>
       </c>
       <c r="B205" s="5" t="inlineStr">
         <is>
-          <t>Universitas Airlangga (Institute of Tropical Disease and RS Universitas Airlangga)</t>
+          <t>RS Otak Dr. Drs. M. Hatta Bukittinggi (RSOMH, Ministry of Health brain hospital)</t>
         </is>
       </c>
       <c r="C205" s="5" t="inlineStr">
         <is>
-          <t>UNAIR News Japanese delegation visits UNAIR Hospital to strengthen research and innovation collaboration</t>
+          <t>Humas RSOMH Bukittinggi RSOMH Bukittinggi Dukung Rencana Program Kerja Sama Bersama Monash Health</t>
         </is>
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
         <is>
-          <t>https://unair.ac.id/en/japanese-delegation-visits-unair-hospital-to-strengthen-research-and-innovation-collaboration/</t>
+          <t>https://keslan.kemkes.go.id/read/4358/rsomh-bukittinggi-dukung-rencana-program-kerja-sama-bersama-monash-health</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
         <is>
-          <t>Ramathibodi Hospital, Mahidol University</t>
+          <t>National Center for Global Health and Medicine (NCGM) and Kobe University</t>
         </is>
       </c>
       <c r="B206" s="5" t="inlineStr">
         <is>
-          <t>Faculty of Medicine Universitas Indonesia and RSCM</t>
+          <t>Universitas Airlangga (Institute of Tropical Disease and RS Universitas Airlangga)</t>
         </is>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>Ramathibodi International Office Ramathibodi Hospital and Universitas Indonesia Strengthen Medical Ties with MOU Signing</t>
+          <t>UNAIR News Japanese delegation visits UNAIR Hospital to strengthen research and innovation collaboration</t>
         </is>
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>https://www.rama.mahidol.ac.th/international/news/event/22052025-1111</t>
+          <t>https://unair.ac.id/en/japanese-delegation-visits-unair-hospital-to-strengthen-research-and-innovation-collaboration/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
         <is>
-          <t>Sapporo Cardio Vascular Clinic</t>
+          <t>Ramathibodi Hospital, Mahidol University</t>
         </is>
       </c>
       <c r="B207" s="5" t="inlineStr">
         <is>
-          <t>Bali International Hospital (PT Pertamedika Bali Hospital, IHC)</t>
+          <t>Faculty of Medicine Universitas Indonesia and RSCM</t>
         </is>
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>Mardiana Makmun, Investor Daily Teknologi TAVI Tangani Penyakit Katup Jantung</t>
+          <t>Ramathibodi International Office Ramathibodi Hospital and Universitas Indonesia Strengthen Medical Ties with MOU Signing</t>
         </is>
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="E207" s="5" t="inlineStr">
         <is>
-          <t>https://investor.id/lifestyle/432385/teknologi-tavi-tangani-penyakit-katup-jantung</t>
+          <t>https://www.rama.mahidol.ac.th/international/news/event/22052025-1111</t>
         </is>
       </c>
     </row>
@@ -13472,17 +13472,17 @@
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>Bali International Hospital (press release) Bali International Hospital Hosts Meet &amp; Greet with Global Medical Partners</t>
+          <t>Mardiana Makmun, Investor Daily Teknologi TAVI Tangani Penyakit Katup Jantung</t>
         </is>
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>https://bali.com/news/press-releases/bali-international-hospital-hosts-meet-greet-with-global-medical-partners</t>
+          <t>https://investor.id/lifestyle/432385/teknologi-tavi-tangani-penyakit-katup-jantung</t>
         </is>
       </c>
     </row>
@@ -13499,44 +13499,44 @@
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>Ministry of Health of Indonesia Atasi Kekurangan Dokter Spesialis, Kemenkes Berangkatkan 27 Dokter Belajar ke RRT dan Jepang</t>
+          <t>Bali International Hospital (press release) Bali International Hospital Hosts Meet &amp; Greet with Global Medical Partners</t>
         </is>
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E209" s="5" t="inlineStr">
         <is>
-          <t>https://kemkes.go.id/eng/atasi-kekurangan-dokter-spesialis-kemenkes-berangkatkan-27-dokter-belajar-ke-rrt-dan-jepang</t>
+          <t>https://bali.com/news/press-releases/bali-international-hospital-hosts-meet-greet-with-global-medical-partners</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
         <is>
-          <t>Seoul National University Hospital (SNUH)</t>
+          <t>Sapporo Cardio Vascular Clinic</t>
         </is>
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>Faculty of Medicine Universitas Indonesia and RSUPN Dr. Cipto Mangunkusumo (RSCM)</t>
+          <t>Bali International Hospital (PT Pertamedika Bali Hospital, IHC)</t>
         </is>
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>Noh Jae-young, Medipharm Health 서울대병원-인도네시아 의대-RSCM 병원 간 AOI 체결</t>
+          <t>Ministry of Health of Indonesia Atasi Kekurangan Dokter Spesialis, Kemenkes Berangkatkan 27 Dokter Belajar ke RRT dan Jepang</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>https://medipharmhealth.co.kr/news/article.html?no=105006</t>
+          <t>https://kemkes.go.id/eng/atasi-kekurangan-dokter-spesialis-kemenkes-berangkatkan-27-dokter-belajar-ke-rrt-dan-jepang</t>
         </is>
       </c>
     </row>
@@ -13548,22 +13548,22 @@
       </c>
       <c r="B211" s="5" t="inlineStr">
         <is>
-          <t>RSUP Fatmawati (Ministry of Health hospital)</t>
+          <t>Faculty of Medicine Universitas Indonesia and RSUPN Dr. Cipto Mangunkusumo (RSCM)</t>
         </is>
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>Ministry of Health of Indonesia Lakukan Transplantasi Hati Ketiga RSUP Fatmawati Perkuat Kemandirian Layanan Dalam Negeri</t>
+          <t>Noh Jae-young, Medipharm Health 서울대병원-인도네시아 의대-RSCM 병원 간 AOI 체결</t>
         </is>
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="E211" s="5" t="inlineStr">
         <is>
-          <t>https://www.kemkes.go.id/eng/lakukan-transplantasi-hati-ketiga-rsup-fatmawati-perkuat-kemandirian-layanan-dalam-negeri</t>
+          <t>https://medipharmhealth.co.kr/news/article.html?no=105006</t>
         </is>
       </c>
     </row>
@@ -13580,44 +13580,44 @@
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>Ministry of Health of Indonesia Kerja Sama Indonesia-Korea Dukung Implementasi Transformasi Kesehatan</t>
+          <t>Ministry of Health of Indonesia Lakukan Transplantasi Hati Ketiga RSUP Fatmawati Perkuat Kemandirian Layanan Dalam Negeri</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>2023-03-27</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
         <is>
-          <t>https://www.kemkes.go.id/eng/kerja-sama-indonesia-korea-dukung-implementasi-transformasi-kesehatan</t>
+          <t>https://www.kemkes.go.id/eng/lakukan-transplantasi-hati-ketiga-rsup-fatmawati-perkuat-kemandirian-layanan-dalam-negeri</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
         <is>
-          <t>SingHealth</t>
+          <t>Seoul National University Hospital (SNUH)</t>
         </is>
       </c>
       <c r="B213" s="5" t="inlineStr">
         <is>
-          <t>Indonesia Healthcare Corporation (PT Pertamina Bina Medika) and Bali International Hospital</t>
+          <t>RSUP Fatmawati (Ministry of Health hospital)</t>
         </is>
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>Bali International Hospital (press release) Bali International Hospital Hosts Meet &amp; Greet with Global Medical Partners</t>
+          <t>Ministry of Health of Indonesia Kerja Sama Indonesia-Korea Dukung Implementasi Transformasi Kesehatan</t>
         </is>
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2023-03-27</t>
         </is>
       </c>
       <c r="E213" s="5" t="inlineStr">
         <is>
-          <t>https://bali.com/news/press-releases/bali-international-hospital-hosts-meet-greet-with-global-medical-partners</t>
+          <t>https://www.kemkes.go.id/eng/kerja-sama-indonesia-korea-dukung-implementasi-transformasi-kesehatan</t>
         </is>
       </c>
     </row>
@@ -13634,17 +13634,17 @@
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>Indonesia Business Post IHC, Singhealth seals deal collaboration to improve patient care</t>
+          <t>Bali International Hospital (press release) Bali International Hospital Hosts Meet &amp; Greet with Global Medical Partners</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
         <is>
-          <t>https://indonesiabusinesspost.com/1823/Politics/ihc-singhealth-seals-deal-collaboration-to-improve-patient-care</t>
+          <t>https://bali.com/news/press-releases/bali-international-hospital-hosts-meet-greet-with-global-medical-partners</t>
         </is>
       </c>
     </row>
@@ -13661,7 +13661,7 @@
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>Pertamina Pertamina Bina Medika IHC and SingHealth collaborate to enhance healthcare services</t>
+          <t>Indonesia Business Post IHC, Singhealth seals deal collaboration to improve patient care</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
@@ -13671,34 +13671,34 @@
       </c>
       <c r="E215" s="5" t="inlineStr">
         <is>
-          <t>https://pertamina.com/en/news-room/news-release/pertamina-bina-medika-ihc-and-singhealth-collaborate-to-enhance-healthcare-services</t>
+          <t>https://indonesiabusinesspost.com/1823/Politics/ihc-singhealth-seals-deal-collaboration-to-improve-patient-care</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
         <is>
-          <t>SingHealth Duke-NUS Global Health Institute (SingHealth and Duke-NUS Medical School)</t>
+          <t>SingHealth</t>
         </is>
       </c>
       <c r="B216" s="5" t="inlineStr">
         <is>
-          <t>Universitas Sumatera Utara (Faculty of Medicine)</t>
+          <t>Indonesia Healthcare Corporation (PT Pertamina Bina Medika) and Bali International Hospital</t>
         </is>
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>Universitas Sumatera Utara Collaboration between the Faculty of Medicine, Universitas Sumatera Utara (USU) and SingHealth Duke-NUS Global Health Institute on the 2025 Summer Course</t>
+          <t>Pertamina Pertamina Bina Medika IHC and SingHealth collaborate to enhance healthcare services</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
         <is>
-          <t>https://www.usu.ac.id/en/news/collaboration-between-the-faculty-of-medicine-universitas-sumatera-utara-usu-and-singhealth-duke-nus-global-health-institute-on-the-2025-summer-course</t>
+          <t>https://pertamina.com/en/news-room/news-release/pertamina-bina-medika-ihc-and-singhealth-collaborate-to-enhance-healthcare-services</t>
         </is>
       </c>
     </row>
@@ -13715,44 +13715,44 @@
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>Universitas Sumatera Utara USU-Duke NUS Global Health Strengthen Partnerships</t>
+          <t>Universitas Sumatera Utara Collaboration between the Faculty of Medicine, Universitas Sumatera Utara (USU) and SingHealth Duke-NUS Global Health Institute on the 2025 Summer Course</t>
         </is>
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E217" s="5" t="inlineStr">
         <is>
-          <t>https://www.usu.ac.id/en/news/usu-duke-nus-global-health-strengthen-partnerships</t>
+          <t>https://www.usu.ac.id/en/news/collaboration-between-the-faculty-of-medicine-universitas-sumatera-utara-usu-and-singhealth-duke-nus-global-health-institute-on-the-2025-summer-course</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
         <is>
-          <t>Sun Medical Center (Sun Healthcare International)</t>
+          <t>SingHealth Duke-NUS Global Health Institute (SingHealth and Duke-NUS Medical School)</t>
         </is>
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>RSUP Prof. Dr. I.G.N.G. Ngoerah</t>
+          <t>Universitas Sumatera Utara (Faculty of Medicine)</t>
         </is>
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>Benedikta Desideria, Liputan6 Dorong Wisata Medis Bali, Menkes Budi: Jangan Pilih yang Kuratif tapi Wellness</t>
+          <t>Universitas Sumatera Utara USU-Duke NUS Global Health Strengthen Partnerships</t>
         </is>
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
         <is>
-          <t>https://www.liputan6.com/health/read/5731675/dorong-wisata-medis-bali-menkes-budi-jangan-pilih-yang-kuratif-tapi-wellness</t>
+          <t>https://www.usu.ac.id/en/news/usu-duke-nus-global-health-strengthen-partnerships</t>
         </is>
       </c>
     </row>
@@ -13769,71 +13769,71 @@
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>Ministry of Health of Indonesia Kerja Sama Indonesia-Korea Dukung Implementasi Transformasi Kesehatan</t>
+          <t>Benedikta Desideria, Liputan6 Dorong Wisata Medis Bali, Menkes Budi: Jangan Pilih yang Kuratif tapi Wellness</t>
         </is>
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>2023-03-27</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="E219" s="5" t="inlineStr">
         <is>
-          <t>https://www.kemkes.go.id/eng/kerja-sama-indonesia-korea-dukung-implementasi-transformasi-kesehatan</t>
+          <t>https://www.liputan6.com/health/read/5731675/dorong-wisata-medis-bali-menkes-budi-jangan-pilih-yang-kuratif-tapi-wellness</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
         <is>
-          <t>Taipei Veterans General Hospital</t>
+          <t>Sun Medical Center (Sun Healthcare International)</t>
         </is>
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>DKH Hospitals Group</t>
+          <t>RSUP Prof. Dr. I.G.N.G. Ngoerah</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>Antara DKH Hospitals dan TVGH teken MoU tingkatkan layanan kesehatan di RI</t>
+          <t>Ministry of Health of Indonesia Kerja Sama Indonesia-Korea Dukung Implementasi Transformasi Kesehatan</t>
         </is>
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2023-03-27</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/4853713/dkh-hospitals-dan-tvgh-teken-mou-tingkatkan-layanan-kesehatan-di-ri</t>
+          <t>https://www.kemkes.go.id/eng/kerja-sama-indonesia-korea-dukung-implementasi-transformasi-kesehatan</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
         <is>
-          <t>Tokushukai Medical Group</t>
+          <t>Taipei Veterans General Hospital</t>
         </is>
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>RSJPD Harapan Kita (National Heart Center) and Ministry of Health</t>
+          <t>DKH Hospitals Group</t>
         </is>
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>Ministry of Health of Indonesia Perkuat Layanan Jantung Berkelas Dunia di Indonesia, Gedung Baru RS Harkit Resmi Topping Off</t>
+          <t>Antara DKH Hospitals dan TVGH teken MoU tingkatkan layanan kesehatan di RI</t>
         </is>
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="E221" s="5" t="inlineStr">
         <is>
-          <t>https://www.kemkes.go.id/eng/perkuat-layanan-jantung-berkelas-dunia-di-indonesia-gedung-baru-rs-harkit-resmi-topping-off</t>
+          <t>https://www.antaranews.com/berita/4853713/dkh-hospitals-dan-tvgh-teken-mou-tingkatkan-layanan-kesehatan-di-ri</t>
         </is>
       </c>
     </row>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>Antara Indonesia, Japan back Harapan Kita as Asia's biggest cardiac hub</t>
+          <t>Ministry of Health of Indonesia Perkuat Layanan Jantung Berkelas Dunia di Indonesia, Gedung Baru RS Harkit Resmi Topping Off</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="E222" s="5" t="inlineStr">
         <is>
-          <t>https://en.antaranews.com/news/412388/indonesia-japan-back-harapan-kita-as-asias-biggest-cardiac-hub</t>
+          <t>https://www.kemkes.go.id/eng/perkuat-layanan-jantung-berkelas-dunia-di-indonesia-gedung-baru-rs-harkit-resmi-topping-off</t>
         </is>
       </c>
     </row>
@@ -13877,51 +13877,51 @@
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>SSEK SSEK Acts for Tokushukai Medical Corporation Group in Major Cooperation Project in Indonesian Health Sector</t>
+          <t>Antara Indonesia, Japan back Harapan Kita as Asia's biggest cardiac hub</t>
         </is>
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>2023-12-11</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E223" s="5" t="inlineStr">
         <is>
-          <t>https://ssek.com/blog/ssek-acts-for-tokushukai-medical-corporation-group-in-major-cooperation-project-in-indonesian-health-sector/?lang=id</t>
+          <t>https://en.antaranews.com/news/412388/indonesia-japan-back-harapan-kita-as-asias-biggest-cardiac-hub</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
         <is>
-          <t>Wuhan Asia Heart Hospital</t>
+          <t>Tokushukai Medical Group</t>
         </is>
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
-          <t>Ministry of Health (Kemenkes)</t>
+          <t>RSJPD Harapan Kita (National Heart Center) and Ministry of Health</t>
         </is>
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>Ministry of Health of Indonesia Perkuat Layanan Jantung Nasional: 13 Dokter Spesialis Jantung Indonesia Berguru ke Tiongkok</t>
+          <t>SSEK SSEK Acts for Tokushukai Medical Corporation Group in Major Cooperation Project in Indonesian Health Sector</t>
         </is>
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2023-12-11</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
         <is>
-          <t>https://kemkes.go.id/id/perkuat-layanan-jantung-nasional-13-dokter-spesialis-jantung-indonesia-berguru-ke-tiongkok</t>
+          <t>https://ssek.com/blog/ssek-acts-for-tokushukai-medical-corporation-group-in-major-cooperation-project-in-indonesian-health-sector/?lang=id</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
         <is>
-          <t>Zhongda Hospital (Southeast University)</t>
+          <t>Wuhan Asia Heart Hospital</t>
         </is>
       </c>
       <c r="B225" s="5" t="inlineStr">
@@ -13931,24 +13931,24 @@
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>Ministry of Health of Indonesia Atasi Kekurangan Dokter Spesialis, Kemenkes Berangkatkan 27 Dokter Belajar ke RRT dan Jepang</t>
+          <t>Ministry of Health of Indonesia Perkuat Layanan Jantung Nasional: 13 Dokter Spesialis Jantung Indonesia Berguru ke Tiongkok</t>
         </is>
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="E225" s="5" t="inlineStr">
         <is>
-          <t>https://kemkes.go.id/eng/atasi-kekurangan-dokter-spesialis-kemenkes-berangkatkan-27-dokter-belajar-ke-rrt-dan-jepang</t>
+          <t>https://kemkes.go.id/id/perkuat-layanan-jantung-nasional-13-dokter-spesialis-jantung-indonesia-berguru-ke-tiongkok</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="5" t="inlineStr">
         <is>
-          <t>Zhongshan Hospital (Fudan University)</t>
+          <t>Zhongda Hospital (Southeast University)</t>
         </is>
       </c>
       <c r="B226" s="5" t="inlineStr">
@@ -13985,17 +13985,17 @@
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>Ministry of Health of Indonesia Perkuat Layanan Jantung Nasional: 13 Dokter Spesialis Jantung Indonesia Berguru ke Tiongkok</t>
+          <t>Ministry of Health of Indonesia Atasi Kekurangan Dokter Spesialis, Kemenkes Berangkatkan 27 Dokter Belajar ke RRT dan Jepang</t>
         </is>
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="E227" s="5" t="inlineStr">
         <is>
-          <t>https://kemkes.go.id/id/perkuat-layanan-jantung-nasional-13-dokter-spesialis-jantung-indonesia-berguru-ke-tiongkok</t>
+          <t>https://kemkes.go.id/eng/atasi-kekurangan-dokter-spesialis-kemenkes-berangkatkan-27-dokter-belajar-ke-rrt-dan-jepang</t>
         </is>
       </c>
     </row>
@@ -14012,44 +14012,44 @@
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>Kemenkes Kemenkes RI dan RS Rizhao Xinyi Kerja Sama Pelatihan Dokter Kardiovaskular</t>
+          <t>Ministry of Health of Indonesia Perkuat Layanan Jantung Nasional: 13 Dokter Spesialis Jantung Indonesia Berguru ke Tiongkok</t>
         </is>
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
         <is>
-          <t>https://www.kemkes.go.id/eng/kemenkes-ri-dan-rs-rizhao-xinyi-kerja-sama-pelatihan-dokter-kardiovaskular</t>
+          <t>https://kemkes.go.id/id/perkuat-layanan-jantung-nasional-13-dokter-spesialis-jantung-indonesia-berguru-ke-tiongkok</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Zhongshan Hospital (Fudan University)</t>
         </is>
       </c>
       <c r="B229" s="5" t="inlineStr">
         <is>
-          <t>Bali International Hospital (Indonesia Healthcare Corporation)</t>
+          <t>Ministry of Health (Kemenkes)</t>
         </is>
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>The Jakarta Post Mayo Clinic only acting as consultant for Bali International Hospital, executive says</t>
+          <t>Kemenkes Kemenkes RI dan RS Rizhao Xinyi Kerja Sama Pelatihan Dokter Kardiovaskular</t>
         </is>
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>2023-03-17</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="E229" s="5" t="inlineStr">
         <is>
-          <t>https://www.thejakartapost.com/business/2023/03/17/mayo-clinic-only-acting-as-consultant-for-bali-international-hospital-executive-says</t>
+          <t>https://www.kemkes.go.id/eng/kemenkes-ri-dan-rs-rizhao-xinyi-kerja-sama-pelatihan-dokter-kardiovaskular</t>
         </is>
       </c>
     </row>
@@ -14066,17 +14066,17 @@
       </c>
       <c r="C230" s="5" t="inlineStr">
         <is>
-          <t>Becker's Hospital Review Mayo Clinic to advise on building, operating hospital in Indonesia</t>
+          <t>The Jakarta Post Mayo Clinic only acting as consultant for Bali International Hospital, executive says</t>
         </is>
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>2021-12</t>
+          <t>2023-03-17</t>
         </is>
       </c>
       <c r="E230" s="5" t="inlineStr">
         <is>
-          <t>https://www.beckershospitalreview.com/capital/mayo-clinic-to-help-build-operate-hospital-in-indonesia/</t>
+          <t>https://www.thejakartapost.com/business/2023/03/17/mayo-clinic-only-acting-as-consultant-for-bali-international-hospital-executive-says</t>
         </is>
       </c>
     </row>
@@ -14093,159 +14093,159 @@
       </c>
       <c r="C231" s="5" t="inlineStr">
         <is>
-          <t>Bali International Hospital (press release) Bali International Hospital Hosts Meet &amp; Greet with Global Medical Partners</t>
+          <t>Becker's Hospital Review Mayo Clinic to advise on building, operating hospital in Indonesia</t>
         </is>
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="E231" s="5" t="inlineStr">
         <is>
-          <t>https://bali.com/news/press-releases/bali-international-hospital-hosts-meet-greet-with-global-medical-partners</t>
+          <t>https://www.beckershospitalreview.com/capital/mayo-clinic-to-help-build-operate-hospital-in-indonesia/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="B232" s="5" t="inlineStr">
         <is>
-          <t>RS Jantung dan Pembuluh Darah Harapan Kita</t>
+          <t>Bali International Hospital (Indonesia Healthcare Corporation)</t>
         </is>
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>Kementerian Kesehatan RI Wujudkan Transformasi Layanan Rujukan, RS Jantung Harapan Kita jadi RS Pertama Transplantasi Jantung di Indonesia</t>
+          <t>Bali International Hospital (press release) Bali International Hospital Hosts Meet &amp; Greet with Global Medical Partners</t>
         </is>
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>2022-11-09</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
         <is>
-          <t>https://kemkes.go.id/eng/wujudkan-transformasi-layanan-rujukan-rs-jantung-harapan-kita-jadi-rs-pertama-transplantasi-jantung-di-indonesia</t>
+          <t>https://bali.com/news/press-releases/bali-international-hospital-hosts-meet-greet-with-global-medical-partners</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
         <is>
-          <t>Asan Medical Center</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="B233" s="5" t="inlineStr">
         <is>
-          <t>Siloam Hospitals Group</t>
+          <t>RS Jantung dan Pembuluh Darah Harapan Kita</t>
         </is>
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>Adv Team Grup RS Siloam Jalin Kerja Sama dengan Asan Medical Center Korea Selatan</t>
+          <t>Kementerian Kesehatan RI Wujudkan Transformasi Layanan Rujukan, RS Jantung Harapan Kita jadi RS Pertama Transplantasi Jantung di Indonesia</t>
         </is>
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2022-11-09</t>
         </is>
       </c>
       <c r="E233" s="5" t="inlineStr">
         <is>
-          <t>https://www.kompas.tv/advertorial/457691/grup-rs-siloam-jalin-kerja-sama-dengan-asan-medical-center-korea-selatan</t>
+          <t>https://kemkes.go.id/eng/wujudkan-transformasi-layanan-rujukan-rs-jantung-harapan-kita-jadi-rs-pertama-transplantasi-jantung-di-indonesia</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
         <is>
-          <t>Icon Group (Icon Cancer Centre, Singapore)</t>
+          <t>Asan Medical Center</t>
         </is>
       </c>
       <c r="B234" s="5" t="inlineStr">
         <is>
-          <t>RS Universitas Airlangga (RSUA)</t>
+          <t>Siloam Hospitals Group</t>
         </is>
       </c>
       <c r="C234" s="5" t="inlineStr">
         <is>
-          <t>BioSpectrum Asia Airlangga University Hospital signs MoU with Singapore's Icon Cancer Center</t>
+          <t>Adv Team Grup RS Siloam Jalin Kerja Sama dengan Asan Medical Center Korea Selatan</t>
         </is>
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>2023-04-10</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
         <is>
-          <t>https://www.biospectrumasia.com/news/54/22260/airlangga-university-hospital-signs-mou-with-singapores-icon-cancer-center.html</t>
+          <t>https://www.kompas.tv/advertorial/457691/grup-rs-siloam-jalin-kerja-sama-dengan-asan-medical-center-korea-selatan</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="5" t="inlineStr">
         <is>
-          <t>National Center for Global Health and Medicine (NCGM)</t>
+          <t>Icon Group (Icon Cancer Centre, Singapore)</t>
         </is>
       </c>
       <c r="B235" s="5" t="inlineStr">
         <is>
-          <t>Siloam Hospitals Group</t>
+          <t>RS Universitas Airlangga (RSUA)</t>
         </is>
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>National Center for Global Health and Medicine The National Center for Global Health and Medicine and the Siloam Hospitals Group have signed a Memorandum of Understanding (MoU) for clinical research cooperation</t>
+          <t>BioSpectrum Asia Airlangga University Hospital signs MoU with Singapore's Icon Cancer Center</t>
         </is>
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2023-04-10</t>
         </is>
       </c>
       <c r="E235" s="5" t="inlineStr">
         <is>
-          <t>https://www.ncgm.go.jp/en/news/FY2022/20221007.html</t>
+          <t>https://www.biospectrumasia.com/news/54/22260/airlangga-university-hospital-signs-mou-with-singapores-icon-cancer-center.html</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>Peking Union Medical College Hospital</t>
+          <t>National Center for Global Health and Medicine (NCGM)</t>
         </is>
       </c>
       <c r="B236" s="5" t="inlineStr">
         <is>
-          <t>Ministry of Health (Kemenkes)</t>
+          <t>Siloam Hospitals Group</t>
         </is>
       </c>
       <c r="C236" s="5" t="inlineStr">
         <is>
-          <t>Kemenkes Kemenkes RI dan RS Rizhao Xinyi Kerja Sama Pelatihan Dokter Kardiovaskular</t>
+          <t>National Center for Global Health and Medicine The National Center for Global Health and Medicine and the Siloam Hospitals Group have signed a Memorandum of Understanding (MoU) for clinical research cooperation</t>
         </is>
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="E236" s="5" t="inlineStr">
         <is>
-          <t>https://www.kemkes.go.id/eng/kemenkes-ri-dan-rs-rizhao-xinyi-kerja-sama-pelatihan-dokter-kardiovaskular</t>
+          <t>https://www.ncgm.go.jp/en/news/FY2022/20221007.html</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
         <is>
-          <t>Rizhao Xinyi Hospital (Rizhao Heart Hospital)</t>
+          <t>Peking Union Medical College Hospital</t>
         </is>
       </c>
       <c r="B237" s="5" t="inlineStr">
@@ -14272,27 +14272,27 @@
     <row r="238">
       <c r="A238" s="5" t="inlineStr">
         <is>
-          <t>Royal Brompton and Harefield Hospitals (Guy's and St Thomas' NHS Foundation Trust)</t>
+          <t>Rizhao Xinyi Hospital (Rizhao Heart Hospital)</t>
         </is>
       </c>
       <c r="B238" s="5" t="inlineStr">
         <is>
-          <t>Mandaya Royal Hospital Puri</t>
+          <t>Ministry of Health (Kemenkes)</t>
         </is>
       </c>
       <c r="C238" s="5" t="inlineStr">
         <is>
-          <t>Mandaya Hospital Group Mandaya Royal Hospital Puri and London's Royal Brompton &amp; Harefield Hospitals Announce Strategic Partnership</t>
+          <t>Kemenkes Kemenkes RI dan RS Rizhao Xinyi Kerja Sama Pelatihan Dokter Kardiovaskular</t>
         </is>
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>2020-12-19</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
         <is>
-          <t>https://mandayahospitalgroup.com/?p=11304</t>
+          <t>https://www.kemkes.go.id/eng/kemenkes-ri-dan-rs-rizhao-xinyi-kerja-sama-pelatihan-dokter-kardiovaskular</t>
         </is>
       </c>
     </row>
@@ -14309,71 +14309,71 @@
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>RM.id Gandeng Royal Brompton, Mandaya Hospital resmikan pusat jantung anak</t>
+          <t>Mandaya Hospital Group Mandaya Royal Hospital Puri and London's Royal Brompton &amp; Harefield Hospitals Announce Strategic Partnership</t>
         </is>
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2020-12-19</t>
         </is>
       </c>
       <c r="E239" s="5" t="inlineStr">
         <is>
-          <t>https://rm.id/baca-berita/life-style/172779/gandeng-royal-brompton-mandaya-hospital-resmikan-pusat-jantung-anak</t>
+          <t>https://mandayahospitalgroup.com/?p=11304</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="5" t="inlineStr">
         <is>
-          <t>UMC Utrecht</t>
+          <t>Royal Brompton and Harefield Hospitals (Guy's and St Thomas' NHS Foundation Trust)</t>
         </is>
       </c>
       <c r="B240" s="5" t="inlineStr">
         <is>
-          <t>RS Jantung dan Pembuluh Darah Harapan Kita</t>
+          <t>Mandaya Royal Hospital Puri</t>
         </is>
       </c>
       <c r="C240" s="5" t="inlineStr">
         <is>
-          <t>Ministry of Health of Indonesia Wujudkan Transformasi Layanan Rujukan, RS Jantung Harapan Kita jadi RS Pertama Transplantasi Jantung di Indonesia</t>
+          <t>RM.id Gandeng Royal Brompton, Mandaya Hospital resmikan pusat jantung anak</t>
         </is>
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>2022-11-09</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="E240" s="5" t="inlineStr">
         <is>
-          <t>https://kemkes.go.id/eng/wujudkan-transformasi-layanan-rujukan-rs-jantung-harapan-kita-jadi-rs-pertama-transplantasi-jantung-di-indonesia</t>
+          <t>https://rm.id/baca-berita/life-style/172779/gandeng-royal-brompton-mandaya-hospital-resmikan-pusat-jantung-anak</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
         <is>
-          <t>KPJ Healthcare</t>
+          <t>UMC Utrecht</t>
         </is>
       </c>
       <c r="B241" s="5" t="inlineStr">
         <is>
-          <t>RS Medika BSD</t>
+          <t>RS Jantung dan Pembuluh Darah Harapan Kita</t>
         </is>
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>Warta Ekonomi Ekspansi Besar-besaran, RS Columbia Asia Buka Dua Rumah Sakit dalam Seminggu</t>
+          <t>Ministry of Health of Indonesia Wujudkan Transformasi Layanan Rujukan, RS Jantung Harapan Kita jadi RS Pertama Transplantasi Jantung di Indonesia</t>
         </is>
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2022-11-09</t>
         </is>
       </c>
       <c r="E241" s="5" t="inlineStr">
         <is>
-          <t>https://wartaekonomi.co.id/read515939/ekspansi-besar-besaran-rs-columbia-asia-buka-dua-rumah-sakit-dalam-seminggu</t>
+          <t>https://kemkes.go.id/eng/wujudkan-transformasi-layanan-rujukan-rs-jantung-harapan-kita-jadi-rs-pertama-transplantasi-jantung-di-indonesia</t>
         </is>
       </c>
     </row>
@@ -14390,42 +14390,69 @@
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>Vina Elvira, Kontan Rumah Sakit Internasional Columbia Asia Resmi Akuisisi RS Medika BSD</t>
+          <t>Warta Ekonomi Ekspansi Besar-besaran, RS Columbia Asia Buka Dua Rumah Sakit dalam Seminggu</t>
         </is>
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="E242" s="5" t="inlineStr">
         <is>
-          <t>https://industri.kontan.co.id/news/rumah-sakit-internasional-columbia-asia-resmi-akuisisi-rs-medika-bsd</t>
+          <t>https://wartaekonomi.co.id/read515939/ekspansi-besar-besaran-rs-columbia-asia-buka-dua-rumah-sakit-dalam-seminggu</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
         <is>
+          <t>KPJ Healthcare</t>
+        </is>
+      </c>
+      <c r="B243" s="5" t="inlineStr">
+        <is>
+          <t>RS Medika BSD</t>
+        </is>
+      </c>
+      <c r="C243" s="5" t="inlineStr">
+        <is>
+          <t>Vina Elvira, Kontan Rumah Sakit Internasional Columbia Asia Resmi Akuisisi RS Medika BSD</t>
+        </is>
+      </c>
+      <c r="D243" s="5" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="E243" s="5" t="inlineStr">
+        <is>
+          <t>https://industri.kontan.co.id/news/rumah-sakit-internasional-columbia-asia-resmi-akuisisi-rs-medika-bsd</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="5" t="inlineStr">
+        <is>
           <t>Ramsay Health Care</t>
         </is>
       </c>
-      <c r="B243" s="5" t="inlineStr">
+      <c r="B244" s="5" t="inlineStr">
         <is>
           <t>RS Premier Jatinegara, Bintaro and Surabaya</t>
         </is>
       </c>
-      <c r="C243" s="5" t="inlineStr">
+      <c r="C244" s="5" t="inlineStr">
         <is>
           <t>The Edge Malaysia Columbia Asia Healthcare renamed Asia OneHealthcare (A1Health) after consolidating assets in Malaysia, Indonesia and Vietnam</t>
         </is>
       </c>
-      <c r="D243" s="5" t="inlineStr">
+      <c r="D244" s="5" t="inlineStr">
         <is>
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="E243" s="5" t="inlineStr">
+      <c r="E244" s="5" t="inlineStr">
         <is>
           <t>https://theedgemalaysia.com/node/725855</t>
         </is>
@@ -14675,6 +14702,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId241"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId243"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Partnerships_Tracker.xlsx
+++ b/output/Partnerships_Tracker.xlsx
@@ -231,8 +231,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tracker" displayName="Tracker" ref="A1:L122" headerRowCount="1">
-  <autoFilter ref="A1:L122"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tracker" displayName="Tracker" ref="A1:L150" headerRowCount="1">
+  <autoFilter ref="A1:L150"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Status"/>
     <tableColumn id="2" name="Country"/>
@@ -558,7 +558,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scope: partnerships that are active, or ended or last active within the past five years. Last checked 2026-10-20.</t>
+          <t>Scope: partnerships that are active, or ended or last active within the past five years. Last checked 2026-10-21.</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF(Tracker!$A$2:$A$122,A5)</f>
+        <f>COUNTIF(Tracker!$A$2:$A$150,A5)</f>
         <v/>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Tracker!$A$2:$A$122,A6)</f>
+        <f>COUNTIF(Tracker!$A$2:$A$150,A6)</f>
         <v/>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Tracker!$A$2:$A$122,A7)</f>
+        <f>COUNTIF(Tracker!$A$2:$A$150,A7)</f>
         <v/>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -670,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L122"/>
+  <dimension ref="A1:L150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7732,6 +7732,1622 @@
       <c r="L122" s="14" t="inlineStr">
         <is>
           <t>The Edge Malaysia, 2024-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C123" s="13" t="inlineStr">
+        <is>
+          <t>Johns Hopkins University (Johns Hopkins Hospital)</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>Afe Babalola University (ABUAD)</t>
+        </is>
+      </c>
+      <c r="F123" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G123" s="12" t="inlineStr">
+        <is>
+          <t>Tripartite agreement with the Little by Little Foundation letting high performing ABUAD medical students do part of their fifth year clinical electives at Johns Hopkins Hospital.</t>
+        </is>
+      </c>
+      <c r="H123" s="12" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="I123" s="12" t="inlineStr"/>
+      <c r="J123" s="12" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="K123" s="12" t="inlineStr">
+        <is>
+          <t>ABUAD notice dated 17 January 2023 reports the signing on 10 January 2023. No later evidence of placements found in 2024 to 2026 searches. ABUAD's 5 February 2025 release on its seventh induction ceremony describes the six-week Johns Hopkins Hospital electives as ongoing.</t>
+        </is>
+      </c>
+      <c r="L123" s="14" t="inlineStr">
+        <is>
+          <t>Afe Babalola University, 2023-01-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C124" s="13" t="inlineStr">
+        <is>
+          <t>Mayo Clinic (Mayo Clinic Global Consulting)</t>
+        </is>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="inlineStr">
+        <is>
+          <t>Iwosan Investments Limited (Iwosan Lagoon Hospitals and Lagos Medipark Hospital)</t>
+        </is>
+      </c>
+      <c r="F124" s="12" t="inlineStr">
+        <is>
+          <t>Advisory and consulting</t>
+        </is>
+      </c>
+      <c r="G124" s="12" t="inlineStr">
+        <is>
+          <t>Iwosan Investments, owner of the Iwosan Lagoon Hospitals group, engaged Mayo Clinic Global Consulting for strategic advice on organisation and clinical practice. The work starts with Iwosan Lagoon Hospitals and the planned Lagos Medipark Hospital.</t>
+        </is>
+      </c>
+      <c r="H124" s="12" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="I124" s="12" t="inlineStr"/>
+      <c r="J124" s="12" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="K124" s="12" t="inlineStr">
+        <is>
+          <t>Iwosan's announcement was syndicated on 17 April 2025 (The Sun) and carried by BusinessDay and BrandIconImage. No page on Mayo's own newsroom was found, so confirmation rests on the Nigerian company's release. No end date or contract term is stated.</t>
+        </is>
+      </c>
+      <c r="L124" s="14" t="inlineStr">
+        <is>
+          <t>The Sun Nigeria, 2025-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C125" s="13" t="inlineStr">
+        <is>
+          <t>Memorial Sloan Kettering Cancer Center</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="inlineStr">
+        <is>
+          <t>Lagos University Teaching Hospital (LUTH) and College of Medicine, University of Lagos</t>
+        </is>
+      </c>
+      <c r="F125" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G125" s="12" t="inlineStr">
+        <is>
+          <t>LUTH and the University of Lagos College of Medicine serve as research and training hubs of the MSK founded ARGO consortium. They take part in joint cancer studies, including a colorectal cancer immunotherapy trial.</t>
+        </is>
+      </c>
+      <c r="H125" s="12" t="inlineStr"/>
+      <c r="I125" s="12" t="inlineStr"/>
+      <c r="J125" s="12" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="K125" s="12" t="inlineStr">
+        <is>
+          <t>MSK's 2025 GCRT Update names OAUTHC and the College of Medicine, University of Lagos/LUTH as ARGO's research and training hubs. MSK's press page describes the colorectal immunotherapy trial with OAUTHC, LUTH and Medserve. Start year not stated on a dated page.</t>
+        </is>
+      </c>
+      <c r="L125" s="14" t="inlineStr">
+        <is>
+          <t>Memorial Sloan Kettering Cancer Center, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B126" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C126" s="13" t="inlineStr">
+        <is>
+          <t>Memorial Sloan Kettering Cancer Center</t>
+        </is>
+      </c>
+      <c r="D126" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E126" s="12" t="inlineStr">
+        <is>
+          <t>Obafemi Awolowo University Teaching Hospitals Complex (OAUTHC)</t>
+        </is>
+      </c>
+      <c r="F126" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G126" s="12" t="inlineStr">
+        <is>
+          <t>MSK's Global Cancer Research and Training program partners with OAUTHC, home of the African Research Group for Oncology (ARGO), an NCI recognised consortium founded in 2013. The work covers cancer research, trials and training for Nigerian clinicians.</t>
+        </is>
+      </c>
+      <c r="H126" s="12" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="I126" s="12" t="inlineStr"/>
+      <c r="J126" s="12" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="K126" s="12" t="inlineStr">
+        <is>
+          <t>MSK's 2025 GCRT Update reports the annual ARGO symposium held at Ile-Ife in September 2025 and a colorectal immunotherapy trial run with OAUTHC. MSK's program page dates the partnership to the 2009 training of OAUTHC surgeon Isaac Alatise; start year is that visit, ARGO itself dates to 2013.</t>
+        </is>
+      </c>
+      <c r="L126" s="14" t="inlineStr">
+        <is>
+          <t>Memorial Sloan Kettering Cancer Center, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C127" s="13" t="inlineStr">
+        <is>
+          <t>St. Jude Children's Research Hospital</t>
+        </is>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>Abubakar Tafawa Balewa University Teaching Hospital (ATBUTH)</t>
+        </is>
+      </c>
+      <c r="F127" s="12" t="inlineStr">
+        <is>
+          <t>Clinical affiliation</t>
+        </is>
+      </c>
+      <c r="G127" s="12" t="inlineStr">
+        <is>
+          <t>ATBUTH signed a Medical Institution Membership Agreement and joined the St. Jude Global Alliance, a care and training network for childhood cancer. Membership gives access to mentorship, shared treatment protocols and training.</t>
+        </is>
+      </c>
+      <c r="H127" s="12" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="I127" s="12" t="inlineStr"/>
+      <c r="J127" s="12" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="K127" s="12" t="inlineStr">
+        <is>
+          <t>Leadership newspaper published the hospital's statement on 26 October 2025 (signing described as the day before). Not confirmed on St. Jude's own site.</t>
+        </is>
+      </c>
+      <c r="L127" s="14" t="inlineStr">
+        <is>
+          <t>Leadership Newspapers, 2025-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B128" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C128" s="13" t="inlineStr">
+        <is>
+          <t>St. Jude Children's Research Hospital</t>
+        </is>
+      </c>
+      <c r="D128" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E128" s="12" t="inlineStr">
+        <is>
+          <t>The Dorcas Cancer Foundation (TDCF)</t>
+        </is>
+      </c>
+      <c r="F128" s="12" t="inlineStr">
+        <is>
+          <t>Clinical affiliation</t>
+        </is>
+      </c>
+      <c r="G128" s="12" t="inlineStr">
+        <is>
+          <t>TDCF joined the St. Jude Global Alliance as the first Nigerian non profit member, to improve paediatric cancer outcomes in Nigeria and sub Saharan Africa. TDCF runs a paediatric radiation oncology training course.</t>
+        </is>
+      </c>
+      <c r="H128" s="12" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="I128" s="12" t="inlineStr"/>
+      <c r="J128" s="12" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="K128" s="12" t="inlineStr">
+        <is>
+          <t>ThisDay and BusinessDay reported the admission on 17 December 2024. The Nigerian party is a non profit, not a hospital, and the tie is an alliance membership; flag for the verifier. Not confirmed on St. Jude's site. Caveat: the Nigerian party is a cancer foundation working with pediatric oncology units, not a hospital.</t>
+        </is>
+      </c>
+      <c r="L128" s="14" t="inlineStr">
+        <is>
+          <t>ThisDay, 2024-12-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C129" s="13" t="inlineStr">
+        <is>
+          <t>University of Illinois Chicago (UIC School of Public Health)</t>
+        </is>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="inlineStr">
+        <is>
+          <t>Lagos State University (LASU)</t>
+        </is>
+      </c>
+      <c r="F129" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G129" s="12" t="inlineStr">
+        <is>
+          <t>Framework agreement signed 28 July 2026 for academic collaboration, joint research and student and faculty exchange, focused on urban health, emergency preparedness and AI-enabled public health tools.</t>
+        </is>
+      </c>
+      <c r="H129" s="12" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="I129" s="12" t="inlineStr"/>
+      <c r="J129" s="12" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K129" s="12" t="inlineStr">
+        <is>
+          <t>UIC School of Public Health news, 4 August 2026, reports the memorandum signed on 28 July 2026 in Chicago by LASU's Vice Chancellor and UIC representatives. A university to university agreement with no hospital named.</t>
+        </is>
+      </c>
+      <c r="L129" s="14" t="inlineStr">
+        <is>
+          <t>UIC School of Public Health, 2026-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B130" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C130" s="13" t="inlineStr">
+        <is>
+          <t>University of Maryland School of Medicine (Institute of Human Virology)</t>
+        </is>
+      </c>
+      <c r="D130" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E130" s="12" t="inlineStr">
+        <is>
+          <t>Institute of Human Virology Nigeria (IHVN)</t>
+        </is>
+      </c>
+      <c r="F130" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G130" s="12" t="inlineStr">
+        <is>
+          <t>IHVN is the Nigerian affiliate of the Maryland Institute of Human Virology, delivering HIV, TB and cancer care, training and research. It opened a multi campus site in Abuja in 2023.</t>
+        </is>
+      </c>
+      <c r="H130" s="12" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="I130" s="12" t="inlineStr"/>
+      <c r="J130" s="12" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="K130" s="12" t="inlineStr">
+        <is>
+          <t>University of Maryland news from June 2023 reports the Abuja campus launch with UMB leadership present. No dated evidence from October 2024 onward found. IHVN is an NGO affiliate, not a hospital; flag for the verifier. NIH RePORTER shows Fogarty training grant D43TW012280 awarded to IHVN for FY2026 (budget start 1 February 2026), co-led with the UMSOM Institute of Human Virology. Caveat: IHVN is the Institute's Nigerian NGO affiliate, not a hospital.</t>
+        </is>
+      </c>
+      <c r="L130" s="14" t="inlineStr">
+        <is>
+          <t>University of Maryland School of Medicine, 2023-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C131" s="13" t="inlineStr">
+        <is>
+          <t>University of Miami (Sylvester Comprehensive Cancer Center)</t>
+        </is>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>Ahmadu Bello University Teaching Hospital (ABUTH)</t>
+        </is>
+      </c>
+      <c r="F131" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G131" s="12" t="inlineStr">
+        <is>
+          <t>ABUTH is a recruiting site in a University of Miami led trial of niraparib maintenance therapy for ovarian cancer in women of African ancestry. The tie began with a Miami delegation visit to ABUTH in 2023.</t>
+        </is>
+      </c>
+      <c r="H131" s="12" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="I131" s="12" t="inlineStr"/>
+      <c r="J131" s="12" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K131" s="12" t="inlineStr">
+        <is>
+          <t>ClinicalTrials.gov NCT06412120 lists ABUTH Zaria as recruiting, study start 28 July 2026, record updated 5 August 2026, Miami investigators Schlumbrecht and George. ABUTH's August 2023 news item reports the planning visit (page not retrievable; seen in search results only).</t>
+        </is>
+      </c>
+      <c r="L131" s="14" t="inlineStr">
+        <is>
+          <t>US National Library of Medicine, 2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B132" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C132" s="13" t="inlineStr">
+        <is>
+          <t>University of Virginia Health System</t>
+        </is>
+      </c>
+      <c r="D132" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E132" s="12" t="inlineStr">
+        <is>
+          <t>Federal Medical Centre Umuahia</t>
+        </is>
+      </c>
+      <c r="F132" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G132" s="12" t="inlineStr">
+        <is>
+          <t>UVA nephrology supports the kidney transplant programme at FMC Umuahia through mentorship, coordinator training and joint research under the ISN and TTS Sister Transplant Centers Program. The pair reached Level B in 2026.</t>
+        </is>
+      </c>
+      <c r="H132" s="12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I132" s="12" t="inlineStr"/>
+      <c r="J132" s="12" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="K132" s="12" t="inlineStr">
+        <is>
+          <t>UVA Medicine in Motion news, 13 May 2026, reports the move from Level C to Level B, shorter post transplant stays (14 to 8 days), four trained coordinators and eight joint publications in the first two years, which puts the start near 2024.</t>
+        </is>
+      </c>
+      <c r="L132" s="14" t="inlineStr">
+        <is>
+          <t>UVA Medicine in Motion, 2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C133" s="13" t="inlineStr">
+        <is>
+          <t>Vanderbilt University Medical Center (Vanderbilt Institute for Global Health)</t>
+        </is>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>Aminu Kano Teaching Hospital and Bayero University Kano</t>
+        </is>
+      </c>
+      <c r="F133" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G133" s="12" t="inlineStr">
+        <is>
+          <t>Long running research and training partnership, now in its second Fogarty funded phase (V-BRCH 2), building Nigerian capacity for clinical research on HIV and related chronic diseases. Related programmes cover child neurology and research administration.</t>
+        </is>
+      </c>
+      <c r="H133" s="12" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="I133" s="12" t="inlineStr"/>
+      <c r="J133" s="12" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="K133" s="12" t="inlineStr">
+        <is>
+          <t>Fogarty grant D43TW011544 lists Aminu Kano Teaching Hospital as principal institution with award years 2020 to 2029, and Vanderbilt's V-BRCH page describes V-BRCH 2 as a continuation. Both pages are undated, so last evidence reflects page content as read on 16 October 2026; flag for the verifier. Start year is the 2020 award; the AKTH tie is older. Fogarty grant D43TW011544 was renewed in 2025 with Aminu Kano Teaching Hospital as grantee; the FY2026 award notice is dated 18 December 2025 (NIH RePORTER).</t>
+        </is>
+      </c>
+      <c r="L133" s="14" t="inlineStr">
+        <is>
+          <t>US National Institutes of Health</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B134" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C134" s="13" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University (VCU Massey Comprehensive Cancer Center)</t>
+        </is>
+      </c>
+      <c r="D134" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E134" s="12" t="inlineStr">
+        <is>
+          <t>National Hospital Abuja</t>
+        </is>
+      </c>
+      <c r="F134" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G134" s="12" t="inlineStr">
+        <is>
+          <t>Two year memorandum of understanding between the National Hospital and VCU Massey Comprehensive Cancer Center to build cancer research capacity. Focus areas are clinical trials, training of new scientists and moving research into patient care.</t>
+        </is>
+      </c>
+      <c r="H134" s="12" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="I134" s="12" t="inlineStr"/>
+      <c r="J134" s="12" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="K134" s="12" t="inlineStr">
+        <is>
+          <t>News Agency of Nigeria and Nairametrics reported the signing on 1 July 2025 by Prof Muhammad Mahmud and Dr Robert Winn, saying it was signed on a Tuesday (24 June or 1 July 2025). Term is two years, so it runs to mid 2027.</t>
+        </is>
+      </c>
+      <c r="L134" s="14" t="inlineStr">
+        <is>
+          <t>Nairametrics, 2025-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B135" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C135" s="13" t="inlineStr">
+        <is>
+          <t>Evercare Group (owned at its 2021 launch by the TPG-managed Evercare Health Fund)</t>
+        </is>
+      </c>
+      <c r="D135" s="12" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E135" s="12" t="inlineStr">
+        <is>
+          <t>Evercare Hospital Lekki</t>
+        </is>
+      </c>
+      <c r="F135" s="12" t="inlineStr">
+        <is>
+          <t>Ownership or management</t>
+        </is>
+      </c>
+      <c r="G135" s="12" t="inlineStr">
+        <is>
+          <t>Evercare Group owns and operates Evercare Hospital Lekki, a 165-bed tertiary hospital in Lagos that opened in February 2021, as part of its network of hospitals in Africa and South Asia.</t>
+        </is>
+      </c>
+      <c r="H135" s="12" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="I135" s="12" t="inlineStr"/>
+      <c r="J135" s="12" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="K135" s="12" t="inlineStr">
+        <is>
+          <t>ThisDay, 10 October 2024, describes Evercare Hospital Lekki as part of the Evercare Group, which operates in Kenya and Pakistan as well as Nigeria, announcing new cochlear implant surgery. TPG's release and a 2021 report document the group's ownership and the February 2021 opening. A 2026 LinkedIn post suggests continued operation but was not verified. Ownership is as of the 2021 launch; no later ownership confirmation was found.</t>
+        </is>
+      </c>
+      <c r="L135" s="14" t="inlineStr">
+        <is>
+          <t>ThisDay, 2024-10-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B136" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C136" s="13" t="inlineStr">
+        <is>
+          <t>King's College Hospital NHS Foundation Trust</t>
+        </is>
+      </c>
+      <c r="D136" s="12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E136" s="12" t="inlineStr">
+        <is>
+          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+        </is>
+      </c>
+      <c r="F136" s="12" t="inlineStr">
+        <is>
+          <t>Advisory and consulting</t>
+        </is>
+      </c>
+      <c r="G136" s="12" t="inlineStr">
+        <is>
+          <t>King's is the appointed Clinical Partner of the AMCE, supporting clinical protocols, governance, service set-up, recruitment and training for the 170-bed specialist hospital in Abuja. Clinical services were commissioned in June 2025.</t>
+        </is>
+      </c>
+      <c r="H136" s="12" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="I136" s="12" t="inlineStr"/>
+      <c r="J136" s="12" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K136" s="12" t="inlineStr">
+        <is>
+          <t>Afreximbank announced on 3 June 2021 that it had signed an agreement appointing King's College Hospital as Clinical Partner. Nairametrics reports the AMCE was commissioned on 5 June 2025 with Vice President Shettima praising the AMCE and King's partnership. Brand Spur (19 September 2026) describes the centre as developed with King's College Hospital and now commissioned.</t>
+        </is>
+      </c>
+      <c r="L136" s="14" t="inlineStr">
+        <is>
+          <t>African Medical Centre of Excellence (amce.net), 2021-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C137" s="13" t="inlineStr">
+        <is>
+          <t>King's College London</t>
+        </is>
+      </c>
+      <c r="D137" s="12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="inlineStr">
+        <is>
+          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+        </is>
+      </c>
+      <c r="F137" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G137" s="12" t="inlineStr">
+        <is>
+          <t>King's College London and Afreximbank agreed to plan a medical and nursing school at the AMCE in Abuja, drawing on King's healthcare education expertise. A further terms of agreement was signed in June 2025.</t>
+        </is>
+      </c>
+      <c r="H137" s="12" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="I137" s="12" t="inlineStr"/>
+      <c r="J137" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="K137" s="12" t="inlineStr">
+        <is>
+          <t>King's news release of 28 November 2023 reports the memorandum of agreement signed on 24 November 2023 for a scoping study of the school. Nairametrics reports a terms of agreement between Afreximbank and King's College London on the school was signed at the AMCE commissioning on 5 June 2025.</t>
+        </is>
+      </c>
+      <c r="L137" s="14" t="inlineStr">
+        <is>
+          <t>King's College London, 2023-11-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B138" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C138" s="13" t="inlineStr">
+        <is>
+          <t>Liverpool School of Tropical Medicine</t>
+        </is>
+      </c>
+      <c r="D138" s="12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E138" s="12" t="inlineStr">
+        <is>
+          <t>National Postgraduate Medical College of Nigeria (with Wellbeing Foundation Africa)</t>
+        </is>
+      </c>
+      <c r="F138" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G138" s="12" t="inlineStr">
+        <is>
+          <t>LSTM leads Advanced Obstetrics and Surgical Skills training for obstetrics and gynaecology examiners and residents of the National Postgraduate Medical College, with centres of excellence in Lagos and Abuja and later sites in Port Harcourt and Gombe. It is funded by the UK Global Health Workforce Programme.</t>
+        </is>
+      </c>
+      <c r="H138" s="12" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="I138" s="12" t="inlineStr"/>
+      <c r="J138" s="12" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="K138" s="12" t="inlineStr">
+        <is>
+          <t>LSTM reports the course began on 6 May 2024 at the college's centre of excellence at LUTH. The Wellbeing Foundation Africa reported on 12 February 2025 that 225 doctors had been trained, and on 22 May 2025 that training had expanded to the University of Port Harcourt Teaching Hospital. LSTM's May 2024 release names the site as 'Lagos State University Teaching Hospital (LUTH)', which is ambiguous; WBFA reported 225 examiners and 120 residents trained by May 2025.</t>
+        </is>
+      </c>
+      <c r="L138" s="14" t="inlineStr">
+        <is>
+          <t>Liverpool School of Tropical Medicine, 2024-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C139" s="13" t="inlineStr">
+        <is>
+          <t>Manipal Hospitals</t>
+        </is>
+      </c>
+      <c r="D139" s="12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>Afe Babalola University Multi-System Hospital</t>
+        </is>
+      </c>
+      <c r="F139" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G139" s="12" t="inlineStr">
+        <is>
+          <t>Afe Babalola University Multi-System Hospital and Manipal Hospitals signed an MoU to expand capacity, deepen specialist training, improve clinical exchange and support advanced surgical care.</t>
+        </is>
+      </c>
+      <c r="H139" s="12" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="I139" s="12" t="inlineStr"/>
+      <c r="J139" s="12" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="K139" s="12" t="inlineStr">
+        <is>
+          <t>News Agency of Nigeria, 26 June 2026, reports the MoU announced at a press briefing by the hospital's chief medical director, with Dr Rajit Sood speaking for Manipal and the university's Vice-Chancellor present.</t>
+        </is>
+      </c>
+      <c r="L139" s="14" t="inlineStr">
+        <is>
+          <t>News Agency of Nigeria, 2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B140" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C140" s="13" t="inlineStr">
+        <is>
+          <t>The Christie NHS Foundation Trust</t>
+        </is>
+      </c>
+      <c r="D140" s="12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E140" s="12" t="inlineStr">
+        <is>
+          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+        </is>
+      </c>
+      <c r="F140" s="12" t="inlineStr">
+        <is>
+          <t>Advisory and consulting</t>
+        </is>
+      </c>
+      <c r="G140" s="12" t="inlineStr">
+        <is>
+          <t>The Christie, through Christie International, is the oncology partner to King's College Hospital in advising the AMCE, supporting oncology staff recruitment, education and quality assurance. It continues to support the oncology service after opening.</t>
+        </is>
+      </c>
+      <c r="H140" s="12" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I140" s="12" t="inlineStr"/>
+      <c r="J140" s="12" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="K140" s="12" t="inlineStr">
+        <is>
+          <t>The Christie's news story of 25 October 2024 reports an AMCE delegation visit to Manchester and says its advice, which began in 2021, would continue into operations. The Christie's project page, as indexed in search, states that clinical services were commissioned on 5 June 2025 with Christie International's head attending.</t>
+        </is>
+      </c>
+      <c r="L140" s="14" t="inlineStr">
+        <is>
+          <t>The Christie NHS Foundation Trust, 2024-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B141" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C141" s="13" t="inlineStr">
+        <is>
+          <t>The Royal Marsden NHS Foundation Trust</t>
+        </is>
+      </c>
+      <c r="D141" s="12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>Marcelle Ruth Cancer Centre &amp; Specialist Hospital</t>
+        </is>
+      </c>
+      <c r="F141" s="12" t="inlineStr">
+        <is>
+          <t>Clinical affiliation</t>
+        </is>
+      </c>
+      <c r="G141" s="12" t="inlineStr">
+        <is>
+          <t>The two cancer centres signed a strategic partnership covering clinical expertise, research, professional development and training, aimed at keeping cancer care in Nigeria and West Africa.</t>
+        </is>
+      </c>
+      <c r="H141" s="12" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I141" s="12" t="inlineStr"/>
+      <c r="J141" s="12" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K141" s="12" t="inlineStr">
+        <is>
+          <t>BusinessDay reported on 24 September 2026 that Marcelle Ruth had entered a strategic partnership with The Royal Marsden. Search results also show the agreement described as an MoU on a Royal Marsden Private Care LinkedIn post; no Royal Marsden press release was found.</t>
+        </is>
+      </c>
+      <c r="L141" s="14" t="inlineStr">
+        <is>
+          <t>BusinessDay, 2026-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B142" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C142" s="13" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="D142" s="12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E142" s="12" t="inlineStr">
+        <is>
+          <t>University of Lagos (with Lagos University Teaching Hospital)</t>
+        </is>
+      </c>
+      <c r="F142" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G142" s="12" t="inlineStr">
+        <is>
+          <t>The University of Lagos and the University of Birmingham signed a memorandum on transnational education covering student and staff exchange and curriculum development. It builds on more than a decade of global surgery collaboration that introduced a master's programme in surgery at LUTH.</t>
+        </is>
+      </c>
+      <c r="H142" s="12" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="I142" s="12" t="inlineStr"/>
+      <c r="J142" s="12" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="K142" s="12" t="inlineStr">
+        <is>
+          <t>Vanguard, 29 January 2026, reports the MoU signed at UNILAG's Senate Chamber, witnessed by the Minister of Education; UNILAG's Vice Chancellor cites the Birmingham global surgery work and the LUTH master's in surgery. Birmingham described the MoU as a statement of intent. Not yet confirmed on Birmingham's newsroom.</t>
+        </is>
+      </c>
+      <c r="L142" s="14" t="inlineStr">
+        <is>
+          <t>Vanguard, 29 January 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C143" s="13" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>Ahmadu Bello University</t>
+        </is>
+      </c>
+      <c r="F143" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G143" s="12" t="inlineStr">
+        <is>
+          <t>A university-level MoU provides a framework for joint research programmes, postgraduate co-supervision and academic exchange on global health challenges, coordinated by the School of Infection and Immunity. A university-wide MoU; no teaching-hospital or clinical component is named.</t>
+        </is>
+      </c>
+      <c r="H143" s="12" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="I143" s="12" t="inlineStr"/>
+      <c r="J143" s="12" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="K143" s="12" t="inlineStr">
+        <is>
+          <t>The University of Glasgow news item of 12 May 2026 reports the MoU signed during a visit on 28 and 29 April 2026, following an exploratory visit in December 2025. The MoU is university-wide and not limited to the teaching hospital.</t>
+        </is>
+      </c>
+      <c r="L143" s="14" t="inlineStr">
+        <is>
+          <t>University of Glasgow, 2026-05-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B144" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C144" s="13" t="inlineStr">
+        <is>
+          <t>University of Maryland School of Medicine</t>
+        </is>
+      </c>
+      <c r="D144" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E144" s="12" t="inlineStr">
+        <is>
+          <t>Lagos University Teaching Hospital (LUTH)</t>
+        </is>
+      </c>
+      <c r="F144" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G144" s="12" t="inlineStr">
+        <is>
+          <t>The University of Maryland School of Medicine and LUTH announced a chronic disease collaboration in August 2024, initially for four to five years with a stated ten-year ambition.</t>
+        </is>
+      </c>
+      <c r="H144" s="12" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="I144" s="12" t="inlineStr"/>
+      <c r="J144" s="12" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="K144" s="12" t="inlineStr">
+        <is>
+          <t>Nairametrics (19 August 2024) and LUTH report a partnership planned over ten years, following a visit by Dean Mark Gladwin. No signed text or later 2024 to 2026 update found, so it falls just before the Active cutoff.</t>
+        </is>
+      </c>
+      <c r="L144" s="14" t="inlineStr">
+        <is>
+          <t>Lagos University Teaching Hospital, 2024-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B145" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C145" s="13" t="inlineStr">
+        <is>
+          <t>University of Virginia Health System</t>
+        </is>
+      </c>
+      <c r="D145" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="inlineStr">
+        <is>
+          <t>Federal Medical Centre Owo</t>
+        </is>
+      </c>
+      <c r="F145" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G145" s="12" t="inlineStr">
+        <is>
+          <t>UVA's nephrology division built a partnership with FMC Owo covering research and career development programmes, with the International Society of Nephrology, and donated textbooks.</t>
+        </is>
+      </c>
+      <c r="H145" s="12" t="inlineStr"/>
+      <c r="I145" s="12" t="inlineStr"/>
+      <c r="J145" s="12" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="K145" s="12" t="inlineStr">
+        <is>
+          <t>UVA news item describes a textbook donation on 6 January 2023. No later dated evidence found, and the work may now sit inside the FMC Umuahia programme.</t>
+        </is>
+      </c>
+      <c r="L145" s="14" t="inlineStr">
+        <is>
+          <t>UVA Medicine in Motion, 2023-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B146" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C146" s="13" t="inlineStr">
+        <is>
+          <t>Yale School of Medicine (Department of Psychiatry)</t>
+        </is>
+      </c>
+      <c r="D146" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E146" s="12" t="inlineStr">
+        <is>
+          <t>Imo State University Teaching Hospital</t>
+        </is>
+      </c>
+      <c r="F146" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G146" s="12" t="inlineStr">
+        <is>
+          <t>Yale's HAPPINESS Project, run with the Imo State teaching hospital, trains primary care workers to treat mental, neurological and substance use disorders, with telemedicine specialist support. It has begun integrating mental health into HIV clinics.</t>
+        </is>
+      </c>
+      <c r="H146" s="12" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="I146" s="12" t="inlineStr"/>
+      <c r="J146" s="12" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="K146" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria Health Watch, 6 September 2023, reports over 100 workers trained; Yale's programme page is undated. No dated evidence from October 2024 onward found. The teaching hospital is in Orlu, Imo State.</t>
+        </is>
+      </c>
+      <c r="L146" s="14" t="inlineStr">
+        <is>
+          <t>Nigeria Health Watch, 2023-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B147" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C147" s="13" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals</t>
+        </is>
+      </c>
+      <c r="D147" s="12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E147" s="12" t="inlineStr">
+        <is>
+          <t>Duchess International Hospital (Reddington Hospital Group)</t>
+        </is>
+      </c>
+      <c r="F147" s="12" t="inlineStr">
+        <is>
+          <t>Ownership or management</t>
+        </is>
+      </c>
+      <c r="G147" s="12" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals supports the operation and management of the 100-bed Duchess International Hospital in Ikeja, Lagos, to strengthen efficiency and clinical quality. The arrangement was announced when the hospital launched in October 2021.</t>
+        </is>
+      </c>
+      <c r="H147" s="12" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="I147" s="12" t="inlineStr"/>
+      <c r="J147" s="12" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="K147" s="12" t="inlineStr">
+        <is>
+          <t>ThisDay (11 November 2021) and New Telegraph report that operation and management of the Duchess are supported by Apollo Hospitals, India. No dated confirmation from October 2024 onward was found; the hospital's 2024 and 2025 award releases do not mention Apollo.</t>
+        </is>
+      </c>
+      <c r="L147" s="14" t="inlineStr">
+        <is>
+          <t>ThisDay, 11 November 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B148" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C148" s="13" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals</t>
+        </is>
+      </c>
+      <c r="D148" s="12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E148" s="12" t="inlineStr">
+        <is>
+          <t>State House Clinic</t>
+        </is>
+      </c>
+      <c r="F148" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G148" s="12" t="inlineStr">
+        <is>
+          <t>Apollo doctors visit the State House Clinic to give free consultations and lectures, and clinic staff have been sent to Apollo in India for up to six weeks of training at no charge.</t>
+        </is>
+      </c>
+      <c r="H148" s="12" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="I148" s="12" t="inlineStr"/>
+      <c r="J148" s="12" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="K148" s="12" t="inlineStr">
+        <is>
+          <t>Blueprint, 29 July 2022, quotes the clinic's medical director describing a collaboration of almost six to seven years and a visiting Apollo team in Abuja. Start year is approximate, back-calculated from that quote. No later dated activity was found; a March 2024 ThisDay report records only Apollo's stated intent to partner with Nigerian hospitals.</t>
+        </is>
+      </c>
+      <c r="L148" s="14" t="inlineStr">
+        <is>
+          <t>Blueprint, 2022-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B149" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C149" s="13" t="inlineStr">
+        <is>
+          <t>Memorial Hospitals Group</t>
+        </is>
+      </c>
+      <c r="D149" s="12" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="E149" s="12" t="inlineStr">
+        <is>
+          <t>Kasi Healthcare</t>
+        </is>
+      </c>
+      <c r="F149" s="12" t="inlineStr">
+        <is>
+          <t>Telehealth and second opinion</t>
+        </is>
+      </c>
+      <c r="G149" s="12" t="inlineStr">
+        <is>
+          <t>Memorial specialists provide second opinions and specialist screenings, with monthly visiting specialists and training courses for Nigerian providers at Kasi's Lagos airport clinic, linked to referral of patients to Turkey. Close to a patient-referral arrangement.</t>
+        </is>
+      </c>
+      <c r="H149" s="12" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="I149" s="12" t="inlineStr"/>
+      <c r="J149" s="12" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="K149" s="12" t="inlineStr">
+        <is>
+          <t>BusinessDay, 27 September 2024, reports the partnership announced with Memorial's country executive. No later dated activity was found.</t>
+        </is>
+      </c>
+      <c r="L149" s="14" t="inlineStr">
+        <is>
+          <t>BusinessDay, 2024-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B150" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C150" s="13" t="inlineStr">
+        <is>
+          <t>Peking University People's Hospital (named variously in press as People's University Hospital, Beijing)</t>
+        </is>
+      </c>
+      <c r="D150" s="12" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E150" s="12" t="inlineStr">
+        <is>
+          <t>University of Abuja Teaching Hospital</t>
+        </is>
+      </c>
+      <c r="F150" s="12" t="inlineStr">
+        <is>
+          <t>Government agreement</t>
+        </is>
+      </c>
+      <c r="G150" s="12" t="inlineStr">
+        <is>
+          <t>A China-Nigeria government letter of intent names these two hospitals as the pioneer project for hospital cooperation under the 2021 FOCAC health programmes, covering knowledge sharing and research.</t>
+        </is>
+      </c>
+      <c r="H150" s="12" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="I150" s="12" t="inlineStr"/>
+      <c r="J150" s="12" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="K150" s="12" t="inlineStr">
+        <is>
+          <t>Within Nigeria and the University of Abuja Teaching Hospital website report the letter of intent signed in Abuja by the Chinese Ambassador and Nigeria's Health Minister in August 2022. No follow-up activity was found. The Chinese hospital's name varies between sources and is inferred.</t>
+        </is>
+      </c>
+      <c r="L150" s="14" t="inlineStr">
+        <is>
+          <t>Within Nigeria, 2022-08-20</t>
         </is>
       </c>
     </row>
@@ -7858,10 +9474,38 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L150" r:id="rId149"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId122"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId150"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7872,7 +9516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E244"/>
+  <dimension ref="A1:E297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -14455,6 +16099,1417 @@
       <c r="E244" s="5" t="inlineStr">
         <is>
           <t>https://theedgemalaysia.com/node/725855</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="5" t="inlineStr">
+        <is>
+          <t>Johns Hopkins University (Johns Hopkins Hospital)</t>
+        </is>
+      </c>
+      <c r="B245" s="5" t="inlineStr">
+        <is>
+          <t>Afe Babalola University (ABUAD)</t>
+        </is>
+      </c>
+      <c r="C245" s="5" t="inlineStr">
+        <is>
+          <t>Afe Babalola University ABUAD Tripartite agreement with John Hopkins University USA and Little by Little Foundation</t>
+        </is>
+      </c>
+      <c r="D245" s="5" t="inlineStr">
+        <is>
+          <t>2023-01-17</t>
+        </is>
+      </c>
+      <c r="E245" s="5" t="inlineStr">
+        <is>
+          <t>https://www.abuad.edu.ng/abuad-tripartite-agreement-with-john-hopkins-university-usa-and-little-by-little-foundation/</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="5" t="inlineStr">
+        <is>
+          <t>Johns Hopkins University (Johns Hopkins Hospital)</t>
+        </is>
+      </c>
+      <c r="B246" s="5" t="inlineStr">
+        <is>
+          <t>Afe Babalola University (ABUAD)</t>
+        </is>
+      </c>
+      <c r="C246" s="5" t="inlineStr">
+        <is>
+          <t>ThisDay ABUAD, John Hopkins Partner to Boost Medical Training</t>
+        </is>
+      </c>
+      <c r="D246" s="5" t="inlineStr">
+        <is>
+          <t>2023-01-18</t>
+        </is>
+      </c>
+      <c r="E246" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thisdaylive.com/2023/01/18/abuad-john-hopkins-partner-to-boost-medical-training/</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="5" t="inlineStr">
+        <is>
+          <t>Johns Hopkins University (Johns Hopkins Hospital)</t>
+        </is>
+      </c>
+      <c r="B247" s="5" t="inlineStr">
+        <is>
+          <t>Afe Babalola University (ABUAD)</t>
+        </is>
+      </c>
+      <c r="C247" s="5" t="inlineStr">
+        <is>
+          <t>Afe Babalola University ABUAD Holds Seventh Induction Ceremony for Fresh Doctors</t>
+        </is>
+      </c>
+      <c r="D247" s="5" t="inlineStr">
+        <is>
+          <t>5 February 2025</t>
+        </is>
+      </c>
+      <c r="E247" s="5" t="inlineStr">
+        <is>
+          <t>https://vc.abuad.edu.ng/abuad-holds-seventh-induction-ceremony-for-fresh-doctors/</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="5" t="inlineStr">
+        <is>
+          <t>Mayo Clinic (Mayo Clinic Global Consulting)</t>
+        </is>
+      </c>
+      <c r="B248" s="5" t="inlineStr">
+        <is>
+          <t>Iwosan Investments Limited (Iwosan Lagoon Hospitals and Lagos Medipark Hospital)</t>
+        </is>
+      </c>
+      <c r="C248" s="5" t="inlineStr">
+        <is>
+          <t>The Sun Iwosan engages Mayo Clinic to advance high-quality patient-centered healthcare</t>
+        </is>
+      </c>
+      <c r="D248" s="5" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="E248" s="5" t="inlineStr">
+        <is>
+          <t>https://thesun.ng/iwosan-engages-mayo-clinic-to-advance-high-quality-patient-centered-healthcare/</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="5" t="inlineStr">
+        <is>
+          <t>Mayo Clinic (Mayo Clinic Global Consulting)</t>
+        </is>
+      </c>
+      <c r="B249" s="5" t="inlineStr">
+        <is>
+          <t>Iwosan Investments Limited (Iwosan Lagoon Hospitals and Lagos Medipark Hospital)</t>
+        </is>
+      </c>
+      <c r="C249" s="5" t="inlineStr">
+        <is>
+          <t>BrandIconImage Iwosan Investments Limited Engages Mayo Clinic Global Consulting to Advance High-Quality Patient-Centered Healthcare in Nigeria</t>
+        </is>
+      </c>
+      <c r="D249" s="5" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="E249" s="5" t="inlineStr">
+        <is>
+          <t>https://www.brandiconimage.com/2025/04/iwosan-investments-limited-engages-mayo.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="5" t="inlineStr">
+        <is>
+          <t>Mayo Clinic (Mayo Clinic Global Consulting)</t>
+        </is>
+      </c>
+      <c r="B250" s="5" t="inlineStr">
+        <is>
+          <t>Iwosan Investments Limited (Iwosan Lagoon Hospitals and Lagos Medipark Hospital)</t>
+        </is>
+      </c>
+      <c r="C250" s="5" t="inlineStr">
+        <is>
+          <t>BusinessDay Iwosan engages Mayo Clinic to advance high quality patient centered healthcare in Nigeria</t>
+        </is>
+      </c>
+      <c r="D250" s="5" t="inlineStr">
+        <is>
+          <t>8 April 2025</t>
+        </is>
+      </c>
+      <c r="E250" s="5" t="inlineStr">
+        <is>
+          <t>https://businessday.ng/health/article/iwosan-engages-mayo-clinic-to-advance-high-quality-patient-centered-healthcare-in-nigeria/</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="5" t="inlineStr">
+        <is>
+          <t>Memorial Sloan Kettering Cancer Center</t>
+        </is>
+      </c>
+      <c r="B251" s="5" t="inlineStr">
+        <is>
+          <t>Lagos University Teaching Hospital (LUTH) and College of Medicine, University of Lagos</t>
+        </is>
+      </c>
+      <c r="C251" s="5" t="inlineStr">
+        <is>
+          <t>Memorial Sloan Kettering Cancer Center Global Cancer Research and Training Program 2025 Update</t>
+        </is>
+      </c>
+      <c r="D251" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E251" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mskcc.org/sites/default/files/node/118066/documents/gcrt_report_2026_6_01-29-98-44.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="5" t="inlineStr">
+        <is>
+          <t>Memorial Sloan Kettering Cancer Center</t>
+        </is>
+      </c>
+      <c r="B252" s="5" t="inlineStr">
+        <is>
+          <t>Obafemi Awolowo University Teaching Hospitals Complex (OAUTHC)</t>
+        </is>
+      </c>
+      <c r="C252" s="5" t="inlineStr">
+        <is>
+          <t>Memorial Sloan Kettering Cancer Center Global Cancer Research and Training Program 2025 Update</t>
+        </is>
+      </c>
+      <c r="D252" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E252" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mskcc.org/sites/default/files/node/118066/documents/gcrt_report_2026_6_01-29-98-44.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="5" t="inlineStr">
+        <is>
+          <t>Memorial Sloan Kettering Cancer Center</t>
+        </is>
+      </c>
+      <c r="B253" s="5" t="inlineStr">
+        <is>
+          <t>Obafemi Awolowo University Teaching Hospitals Complex (OAUTHC)</t>
+        </is>
+      </c>
+      <c r="C253" s="5" t="inlineStr">
+        <is>
+          <t>Memorial Sloan Kettering Cancer Center MSK's Global Cancer Research and Training (GCRT) Program</t>
+        </is>
+      </c>
+      <c r="D253" s="5" t="inlineStr"/>
+      <c r="E253" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mskcc.org/hcp-education-training/international/global-cancer-disparities-initiatives</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="5" t="inlineStr">
+        <is>
+          <t>St. Jude Children's Research Hospital</t>
+        </is>
+      </c>
+      <c r="B254" s="5" t="inlineStr">
+        <is>
+          <t>Abubakar Tafawa Balewa University Teaching Hospital (ATBUTH)</t>
+        </is>
+      </c>
+      <c r="C254" s="5" t="inlineStr">
+        <is>
+          <t>Leadership Bauchi Teaching Hospital Seeks Alliance To Strengthen Cancer Care</t>
+        </is>
+      </c>
+      <c r="D254" s="5" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="E254" s="5" t="inlineStr">
+        <is>
+          <t>https://leadership.ng/bauchi-teaching-hospital-seeks-alliance-to-strengthen-cancer-care/</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="5" t="inlineStr">
+        <is>
+          <t>St. Jude Children's Research Hospital</t>
+        </is>
+      </c>
+      <c r="B255" s="5" t="inlineStr">
+        <is>
+          <t>The Dorcas Cancer Foundation (TDCF)</t>
+        </is>
+      </c>
+      <c r="C255" s="5" t="inlineStr">
+        <is>
+          <t>Sunday Ehigiator TDCF, St. Jude Global Alliance, Partner on Improving Pediatric Cancer Outcomes in Nigeria, Others</t>
+        </is>
+      </c>
+      <c r="D255" s="5" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="E255" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thisdaylive.com/2024/12/17/tdcf-st-jude-global-alliance-partner-on-improving-pediatric-cancer-outcomes-in-nigeria-others/</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="5" t="inlineStr">
+        <is>
+          <t>St. Jude Children's Research Hospital</t>
+        </is>
+      </c>
+      <c r="B256" s="5" t="inlineStr">
+        <is>
+          <t>The Dorcas Cancer Foundation (TDCF)</t>
+        </is>
+      </c>
+      <c r="C256" s="5" t="inlineStr">
+        <is>
+          <t>BusinessDay TDCF admitted into St Jude Global Alliance to improve pediatric cancer outcomes in Nigeria</t>
+        </is>
+      </c>
+      <c r="D256" s="5" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="E256" s="5" t="inlineStr">
+        <is>
+          <t>https://businessday.ng/life/article/tdcf-admitted-into-st-jude-global-alliance-to-improve-pediatric-cancer-outcomes-in-nigeria/</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="5" t="inlineStr">
+        <is>
+          <t>University of Illinois Chicago (UIC School of Public Health)</t>
+        </is>
+      </c>
+      <c r="B257" s="5" t="inlineStr">
+        <is>
+          <t>Lagos State University (LASU)</t>
+        </is>
+      </c>
+      <c r="C257" s="5" t="inlineStr">
+        <is>
+          <t>UIC School of Public Health UIC and Lagos State University Sign Memorandum of Agreement</t>
+        </is>
+      </c>
+      <c r="D257" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E257" s="5" t="inlineStr">
+        <is>
+          <t>https://publichealth.uic.edu/news-stories/uic-and-lagos-state-university-sign-memorandum-of-agreement/</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="5" t="inlineStr">
+        <is>
+          <t>University of Maryland School of Medicine (Institute of Human Virology)</t>
+        </is>
+      </c>
+      <c r="B258" s="5" t="inlineStr">
+        <is>
+          <t>Institute of Human Virology Nigeria (IHVN)</t>
+        </is>
+      </c>
+      <c r="C258" s="5" t="inlineStr">
+        <is>
+          <t>University of Maryland School of Medicine University of Maryland Baltimore leadership helps IHV Nigeria launch campus in Abuja</t>
+        </is>
+      </c>
+      <c r="D258" s="5" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="E258" s="5" t="inlineStr">
+        <is>
+          <t>https://ihv.umaryland.edu/news/2023/university-of-maryland-baltimore-leadership-helps-ihv-nigeria-launch-state-of-the-art-campus-in-public-healthcare-treatment-training-and-research-in-nigeria.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="5" t="inlineStr">
+        <is>
+          <t>University of Maryland School of Medicine (Institute of Human Virology)</t>
+        </is>
+      </c>
+      <c r="B259" s="5" t="inlineStr">
+        <is>
+          <t>Institute of Human Virology Nigeria (IHVN)</t>
+        </is>
+      </c>
+      <c r="C259" s="5" t="inlineStr">
+        <is>
+          <t>US National Institutes of Health RePORTER: 5D43TW012280-05, Expanding the pool of Independent Investigators in Implementation Science (Institute of Human Virology Nigeria)</t>
+        </is>
+      </c>
+      <c r="D259" s="5" t="inlineStr">
+        <is>
+          <t>FY2026 (budget start 1 February 2026)</t>
+        </is>
+      </c>
+      <c r="E259" s="5" t="inlineStr">
+        <is>
+          <t>https://reporter.nih.gov/project-details/11251575</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="5" t="inlineStr">
+        <is>
+          <t>University of Miami (Sylvester Comprehensive Cancer Center)</t>
+        </is>
+      </c>
+      <c r="B260" s="5" t="inlineStr">
+        <is>
+          <t>Ahmadu Bello University Teaching Hospital (ABUTH)</t>
+        </is>
+      </c>
+      <c r="C260" s="5" t="inlineStr">
+        <is>
+          <t>ClinicalTrials.gov Study Evaluating Safety, Tolerability, and Metabolism of Niraparib (NCT06412120)</t>
+        </is>
+      </c>
+      <c r="D260" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E260" s="5" t="inlineStr">
+        <is>
+          <t>https://clinicaltrials.gov/study/NCT06412120</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="5" t="inlineStr">
+        <is>
+          <t>University of Miami (Sylvester Comprehensive Cancer Center)</t>
+        </is>
+      </c>
+      <c r="B261" s="5" t="inlineStr">
+        <is>
+          <t>Ahmadu Bello University Teaching Hospital (ABUTH)</t>
+        </is>
+      </c>
+      <c r="C261" s="5" t="inlineStr">
+        <is>
+          <t>Ahmadu Bello University ABUTH to begin clinical trials on ovarian cancer next year</t>
+        </is>
+      </c>
+      <c r="D261" s="5" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="E261" s="5" t="inlineStr">
+        <is>
+          <t>https://abu.edu.ng/abuth-to-begin-clinical-trials-on-ovarian-cancer-next-year/</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="5" t="inlineStr">
+        <is>
+          <t>University of Miami (Sylvester Comprehensive Cancer Center)</t>
+        </is>
+      </c>
+      <c r="B262" s="5" t="inlineStr">
+        <is>
+          <t>Ahmadu Bello University Teaching Hospital (ABUTH)</t>
+        </is>
+      </c>
+      <c r="C262" s="5" t="inlineStr">
+        <is>
+          <t>US National Library of Medicine NCT06412120: Niraparib as Maintenance Following Front-Line Treatment for Ovarian Cancer in Women of African Ancestry</t>
+        </is>
+      </c>
+      <c r="D262" s="5" t="inlineStr">
+        <is>
+          <t>5 August 2026</t>
+        </is>
+      </c>
+      <c r="E262" s="5" t="inlineStr">
+        <is>
+          <t>https://clinicaltrials.gov/study/NCT06412120</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="5" t="inlineStr">
+        <is>
+          <t>University of Virginia Health System</t>
+        </is>
+      </c>
+      <c r="B263" s="5" t="inlineStr">
+        <is>
+          <t>Federal Medical Centre Umuahia</t>
+        </is>
+      </c>
+      <c r="C263" s="5" t="inlineStr">
+        <is>
+          <t>UVA School of Medicine UVA Partners With Federal Medical Center in Nigeria to Elevate Global Kidney Care</t>
+        </is>
+      </c>
+      <c r="D263" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E263" s="5" t="inlineStr">
+        <is>
+          <t>https://news.med.virginia.edu/community/uva-nigeria-elevating-global-kidney-care/</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="5" t="inlineStr">
+        <is>
+          <t>Vanderbilt University Medical Center (Vanderbilt Institute for Global Health)</t>
+        </is>
+      </c>
+      <c r="B264" s="5" t="inlineStr">
+        <is>
+          <t>Aminu Kano Teaching Hospital and Bayero University Kano</t>
+        </is>
+      </c>
+      <c r="C264" s="5" t="inlineStr">
+        <is>
+          <t>Fogarty International Center Vanderbilt-Nigeria Building Research Capacity in HIV and NCDs (V-BRCH)</t>
+        </is>
+      </c>
+      <c r="D264" s="5" t="inlineStr"/>
+      <c r="E264" s="5" t="inlineStr">
+        <is>
+          <t>https://fic.nih.gov/Grants/Search/Pages/hiv-research-training-d43tw011544.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="5" t="inlineStr">
+        <is>
+          <t>Vanderbilt University Medical Center (Vanderbilt Institute for Global Health)</t>
+        </is>
+      </c>
+      <c r="B265" s="5" t="inlineStr">
+        <is>
+          <t>Aminu Kano Teaching Hospital and Bayero University Kano</t>
+        </is>
+      </c>
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>Vanderbilt Institute for Global Health V-BRCH</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="inlineStr"/>
+      <c r="E265" s="5" t="inlineStr">
+        <is>
+          <t>https://www.vumc.org/global-health/v-brch</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="5" t="inlineStr">
+        <is>
+          <t>Vanderbilt University Medical Center (Vanderbilt Institute for Global Health)</t>
+        </is>
+      </c>
+      <c r="B266" s="5" t="inlineStr">
+        <is>
+          <t>Aminu Kano Teaching Hospital and Bayero University Kano</t>
+        </is>
+      </c>
+      <c r="C266" s="5" t="inlineStr">
+        <is>
+          <t>US National Institutes of Health RePORTER: 5D43TW011544-07, Vanderbilt-Nigeria Building Research Capacity in HIV and Non-communicable Diseases (V-BRCH)</t>
+        </is>
+      </c>
+      <c r="D266" s="5" t="inlineStr">
+        <is>
+          <t>FY2026 (budget start 1 January 2026)</t>
+        </is>
+      </c>
+      <c r="E266" s="5" t="inlineStr">
+        <is>
+          <t>https://reporter.nih.gov/project-details/11378551</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="5" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University (VCU Massey Comprehensive Cancer Center)</t>
+        </is>
+      </c>
+      <c r="B267" s="5" t="inlineStr">
+        <is>
+          <t>National Hospital Abuja</t>
+        </is>
+      </c>
+      <c r="C267" s="5" t="inlineStr">
+        <is>
+          <t>Anthonia Obokoh National Hospital signs MoU with U.S. cancer center to boost research, clinical trials in Nigeria</t>
+        </is>
+      </c>
+      <c r="D267" s="5" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="E267" s="5" t="inlineStr">
+        <is>
+          <t>https://nairametrics.com/2025/07/01/national-hospital-signs-mou-with-u-s-cancer-center-to-boost-research-clinical-trials-in-nigeria/</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="5" t="inlineStr">
+        <is>
+          <t>Evercare Group (owned at its 2021 launch by the TPG-managed Evercare Health Fund)</t>
+        </is>
+      </c>
+      <c r="B268" s="5" t="inlineStr">
+        <is>
+          <t>Evercare Hospital Lekki</t>
+        </is>
+      </c>
+      <c r="C268" s="5" t="inlineStr">
+        <is>
+          <t>Esther Oluku Evercare, MedEI, Commence Advanced Cochlear Implant Surgery in Nigeria</t>
+        </is>
+      </c>
+      <c r="D268" s="5" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="E268" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thisdaylive.com/2024/10/10/evercare-medei-commence-advanced-cochlear-implant-surgery-in-nigeria/</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="5" t="inlineStr">
+        <is>
+          <t>Evercare Group (owned at its 2021 launch by the TPG-managed Evercare Health Fund)</t>
+        </is>
+      </c>
+      <c r="B269" s="5" t="inlineStr">
+        <is>
+          <t>Evercare Hospital Lekki</t>
+        </is>
+      </c>
+      <c r="C269" s="5" t="inlineStr">
+        <is>
+          <t>TPG Evercare Group set to deliver accessible, quality healthcare in Nigeria</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E269" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tpg.com/news-and-insights/evercare-group-set-deliver-accessible-quality-healthcare-nigeria</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="5" t="inlineStr">
+        <is>
+          <t>Evercare Group (owned at its 2021 launch by the TPG-managed Evercare Health Fund)</t>
+        </is>
+      </c>
+      <c r="B270" s="5" t="inlineStr">
+        <is>
+          <t>Evercare Hospital Lekki</t>
+        </is>
+      </c>
+      <c r="C270" s="5" t="inlineStr">
+        <is>
+          <t>TPG Evercare Group set to deliver accessible, quality healthcare in Nigeria through a new world-class multispecialty hospital</t>
+        </is>
+      </c>
+      <c r="D270" s="5" t="inlineStr">
+        <is>
+          <t>26 February 2021</t>
+        </is>
+      </c>
+      <c r="E270" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tpg.com/news-and-insights/evercare-group-set-deliver-accessible-quality-healthcare-nigeria</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="5" t="inlineStr">
+        <is>
+          <t>King's College Hospital NHS Foundation Trust</t>
+        </is>
+      </c>
+      <c r="B271" s="5" t="inlineStr">
+        <is>
+          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+        </is>
+      </c>
+      <c r="C271" s="5" t="inlineStr">
+        <is>
+          <t>Afreximbank King's College Hospital, London (KCH) affirmed as Clinical Partner</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="inlineStr">
+        <is>
+          <t>2021-06-03</t>
+        </is>
+      </c>
+      <c r="E271" s="5" t="inlineStr">
+        <is>
+          <t>https://www.amce.net/?p=10738</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="5" t="inlineStr">
+        <is>
+          <t>King's College Hospital NHS Foundation Trust</t>
+        </is>
+      </c>
+      <c r="B272" s="5" t="inlineStr">
+        <is>
+          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+        </is>
+      </c>
+      <c r="C272" s="5" t="inlineStr">
+        <is>
+          <t>Nnaemeka Onyekachi Afreximbank, BOI sign $75 million financing support for local manufacturers in Nigerian healthcare sector (reports AMCE commissioning)</t>
+        </is>
+      </c>
+      <c r="D272" s="5" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="E272" s="5" t="inlineStr">
+        <is>
+          <t>https://nairametrics.com/2025/06/05/afreximbank-boi-sign-75-million-financing-support-for-local-manufacturers-in-nigerian-healthcare-sector/</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="5" t="inlineStr">
+        <is>
+          <t>King's College Hospital NHS Foundation Trust</t>
+        </is>
+      </c>
+      <c r="B273" s="5" t="inlineStr">
+        <is>
+          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+        </is>
+      </c>
+      <c r="C273" s="5" t="inlineStr">
+        <is>
+          <t>Brand Spur African Medical Centre Of Excellence Opens In Abuja As Nigeria Targets $2.2bn Health Sector Overhaul</t>
+        </is>
+      </c>
+      <c r="D273" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E273" s="5" t="inlineStr">
+        <is>
+          <t>https://brandspurng.com/2026/09/19/african-medical-centre-of-excellence-opens-in-abuja-as-nigeria-targets-2-2bn-health-sector-overhaul/</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="5" t="inlineStr">
+        <is>
+          <t>King's College London</t>
+        </is>
+      </c>
+      <c r="B274" s="5" t="inlineStr">
+        <is>
+          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+        </is>
+      </c>
+      <c r="C274" s="5" t="inlineStr">
+        <is>
+          <t>King's College London New partnership to deliver medical excellence in Nigeria</t>
+        </is>
+      </c>
+      <c r="D274" s="5" t="inlineStr">
+        <is>
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="E274" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/news/new-partnership-to-deliver-medical-excellence-in-nigeria</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="5" t="inlineStr">
+        <is>
+          <t>King's College London</t>
+        </is>
+      </c>
+      <c r="B275" s="5" t="inlineStr">
+        <is>
+          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+        </is>
+      </c>
+      <c r="C275" s="5" t="inlineStr">
+        <is>
+          <t>Nnaemeka Onyekachi Afreximbank, BOI sign $75 million financing support for local manufacturers in Nigerian healthcare sector (reports KCL terms of agreement)</t>
+        </is>
+      </c>
+      <c r="D275" s="5" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="E275" s="5" t="inlineStr">
+        <is>
+          <t>https://nairametrics.com/2025/06/05/afreximbank-boi-sign-75-million-financing-support-for-local-manufacturers-in-nigerian-healthcare-sector/</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="5" t="inlineStr">
+        <is>
+          <t>Liverpool School of Tropical Medicine</t>
+        </is>
+      </c>
+      <c r="B276" s="5" t="inlineStr">
+        <is>
+          <t>National Postgraduate Medical College of Nigeria (with Wellbeing Foundation Africa)</t>
+        </is>
+      </c>
+      <c r="C276" s="5" t="inlineStr">
+        <is>
+          <t>Liverpool School of Tropical Medicine LSTM and Wellbeing Foundation Africa launch Advanced Training for Resident Doctors in Nigeria</t>
+        </is>
+      </c>
+      <c r="D276" s="5" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="E276" s="5" t="inlineStr">
+        <is>
+          <t>https://lstmed.ac.uk/news/liverpool-school-of-tropical-medicine-and-wellbeing-foundation-africa-launch-advanced-training-for-resident-doctors-in-nigeria/</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="5" t="inlineStr">
+        <is>
+          <t>Liverpool School of Tropical Medicine</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="inlineStr">
+        <is>
+          <t>National Postgraduate Medical College of Nigeria (with Wellbeing Foundation Africa)</t>
+        </is>
+      </c>
+      <c r="C277" s="5" t="inlineStr">
+        <is>
+          <t>Wellbeing Foundation Africa AOSS Training Expands to Port Harcourt and Gombe</t>
+        </is>
+      </c>
+      <c r="D277" s="5" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="E277" s="5" t="inlineStr">
+        <is>
+          <t>https://wbfafrica.org/aoss-training-expands-to-port-harcourt-and-gombe-ghwp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="5" t="inlineStr">
+        <is>
+          <t>Liverpool School of Tropical Medicine</t>
+        </is>
+      </c>
+      <c r="B278" s="5" t="inlineStr">
+        <is>
+          <t>National Postgraduate Medical College of Nigeria (with Wellbeing Foundation Africa)</t>
+        </is>
+      </c>
+      <c r="C278" s="5" t="inlineStr">
+        <is>
+          <t>Wellbeing Foundation Africa Liverpool School of Tropical Medicine, Wellbeing Foundation Africa, and Global Health Workforce Partnership</t>
+        </is>
+      </c>
+      <c r="D278" s="5" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="E278" s="5" t="inlineStr">
+        <is>
+          <t>https://wbfafrica.org/liverpool-school-of-tropical-medicine-wellbeing-foundation-africa-and-global-health-workforce-partnership/</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="5" t="inlineStr">
+        <is>
+          <t>Manipal Hospitals</t>
+        </is>
+      </c>
+      <c r="B279" s="5" t="inlineStr">
+        <is>
+          <t>Afe Babalola University Multi-System Hospital</t>
+        </is>
+      </c>
+      <c r="C279" s="5" t="inlineStr">
+        <is>
+          <t>Folasade Akpan ABUAD multi-system hospital records 50 successful kidney transplants</t>
+        </is>
+      </c>
+      <c r="D279" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E279" s="5" t="inlineStr">
+        <is>
+          <t>https://nannews.ng/abuad-multi-system-hospital-records-50-successful-kidney-transplants/</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="5" t="inlineStr">
+        <is>
+          <t>The Christie NHS Foundation Trust</t>
+        </is>
+      </c>
+      <c r="B280" s="5" t="inlineStr">
+        <is>
+          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+        </is>
+      </c>
+      <c r="C280" s="5" t="inlineStr">
+        <is>
+          <t>The Christie NHS Foundation Trust The Christie International hosts African Medical Centre of Excellence visit</t>
+        </is>
+      </c>
+      <c r="D280" s="5" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="E280" s="5" t="inlineStr">
+        <is>
+          <t>https://christie.nhs.uk/about-us/news-at-the-christie/latest-news-stories/the-christie-international-hosts-african-medical-centre-of-excellence-visit</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="5" t="inlineStr">
+        <is>
+          <t>The Christie NHS Foundation Trust</t>
+        </is>
+      </c>
+      <c r="B281" s="5" t="inlineStr">
+        <is>
+          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+        </is>
+      </c>
+      <c r="C281" s="5" t="inlineStr">
+        <is>
+          <t>The Christie NHS Foundation Trust The Christie supporting a new African Medical Centre of Excellence project</t>
+        </is>
+      </c>
+      <c r="D281" s="5" t="inlineStr"/>
+      <c r="E281" s="5" t="inlineStr">
+        <is>
+          <t>https://christie.nhs.uk/about-us/about-the-christie/the-christie-international/partnerships-experience/the-christie-supporting-a-new-african-medical-centre-of-excellence-project</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="5" t="inlineStr">
+        <is>
+          <t>The Royal Marsden NHS Foundation Trust</t>
+        </is>
+      </c>
+      <c r="B282" s="5" t="inlineStr">
+        <is>
+          <t>Marcelle Ruth Cancer Centre &amp; Specialist Hospital</t>
+        </is>
+      </c>
+      <c r="C282" s="5" t="inlineStr">
+        <is>
+          <t>BusinessDay Marcelle Ruth Cancer Centre partners UK's Royal Marsden to improve healthcare delivery in West Africa</t>
+        </is>
+      </c>
+      <c r="D282" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E282" s="5" t="inlineStr">
+        <is>
+          <t>https://businessday.ng/news/article/marcelle-ruth-cancer-centre-royal-marsden-partner-to-elevate-west-africas-oncology-care/</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="5" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="B283" s="5" t="inlineStr">
+        <is>
+          <t>University of Lagos (with Lagos University Teaching Hospital)</t>
+        </is>
+      </c>
+      <c r="C283" s="5" t="inlineStr">
+        <is>
+          <t>Adesina Wahab UNILAG, University of Birmingham sign MoU on Transnational Education Engagement</t>
+        </is>
+      </c>
+      <c r="D283" s="5" t="inlineStr">
+        <is>
+          <t>29 January 2026</t>
+        </is>
+      </c>
+      <c r="E283" s="5" t="inlineStr">
+        <is>
+          <t>https://www.vanguardngr.com/2026/01/unilag-university-of-birmingham-sign-mou-on-transnational-education-engagement/</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="5" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B284" s="5" t="inlineStr">
+        <is>
+          <t>Ahmadu Bello University</t>
+        </is>
+      </c>
+      <c r="C284" s="5" t="inlineStr">
+        <is>
+          <t>University of Glasgow School of Infection &amp; Immunity's Professor Harry de-Koning helps facilitate UofG-ABU MoU</t>
+        </is>
+      </c>
+      <c r="D284" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E284" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gla.ac.uk/schools/infectionimmunity/newsevents/headline_1265451_en.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="5" t="inlineStr">
+        <is>
+          <t>University of Maryland School of Medicine</t>
+        </is>
+      </c>
+      <c r="B285" s="5" t="inlineStr">
+        <is>
+          <t>Lagos University Teaching Hospital (LUTH)</t>
+        </is>
+      </c>
+      <c r="C285" s="5" t="inlineStr">
+        <is>
+          <t>Lagos University Teaching Hospital Maryland LUTH</t>
+        </is>
+      </c>
+      <c r="D285" s="5" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="E285" s="5" t="inlineStr">
+        <is>
+          <t>https://luth.gov.ng/news/maryland-luth</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="5" t="inlineStr">
+        <is>
+          <t>University of Maryland School of Medicine</t>
+        </is>
+      </c>
+      <c r="B286" s="5" t="inlineStr">
+        <is>
+          <t>Lagos University Teaching Hospital (LUTH)</t>
+        </is>
+      </c>
+      <c r="C286" s="5" t="inlineStr">
+        <is>
+          <t>Lagos University Teaching Hospital University of Maryland School of Medicine Collaborates with Lagos University Teaching Hospital on Non-Communicable Diseases</t>
+        </is>
+      </c>
+      <c r="D286" s="5" t="inlineStr">
+        <is>
+          <t>August 2024</t>
+        </is>
+      </c>
+      <c r="E286" s="5" t="inlineStr">
+        <is>
+          <t>https://luth.gov.ng/news/maryland-luth</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="5" t="inlineStr">
+        <is>
+          <t>University of Maryland School of Medicine</t>
+        </is>
+      </c>
+      <c r="B287" s="5" t="inlineStr">
+        <is>
+          <t>Lagos University Teaching Hospital (LUTH)</t>
+        </is>
+      </c>
+      <c r="C287" s="5" t="inlineStr">
+        <is>
+          <t>IHV Nigeria University of Maryland Dean of Medicine Visits LUTH</t>
+        </is>
+      </c>
+      <c r="D287" s="5" t="inlineStr">
+        <is>
+          <t>August 2024</t>
+        </is>
+      </c>
+      <c r="E287" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ihvnigeria.org/university-of-maryland-dean-of-medicine-visits-luth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="5" t="inlineStr">
+        <is>
+          <t>University of Virginia Health System</t>
+        </is>
+      </c>
+      <c r="B288" s="5" t="inlineStr">
+        <is>
+          <t>Federal Medical Centre Owo</t>
+        </is>
+      </c>
+      <c r="C288" s="5" t="inlineStr">
+        <is>
+          <t>UVA School of Medicine UVA Department of Nephrology Partners With Nigerian Federal Medical Center</t>
+        </is>
+      </c>
+      <c r="D288" s="5" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="E288" s="5" t="inlineStr">
+        <is>
+          <t>https://news.med.virginia.edu/community/uva-department-of-nephrology-partners-with-nigerian-federal-medical-center/</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="5" t="inlineStr">
+        <is>
+          <t>Yale School of Medicine (Department of Psychiatry)</t>
+        </is>
+      </c>
+      <c r="B289" s="5" t="inlineStr">
+        <is>
+          <t>Imo State University Teaching Hospital</t>
+        </is>
+      </c>
+      <c r="C289" s="5" t="inlineStr">
+        <is>
+          <t>Nigeria Health Watch Making Happiness Local: How a Project is Improving Access to Mental Healthcare in Imo State</t>
+        </is>
+      </c>
+      <c r="D289" s="5" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="E289" s="5" t="inlineStr">
+        <is>
+          <t>https://nigeriahealthwatch.com/articles/torchlight/making-happiness-local-how-a-project-is-improving-access-to-mental-healthcare-in-imo-state/</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="5" t="inlineStr">
+        <is>
+          <t>Yale School of Medicine (Department of Psychiatry)</t>
+        </is>
+      </c>
+      <c r="B290" s="5" t="inlineStr">
+        <is>
+          <t>Imo State University Teaching Hospital</t>
+        </is>
+      </c>
+      <c r="C290" s="5" t="inlineStr">
+        <is>
+          <t>Yale School of Medicine The HAPPINESS Project</t>
+        </is>
+      </c>
+      <c r="D290" s="5" t="inlineStr"/>
+      <c r="E290" s="5" t="inlineStr">
+        <is>
+          <t>https://medicine.yale.edu/psychiatry/education/programs-and-initiatives/happiness</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="5" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals</t>
+        </is>
+      </c>
+      <c r="B291" s="5" t="inlineStr">
+        <is>
+          <t>Duchess International Hospital (Reddington Hospital Group)</t>
+        </is>
+      </c>
+      <c r="C291" s="5" t="inlineStr">
+        <is>
+          <t>ThisDay Duchess International Hospital Has Put Lagos on World Healthcare Map, Says US Consul General</t>
+        </is>
+      </c>
+      <c r="D291" s="5" t="inlineStr">
+        <is>
+          <t>11 November 2021</t>
+        </is>
+      </c>
+      <c r="E291" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thisdaylive.com/index.php/2021/11/11/duchess-international-hospital-has-put-lagos-on-world-healthcare-map-says-us-consul-general/</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="5" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals</t>
+        </is>
+      </c>
+      <c r="B292" s="5" t="inlineStr">
+        <is>
+          <t>Duchess International Hospital (Reddington Hospital Group)</t>
+        </is>
+      </c>
+      <c r="C292" s="5" t="inlineStr">
+        <is>
+          <t>Appolonia Adeyemi Duchess International Hospital debuts in Lagos, builds capacity</t>
+        </is>
+      </c>
+      <c r="D292" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E292" s="5" t="inlineStr">
+        <is>
+          <t>https://newtelegraphng.com/?p=192437</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="5" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals</t>
+        </is>
+      </c>
+      <c r="B293" s="5" t="inlineStr">
+        <is>
+          <t>State House Clinic</t>
+        </is>
+      </c>
+      <c r="C293" s="5" t="inlineStr">
+        <is>
+          <t>Blueprint State House Clinic, Indian hospital collaborate to assist heart, kidney, cancer patients</t>
+        </is>
+      </c>
+      <c r="D293" s="5" t="inlineStr">
+        <is>
+          <t>2022-07-29</t>
+        </is>
+      </c>
+      <c r="E293" s="5" t="inlineStr">
+        <is>
+          <t>https://blueprint.ng/state-house-clinic-indian-hospital-collaborate-to-assist-heart-kidney-cancer-patients/</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="5" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals</t>
+        </is>
+      </c>
+      <c r="B294" s="5" t="inlineStr">
+        <is>
+          <t>State House Clinic</t>
+        </is>
+      </c>
+      <c r="C294" s="5" t="inlineStr">
+        <is>
+          <t>ThisDay Medical Tourism: Indian Hospital to Train Nigerian Doctors on Cancer Treatment</t>
+        </is>
+      </c>
+      <c r="D294" s="5" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="E294" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thisdaylive.com/2024/03/05/medical-tourism-indian-hospital-to-train-nigerian-doctors-on-cancer-treatment/</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="5" t="inlineStr">
+        <is>
+          <t>Memorial Hospitals Group</t>
+        </is>
+      </c>
+      <c r="B295" s="5" t="inlineStr">
+        <is>
+          <t>Kasi Healthcare</t>
+        </is>
+      </c>
+      <c r="C295" s="5" t="inlineStr">
+        <is>
+          <t>Temitayo Ayetoto-Oladehinde Nigeria partners Turkey to tap $8.5trn healthcare market</t>
+        </is>
+      </c>
+      <c r="D295" s="5" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="E295" s="5" t="inlineStr">
+        <is>
+          <t>https://businessday.ng/news/article/nigeria-partners-turkey-to-tap-8-5trn-healthcare-market/</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="5" t="inlineStr">
+        <is>
+          <t>Peking University People's Hospital (named variously in press as People's University Hospital, Beijing)</t>
+        </is>
+      </c>
+      <c r="B296" s="5" t="inlineStr">
+        <is>
+          <t>University of Abuja Teaching Hospital</t>
+        </is>
+      </c>
+      <c r="C296" s="5" t="inlineStr">
+        <is>
+          <t>Within Nigeria Nigeria signs letter of intent with China to improve health sector</t>
+        </is>
+      </c>
+      <c r="D296" s="5" t="inlineStr">
+        <is>
+          <t>2022-08-20</t>
+        </is>
+      </c>
+      <c r="E296" s="5" t="inlineStr">
+        <is>
+          <t>https://www.withinnigeria.com/broadnews/2022/08/20/nigeria-signs-letter-of-intent-with-china-to-improve-health-sector/</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="5" t="inlineStr">
+        <is>
+          <t>Peking University People's Hospital (named variously in press as People's University Hospital, Beijing)</t>
+        </is>
+      </c>
+      <c r="B297" s="5" t="inlineStr">
+        <is>
+          <t>University of Abuja Teaching Hospital</t>
+        </is>
+      </c>
+      <c r="C297" s="5" t="inlineStr">
+        <is>
+          <t>University of Abuja Teaching Hospital Nigeria, China signs letter of intent to improve health sector</t>
+        </is>
+      </c>
+      <c r="D297" s="5" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="E297" s="5" t="inlineStr">
+        <is>
+          <t>https://uathospital.ng/nigeria-china-signs-letter-of-intent-to-improve-health-sector/</t>
         </is>
       </c>
     </row>
@@ -14703,6 +17758,59 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId241"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId242"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E297" r:id="rId296"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Partnerships_Tracker.xlsx
+++ b/output/Partnerships_Tracker.xlsx
@@ -231,8 +231,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tracker" displayName="Tracker" ref="A1:L150" headerRowCount="1">
-  <autoFilter ref="A1:L150"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tracker" displayName="Tracker" ref="A1:L165" headerRowCount="1">
+  <autoFilter ref="A1:L165"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Status"/>
     <tableColumn id="2" name="Country"/>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF(Tracker!$A$2:$A$150,A5)</f>
+        <f>COUNTIF(Tracker!$A$2:$A$165,A5)</f>
         <v/>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Tracker!$A$2:$A$150,A6)</f>
+        <f>COUNTIF(Tracker!$A$2:$A$165,A6)</f>
         <v/>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Tracker!$A$2:$A$150,A7)</f>
+        <f>COUNTIF(Tracker!$A$2:$A$165,A7)</f>
         <v/>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -670,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L150"/>
+  <dimension ref="A1:L165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7743,12 +7743,12 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C123" s="13" t="inlineStr">
         <is>
-          <t>Johns Hopkins University (Johns Hopkins Hospital)</t>
+          <t>Johns Hopkins University (Bloomberg School of Public Health, Center for Indigenous Health)</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="E123" s="12" t="inlineStr">
         <is>
-          <t>Afe Babalola University (ABUAD)</t>
+          <t>University of Otago, Te Rōpū Rangahau Hauora a Eru Pōmare (Eru Pōmare Māori Health Research Centre)</t>
         </is>
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>Training and education</t>
+          <t>Research collaboration</t>
         </is>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>Tripartite agreement with the Little by Little Foundation letting high performing ABUAD medical students do part of their fifth year clinical electives at Johns Hopkins Hospital.</t>
+          <t>The Johns Hopkins Center for Indigenous Health runs the SPIRIT collective, a five year program funded by the LEGO Foundation that adapts its Family Spirit home visiting model and builds Indigenous playspaces. Its lead partner in New Zealand is the Eru Pōmare Māori Health Research Centre at the University of Otago, working with three Māori community sites.</t>
         </is>
       </c>
       <c r="H123" s="12" t="inlineStr">
@@ -7779,17 +7779,17 @@
       <c r="I123" s="12" t="inlineStr"/>
       <c r="J123" s="12" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="K123" s="12" t="inlineStr">
         <is>
-          <t>ABUAD notice dated 17 January 2023 reports the signing on 10 January 2023. No later evidence of placements found in 2024 to 2026 searches. ABUAD's 5 February 2025 release on its seventh induction ceremony describes the six-week Johns Hopkins Hospital electives as ongoing.</t>
+          <t>JHCIH won the LEGO Foundation Build a World of Play Challenge in December 2022 and funding began in 2023. A JHCIH Q&amp;A published 21 January 2026 says the program is past its halfway point and names the University of Otago's Eru Pōmare centre as lead partner in Aotearoa, with partners meeting in Alice Springs in August 2024. The program page lists its status as Active.</t>
         </is>
       </c>
       <c r="L123" s="14" t="inlineStr">
         <is>
-          <t>Afe Babalola University, 2023-01-17</t>
+          <t>Johns Hopkins Center for Indigenous Health, 2026-01-21</t>
         </is>
       </c>
     </row>
@@ -7801,53 +7801,53 @@
       </c>
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C124" s="13" t="inlineStr">
         <is>
-          <t>Mayo Clinic (Mayo Clinic Global Consulting)</t>
+          <t>Icon Oncology Group (Icon Group)</t>
         </is>
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E124" s="12" t="inlineStr">
         <is>
-          <t>Iwosan Investments Limited (Iwosan Lagoon Hospitals and Lagos Medipark Hospital)</t>
+          <t>Bowen Icon Cancer Centre (joint venture with Evolution Healthcare, Bowen Hospital)</t>
         </is>
       </c>
       <c r="F124" s="12" t="inlineStr">
         <is>
-          <t>Advisory and consulting</t>
+          <t>Ownership or management</t>
         </is>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
-          <t>Iwosan Investments, owner of the Iwosan Lagoon Hospitals group, engaged Mayo Clinic Global Consulting for strategic advice on organisation and clinical practice. The work starts with Iwosan Lagoon Hospitals and the planned Lagos Medipark Hospital.</t>
+          <t>Icon, Australia's largest dedicated cancer care provider, co-owns and runs the Bowen Icon Cancer Centre in Wellington as a joint venture with Evolution Healthcare. The centre offers private chemotherapy, haematology and, since 2019, radiation therapy.</t>
         </is>
       </c>
       <c r="H124" s="12" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2017-07</t>
         </is>
       </c>
       <c r="I124" s="12" t="inlineStr"/>
       <c r="J124" s="12" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="K124" s="12" t="inlineStr">
         <is>
-          <t>Iwosan's announcement was syndicated on 17 April 2025 (The Sun) and carried by BusinessDay and BrandIconImage. No page on Mayo's own newsroom was found, so confirmation rests on the Nigerian company's release. No end date or contract term is stated.</t>
+          <t>Newshub reported the Prime Minister opening the centre in July 2017. Icon's current group pages (copyright 2026, and mentioning its 2024 Pharmaxo acquisition) still describe Bowen Icon Cancer Centre as a joint venture with Evolution Healthcare, and the centre's own site is live under Icon branding. None of these pages carries a dated news item on the joint venture after 2017, so Active rests on current corporate pages rather than a dated release. Icon's 4 February 2025 news item says it introduced clinical trials at Bowen Icon Cancer Centre.</t>
         </is>
       </c>
       <c r="L124" s="14" t="inlineStr">
         <is>
-          <t>The Sun Nigeria, 2025-04-17</t>
+          <t>Icon Oncology Group, 2026</t>
         </is>
       </c>
     </row>
@@ -7859,22 +7859,22 @@
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C125" s="13" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>National University of Singapore and National University Health System</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="E125" s="12" t="inlineStr">
         <is>
-          <t>Lagos University Teaching Hospital (LUTH) and College of Medicine, University of Lagos</t>
+          <t>Liggins Institute, University of Auckland</t>
         </is>
       </c>
       <c r="F125" s="12" t="inlineStr">
@@ -7884,24 +7884,28 @@
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
-          <t>LUTH and the University of Lagos College of Medicine serve as research and training hubs of the MSK founded ARGO consortium. They take part in joint cancer studies, including a colorectal cancer immunotherapy trial.</t>
-        </is>
-      </c>
-      <c r="H125" s="12" t="inlineStr"/>
+          <t>The Liggins Institute has formal agreements with the National University of Singapore and works with NUS and National University Hospital in the EpiGen consortium. Their joint NiPPeR trial and child follow-up study enrolled families in Auckland, Singapore and Southampton.</t>
+        </is>
+      </c>
+      <c r="H125" s="12" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
       <c r="I125" s="12" t="inlineStr"/>
       <c r="J125" s="12" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="K125" s="12" t="inlineStr">
         <is>
-          <t>MSK's 2025 GCRT Update names OAUTHC and the College of Medicine, University of Lagos/LUTH as ARGO's research and training hubs. MSK's press page describes the colorectal immunotherapy trial with OAUTHC, LUTH and Medserve. Start year not stated on a dated page.</t>
+          <t>The Liggins Institute's partnerships page cites formal agreements with NUS and the Singapore Institute for Clinical Sciences. The NiPPeR Child study (NCT05934422) names NUS, NUHS and National University Hospital as collaborators and Shiao-Yng Chan of NUS as a principal investigator alongside Auckland. It completed in August 2025, and the record was updated in November 2025. The NiPPeR Child follow-up ran from June 2023 to its completion on 14 August 2025.</t>
         </is>
       </c>
       <c r="L125" s="14" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center, 2026</t>
+          <t>University of Auckland</t>
         </is>
       </c>
     </row>
@@ -7913,53 +7917,53 @@
       </c>
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C126" s="13" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>UCLPartners</t>
         </is>
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E126" s="12" t="inlineStr">
         <is>
-          <t>Obafemi Awolowo University Teaching Hospitals Complex (OAUTHC)</t>
+          <t>Health New Zealand Te Whatu Ora (HealthX programme)</t>
         </is>
       </c>
       <c r="F126" s="12" t="inlineStr">
         <is>
-          <t>Research collaboration</t>
+          <t>Advisory and consulting</t>
         </is>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
-          <t>MSK's Global Cancer Research and Training program partners with OAUTHC, home of the African Research Group for Oncology (ARGO), an NCI recognised consortium founded in 2013. The work covers cancer research, trials and training for Nigerian clinicians.</t>
+          <t>Health New Zealand's HealthX programme signed an agreement with UCLPartners, the London academic health science partnership of NHS organisations and universities. UCLPartners advises on testing and scaling digital and AI tools such as emergency department AI scribes.</t>
         </is>
       </c>
       <c r="H126" s="12" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="I126" s="12" t="inlineStr"/>
       <c r="J126" s="12" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="K126" s="12" t="inlineStr">
         <is>
-          <t>MSK's 2025 GCRT Update reports the annual ARGO symposium held at Ile-Ife in September 2025 and a colorectal immunotherapy trial run with OAUTHC. MSK's program page dates the partnership to the 2009 training of OAUTHC surgeon Isaac Alatise; start year is that visit, ARGO itself dates to 2013.</t>
+          <t>A Health NZ sector update republished by HiNZ on 8 July 2026 announces the agreement, quotes Health NZ chief executive Dale Bramley and UCLPartners chief executive Chris Laing, and says UCLPartners horizon scanning already informed the AI scribe rollout.</t>
         </is>
       </c>
       <c r="L126" s="14" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center, 2026</t>
+          <t>HiNZ (eHealthNews.nz), 2026-07-08</t>
         </is>
       </c>
     </row>
@@ -7971,37 +7975,37 @@
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C127" s="13" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital</t>
+          <t>Universitas Indonesia (Faculty of Public Health)</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="E127" s="12" t="inlineStr">
         <is>
-          <t>Abubakar Tafawa Balewa University Teaching Hospital (ATBUTH)</t>
+          <t>University of Otago (Faculty of Medicine)</t>
         </is>
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>Clinical affiliation</t>
+          <t>Training and education</t>
         </is>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>ATBUTH signed a Medical Institution Membership Agreement and joined the St. Jude Global Alliance, a care and training network for childhood cancer. Membership gives access to mentorship, shared treatment protocols and training.</t>
+          <t>Universitas Indonesia's Faculty of Public Health and Otago's Faculty of Medicine signed an implementation agreement for a joint Master of Public Health, with study split between Jakarta and Otago. It builds on a 2024 university MoU.</t>
         </is>
       </c>
       <c r="H127" s="12" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I127" s="12" t="inlineStr"/>
@@ -8012,12 +8016,12 @@
       </c>
       <c r="K127" s="12" t="inlineStr">
         <is>
-          <t>Leadership newspaper published the hospital's statement on 26 October 2025 (signing described as the day before). Not confirmed on St. Jude's own site.</t>
+          <t>An FPH UI release dated 31 October 2025 reports that Otago's Associate Dean of International Health Sciences signed the Agreement of Implementation on a 23 to 24 October 2025 visit, extending MoU No. 56/MOU/R/UI/2024.</t>
         </is>
       </c>
       <c r="L127" s="14" t="inlineStr">
         <is>
-          <t>Leadership Newspapers, 2025-10-26</t>
+          <t>Universitas Indonesia, 2025-11-04</t>
         </is>
       </c>
     </row>
@@ -8029,53 +8033,53 @@
       </c>
       <c r="B128" s="12" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C128" s="13" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital</t>
+          <t>University of Southampton (MRC Lifecourse Epidemiology Centre, EpiGen Global Research Consortium)</t>
         </is>
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E128" s="12" t="inlineStr">
         <is>
-          <t>The Dorcas Cancer Foundation (TDCF)</t>
+          <t>Liggins Institute, University of Auckland</t>
         </is>
       </c>
       <c r="F128" s="12" t="inlineStr">
         <is>
-          <t>Clinical affiliation</t>
+          <t>Research collaboration</t>
         </is>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
-          <t>TDCF joined the St. Jude Global Alliance as the first Nigerian non profit member, to improve paediatric cancer outcomes in Nigeria and sub Saharan Africa. TDCF runs a paediatric radiation oncology training course.</t>
+          <t>Southampton and the University of Auckland's Liggins Institute are founding partners of the EpiGen Global Research Consortium, with Singapore partners. Together they run the NiPPeR preconception nutrition trial and its child follow-up study.</t>
         </is>
       </c>
       <c r="H128" s="12" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="I128" s="12" t="inlineStr"/>
       <c r="J128" s="12" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="K128" s="12" t="inlineStr">
         <is>
-          <t>ThisDay and BusinessDay reported the admission on 17 December 2024. The Nigerian party is a non profit, not a hospital, and the tie is an alliance membership; flag for the verifier. Not confirmed on St. Jude's site. Caveat: the Nigerian party is a cancer foundation working with pediatric oncology units, not a hospital.</t>
+          <t>The Liggins Institute lists itself as a foundation partner of EpiGen, established 2006, with two Southampton units. The NiPPeR Child follow-up study (NCT05934422), sponsored by Southampton with Auckland as a site and Wayne Cutfield as a principal investigator, ran from June 2023 to August 2025, and its registry record was updated in November 2025. The NiPPeR Child follow-up ran from June 2023 to its completion on 14 August 2025.</t>
         </is>
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
-          <t>ThisDay, 2024-12-17</t>
+          <t>University of Auckland</t>
         </is>
       </c>
     </row>
@@ -8087,22 +8091,22 @@
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C129" s="13" t="inlineStr">
         <is>
-          <t>University of Illinois Chicago (UIC School of Public Health)</t>
+          <t>University of Wollongong (Graduate School of Medicine)</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
-          <t>Lagos State University (LASU)</t>
+          <t>University of Waikato (New Zealand Graduate School of Medicine)</t>
         </is>
       </c>
       <c r="F129" s="12" t="inlineStr">
@@ -8112,28 +8116,28 @@
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>Framework agreement signed 28 July 2026 for academic collaboration, joint research and student and faculty exchange, focused on urban health, emergency preparedness and AI-enabled public health tools.</t>
+          <t>Wollongong and Waikato signed a memorandum of understanding under which Wollongong's rural medical education staff help design the curriculum of Waikato's new graduate entry medical school. The school focuses on primary care, rural health and equity.</t>
         </is>
       </c>
       <c r="H129" s="12" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="I129" s="12" t="inlineStr"/>
       <c r="J129" s="12" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="K129" s="12" t="inlineStr">
         <is>
-          <t>UIC School of Public Health news, 4 August 2026, reports the memorandum signed on 28 July 2026 in Chicago by LASU's Vice Chancellor and UIC representatives. A university to university agreement with no hospital named.</t>
+          <t>A University of Wollongong release dated 17 October 2025 announces the MoU signing by Vice-Chancellors Max Lu and Neil Quigley, with quotes from Waikato's Pro Vice-Chancellor Health.</t>
         </is>
       </c>
       <c r="L129" s="14" t="inlineStr">
         <is>
-          <t>UIC School of Public Health, 2026-08-04</t>
+          <t>University of Wollongong, 2025-10-20</t>
         </is>
       </c>
     </row>
@@ -8145,22 +8149,22 @@
       </c>
       <c r="B130" s="12" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C130" s="13" t="inlineStr">
         <is>
-          <t>University of Maryland School of Medicine (Institute of Human Virology)</t>
+          <t>West Visayas State University</t>
         </is>
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="E130" s="12" t="inlineStr">
         <is>
-          <t>Institute of Human Virology Nigeria (IHVN)</t>
+          <t>University of Otago</t>
         </is>
       </c>
       <c r="F130" s="12" t="inlineStr">
@@ -8170,45 +8174,45 @@
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
-          <t>IHVN is the Nigerian affiliate of the Maryland Institute of Human Virology, delivering HIV, TB and cancer care, training and research. It opened a multi campus site in Abuja in 2023.</t>
+          <t>West Visayas State University and Otago signed a memorandum of understanding covering joint research in digital health and medicine, faculty and student exchange, and co-development of digital health tools.</t>
         </is>
       </c>
       <c r="H130" s="12" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="I130" s="12" t="inlineStr"/>
       <c r="J130" s="12" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="K130" s="12" t="inlineStr">
         <is>
-          <t>University of Maryland news from June 2023 reports the Abuja campus launch with UMB leadership present. No dated evidence from October 2024 onward found. IHVN is an NGO affiliate, not a hospital; flag for the verifier. NIH RePORTER shows Fogarty training grant D43TW012280 awarded to IHVN for FY2026 (budget start 1 February 2026), co-led with the UMSOM Institute of Human Virology. Caveat: IHVN is the Institute's Nigerian NGO affiliate, not a hospital.</t>
+          <t>A WVSU release reports the MoU was signed on 27 June 2025 in Dunedin by WVSU President Joselito Villaruz and Otago Vice-Chancellor Grant Robertson during a CHED higher education mission. No Otago-side release was found.</t>
         </is>
       </c>
       <c r="L130" s="14" t="inlineStr">
         <is>
-          <t>University of Maryland School of Medicine, 2023-06</t>
+          <t>West Visayas State University, 2025-06</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="11" t="inlineStr">
-        <is>
-          <t>Active</t>
+      <c r="A131" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C131" s="13" t="inlineStr">
         <is>
-          <t>University of Miami (Sylvester Comprehensive Cancer Center)</t>
+          <t>Sanford Health (Sanford World Clinic)</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
@@ -8218,123 +8222,123 @@
       </c>
       <c r="E131" s="12" t="inlineStr">
         <is>
-          <t>Ahmadu Bello University Teaching Hospital (ABUTH)</t>
+          <t>Omni Health (OmniHealth) primary care network</t>
         </is>
       </c>
       <c r="F131" s="12" t="inlineStr">
         <is>
-          <t>Research collaboration</t>
+          <t>Ownership or management</t>
         </is>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>ABUTH is a recruiting site in a University of Miami led trial of niraparib maintenance therapy for ovarian cancer in women of African ancestry. The tie began with a Miami delegation visit to ABUTH in 2023.</t>
+          <t>Sanford World Clinic and Omni Health opened a general practice clinic in central Auckland in early 2018 and Sanford has since invested in and helped run Omni Health's national primary care network. The network now has about 22 medical centres in 21 towns, and Sanford recruits doctors for it.</t>
         </is>
       </c>
       <c r="H131" s="12" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="I131" s="12" t="inlineStr"/>
       <c r="J131" s="12" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2021-05</t>
         </is>
       </c>
       <c r="K131" s="12" t="inlineStr">
         <is>
-          <t>ClinicalTrials.gov NCT06412120 lists ABUTH Zaria as recruiting, study start 28 July 2026, record updated 5 August 2026, Miami investigators Schlumbrecht and George. ABUTH's August 2023 news item reports the planning visit (page not retrievable; seen in search results only).</t>
+          <t>A May 2021 SiouxFalls.Business report says Sanford helped build a $30 million network of clinics with Omni Health through multiple investments, with a Sanford executive acting as its COO from Sioux Falls. Sanford's current World Clinic page says it has collaborated with Omni Health since 2018. Sanford World Clinic's recruiting page on PracticeMatch lists Omni Health physician openings posted 6 October 2025. The October 2025 recruitment listing could not be re-verified; Sanford's current page says in the present tense that it has collaborated with Omni Health since 2018 but carries no date.</t>
         </is>
       </c>
       <c r="L131" s="14" t="inlineStr">
         <is>
-          <t>US National Library of Medicine, 2026-08-05</t>
+          <t>Sanford Health</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="11" t="inlineStr">
-        <is>
-          <t>Active</t>
+      <c r="A132" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="B132" s="12" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C132" s="13" t="inlineStr">
         <is>
-          <t>University of Virginia Health System</t>
+          <t>Children's Cancer Institute and Sydney Children's Hospital, Randwick (Zero Childhood Cancer Program)</t>
         </is>
       </c>
       <c r="D132" s="12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E132" s="12" t="inlineStr">
         <is>
-          <t>Federal Medical Centre Umuahia</t>
+          <t>Starship Children's Hospital and Christchurch Hospital (Health New Zealand)</t>
         </is>
       </c>
       <c r="F132" s="12" t="inlineStr">
         <is>
-          <t>Training and education</t>
+          <t>Research collaboration</t>
         </is>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
-          <t>UVA nephrology supports the kidney transplant programme at FMC Umuahia through mentorship, coordinator training and joint research under the ISN and TTS Sister Transplant Centers Program. The pair reached Level B in 2026.</t>
+          <t>The ZERO precision medicine program, led by Children's Cancer Institute and Sydney Children's Hospital Randwick, opened to New Zealand children in 2024. Starship's tumours are sent for genomic analysis that guides treatment, and Christchurch was listed as a second site.</t>
         </is>
       </c>
       <c r="H132" s="12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="I132" s="12" t="inlineStr"/>
       <c r="J132" s="12" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="K132" s="12" t="inlineStr">
         <is>
-          <t>UVA Medicine in Motion news, 13 May 2026, reports the move from Level C to Level B, shorter post transplant stays (14 to 8 days), four trained coordinators and eight joint publications in the first two years, which puts the start near 2024.</t>
+          <t>ANZCHOG, the study sponsor, announced on 19 August 2024 that ZERO2 opened at Starship on 17 July 2024. The ZERO2 registry record (NCT05504772, last updated July 2024) lists Starship as recruiting and Christchurch as not yet recruiting. Children's Cancer Institute's undated program page says both New Zealand sites opened in 2024. No dated evidence from October 2024 or later was found.</t>
         </is>
       </c>
       <c r="L132" s="14" t="inlineStr">
         <is>
-          <t>UVA Medicine in Motion, 2026-05-13</t>
+          <t>Australian and New Zealand Children's Haematology/Oncology Group, 2024-08-19</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="11" t="inlineStr">
-        <is>
-          <t>Active</t>
+      <c r="A133" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C133" s="13" t="inlineStr">
         <is>
-          <t>Vanderbilt University Medical Center (Vanderbilt Institute for Global Health)</t>
+          <t>Children's Hospital of Zhejiang University School of Medicine</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
-          <t>Aminu Kano Teaching Hospital and Bayero University Kano</t>
+          <t>NZ-China Non-Communicable Diseases Research Collaboration Centre (University of Otago)</t>
         </is>
       </c>
       <c r="F133" s="12" t="inlineStr">
@@ -8344,260 +8348,264 @@
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>Long running research and training partnership, now in its second Fogarty funded phase (V-BRCH 2), building Nigerian capacity for clinical research on HIV and related chronic diseases. Related programmes cover child neurology and research administration.</t>
+          <t>The Children's Hospital of Zhejiang University signed a 2017 memorandum of understanding with the Otago-hosted NZ-China NCD Research Collaboration Centre on childhood obesity and diabetes research. Its vice president presented at the centre's 2022 forum.</t>
         </is>
       </c>
       <c r="H133" s="12" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2017-10</t>
         </is>
       </c>
       <c r="I133" s="12" t="inlineStr"/>
       <c r="J133" s="12" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="K133" s="12" t="inlineStr">
         <is>
-          <t>Fogarty grant D43TW011544 lists Aminu Kano Teaching Hospital as principal institution with award years 2020 to 2029, and Vanderbilt's V-BRCH page describes V-BRCH 2 as a continuation. Both pages are undated, so last evidence reflects page content as read on 16 October 2026; flag for the verifier. Start year is the 2020 award; the AKTH tie is older. Fogarty grant D43TW011544 was renewed in 2025 with Aminu Kano Teaching Hospital as grantee; the FY2026 award notice is dated 18 December 2025 (NIH RePORTER).</t>
+          <t>The centre reported the October 2017 MoU signing. Its report on the 5 to 6 July 2022 forum cites a presentation by the hospital's vice president Jun-Fen Fu on obesity and diabetes in children. Nothing later was found. Later evidence is forum participation only (a virtual 2022 forum); the MoU dates from 2017.</t>
         </is>
       </c>
       <c r="L133" s="14" t="inlineStr">
         <is>
-          <t>US National Institutes of Health</t>
+          <t>NZ-China NCD CRCC, 2017-11-02</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="11" t="inlineStr">
-        <is>
-          <t>Active</t>
+      <c r="A134" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="B134" s="12" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C134" s="13" t="inlineStr">
         <is>
-          <t>Virginia Commonwealth University (VCU Massey Comprehensive Cancer Center)</t>
+          <t>Fiji National University (College of Medicine, Nursing and Health Sciences)</t>
         </is>
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Fiji</t>
         </is>
       </c>
       <c r="E134" s="12" t="inlineStr">
         <is>
-          <t>National Hospital Abuja</t>
+          <t>University of Auckland</t>
         </is>
       </c>
       <c r="F134" s="12" t="inlineStr">
         <is>
-          <t>Research collaboration</t>
+          <t>Training and education</t>
         </is>
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
-          <t>Two year memorandum of understanding between the National Hospital and VCU Massey Comprehensive Cancer Center to build cancer research capacity. Focus areas are clinical trials, training of new scientists and moving research into patient care.</t>
+          <t>Fiji National University and the University of Auckland signed a memorandum of understanding, driven by FNU's medical college and Auckland's paediatrics department, covering staff capacity building, exchanges and joint research.</t>
         </is>
       </c>
       <c r="H134" s="12" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="I134" s="12" t="inlineStr"/>
       <c r="J134" s="12" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="K134" s="12" t="inlineStr">
         <is>
-          <t>News Agency of Nigeria and Nairametrics reported the signing on 1 July 2025 by Prof Muhammad Mahmud and Dr Robert Winn, saying it was signed on a Tuesday (24 June or 1 July 2025). Term is two years, so it runs to mid 2027.</t>
+          <t>An FNU press release dated 9 May 2022 reports the MoU signing, attended by Auckland paediatrics Associate Professor Stephen Howie. No later activity was found.</t>
         </is>
       </c>
       <c r="L134" s="14" t="inlineStr">
         <is>
-          <t>Nairametrics, 2025-07-01</t>
+          <t>Fiji National University, 2022-05-09</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="11" t="inlineStr">
-        <is>
-          <t>Active</t>
+      <c r="A135" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C135" s="13" t="inlineStr">
         <is>
-          <t>Evercare Group (owned at its 2021 launch by the TPG-managed Evercare Health Fund)</t>
+          <t>Huashan Hospital (Fudan University)</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>Evercare Hospital Lekki</t>
+          <t>NZ-China Non-Communicable Diseases Research Collaboration Centre (University of Otago)</t>
         </is>
       </c>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>Ownership or management</t>
+          <t>Research collaboration</t>
         </is>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>Evercare Group owns and operates Evercare Hospital Lekki, a 165-bed tertiary hospital in Lagos that opened in February 2021, as part of its network of hospitals in Africa and South Asia.</t>
+          <t>Huashan Hospital signed a 2017 memorandum of understanding with the Otago-hosted NZ-China NCD Research Collaboration Centre for joint research on brain and other non-communicable diseases. Its researchers took part in the centre's 2022 forum.</t>
         </is>
       </c>
       <c r="H135" s="12" t="inlineStr">
         <is>
-          <t>2021-03</t>
+          <t>2017-10</t>
         </is>
       </c>
       <c r="I135" s="12" t="inlineStr"/>
       <c r="J135" s="12" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="K135" s="12" t="inlineStr">
         <is>
-          <t>ThisDay, 10 October 2024, describes Evercare Hospital Lekki as part of the Evercare Group, which operates in Kenya and Pakistan as well as Nigeria, announcing new cochlear implant surgery. TPG's release and a 2021 report document the group's ownership and the February 2021 opening. A 2026 LinkedIn post suggests continued operation but was not verified. Ownership is as of the 2021 launch; no later ownership confirmation was found.</t>
+          <t>The centre reported the October 2017 signing of four MoUs including Huashan. Its report on the 3rd NZ-China NCD forum, held 5 to 6 July 2022, cites a Huashan Hospital presentation on AI digital monitoring. Nothing later was found. Later evidence is forum participation only (a virtual 2022 forum); the MoU dates from 2017.</t>
         </is>
       </c>
       <c r="L135" s="14" t="inlineStr">
         <is>
-          <t>ThisDay, 2024-10-10</t>
+          <t>NZ-China NCD CRCC, 2017-11-02</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="11" t="inlineStr">
-        <is>
-          <t>Active</t>
+      <c r="A136" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="B136" s="12" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C136" s="13" t="inlineStr">
         <is>
-          <t>King's College Hospital NHS Foundation Trust</t>
+          <t>Shanghai Ninth People's Hospital (Shanghai Jiao Tong University School of Medicine)</t>
         </is>
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E136" s="12" t="inlineStr">
         <is>
-          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+          <t>University of Otago Faculty of Dentistry</t>
         </is>
       </c>
       <c r="F136" s="12" t="inlineStr">
         <is>
-          <t>Advisory and consulting</t>
+          <t>Research collaboration</t>
         </is>
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
-          <t>King's is the appointed Clinical Partner of the AMCE, supporting clinical protocols, governance, service set-up, recruitment and training for the 170-bed specialist hospital in Abuja. Clinical services were commissioned in June 2025.</t>
+          <t>Shanghai Ninth People's Hospital and Otago's Faculty of Dentistry signed a memorandum of understanding and opened the Shanghai-New Zealand Joint Laboratory of Dentistry for craniofacial research.</t>
         </is>
       </c>
       <c r="H136" s="12" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="I136" s="12" t="inlineStr"/>
       <c r="J136" s="12" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="K136" s="12" t="inlineStr">
         <is>
-          <t>Afreximbank announced on 3 June 2021 that it had signed an agreement appointing King's College Hospital as Clinical Partner. Nairametrics reports the AMCE was commissioned on 5 June 2025 with Vice President Shettima praising the AMCE and King's partnership. Brand Spur (19 September 2026) describes the centre as developed with King's College Hospital and now commissioned.</t>
+          <t>A Shanghai Jiao Tong University School of Medicine release dated 28 November 2023 reports the signing on 27 November 2023 by hospital president Wu Hao and Otago dental dean Paul Cooper. No later activity was found.</t>
         </is>
       </c>
       <c r="L136" s="14" t="inlineStr">
         <is>
-          <t>African Medical Centre of Excellence (amce.net), 2021-06-03</t>
+          <t>Shanghai Jiao Tong University School of Medicine, 2023-11-28</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="11" t="inlineStr">
-        <is>
-          <t>Active</t>
+      <c r="A137" s="16" t="inlineStr">
+        <is>
+          <t>Ended</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C137" s="13" t="inlineStr">
         <is>
-          <t>King's College London</t>
+          <t>Healthe Care Australia (then a subsidiary of Luye Medical Group)</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E137" s="12" t="inlineStr">
         <is>
-          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+          <t>Boulcott Hospital (Pulse Health NZ)</t>
         </is>
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>Training and education</t>
+          <t>Ownership or management</t>
         </is>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>King's College London and Afreximbank agreed to plan a medical and nursing school at the AMCE in Abuja, drawing on King's healthcare education expertise. A further terms of agreement was signed in June 2025.</t>
+          <t>Healthe Care, an Australian private hospital operator, owned Pulse Health NZ and through it ran Boulcott Hospital in Lower Hutt. It sold Pulse Health NZ to a Pacific Equity Partners vehicle in late 2021, and Boulcott's operations passed to Rangatira Investments in March 2022.</t>
         </is>
       </c>
       <c r="H137" s="12" t="inlineStr">
         <is>
-          <t>2023-11</t>
-        </is>
-      </c>
-      <c r="I137" s="12" t="inlineStr"/>
+          <t>2017-05</t>
+        </is>
+      </c>
+      <c r="I137" s="12" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
       <c r="J137" s="12" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="K137" s="12" t="inlineStr">
         <is>
-          <t>King's news release of 28 November 2023 reports the memorandum of agreement signed on 24 November 2023 for a scoping study of the school. Nairametrics reports a terms of agreement between Afreximbank and King's College London on the school was signed at the AMCE commissioning on 5 June 2025.</t>
+          <t>Healthe Care acquired ASX-listed Pulse Health, Boulcott's operator, in May 2017. The Commerce Commission on 17 November 2021 cleared Pacific 2021 Bidco to buy 100% of Pulse Health NZ from Healthe Care, on condition that Boulcott be sold. NBR reported on 2 March 2022 that Rangatira Investments had bought Boulcott's operations. The end month is the clearance date; completion fell between November 2021 and March 2022.</t>
         </is>
       </c>
       <c r="L137" s="14" t="inlineStr">
         <is>
-          <t>King's College London, 2023-11-28</t>
+          <t>Commerce Commission New Zealand, 2021-11-17</t>
         </is>
       </c>
     </row>
@@ -8614,17 +8622,17 @@
       </c>
       <c r="C138" s="13" t="inlineStr">
         <is>
-          <t>Liverpool School of Tropical Medicine</t>
+          <t>Johns Hopkins University (Johns Hopkins Hospital)</t>
         </is>
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E138" s="12" t="inlineStr">
         <is>
-          <t>National Postgraduate Medical College of Nigeria (with Wellbeing Foundation Africa)</t>
+          <t>Afe Babalola University (ABUAD)</t>
         </is>
       </c>
       <c r="F138" s="12" t="inlineStr">
@@ -8634,28 +8642,28 @@
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
-          <t>LSTM leads Advanced Obstetrics and Surgical Skills training for obstetrics and gynaecology examiners and residents of the National Postgraduate Medical College, with centres of excellence in Lagos and Abuja and later sites in Port Harcourt and Gombe. It is funded by the UK Global Health Workforce Programme.</t>
+          <t>Tripartite agreement with the Little by Little Foundation letting high performing ABUAD medical students do part of their fifth year clinical electives at Johns Hopkins Hospital.</t>
         </is>
       </c>
       <c r="H138" s="12" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="I138" s="12" t="inlineStr"/>
       <c r="J138" s="12" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="K138" s="12" t="inlineStr">
         <is>
-          <t>LSTM reports the course began on 6 May 2024 at the college's centre of excellence at LUTH. The Wellbeing Foundation Africa reported on 12 February 2025 that 225 doctors had been trained, and on 22 May 2025 that training had expanded to the University of Port Harcourt Teaching Hospital. LSTM's May 2024 release names the site as 'Lagos State University Teaching Hospital (LUTH)', which is ambiguous; WBFA reported 225 examiners and 120 residents trained by May 2025.</t>
+          <t>ABUAD notice dated 17 January 2023 reports the signing on 10 January 2023. No later evidence of placements found in 2024 to 2026 searches. ABUAD's 5 February 2025 release on its seventh induction ceremony describes the six-week Johns Hopkins Hospital electives as ongoing.</t>
         </is>
       </c>
       <c r="L138" s="14" t="inlineStr">
         <is>
-          <t>Liverpool School of Tropical Medicine, 2024-05</t>
+          <t>Afe Babalola University, 2023-01-17</t>
         </is>
       </c>
     </row>
@@ -8672,48 +8680,48 @@
       </c>
       <c r="C139" s="13" t="inlineStr">
         <is>
-          <t>Manipal Hospitals</t>
+          <t>Mayo Clinic (Mayo Clinic Global Consulting)</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E139" s="12" t="inlineStr">
         <is>
-          <t>Afe Babalola University Multi-System Hospital</t>
+          <t>Iwosan Investments Limited (Iwosan Lagoon Hospitals and Lagos Medipark Hospital)</t>
         </is>
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>Training and education</t>
+          <t>Advisory and consulting</t>
         </is>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>Afe Babalola University Multi-System Hospital and Manipal Hospitals signed an MoU to expand capacity, deepen specialist training, improve clinical exchange and support advanced surgical care.</t>
+          <t>Iwosan Investments, owner of the Iwosan Lagoon Hospitals group, engaged Mayo Clinic Global Consulting for strategic advice on organisation and clinical practice. The work starts with Iwosan Lagoon Hospitals and the planned Lagos Medipark Hospital.</t>
         </is>
       </c>
       <c r="H139" s="12" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="I139" s="12" t="inlineStr"/>
       <c r="J139" s="12" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="K139" s="12" t="inlineStr">
         <is>
-          <t>News Agency of Nigeria, 26 June 2026, reports the MoU announced at a press briefing by the hospital's chief medical director, with Dr Rajit Sood speaking for Manipal and the university's Vice-Chancellor present.</t>
+          <t>Iwosan's announcement was syndicated on 17 April 2025 (The Sun) and carried by BusinessDay and BrandIconImage. No page on Mayo's own newsroom was found, so confirmation rests on the Nigerian company's release. No end date or contract term is stated.</t>
         </is>
       </c>
       <c r="L139" s="14" t="inlineStr">
         <is>
-          <t>News Agency of Nigeria, 2026-06-26</t>
+          <t>The Sun Nigeria, 2025-04-17</t>
         </is>
       </c>
     </row>
@@ -8730,48 +8738,44 @@
       </c>
       <c r="C140" s="13" t="inlineStr">
         <is>
-          <t>The Christie NHS Foundation Trust</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E140" s="12" t="inlineStr">
         <is>
-          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+          <t>Lagos University Teaching Hospital (LUTH) and College of Medicine, University of Lagos</t>
         </is>
       </c>
       <c r="F140" s="12" t="inlineStr">
         <is>
-          <t>Advisory and consulting</t>
+          <t>Research collaboration</t>
         </is>
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
-          <t>The Christie, through Christie International, is the oncology partner to King's College Hospital in advising the AMCE, supporting oncology staff recruitment, education and quality assurance. It continues to support the oncology service after opening.</t>
-        </is>
-      </c>
-      <c r="H140" s="12" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
+          <t>LUTH and the University of Lagos College of Medicine serve as research and training hubs of the MSK founded ARGO consortium. They take part in joint cancer studies, including a colorectal cancer immunotherapy trial.</t>
+        </is>
+      </c>
+      <c r="H140" s="12" t="inlineStr"/>
       <c r="I140" s="12" t="inlineStr"/>
       <c r="J140" s="12" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="K140" s="12" t="inlineStr">
         <is>
-          <t>The Christie's news story of 25 October 2024 reports an AMCE delegation visit to Manchester and says its advice, which began in 2021, would continue into operations. The Christie's project page, as indexed in search, states that clinical services were commissioned on 5 June 2025 with Christie International's head attending.</t>
+          <t>MSK's 2025 GCRT Update names OAUTHC and the College of Medicine, University of Lagos/LUTH as ARGO's research and training hubs. MSK's press page describes the colorectal immunotherapy trial with OAUTHC, LUTH and Medserve. Start year not stated on a dated page.</t>
         </is>
       </c>
       <c r="L140" s="14" t="inlineStr">
         <is>
-          <t>The Christie NHS Foundation Trust, 2024-10-25</t>
+          <t>Memorial Sloan Kettering Cancer Center, 2026</t>
         </is>
       </c>
     </row>
@@ -8788,48 +8792,48 @@
       </c>
       <c r="C141" s="13" t="inlineStr">
         <is>
-          <t>The Royal Marsden NHS Foundation Trust</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E141" s="12" t="inlineStr">
         <is>
-          <t>Marcelle Ruth Cancer Centre &amp; Specialist Hospital</t>
+          <t>Obafemi Awolowo University Teaching Hospitals Complex (OAUTHC)</t>
         </is>
       </c>
       <c r="F141" s="12" t="inlineStr">
         <is>
-          <t>Clinical affiliation</t>
+          <t>Research collaboration</t>
         </is>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>The two cancer centres signed a strategic partnership covering clinical expertise, research, professional development and training, aimed at keeping cancer care in Nigeria and West Africa.</t>
+          <t>MSK's Global Cancer Research and Training program partners with OAUTHC, home of the African Research Group for Oncology (ARGO), an NCI recognised consortium founded in 2013. The work covers cancer research, trials and training for Nigerian clinicians.</t>
         </is>
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="I141" s="12" t="inlineStr"/>
       <c r="J141" s="12" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="K141" s="12" t="inlineStr">
         <is>
-          <t>BusinessDay reported on 24 September 2026 that Marcelle Ruth had entered a strategic partnership with The Royal Marsden. Search results also show the agreement described as an MoU on a Royal Marsden Private Care LinkedIn post; no Royal Marsden press release was found.</t>
+          <t>MSK's 2025 GCRT Update reports the annual ARGO symposium held at Ile-Ife in September 2025 and a colorectal immunotherapy trial run with OAUTHC. MSK's program page dates the partnership to the 2009 training of OAUTHC surgeon Isaac Alatise; start year is that visit, ARGO itself dates to 2013.</t>
         </is>
       </c>
       <c r="L141" s="14" t="inlineStr">
         <is>
-          <t>BusinessDay, 2026-09-24</t>
+          <t>Memorial Sloan Kettering Cancer Center, 2026</t>
         </is>
       </c>
     </row>
@@ -8846,48 +8850,48 @@
       </c>
       <c r="C142" s="13" t="inlineStr">
         <is>
-          <t>University of Birmingham</t>
+          <t>St. Jude Children's Research Hospital</t>
         </is>
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E142" s="12" t="inlineStr">
         <is>
-          <t>University of Lagos (with Lagos University Teaching Hospital)</t>
+          <t>Abubakar Tafawa Balewa University Teaching Hospital (ATBUTH)</t>
         </is>
       </c>
       <c r="F142" s="12" t="inlineStr">
         <is>
-          <t>Training and education</t>
+          <t>Clinical affiliation</t>
         </is>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
-          <t>The University of Lagos and the University of Birmingham signed a memorandum on transnational education covering student and staff exchange and curriculum development. It builds on more than a decade of global surgery collaboration that introduced a master's programme in surgery at LUTH.</t>
+          <t>ATBUTH signed a Medical Institution Membership Agreement and joined the St. Jude Global Alliance, a care and training network for childhood cancer. Membership gives access to mentorship, shared treatment protocols and training.</t>
         </is>
       </c>
       <c r="H142" s="12" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="I142" s="12" t="inlineStr"/>
       <c r="J142" s="12" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="K142" s="12" t="inlineStr">
         <is>
-          <t>Vanguard, 29 January 2026, reports the MoU signed at UNILAG's Senate Chamber, witnessed by the Minister of Education; UNILAG's Vice Chancellor cites the Birmingham global surgery work and the LUTH master's in surgery. Birmingham described the MoU as a statement of intent. Not yet confirmed on Birmingham's newsroom.</t>
+          <t>Leadership newspaper published the hospital's statement on 26 October 2025 (signing described as the day before). Not confirmed on St. Jude's own site.</t>
         </is>
       </c>
       <c r="L142" s="14" t="inlineStr">
         <is>
-          <t>Vanguard, 29 January 2026</t>
+          <t>Leadership Newspapers, 2025-10-26</t>
         </is>
       </c>
     </row>
@@ -8904,55 +8908,55 @@
       </c>
       <c r="C143" s="13" t="inlineStr">
         <is>
-          <t>University of Glasgow</t>
+          <t>St. Jude Children's Research Hospital</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>Ahmadu Bello University</t>
+          <t>The Dorcas Cancer Foundation (TDCF)</t>
         </is>
       </c>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>Research collaboration</t>
+          <t>Clinical affiliation</t>
         </is>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>A university-level MoU provides a framework for joint research programmes, postgraduate co-supervision and academic exchange on global health challenges, coordinated by the School of Infection and Immunity. A university-wide MoU; no teaching-hospital or clinical component is named.</t>
+          <t>TDCF joined the St. Jude Global Alliance as the first Nigerian non profit member, to improve paediatric cancer outcomes in Nigeria and sub Saharan Africa. TDCF runs a paediatric radiation oncology training course.</t>
         </is>
       </c>
       <c r="H143" s="12" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="I143" s="12" t="inlineStr"/>
       <c r="J143" s="12" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="K143" s="12" t="inlineStr">
         <is>
-          <t>The University of Glasgow news item of 12 May 2026 reports the MoU signed during a visit on 28 and 29 April 2026, following an exploratory visit in December 2025. The MoU is university-wide and not limited to the teaching hospital.</t>
+          <t>ThisDay and BusinessDay reported the admission on 17 December 2024. The Nigerian party is a non profit, not a hospital, and the tie is an alliance membership; flag for the verifier. Not confirmed on St. Jude's site. Caveat: the Nigerian party is a cancer foundation working with pediatric oncology units, not a hospital.</t>
         </is>
       </c>
       <c r="L143" s="14" t="inlineStr">
         <is>
-          <t>University of Glasgow, 2026-05-12</t>
+          <t>ThisDay, 2024-12-17</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="15" t="inlineStr">
-        <is>
-          <t>Unclear</t>
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="B144" s="12" t="inlineStr">
@@ -8962,7 +8966,7 @@
       </c>
       <c r="C144" s="13" t="inlineStr">
         <is>
-          <t>University of Maryland School of Medicine</t>
+          <t>University of Illinois Chicago (UIC School of Public Health)</t>
         </is>
       </c>
       <c r="D144" s="12" t="inlineStr">
@@ -8972,45 +8976,45 @@
       </c>
       <c r="E144" s="12" t="inlineStr">
         <is>
-          <t>Lagos University Teaching Hospital (LUTH)</t>
+          <t>Lagos State University (LASU)</t>
         </is>
       </c>
       <c r="F144" s="12" t="inlineStr">
         <is>
-          <t>Research collaboration</t>
+          <t>Training and education</t>
         </is>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
-          <t>The University of Maryland School of Medicine and LUTH announced a chronic disease collaboration in August 2024, initially for four to five years with a stated ten-year ambition.</t>
+          <t>Framework agreement signed 28 July 2026 for academic collaboration, joint research and student and faculty exchange, focused on urban health, emergency preparedness and AI-enabled public health tools.</t>
         </is>
       </c>
       <c r="H144" s="12" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="I144" s="12" t="inlineStr"/>
       <c r="J144" s="12" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K144" s="12" t="inlineStr">
         <is>
-          <t>Nairametrics (19 August 2024) and LUTH report a partnership planned over ten years, following a visit by Dean Mark Gladwin. No signed text or later 2024 to 2026 update found, so it falls just before the Active cutoff.</t>
+          <t>UIC School of Public Health news, 4 August 2026, reports the memorandum signed on 28 July 2026 in Chicago by LASU's Vice Chancellor and UIC representatives. A university to university agreement with no hospital named.</t>
         </is>
       </c>
       <c r="L144" s="14" t="inlineStr">
         <is>
-          <t>Lagos University Teaching Hospital, 2024-08</t>
+          <t>UIC School of Public Health, 2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="15" t="inlineStr">
-        <is>
-          <t>Unclear</t>
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
@@ -9020,7 +9024,7 @@
       </c>
       <c r="C145" s="13" t="inlineStr">
         <is>
-          <t>University of Virginia Health System</t>
+          <t>University of Maryland School of Medicine (Institute of Human Virology)</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
@@ -9030,41 +9034,45 @@
       </c>
       <c r="E145" s="12" t="inlineStr">
         <is>
-          <t>Federal Medical Centre Owo</t>
+          <t>Institute of Human Virology Nigeria (IHVN)</t>
         </is>
       </c>
       <c r="F145" s="12" t="inlineStr">
         <is>
-          <t>Training and education</t>
+          <t>Research collaboration</t>
         </is>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>UVA's nephrology division built a partnership with FMC Owo covering research and career development programmes, with the International Society of Nephrology, and donated textbooks.</t>
-        </is>
-      </c>
-      <c r="H145" s="12" t="inlineStr"/>
+          <t>IHVN is the Nigerian affiliate of the Maryland Institute of Human Virology, delivering HIV, TB and cancer care, training and research. It opened a multi campus site in Abuja in 2023.</t>
+        </is>
+      </c>
+      <c r="H145" s="12" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
       <c r="I145" s="12" t="inlineStr"/>
       <c r="J145" s="12" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="K145" s="12" t="inlineStr">
         <is>
-          <t>UVA news item describes a textbook donation on 6 January 2023. No later dated evidence found, and the work may now sit inside the FMC Umuahia programme.</t>
+          <t>University of Maryland news from June 2023 reports the Abuja campus launch with UMB leadership present. No dated evidence from October 2024 onward found. IHVN is an NGO affiliate, not a hospital; flag for the verifier. NIH RePORTER shows Fogarty training grant D43TW012280 awarded to IHVN for FY2026 (budget start 1 February 2026), co-led with the UMSOM Institute of Human Virology. Caveat: IHVN is the Institute's Nigerian NGO affiliate, not a hospital.</t>
         </is>
       </c>
       <c r="L145" s="14" t="inlineStr">
         <is>
-          <t>UVA Medicine in Motion, 2023-01</t>
+          <t>University of Maryland School of Medicine, 2023-06</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="15" t="inlineStr">
-        <is>
-          <t>Unclear</t>
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="B146" s="12" t="inlineStr">
@@ -9074,7 +9082,7 @@
       </c>
       <c r="C146" s="13" t="inlineStr">
         <is>
-          <t>Yale School of Medicine (Department of Psychiatry)</t>
+          <t>University of Miami (Sylvester Comprehensive Cancer Center)</t>
         </is>
       </c>
       <c r="D146" s="12" t="inlineStr">
@@ -9084,45 +9092,45 @@
       </c>
       <c r="E146" s="12" t="inlineStr">
         <is>
-          <t>Imo State University Teaching Hospital</t>
+          <t>Ahmadu Bello University Teaching Hospital (ABUTH)</t>
         </is>
       </c>
       <c r="F146" s="12" t="inlineStr">
         <is>
-          <t>Training and education</t>
+          <t>Research collaboration</t>
         </is>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
-          <t>Yale's HAPPINESS Project, run with the Imo State teaching hospital, trains primary care workers to treat mental, neurological and substance use disorders, with telemedicine specialist support. It has begun integrating mental health into HIV clinics.</t>
+          <t>ABUTH is a recruiting site in a University of Miami led trial of niraparib maintenance therapy for ovarian cancer in women of African ancestry. The tie began with a Miami delegation visit to ABUTH in 2023.</t>
         </is>
       </c>
       <c r="H146" s="12" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="I146" s="12" t="inlineStr"/>
       <c r="J146" s="12" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="K146" s="12" t="inlineStr">
         <is>
-          <t>Nigeria Health Watch, 6 September 2023, reports over 100 workers trained; Yale's programme page is undated. No dated evidence from October 2024 onward found. The teaching hospital is in Orlu, Imo State.</t>
+          <t>ClinicalTrials.gov NCT06412120 lists ABUTH Zaria as recruiting, study start 28 July 2026, record updated 5 August 2026, Miami investigators Schlumbrecht and George. ABUTH's August 2023 news item reports the planning visit (page not retrievable; seen in search results only).</t>
         </is>
       </c>
       <c r="L146" s="14" t="inlineStr">
         <is>
-          <t>Nigeria Health Watch, 2023-09-06</t>
+          <t>US National Library of Medicine, 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="15" t="inlineStr">
-        <is>
-          <t>Unclear</t>
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
@@ -9132,55 +9140,55 @@
       </c>
       <c r="C147" s="13" t="inlineStr">
         <is>
-          <t>Apollo Hospitals</t>
+          <t>University of Virginia Health System</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E147" s="12" t="inlineStr">
         <is>
-          <t>Duchess International Hospital (Reddington Hospital Group)</t>
+          <t>Federal Medical Centre Umuahia</t>
         </is>
       </c>
       <c r="F147" s="12" t="inlineStr">
         <is>
-          <t>Ownership or management</t>
+          <t>Training and education</t>
         </is>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
-          <t>Apollo Hospitals supports the operation and management of the 100-bed Duchess International Hospital in Ikeja, Lagos, to strengthen efficiency and clinical quality. The arrangement was announced when the hospital launched in October 2021.</t>
+          <t>UVA nephrology supports the kidney transplant programme at FMC Umuahia through mentorship, coordinator training and joint research under the ISN and TTS Sister Transplant Centers Program. The pair reached Level B in 2026.</t>
         </is>
       </c>
       <c r="H147" s="12" t="inlineStr">
         <is>
-          <t>2021-10</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I147" s="12" t="inlineStr"/>
       <c r="J147" s="12" t="inlineStr">
         <is>
-          <t>2021-11</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="K147" s="12" t="inlineStr">
         <is>
-          <t>ThisDay (11 November 2021) and New Telegraph report that operation and management of the Duchess are supported by Apollo Hospitals, India. No dated confirmation from October 2024 onward was found; the hospital's 2024 and 2025 award releases do not mention Apollo.</t>
+          <t>UVA Medicine in Motion news, 13 May 2026, reports the move from Level C to Level B, shorter post transplant stays (14 to 8 days), four trained coordinators and eight joint publications in the first two years, which puts the start near 2024.</t>
         </is>
       </c>
       <c r="L147" s="14" t="inlineStr">
         <is>
-          <t>ThisDay, 11 November 2021</t>
+          <t>UVA Medicine in Motion, 2026-05-13</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="15" t="inlineStr">
-        <is>
-          <t>Unclear</t>
+      <c r="A148" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="B148" s="12" t="inlineStr">
@@ -9190,55 +9198,55 @@
       </c>
       <c r="C148" s="13" t="inlineStr">
         <is>
-          <t>Apollo Hospitals</t>
+          <t>Vanderbilt University Medical Center (Vanderbilt Institute for Global Health)</t>
         </is>
       </c>
       <c r="D148" s="12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E148" s="12" t="inlineStr">
         <is>
-          <t>State House Clinic</t>
+          <t>Aminu Kano Teaching Hospital and Bayero University Kano</t>
         </is>
       </c>
       <c r="F148" s="12" t="inlineStr">
         <is>
-          <t>Training and education</t>
+          <t>Research collaboration</t>
         </is>
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
-          <t>Apollo doctors visit the State House Clinic to give free consultations and lectures, and clinic staff have been sent to Apollo in India for up to six weeks of training at no charge.</t>
+          <t>Long running research and training partnership, now in its second Fogarty funded phase (V-BRCH 2), building Nigerian capacity for clinical research on HIV and related chronic diseases. Related programmes cover child neurology and research administration.</t>
         </is>
       </c>
       <c r="H148" s="12" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I148" s="12" t="inlineStr"/>
       <c r="J148" s="12" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="K148" s="12" t="inlineStr">
         <is>
-          <t>Blueprint, 29 July 2022, quotes the clinic's medical director describing a collaboration of almost six to seven years and a visiting Apollo team in Abuja. Start year is approximate, back-calculated from that quote. No later dated activity was found; a March 2024 ThisDay report records only Apollo's stated intent to partner with Nigerian hospitals.</t>
+          <t>Fogarty grant D43TW011544 lists Aminu Kano Teaching Hospital as principal institution with award years 2020 to 2029, and Vanderbilt's V-BRCH page describes V-BRCH 2 as a continuation. Both pages are undated, so last evidence reflects page content as read on 16 October 2026; flag for the verifier. Start year is the 2020 award; the AKTH tie is older. Fogarty grant D43TW011544 was renewed in 2025 with Aminu Kano Teaching Hospital as grantee; the FY2026 award notice is dated 18 December 2025 (NIH RePORTER).</t>
         </is>
       </c>
       <c r="L148" s="14" t="inlineStr">
         <is>
-          <t>Blueprint, 2022-07-29</t>
+          <t>US National Institutes of Health</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="15" t="inlineStr">
-        <is>
-          <t>Unclear</t>
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
@@ -9248,55 +9256,55 @@
       </c>
       <c r="C149" s="13" t="inlineStr">
         <is>
-          <t>Memorial Hospitals Group</t>
+          <t>Virginia Commonwealth University (VCU Massey Comprehensive Cancer Center)</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E149" s="12" t="inlineStr">
         <is>
-          <t>Kasi Healthcare</t>
+          <t>National Hospital Abuja</t>
         </is>
       </c>
       <c r="F149" s="12" t="inlineStr">
         <is>
-          <t>Telehealth and second opinion</t>
+          <t>Research collaboration</t>
         </is>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>Memorial specialists provide second opinions and specialist screenings, with monthly visiting specialists and training courses for Nigerian providers at Kasi's Lagos airport clinic, linked to referral of patients to Turkey. Close to a patient-referral arrangement.</t>
+          <t>Two year memorandum of understanding between the National Hospital and VCU Massey Comprehensive Cancer Center to build cancer research capacity. Focus areas are clinical trials, training of new scientists and moving research into patient care.</t>
         </is>
       </c>
       <c r="H149" s="12" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="I149" s="12" t="inlineStr"/>
       <c r="J149" s="12" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="K149" s="12" t="inlineStr">
         <is>
-          <t>BusinessDay, 27 September 2024, reports the partnership announced with Memorial's country executive. No later dated activity was found.</t>
+          <t>News Agency of Nigeria and Nairametrics reported the signing on 1 July 2025 by Prof Muhammad Mahmud and Dr Robert Winn, saying it was signed on a Tuesday (24 June or 1 July 2025). Term is two years, so it runs to mid 2027.</t>
         </is>
       </c>
       <c r="L149" s="14" t="inlineStr">
         <is>
-          <t>BusinessDay, 2024-09-27</t>
+          <t>Nairametrics, 2025-07-01</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="15" t="inlineStr">
-        <is>
-          <t>Unclear</t>
+      <c r="A150" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="B150" s="12" t="inlineStr">
@@ -9306,46 +9314,912 @@
       </c>
       <c r="C150" s="13" t="inlineStr">
         <is>
-          <t>Peking University People's Hospital (named variously in press as People's University Hospital, Beijing)</t>
+          <t>Evercare Group (owned at its 2021 launch by the TPG-managed Evercare Health Fund)</t>
         </is>
       </c>
       <c r="D150" s="12" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E150" s="12" t="inlineStr">
         <is>
-          <t>University of Abuja Teaching Hospital</t>
+          <t>Evercare Hospital Lekki</t>
         </is>
       </c>
       <c r="F150" s="12" t="inlineStr">
         <is>
-          <t>Government agreement</t>
+          <t>Ownership or management</t>
         </is>
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
-          <t>A China-Nigeria government letter of intent names these two hospitals as the pioneer project for hospital cooperation under the 2021 FOCAC health programmes, covering knowledge sharing and research.</t>
+          <t>Evercare Group owns and operates Evercare Hospital Lekki, a 165-bed tertiary hospital in Lagos that opened in February 2021, as part of its network of hospitals in Africa and South Asia.</t>
         </is>
       </c>
       <c r="H150" s="12" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2021-03</t>
         </is>
       </c>
       <c r="I150" s="12" t="inlineStr"/>
       <c r="J150" s="12" t="inlineStr">
         <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="K150" s="12" t="inlineStr">
+        <is>
+          <t>ThisDay, 10 October 2024, describes Evercare Hospital Lekki as part of the Evercare Group, which operates in Kenya and Pakistan as well as Nigeria, announcing new cochlear implant surgery. TPG's release and a 2021 report document the group's ownership and the February 2021 opening. A 2026 LinkedIn post suggests continued operation but was not verified. Ownership is as of the 2021 launch; no later ownership confirmation was found.</t>
+        </is>
+      </c>
+      <c r="L150" s="14" t="inlineStr">
+        <is>
+          <t>ThisDay, 2024-10-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B151" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C151" s="13" t="inlineStr">
+        <is>
+          <t>King's College Hospital NHS Foundation Trust</t>
+        </is>
+      </c>
+      <c r="D151" s="12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E151" s="12" t="inlineStr">
+        <is>
+          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+        </is>
+      </c>
+      <c r="F151" s="12" t="inlineStr">
+        <is>
+          <t>Advisory and consulting</t>
+        </is>
+      </c>
+      <c r="G151" s="12" t="inlineStr">
+        <is>
+          <t>King's is the appointed Clinical Partner of the AMCE, supporting clinical protocols, governance, service set-up, recruitment and training for the 170-bed specialist hospital in Abuja. Clinical services were commissioned in June 2025.</t>
+        </is>
+      </c>
+      <c r="H151" s="12" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="I151" s="12" t="inlineStr"/>
+      <c r="J151" s="12" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K151" s="12" t="inlineStr">
+        <is>
+          <t>Afreximbank announced on 3 June 2021 that it had signed an agreement appointing King's College Hospital as Clinical Partner. Nairametrics reports the AMCE was commissioned on 5 June 2025 with Vice President Shettima praising the AMCE and King's partnership. Brand Spur (19 September 2026) describes the centre as developed with King's College Hospital and now commissioned.</t>
+        </is>
+      </c>
+      <c r="L151" s="14" t="inlineStr">
+        <is>
+          <t>African Medical Centre of Excellence (amce.net), 2021-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B152" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C152" s="13" t="inlineStr">
+        <is>
+          <t>King's College London</t>
+        </is>
+      </c>
+      <c r="D152" s="12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E152" s="12" t="inlineStr">
+        <is>
+          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+        </is>
+      </c>
+      <c r="F152" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G152" s="12" t="inlineStr">
+        <is>
+          <t>King's College London and Afreximbank agreed to plan a medical and nursing school at the AMCE in Abuja, drawing on King's healthcare education expertise. A further terms of agreement was signed in June 2025.</t>
+        </is>
+      </c>
+      <c r="H152" s="12" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="I152" s="12" t="inlineStr"/>
+      <c r="J152" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="K152" s="12" t="inlineStr">
+        <is>
+          <t>King's news release of 28 November 2023 reports the memorandum of agreement signed on 24 November 2023 for a scoping study of the school. Nairametrics reports a terms of agreement between Afreximbank and King's College London on the school was signed at the AMCE commissioning on 5 June 2025.</t>
+        </is>
+      </c>
+      <c r="L152" s="14" t="inlineStr">
+        <is>
+          <t>King's College London, 2023-11-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B153" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C153" s="13" t="inlineStr">
+        <is>
+          <t>Liverpool School of Tropical Medicine</t>
+        </is>
+      </c>
+      <c r="D153" s="12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E153" s="12" t="inlineStr">
+        <is>
+          <t>National Postgraduate Medical College of Nigeria (with Wellbeing Foundation Africa)</t>
+        </is>
+      </c>
+      <c r="F153" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G153" s="12" t="inlineStr">
+        <is>
+          <t>LSTM leads Advanced Obstetrics and Surgical Skills training for obstetrics and gynaecology examiners and residents of the National Postgraduate Medical College, with centres of excellence in Lagos and Abuja and later sites in Port Harcourt and Gombe. It is funded by the UK Global Health Workforce Programme.</t>
+        </is>
+      </c>
+      <c r="H153" s="12" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="I153" s="12" t="inlineStr"/>
+      <c r="J153" s="12" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="K153" s="12" t="inlineStr">
+        <is>
+          <t>LSTM reports the course began on 6 May 2024 at the college's centre of excellence at LUTH. The Wellbeing Foundation Africa reported on 12 February 2025 that 225 doctors had been trained, and on 22 May 2025 that training had expanded to the University of Port Harcourt Teaching Hospital. LSTM's May 2024 release names the site as 'Lagos State University Teaching Hospital (LUTH)', which is ambiguous; WBFA reported 225 examiners and 120 residents trained by May 2025.</t>
+        </is>
+      </c>
+      <c r="L153" s="14" t="inlineStr">
+        <is>
+          <t>Liverpool School of Tropical Medicine, 2024-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B154" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C154" s="13" t="inlineStr">
+        <is>
+          <t>Manipal Hospitals</t>
+        </is>
+      </c>
+      <c r="D154" s="12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E154" s="12" t="inlineStr">
+        <is>
+          <t>Afe Babalola University Multi-System Hospital</t>
+        </is>
+      </c>
+      <c r="F154" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G154" s="12" t="inlineStr">
+        <is>
+          <t>Afe Babalola University Multi-System Hospital and Manipal Hospitals signed an MoU to expand capacity, deepen specialist training, improve clinical exchange and support advanced surgical care.</t>
+        </is>
+      </c>
+      <c r="H154" s="12" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="I154" s="12" t="inlineStr"/>
+      <c r="J154" s="12" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="K154" s="12" t="inlineStr">
+        <is>
+          <t>News Agency of Nigeria, 26 June 2026, reports the MoU announced at a press briefing by the hospital's chief medical director, with Dr Rajit Sood speaking for Manipal and the university's Vice-Chancellor present.</t>
+        </is>
+      </c>
+      <c r="L154" s="14" t="inlineStr">
+        <is>
+          <t>News Agency of Nigeria, 2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B155" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C155" s="13" t="inlineStr">
+        <is>
+          <t>The Christie NHS Foundation Trust</t>
+        </is>
+      </c>
+      <c r="D155" s="12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E155" s="12" t="inlineStr">
+        <is>
+          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+        </is>
+      </c>
+      <c r="F155" s="12" t="inlineStr">
+        <is>
+          <t>Advisory and consulting</t>
+        </is>
+      </c>
+      <c r="G155" s="12" t="inlineStr">
+        <is>
+          <t>The Christie, through Christie International, is the oncology partner to King's College Hospital in advising the AMCE, supporting oncology staff recruitment, education and quality assurance. It continues to support the oncology service after opening.</t>
+        </is>
+      </c>
+      <c r="H155" s="12" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I155" s="12" t="inlineStr"/>
+      <c r="J155" s="12" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="K155" s="12" t="inlineStr">
+        <is>
+          <t>The Christie's news story of 25 October 2024 reports an AMCE delegation visit to Manchester and says its advice, which began in 2021, would continue into operations. The Christie's project page, as indexed in search, states that clinical services were commissioned on 5 June 2025 with Christie International's head attending.</t>
+        </is>
+      </c>
+      <c r="L155" s="14" t="inlineStr">
+        <is>
+          <t>The Christie NHS Foundation Trust, 2024-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B156" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C156" s="13" t="inlineStr">
+        <is>
+          <t>The Royal Marsden NHS Foundation Trust</t>
+        </is>
+      </c>
+      <c r="D156" s="12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E156" s="12" t="inlineStr">
+        <is>
+          <t>Marcelle Ruth Cancer Centre &amp; Specialist Hospital</t>
+        </is>
+      </c>
+      <c r="F156" s="12" t="inlineStr">
+        <is>
+          <t>Clinical affiliation</t>
+        </is>
+      </c>
+      <c r="G156" s="12" t="inlineStr">
+        <is>
+          <t>The two cancer centres signed a strategic partnership covering clinical expertise, research, professional development and training, aimed at keeping cancer care in Nigeria and West Africa.</t>
+        </is>
+      </c>
+      <c r="H156" s="12" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I156" s="12" t="inlineStr"/>
+      <c r="J156" s="12" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K156" s="12" t="inlineStr">
+        <is>
+          <t>BusinessDay reported on 24 September 2026 that Marcelle Ruth had entered a strategic partnership with The Royal Marsden. Search results also show the agreement described as an MoU on a Royal Marsden Private Care LinkedIn post; no Royal Marsden press release was found.</t>
+        </is>
+      </c>
+      <c r="L156" s="14" t="inlineStr">
+        <is>
+          <t>BusinessDay, 2026-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B157" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C157" s="13" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="D157" s="12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E157" s="12" t="inlineStr">
+        <is>
+          <t>University of Lagos (with Lagos University Teaching Hospital)</t>
+        </is>
+      </c>
+      <c r="F157" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G157" s="12" t="inlineStr">
+        <is>
+          <t>The University of Lagos and the University of Birmingham signed a memorandum on transnational education covering student and staff exchange and curriculum development. It builds on more than a decade of global surgery collaboration that introduced a master's programme in surgery at LUTH.</t>
+        </is>
+      </c>
+      <c r="H157" s="12" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="I157" s="12" t="inlineStr"/>
+      <c r="J157" s="12" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="K157" s="12" t="inlineStr">
+        <is>
+          <t>Vanguard, 29 January 2026, reports the MoU signed at UNILAG's Senate Chamber, witnessed by the Minister of Education; UNILAG's Vice Chancellor cites the Birmingham global surgery work and the LUTH master's in surgery. Birmingham described the MoU as a statement of intent. Not yet confirmed on Birmingham's newsroom.</t>
+        </is>
+      </c>
+      <c r="L157" s="14" t="inlineStr">
+        <is>
+          <t>Vanguard, 29 January 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B158" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C158" s="13" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="D158" s="12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E158" s="12" t="inlineStr">
+        <is>
+          <t>Ahmadu Bello University</t>
+        </is>
+      </c>
+      <c r="F158" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G158" s="12" t="inlineStr">
+        <is>
+          <t>A university-level MoU provides a framework for joint research programmes, postgraduate co-supervision and academic exchange on global health challenges, coordinated by the School of Infection and Immunity. A university-wide MoU; no teaching-hospital or clinical component is named.</t>
+        </is>
+      </c>
+      <c r="H158" s="12" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="I158" s="12" t="inlineStr"/>
+      <c r="J158" s="12" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="K158" s="12" t="inlineStr">
+        <is>
+          <t>The University of Glasgow news item of 12 May 2026 reports the MoU signed during a visit on 28 and 29 April 2026, following an exploratory visit in December 2025. The MoU is university-wide and not limited to the teaching hospital.</t>
+        </is>
+      </c>
+      <c r="L158" s="14" t="inlineStr">
+        <is>
+          <t>University of Glasgow, 2026-05-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B159" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C159" s="13" t="inlineStr">
+        <is>
+          <t>University of Maryland School of Medicine</t>
+        </is>
+      </c>
+      <c r="D159" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E159" s="12" t="inlineStr">
+        <is>
+          <t>Lagos University Teaching Hospital (LUTH)</t>
+        </is>
+      </c>
+      <c r="F159" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G159" s="12" t="inlineStr">
+        <is>
+          <t>The University of Maryland School of Medicine and LUTH announced a chronic disease collaboration in August 2024, initially for four to five years with a stated ten-year ambition.</t>
+        </is>
+      </c>
+      <c r="H159" s="12" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="I159" s="12" t="inlineStr"/>
+      <c r="J159" s="12" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="K159" s="12" t="inlineStr">
+        <is>
+          <t>Nairametrics (19 August 2024) and LUTH report a partnership planned over ten years, following a visit by Dean Mark Gladwin. No signed text or later 2024 to 2026 update found, so it falls just before the Active cutoff.</t>
+        </is>
+      </c>
+      <c r="L159" s="14" t="inlineStr">
+        <is>
+          <t>Lagos University Teaching Hospital, 2024-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B160" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C160" s="13" t="inlineStr">
+        <is>
+          <t>University of Virginia Health System</t>
+        </is>
+      </c>
+      <c r="D160" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E160" s="12" t="inlineStr">
+        <is>
+          <t>Federal Medical Centre Owo</t>
+        </is>
+      </c>
+      <c r="F160" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G160" s="12" t="inlineStr">
+        <is>
+          <t>UVA's nephrology division built a partnership with FMC Owo covering research and career development programmes, with the International Society of Nephrology, and donated textbooks.</t>
+        </is>
+      </c>
+      <c r="H160" s="12" t="inlineStr"/>
+      <c r="I160" s="12" t="inlineStr"/>
+      <c r="J160" s="12" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="K160" s="12" t="inlineStr">
+        <is>
+          <t>UVA news item describes a textbook donation on 6 January 2023. No later dated evidence found, and the work may now sit inside the FMC Umuahia programme.</t>
+        </is>
+      </c>
+      <c r="L160" s="14" t="inlineStr">
+        <is>
+          <t>UVA Medicine in Motion, 2023-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B161" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C161" s="13" t="inlineStr">
+        <is>
+          <t>Yale School of Medicine (Department of Psychiatry)</t>
+        </is>
+      </c>
+      <c r="D161" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E161" s="12" t="inlineStr">
+        <is>
+          <t>Imo State University Teaching Hospital</t>
+        </is>
+      </c>
+      <c r="F161" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G161" s="12" t="inlineStr">
+        <is>
+          <t>Yale's HAPPINESS Project, run with the Imo State teaching hospital, trains primary care workers to treat mental, neurological and substance use disorders, with telemedicine specialist support. It has begun integrating mental health into HIV clinics.</t>
+        </is>
+      </c>
+      <c r="H161" s="12" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="I161" s="12" t="inlineStr"/>
+      <c r="J161" s="12" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="K161" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria Health Watch, 6 September 2023, reports over 100 workers trained; Yale's programme page is undated. No dated evidence from October 2024 onward found. The teaching hospital is in Orlu, Imo State.</t>
+        </is>
+      </c>
+      <c r="L161" s="14" t="inlineStr">
+        <is>
+          <t>Nigeria Health Watch, 2023-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B162" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C162" s="13" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals</t>
+        </is>
+      </c>
+      <c r="D162" s="12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E162" s="12" t="inlineStr">
+        <is>
+          <t>Duchess International Hospital (Reddington Hospital Group)</t>
+        </is>
+      </c>
+      <c r="F162" s="12" t="inlineStr">
+        <is>
+          <t>Ownership or management</t>
+        </is>
+      </c>
+      <c r="G162" s="12" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals supports the operation and management of the 100-bed Duchess International Hospital in Ikeja, Lagos, to strengthen efficiency and clinical quality. The arrangement was announced when the hospital launched in October 2021.</t>
+        </is>
+      </c>
+      <c r="H162" s="12" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="I162" s="12" t="inlineStr"/>
+      <c r="J162" s="12" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="K162" s="12" t="inlineStr">
+        <is>
+          <t>ThisDay (11 November 2021) and New Telegraph report that operation and management of the Duchess are supported by Apollo Hospitals, India. No dated confirmation from October 2024 onward was found; the hospital's 2024 and 2025 award releases do not mention Apollo.</t>
+        </is>
+      </c>
+      <c r="L162" s="14" t="inlineStr">
+        <is>
+          <t>ThisDay, 11 November 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B163" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C163" s="13" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals</t>
+        </is>
+      </c>
+      <c r="D163" s="12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E163" s="12" t="inlineStr">
+        <is>
+          <t>State House Clinic</t>
+        </is>
+      </c>
+      <c r="F163" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G163" s="12" t="inlineStr">
+        <is>
+          <t>Apollo doctors visit the State House Clinic to give free consultations and lectures, and clinic staff have been sent to Apollo in India for up to six weeks of training at no charge.</t>
+        </is>
+      </c>
+      <c r="H163" s="12" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="I163" s="12" t="inlineStr"/>
+      <c r="J163" s="12" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="K163" s="12" t="inlineStr">
+        <is>
+          <t>Blueprint, 29 July 2022, quotes the clinic's medical director describing a collaboration of almost six to seven years and a visiting Apollo team in Abuja. Start year is approximate, back-calculated from that quote. No later dated activity was found; a March 2024 ThisDay report records only Apollo's stated intent to partner with Nigerian hospitals.</t>
+        </is>
+      </c>
+      <c r="L163" s="14" t="inlineStr">
+        <is>
+          <t>Blueprint, 2022-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B164" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C164" s="13" t="inlineStr">
+        <is>
+          <t>Memorial Hospitals Group</t>
+        </is>
+      </c>
+      <c r="D164" s="12" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="E164" s="12" t="inlineStr">
+        <is>
+          <t>Kasi Healthcare</t>
+        </is>
+      </c>
+      <c r="F164" s="12" t="inlineStr">
+        <is>
+          <t>Telehealth and second opinion</t>
+        </is>
+      </c>
+      <c r="G164" s="12" t="inlineStr">
+        <is>
+          <t>Memorial specialists provide second opinions and specialist screenings, with monthly visiting specialists and training courses for Nigerian providers at Kasi's Lagos airport clinic, linked to referral of patients to Turkey. Close to a patient-referral arrangement.</t>
+        </is>
+      </c>
+      <c r="H164" s="12" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="I164" s="12" t="inlineStr"/>
+      <c r="J164" s="12" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="K164" s="12" t="inlineStr">
+        <is>
+          <t>BusinessDay, 27 September 2024, reports the partnership announced with Memorial's country executive. No later dated activity was found.</t>
+        </is>
+      </c>
+      <c r="L164" s="14" t="inlineStr">
+        <is>
+          <t>BusinessDay, 2024-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B165" s="12" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C165" s="13" t="inlineStr">
+        <is>
+          <t>Peking University People's Hospital (named variously in press as People's University Hospital, Beijing)</t>
+        </is>
+      </c>
+      <c r="D165" s="12" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E165" s="12" t="inlineStr">
+        <is>
+          <t>University of Abuja Teaching Hospital</t>
+        </is>
+      </c>
+      <c r="F165" s="12" t="inlineStr">
+        <is>
+          <t>Government agreement</t>
+        </is>
+      </c>
+      <c r="G165" s="12" t="inlineStr">
+        <is>
+          <t>A China-Nigeria government letter of intent names these two hospitals as the pioneer project for hospital cooperation under the 2021 FOCAC health programmes, covering knowledge sharing and research.</t>
+        </is>
+      </c>
+      <c r="H165" s="12" t="inlineStr">
+        <is>
           <t>2022-08</t>
         </is>
       </c>
-      <c r="K150" s="12" t="inlineStr">
+      <c r="I165" s="12" t="inlineStr"/>
+      <c r="J165" s="12" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="K165" s="12" t="inlineStr">
         <is>
           <t>Within Nigeria and the University of Abuja Teaching Hospital website report the letter of intent signed in Abuja by the Chinese Ambassador and Nigeria's Health Minister in August 2022. No follow-up activity was found. The Chinese hospital's name varies between sources and is inferred.</t>
         </is>
       </c>
-      <c r="L150" s="14" t="inlineStr">
+      <c r="L165" s="14" t="inlineStr">
         <is>
           <t>Within Nigeria, 2022-08-20</t>
         </is>
@@ -9502,10 +10376,25 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L148" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L165" r:id="rId164"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId150"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId165"/>
   </tableParts>
 </worksheet>
 </file>
@@ -9516,7 +10405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E297"/>
+  <dimension ref="A1:E328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -16105,1409 +16994,2222 @@
     <row r="245">
       <c r="A245" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins University (Johns Hopkins Hospital)</t>
+          <t>Johns Hopkins University (Bloomberg School of Public Health, Center for Indigenous Health)</t>
         </is>
       </c>
       <c r="B245" s="5" t="inlineStr">
         <is>
-          <t>Afe Babalola University (ABUAD)</t>
+          <t>University of Otago, Te Rōpū Rangahau Hauora a Eru Pōmare (Eru Pōmare Māori Health Research Centre)</t>
         </is>
       </c>
       <c r="C245" s="5" t="inlineStr">
         <is>
-          <t>Afe Babalola University ABUAD Tripartite agreement with John Hopkins University USA and Little by Little Foundation</t>
+          <t>Johns Hopkins Center for Indigenous Health SPIRIT Program Q&amp;A: A Global Collaboration Rooted In Indigenous Play</t>
         </is>
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>2023-01-17</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E245" s="5" t="inlineStr">
         <is>
-          <t>https://www.abuad.edu.ng/abuad-tripartite-agreement-with-john-hopkins-university-usa-and-little-by-little-foundation/</t>
+          <t>https://cih.jhu.edu/spirit-program-qa</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins University (Johns Hopkins Hospital)</t>
+          <t>Johns Hopkins University (Bloomberg School of Public Health, Center for Indigenous Health)</t>
         </is>
       </c>
       <c r="B246" s="5" t="inlineStr">
         <is>
-          <t>Afe Babalola University (ABUAD)</t>
+          <t>University of Otago, Te Rōpū Rangahau Hauora a Eru Pōmare (Eru Pōmare Māori Health Research Centre)</t>
         </is>
       </c>
       <c r="C246" s="5" t="inlineStr">
         <is>
-          <t>ThisDay ABUAD, John Hopkins Partner to Boost Medical Training</t>
-        </is>
-      </c>
-      <c r="D246" s="5" t="inlineStr">
-        <is>
-          <t>2023-01-18</t>
-        </is>
-      </c>
+          <t>Johns Hopkins Center for Indigenous Health SPIRIT</t>
+        </is>
+      </c>
+      <c r="D246" s="5" t="inlineStr"/>
       <c r="E246" s="5" t="inlineStr">
         <is>
-          <t>https://www.thisdaylive.com/2023/01/18/abuad-john-hopkins-partner-to-boost-medical-training/</t>
+          <t>https://cih.jhu.edu/programs/spirit/</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins University (Johns Hopkins Hospital)</t>
+          <t>Johns Hopkins University (Bloomberg School of Public Health, Center for Indigenous Health)</t>
         </is>
       </c>
       <c r="B247" s="5" t="inlineStr">
         <is>
-          <t>Afe Babalola University (ABUAD)</t>
+          <t>University of Otago, Te Rōpū Rangahau Hauora a Eru Pōmare (Eru Pōmare Māori Health Research Centre)</t>
         </is>
       </c>
       <c r="C247" s="5" t="inlineStr">
         <is>
-          <t>Afe Babalola University ABUAD Holds Seventh Induction Ceremony for Fresh Doctors</t>
+          <t>Johns Hopkins University Bloomberg School announces expanded Center for Indigenous Health</t>
         </is>
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>5 February 2025</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="E247" s="5" t="inlineStr">
         <is>
-          <t>https://vc.abuad.edu.ng/abuad-holds-seventh-induction-ceremony-for-fresh-doctors/</t>
+          <t>https://hub.jhu.edu/2022/09/15/center-for-indigenous-health-johns-hopkins/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic (Mayo Clinic Global Consulting)</t>
+          <t>Icon Oncology Group (Icon Group)</t>
         </is>
       </c>
       <c r="B248" s="5" t="inlineStr">
         <is>
-          <t>Iwosan Investments Limited (Iwosan Lagoon Hospitals and Lagos Medipark Hospital)</t>
+          <t>Bowen Icon Cancer Centre (joint venture with Evolution Healthcare, Bowen Hospital)</t>
         </is>
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>The Sun Iwosan engages Mayo Clinic to advance high-quality patient-centered healthcare</t>
+          <t>Icon Oncology Group About us</t>
         </is>
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E248" s="5" t="inlineStr">
         <is>
-          <t>https://thesun.ng/iwosan-engages-mayo-clinic-to-advance-high-quality-patient-centered-healthcare/</t>
+          <t>https://icongroup.global/about-us/</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic (Mayo Clinic Global Consulting)</t>
+          <t>Icon Oncology Group (Icon Group)</t>
         </is>
       </c>
       <c r="B249" s="5" t="inlineStr">
         <is>
-          <t>Iwosan Investments Limited (Iwosan Lagoon Hospitals and Lagos Medipark Hospital)</t>
+          <t>Bowen Icon Cancer Centre (joint venture with Evolution Healthcare, Bowen Hospital)</t>
         </is>
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>BrandIconImage Iwosan Investments Limited Engages Mayo Clinic Global Consulting to Advance High-Quality Patient-Centered Healthcare in Nigeria</t>
+          <t>Icon Oncology Group Cancer Services – New Zealand</t>
         </is>
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E249" s="5" t="inlineStr">
         <is>
-          <t>https://www.brandiconimage.com/2025/04/iwosan-investments-limited-engages-mayo.html</t>
+          <t>https://icongroup.global/our-services/cancer-services-new-zealand/</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="5" t="inlineStr">
         <is>
-          <t>Mayo Clinic (Mayo Clinic Global Consulting)</t>
+          <t>Icon Oncology Group (Icon Group)</t>
         </is>
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
-          <t>Iwosan Investments Limited (Iwosan Lagoon Hospitals and Lagos Medipark Hospital)</t>
+          <t>Bowen Icon Cancer Centre (joint venture with Evolution Healthcare, Bowen Hospital)</t>
         </is>
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>BusinessDay Iwosan engages Mayo Clinic to advance high quality patient centered healthcare in Nigeria</t>
+          <t>Newshub PM opens Wellington's first private cancer care facility</t>
         </is>
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>8 April 2025</t>
+          <t>2017-07</t>
         </is>
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
-          <t>https://businessday.ng/health/article/iwosan-engages-mayo-clinic-to-advance-high-quality-patient-centered-healthcare-in-nigeria/</t>
+          <t>https://www.newshub.co.nz/home/health/2017/07/pm-opens-wellington-s-first-private-cancer-care-facility.html</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>Icon Oncology Group (Icon Group)</t>
         </is>
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
-          <t>Lagos University Teaching Hospital (LUTH) and College of Medicine, University of Lagos</t>
+          <t>Bowen Icon Cancer Centre (joint venture with Evolution Healthcare, Bowen Hospital)</t>
         </is>
       </c>
       <c r="C251" s="5" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center Global Cancer Research and Training Program 2025 Update</t>
+          <t>Icon Writers United by Unique this World Cancer Day</t>
         </is>
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
-          <t>https://www.mskcc.org/sites/default/files/node/118066/documents/gcrt_report_2026_6_01-29-98-44.pdf</t>
+          <t>https://icongroup.global/en/news/2025-02-04/world-cancer-day/</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="5" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>National University of Singapore and National University Health System</t>
         </is>
       </c>
       <c r="B252" s="5" t="inlineStr">
         <is>
-          <t>Obafemi Awolowo University Teaching Hospitals Complex (OAUTHC)</t>
+          <t>Liggins Institute, University of Auckland</t>
         </is>
       </c>
       <c r="C252" s="5" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center Global Cancer Research and Training Program 2025 Update</t>
-        </is>
-      </c>
-      <c r="D252" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+          <t>Liggins Institute Research partnerships</t>
+        </is>
+      </c>
+      <c r="D252" s="5" t="inlineStr"/>
       <c r="E252" s="5" t="inlineStr">
         <is>
-          <t>https://www.mskcc.org/sites/default/files/node/118066/documents/gcrt_report_2026_6_01-29-98-44.pdf</t>
+          <t>https://www.auckland.ac.nz/en/liggins/in-the-community/scientists-researchers/research-partnerships.html</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>National University of Singapore and National University Health System</t>
         </is>
       </c>
       <c r="B253" s="5" t="inlineStr">
         <is>
-          <t>Obafemi Awolowo University Teaching Hospitals Complex (OAUTHC)</t>
+          <t>Liggins Institute, University of Auckland</t>
         </is>
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center MSK's Global Cancer Research and Training (GCRT) Program</t>
-        </is>
-      </c>
-      <c r="D253" s="5" t="inlineStr"/>
+          <t>University of Southampton NiPPeR Randomised Trial - Child Follow Up Study (NCT05934422)</t>
+        </is>
+      </c>
+      <c r="D253" s="5" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
       <c r="E253" s="5" t="inlineStr">
         <is>
-          <t>https://www.mskcc.org/hcp-education-training/international/global-cancer-disparities-initiatives</t>
+          <t>https://clinicaltrials.gov/study/NCT05934422</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital</t>
+          <t>UCLPartners</t>
         </is>
       </c>
       <c r="B254" s="5" t="inlineStr">
         <is>
-          <t>Abubakar Tafawa Balewa University Teaching Hospital (ATBUTH)</t>
+          <t>Health New Zealand Te Whatu Ora (HealthX programme)</t>
         </is>
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>Leadership Bauchi Teaching Hospital Seeks Alliance To Strengthen Cancer Care</t>
+          <t>Health New Zealand Te Whatu Ora Health NZ international partnership strengthens approach to digital and AI innovation</t>
         </is>
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
-          <t>https://leadership.ng/bauchi-teaching-hospital-seeks-alliance-to-strengthen-cancer-care/</t>
+          <t>https://www.hinz.org.nz/news/730824/Health-NZ-international-partnership-strengthens-digital-innovation.htm</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital</t>
+          <t>Universitas Indonesia (Faculty of Public Health)</t>
         </is>
       </c>
       <c r="B255" s="5" t="inlineStr">
         <is>
-          <t>The Dorcas Cancer Foundation (TDCF)</t>
+          <t>University of Otago (Faculty of Medicine)</t>
         </is>
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>Sunday Ehigiator TDCF, St. Jude Global Alliance, Partner on Improving Pediatric Cancer Outcomes in Nigeria, Others</t>
+          <t>Faculty of Public Health, Universitas Indonesia FPH UI and the University of Otago, New Zealand: joint Master of Public Health agreement</t>
         </is>
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E255" s="5" t="inlineStr">
         <is>
-          <t>https://www.thisdaylive.com/2024/12/17/tdcf-st-jude-global-alliance-partner-on-improving-pediatric-cancer-outcomes-in-nigeria-others/</t>
+          <t>https://fkm.ui.ac.id/?p=44053</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital</t>
+          <t>University of Southampton (MRC Lifecourse Epidemiology Centre, EpiGen Global Research Consortium)</t>
         </is>
       </c>
       <c r="B256" s="5" t="inlineStr">
         <is>
-          <t>The Dorcas Cancer Foundation (TDCF)</t>
+          <t>Liggins Institute, University of Auckland</t>
         </is>
       </c>
       <c r="C256" s="5" t="inlineStr">
         <is>
-          <t>BusinessDay TDCF admitted into St Jude Global Alliance to improve pediatric cancer outcomes in Nigeria</t>
-        </is>
-      </c>
-      <c r="D256" s="5" t="inlineStr">
-        <is>
-          <t>2024-12</t>
-        </is>
-      </c>
+          <t>Liggins Institute EpiGen Global Research Consortium</t>
+        </is>
+      </c>
+      <c r="D256" s="5" t="inlineStr"/>
       <c r="E256" s="5" t="inlineStr">
         <is>
-          <t>https://businessday.ng/life/article/tdcf-admitted-into-st-jude-global-alliance-to-improve-pediatric-cancer-outcomes-in-nigeria/</t>
+          <t>https://auckland.ac.nz/en/liggins/in-the-community/scientists-researchers/research-partnerships/epigen.html</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
         <is>
-          <t>University of Illinois Chicago (UIC School of Public Health)</t>
+          <t>University of Southampton (MRC Lifecourse Epidemiology Centre, EpiGen Global Research Consortium)</t>
         </is>
       </c>
       <c r="B257" s="5" t="inlineStr">
         <is>
-          <t>Lagos State University (LASU)</t>
+          <t>Liggins Institute, University of Auckland</t>
         </is>
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>UIC School of Public Health UIC and Lagos State University Sign Memorandum of Agreement</t>
+          <t>University of Southampton NiPPeR Randomised Trial - Child Follow Up Study (NCT05934422)</t>
         </is>
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E257" s="5" t="inlineStr">
         <is>
-          <t>https://publichealth.uic.edu/news-stories/uic-and-lagos-state-university-sign-memorandum-of-agreement/</t>
+          <t>https://clinicaltrials.gov/study/NCT05934422</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>University of Maryland School of Medicine (Institute of Human Virology)</t>
+          <t>University of Wollongong (Graduate School of Medicine)</t>
         </is>
       </c>
       <c r="B258" s="5" t="inlineStr">
         <is>
-          <t>Institute of Human Virology Nigeria (IHVN)</t>
+          <t>University of Waikato (New Zealand Graduate School of Medicine)</t>
         </is>
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>University of Maryland School of Medicine University of Maryland Baltimore leadership helps IHV Nigeria launch campus in Abuja</t>
+          <t>University of Wollongong Wollongong and Waikato partner to shape future of rural health in New Zealand</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="E258" s="5" t="inlineStr">
         <is>
-          <t>https://ihv.umaryland.edu/news/2023/university-of-maryland-baltimore-leadership-helps-ihv-nigeria-launch-state-of-the-art-campus-in-public-healthcare-treatment-training-and-research-in-nigeria.html</t>
+          <t>https://www.uow.edu.au/media/2025/wollongong-and-waikato-partner-to-shape-future-of-rural-health-in-new-zealand.php</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
         <is>
-          <t>University of Maryland School of Medicine (Institute of Human Virology)</t>
+          <t>University of Wollongong (Graduate School of Medicine)</t>
         </is>
       </c>
       <c r="B259" s="5" t="inlineStr">
         <is>
-          <t>Institute of Human Virology Nigeria (IHVN)</t>
+          <t>University of Waikato (New Zealand Graduate School of Medicine)</t>
         </is>
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
-          <t>US National Institutes of Health RePORTER: 5D43TW012280-05, Expanding the pool of Independent Investigators in Implementation Science (Institute of Human Virology Nigeria)</t>
+          <t>University of Waikato Waikato to work with regional health education experts to shape med school curriculum</t>
         </is>
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>FY2026 (budget start 1 February 2026)</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="E259" s="5" t="inlineStr">
         <is>
-          <t>https://reporter.nih.gov/project-details/11251575</t>
+          <t>https://www.waikato.ac.nz/news-events/news/waikato-wollongong-mou/</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
         <is>
-          <t>University of Miami (Sylvester Comprehensive Cancer Center)</t>
+          <t>West Visayas State University</t>
         </is>
       </c>
       <c r="B260" s="5" t="inlineStr">
         <is>
-          <t>Ahmadu Bello University Teaching Hospital (ABUTH)</t>
+          <t>University of Otago</t>
         </is>
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>ClinicalTrials.gov Study Evaluating Safety, Tolerability, and Metabolism of Niraparib (NCT06412120)</t>
+          <t>West Visayas State University WVSU forges digital health alliance with New Zealand's University of Otago</t>
         </is>
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="E260" s="5" t="inlineStr">
         <is>
-          <t>https://clinicaltrials.gov/study/NCT06412120</t>
+          <t>https://wvsu.edu.ph/wvsu-forges-digital-health-alliance-with-new-zealands-university-of-otago/</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
         <is>
-          <t>University of Miami (Sylvester Comprehensive Cancer Center)</t>
+          <t>Sanford Health (Sanford World Clinic)</t>
         </is>
       </c>
       <c r="B261" s="5" t="inlineStr">
         <is>
-          <t>Ahmadu Bello University Teaching Hospital (ABUTH)</t>
+          <t>Omni Health (OmniHealth) primary care network</t>
         </is>
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>Ahmadu Bello University ABUTH to begin clinical trials on ovarian cancer next year</t>
-        </is>
-      </c>
-      <c r="D261" s="5" t="inlineStr">
-        <is>
-          <t>2023-08</t>
-        </is>
-      </c>
+          <t>Sanford Health Sanford World Clinic New Zealand</t>
+        </is>
+      </c>
+      <c r="D261" s="5" t="inlineStr"/>
       <c r="E261" s="5" t="inlineStr">
         <is>
-          <t>https://abu.edu.ng/abuth-to-begin-clinical-trials-on-ovarian-cancer-next-year/</t>
+          <t>https://www.sanfordhealth.org/initiatives/world-clinic/new-zealand</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
         <is>
-          <t>University of Miami (Sylvester Comprehensive Cancer Center)</t>
+          <t>Sanford Health (Sanford World Clinic)</t>
         </is>
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
-          <t>Ahmadu Bello University Teaching Hospital (ABUTH)</t>
+          <t>Omni Health (OmniHealth) primary care network</t>
         </is>
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>US National Library of Medicine NCT06412120: Niraparib as Maintenance Following Front-Line Treatment for Ovarian Cancer in Women of African Ancestry</t>
+          <t>Jodi Schwan Sanford World Clinic finds broader global reach despite pandemic</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>5 August 2026</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="E262" s="5" t="inlineStr">
         <is>
-          <t>https://clinicaltrials.gov/study/NCT06412120</t>
+          <t>https://siouxfalls.business/?p=89679</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
         <is>
-          <t>University of Virginia Health System</t>
+          <t>Sanford Health (Sanford World Clinic)</t>
         </is>
       </c>
       <c r="B263" s="5" t="inlineStr">
         <is>
-          <t>Federal Medical Centre Umuahia</t>
+          <t>Omni Health (OmniHealth) primary care network</t>
         </is>
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
-          <t>UVA School of Medicine UVA Partners With Federal Medical Center in Nigeria to Elevate Global Kidney Care</t>
+          <t>Sanford World Clinic Sanford World Clinic Partnering with Omni Health</t>
         </is>
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E263" s="5" t="inlineStr">
         <is>
-          <t>https://news.med.virginia.edu/community/uva-nigeria-elevating-global-kidney-care/</t>
+          <t>https://employer.practicematch.com/employer/sanford-world-clinic/968142</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="5" t="inlineStr">
         <is>
-          <t>Vanderbilt University Medical Center (Vanderbilt Institute for Global Health)</t>
+          <t>Sanford Health (Sanford World Clinic)</t>
         </is>
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>Aminu Kano Teaching Hospital and Bayero University Kano</t>
+          <t>Omni Health (OmniHealth) primary care network</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>Fogarty International Center Vanderbilt-Nigeria Building Research Capacity in HIV and NCDs (V-BRCH)</t>
+          <t>New Zealand Doctor Big US health player buddies up with local network in new Auckland clinic</t>
         </is>
       </c>
       <c r="D264" s="5" t="inlineStr"/>
       <c r="E264" s="5" t="inlineStr">
         <is>
-          <t>https://fic.nih.gov/Grants/Search/Pages/hiv-research-training-d43tw011544.aspx</t>
+          <t>https://nzdoctor.co.nz/node/2668</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="5" t="inlineStr">
         <is>
-          <t>Vanderbilt University Medical Center (Vanderbilt Institute for Global Health)</t>
+          <t>Children's Cancer Institute and Sydney Children's Hospital, Randwick (Zero Childhood Cancer Program)</t>
         </is>
       </c>
       <c r="B265" s="5" t="inlineStr">
         <is>
-          <t>Aminu Kano Teaching Hospital and Bayero University Kano</t>
+          <t>Starship Children's Hospital and Christchurch Hospital (Health New Zealand)</t>
         </is>
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>Vanderbilt Institute for Global Health V-BRCH</t>
-        </is>
-      </c>
-      <c r="D265" s="5" t="inlineStr"/>
+          <t>ANZCHOG ZERO2 opens in NZ</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
       <c r="E265" s="5" t="inlineStr">
         <is>
-          <t>https://www.vumc.org/global-health/v-brch</t>
+          <t>https://anzchog.org/zero2-opens-in-nz/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="5" t="inlineStr">
         <is>
-          <t>Vanderbilt University Medical Center (Vanderbilt Institute for Global Health)</t>
+          <t>Children's Cancer Institute and Sydney Children's Hospital, Randwick (Zero Childhood Cancer Program)</t>
         </is>
       </c>
       <c r="B266" s="5" t="inlineStr">
         <is>
-          <t>Aminu Kano Teaching Hospital and Bayero University Kano</t>
+          <t>Starship Children's Hospital and Christchurch Hospital (Health New Zealand)</t>
         </is>
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>US National Institutes of Health RePORTER: 5D43TW011544-07, Vanderbilt-Nigeria Building Research Capacity in HIV and Non-communicable Diseases (V-BRCH)</t>
-        </is>
-      </c>
-      <c r="D266" s="5" t="inlineStr">
-        <is>
-          <t>FY2026 (budget start 1 January 2026)</t>
-        </is>
-      </c>
+          <t>Children's Cancer Institute Zero Childhood Cancer</t>
+        </is>
+      </c>
+      <c r="D266" s="5" t="inlineStr"/>
       <c r="E266" s="5" t="inlineStr">
         <is>
-          <t>https://reporter.nih.gov/project-details/11378551</t>
+          <t>https://www.ccia.org.au/personalised-medicine/zero-childhood-cancer</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
         <is>
-          <t>Virginia Commonwealth University (VCU Massey Comprehensive Cancer Center)</t>
+          <t>Children's Cancer Institute and Sydney Children's Hospital, Randwick (Zero Childhood Cancer Program)</t>
         </is>
       </c>
       <c r="B267" s="5" t="inlineStr">
         <is>
-          <t>National Hospital Abuja</t>
+          <t>Starship Children's Hospital and Christchurch Hospital (Health New Zealand)</t>
         </is>
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>Anthonia Obokoh National Hospital signs MoU with U.S. cancer center to boost research, clinical trials in Nigeria</t>
+          <t>ANZCHOG Precision Medicine for Every Child With Cancer (NCT05504772)</t>
         </is>
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="E267" s="5" t="inlineStr">
         <is>
-          <t>https://nairametrics.com/2025/07/01/national-hospital-signs-mou-with-u-s-cancer-center-to-boost-research-clinical-trials-in-nigeria/</t>
+          <t>https://clinicaltrials.gov/study/NCT05504772</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
         <is>
-          <t>Evercare Group (owned at its 2021 launch by the TPG-managed Evercare Health Fund)</t>
+          <t>Children's Hospital of Zhejiang University School of Medicine</t>
         </is>
       </c>
       <c r="B268" s="5" t="inlineStr">
         <is>
-          <t>Evercare Hospital Lekki</t>
+          <t>NZ-China Non-Communicable Diseases Research Collaboration Centre (University of Otago)</t>
         </is>
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>Esther Oluku Evercare, MedEI, Commence Advanced Cochlear Implant Surgery in Nigeria</t>
+          <t>NZ-China NCD Research Collaboration Centre NZ-China non-communicable disease research strengthened</t>
         </is>
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2017-11-02</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
-          <t>https://www.thisdaylive.com/2024/10/10/evercare-medei-commence-advanced-cochlear-implant-surgery-in-nigeria/</t>
+          <t>https://crcc.nz/crcc/?p=374</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
         <is>
-          <t>Evercare Group (owned at its 2021 launch by the TPG-managed Evercare Health Fund)</t>
+          <t>Children's Hospital of Zhejiang University School of Medicine</t>
         </is>
       </c>
       <c r="B269" s="5" t="inlineStr">
         <is>
-          <t>Evercare Hospital Lekki</t>
+          <t>NZ-China Non-Communicable Diseases Research Collaboration Centre (University of Otago)</t>
         </is>
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>TPG Evercare Group set to deliver accessible, quality healthcare in Nigeria</t>
+          <t>NZ-China NCD Research Collaboration Centre The 3rd NZ-China Non-Communicable Diseases Research Cooperation Forum deemed major success</t>
         </is>
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
         <is>
-          <t>https://www.tpg.com/news-and-insights/evercare-group-set-deliver-accessible-quality-healthcare-nigeria</t>
+          <t>https://crcc.nz/crcc/?p=80</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="5" t="inlineStr">
         <is>
-          <t>Evercare Group (owned at its 2021 launch by the TPG-managed Evercare Health Fund)</t>
+          <t>Fiji National University (College of Medicine, Nursing and Health Sciences)</t>
         </is>
       </c>
       <c r="B270" s="5" t="inlineStr">
         <is>
-          <t>Evercare Hospital Lekki</t>
+          <t>University of Auckland</t>
         </is>
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>TPG Evercare Group set to deliver accessible, quality healthcare in Nigeria through a new world-class multispecialty hospital</t>
+          <t>Fiji National University FNU formalises collaboration with the University of Auckland</t>
         </is>
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>26 February 2021</t>
+          <t>2022-05-09</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
-          <t>https://www.tpg.com/news-and-insights/evercare-group-set-deliver-accessible-quality-healthcare-nigeria</t>
+          <t>https://www.fnu.ac.fj/?p=17198</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
         <is>
-          <t>King's College Hospital NHS Foundation Trust</t>
+          <t>Huashan Hospital (Fudan University)</t>
         </is>
       </c>
       <c r="B271" s="5" t="inlineStr">
         <is>
-          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+          <t>NZ-China Non-Communicable Diseases Research Collaboration Centre (University of Otago)</t>
         </is>
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>Afreximbank King's College Hospital, London (KCH) affirmed as Clinical Partner</t>
+          <t>NZ-China NCD Research Collaboration Centre NZ-China non-communicable disease research strengthened</t>
         </is>
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
+          <t>2017-11-02</t>
         </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
         <is>
-          <t>https://www.amce.net/?p=10738</t>
+          <t>https://crcc.nz/crcc/?p=374</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
         <is>
-          <t>King's College Hospital NHS Foundation Trust</t>
+          <t>Huashan Hospital (Fudan University)</t>
         </is>
       </c>
       <c r="B272" s="5" t="inlineStr">
         <is>
-          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+          <t>NZ-China Non-Communicable Diseases Research Collaboration Centre (University of Otago)</t>
         </is>
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>Nnaemeka Onyekachi Afreximbank, BOI sign $75 million financing support for local manufacturers in Nigerian healthcare sector (reports AMCE commissioning)</t>
+          <t>NZ-China NCD Research Collaboration Centre The 3rd NZ-China Non-Communicable Diseases Research Cooperation Forum deemed major success</t>
         </is>
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
-          <t>https://nairametrics.com/2025/06/05/afreximbank-boi-sign-75-million-financing-support-for-local-manufacturers-in-nigerian-healthcare-sector/</t>
+          <t>https://crcc.nz/crcc/?p=80</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
         <is>
-          <t>King's College Hospital NHS Foundation Trust</t>
+          <t>Shanghai Ninth People's Hospital (Shanghai Jiao Tong University School of Medicine)</t>
         </is>
       </c>
       <c r="B273" s="5" t="inlineStr">
         <is>
-          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+          <t>University of Otago Faculty of Dentistry</t>
         </is>
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
-          <t>Brand Spur African Medical Centre Of Excellence Opens In Abuja As Nigeria Targets $2.2bn Health Sector Overhaul</t>
+          <t>Shanghai Jiao Tong University School of Medicine Shanghai Ninth People's Hospital and University of Otago Faculty of Dentistry in New Zealand Signed Memorandum of Understanding and Launched Joint Laboratory</t>
         </is>
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="E273" s="5" t="inlineStr">
         <is>
-          <t>https://brandspurng.com/2026/09/19/african-medical-centre-of-excellence-opens-in-abuja-as-nigeria-targets-2-2bn-health-sector-overhaul/</t>
+          <t>https://www.shsmu.edu.cn/english/info/1021/4710.htm</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
         <is>
-          <t>King's College London</t>
+          <t>Healthe Care Australia (then a subsidiary of Luye Medical Group)</t>
         </is>
       </c>
       <c r="B274" s="5" t="inlineStr">
         <is>
-          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+          <t>Boulcott Hospital (Pulse Health NZ)</t>
         </is>
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
-          <t>King's College London New partnership to deliver medical excellence in Nigeria</t>
+          <t>Commerce Commission Commission clears private hospitals merger subject to divestment</t>
         </is>
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="E274" s="5" t="inlineStr">
         <is>
-          <t>https://www.kcl.ac.uk/news/new-partnership-to-deliver-medical-excellence-in-nigeria</t>
+          <t>https://comcom.govt.nz/news-and-media/media-releases/2021/commission-clears-private-hospitals-merger-subject-to-divestment</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
         <is>
-          <t>King's College London</t>
+          <t>Healthe Care Australia (then a subsidiary of Luye Medical Group)</t>
         </is>
       </c>
       <c r="B275" s="5" t="inlineStr">
         <is>
-          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+          <t>Boulcott Hospital (Pulse Health NZ)</t>
         </is>
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>Nnaemeka Onyekachi Afreximbank, BOI sign $75 million financing support for local manufacturers in Nigerian healthcare sector (reports KCL terms of agreement)</t>
+          <t>Andrew Bevin Rangatira buys Boulcott Hospital operations for undisclosed sum</t>
         </is>
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2022-03-02</t>
         </is>
       </c>
       <c r="E275" s="5" t="inlineStr">
         <is>
-          <t>https://nairametrics.com/2025/06/05/afreximbank-boi-sign-75-million-financing-support-for-local-manufacturers-in-nigerian-healthcare-sector/</t>
+          <t>https://nbr.co.nz/story/rangatira-buys-boulcott-hospital-operations</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="inlineStr">
         <is>
-          <t>Liverpool School of Tropical Medicine</t>
+          <t>Johns Hopkins University (Johns Hopkins Hospital)</t>
         </is>
       </c>
       <c r="B276" s="5" t="inlineStr">
         <is>
-          <t>National Postgraduate Medical College of Nigeria (with Wellbeing Foundation Africa)</t>
+          <t>Afe Babalola University (ABUAD)</t>
         </is>
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>Liverpool School of Tropical Medicine LSTM and Wellbeing Foundation Africa launch Advanced Training for Resident Doctors in Nigeria</t>
+          <t>Afe Babalola University ABUAD Tripartite agreement with John Hopkins University USA and Little by Little Foundation</t>
         </is>
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2023-01-17</t>
         </is>
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
-          <t>https://lstmed.ac.uk/news/liverpool-school-of-tropical-medicine-and-wellbeing-foundation-africa-launch-advanced-training-for-resident-doctors-in-nigeria/</t>
+          <t>https://www.abuad.edu.ng/abuad-tripartite-agreement-with-john-hopkins-university-usa-and-little-by-little-foundation/</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>Liverpool School of Tropical Medicine</t>
+          <t>Johns Hopkins University (Johns Hopkins Hospital)</t>
         </is>
       </c>
       <c r="B277" s="5" t="inlineStr">
         <is>
-          <t>National Postgraduate Medical College of Nigeria (with Wellbeing Foundation Africa)</t>
+          <t>Afe Babalola University (ABUAD)</t>
         </is>
       </c>
       <c r="C277" s="5" t="inlineStr">
         <is>
-          <t>Wellbeing Foundation Africa AOSS Training Expands to Port Harcourt and Gombe</t>
+          <t>ThisDay ABUAD, John Hopkins Partner to Boost Medical Training</t>
         </is>
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2023-01-18</t>
         </is>
       </c>
       <c r="E277" s="5" t="inlineStr">
         <is>
-          <t>https://wbfafrica.org/aoss-training-expands-to-port-harcourt-and-gombe-ghwp/</t>
+          <t>https://www.thisdaylive.com/2023/01/18/abuad-john-hopkins-partner-to-boost-medical-training/</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="5" t="inlineStr">
         <is>
-          <t>Liverpool School of Tropical Medicine</t>
+          <t>Johns Hopkins University (Johns Hopkins Hospital)</t>
         </is>
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
-          <t>National Postgraduate Medical College of Nigeria (with Wellbeing Foundation Africa)</t>
+          <t>Afe Babalola University (ABUAD)</t>
         </is>
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>Wellbeing Foundation Africa Liverpool School of Tropical Medicine, Wellbeing Foundation Africa, and Global Health Workforce Partnership</t>
+          <t>Afe Babalola University ABUAD Holds Seventh Induction Ceremony for Fresh Doctors</t>
         </is>
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>5 February 2025</t>
         </is>
       </c>
       <c r="E278" s="5" t="inlineStr">
         <is>
-          <t>https://wbfafrica.org/liverpool-school-of-tropical-medicine-wellbeing-foundation-africa-and-global-health-workforce-partnership/</t>
+          <t>https://vc.abuad.edu.ng/abuad-holds-seventh-induction-ceremony-for-fresh-doctors/</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>Manipal Hospitals</t>
+          <t>Mayo Clinic (Mayo Clinic Global Consulting)</t>
         </is>
       </c>
       <c r="B279" s="5" t="inlineStr">
         <is>
-          <t>Afe Babalola University Multi-System Hospital</t>
+          <t>Iwosan Investments Limited (Iwosan Lagoon Hospitals and Lagos Medipark Hospital)</t>
         </is>
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>Folasade Akpan ABUAD multi-system hospital records 50 successful kidney transplants</t>
+          <t>The Sun Iwosan engages Mayo Clinic to advance high-quality patient-centered healthcare</t>
         </is>
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E279" s="5" t="inlineStr">
         <is>
-          <t>https://nannews.ng/abuad-multi-system-hospital-records-50-successful-kidney-transplants/</t>
+          <t>https://thesun.ng/iwosan-engages-mayo-clinic-to-advance-high-quality-patient-centered-healthcare/</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
         <is>
-          <t>The Christie NHS Foundation Trust</t>
+          <t>Mayo Clinic (Mayo Clinic Global Consulting)</t>
         </is>
       </c>
       <c r="B280" s="5" t="inlineStr">
         <is>
-          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+          <t>Iwosan Investments Limited (Iwosan Lagoon Hospitals and Lagos Medipark Hospital)</t>
         </is>
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>The Christie NHS Foundation Trust The Christie International hosts African Medical Centre of Excellence visit</t>
+          <t>BrandIconImage Iwosan Investments Limited Engages Mayo Clinic Global Consulting to Advance High-Quality Patient-Centered Healthcare in Nigeria</t>
         </is>
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
-          <t>https://christie.nhs.uk/about-us/news-at-the-christie/latest-news-stories/the-christie-international-hosts-african-medical-centre-of-excellence-visit</t>
+          <t>https://www.brandiconimage.com/2025/04/iwosan-investments-limited-engages-mayo.html</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>The Christie NHS Foundation Trust</t>
+          <t>Mayo Clinic (Mayo Clinic Global Consulting)</t>
         </is>
       </c>
       <c r="B281" s="5" t="inlineStr">
         <is>
-          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+          <t>Iwosan Investments Limited (Iwosan Lagoon Hospitals and Lagos Medipark Hospital)</t>
         </is>
       </c>
       <c r="C281" s="5" t="inlineStr">
         <is>
-          <t>The Christie NHS Foundation Trust The Christie supporting a new African Medical Centre of Excellence project</t>
-        </is>
-      </c>
-      <c r="D281" s="5" t="inlineStr"/>
+          <t>BusinessDay Iwosan engages Mayo Clinic to advance high quality patient centered healthcare in Nigeria</t>
+        </is>
+      </c>
+      <c r="D281" s="5" t="inlineStr">
+        <is>
+          <t>8 April 2025</t>
+        </is>
+      </c>
       <c r="E281" s="5" t="inlineStr">
         <is>
-          <t>https://christie.nhs.uk/about-us/about-the-christie/the-christie-international/partnerships-experience/the-christie-supporting-a-new-african-medical-centre-of-excellence-project</t>
+          <t>https://businessday.ng/health/article/iwosan-engages-mayo-clinic-to-advance-high-quality-patient-centered-healthcare-in-nigeria/</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
         <is>
-          <t>The Royal Marsden NHS Foundation Trust</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="B282" s="5" t="inlineStr">
         <is>
-          <t>Marcelle Ruth Cancer Centre &amp; Specialist Hospital</t>
+          <t>Lagos University Teaching Hospital (LUTH) and College of Medicine, University of Lagos</t>
         </is>
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
-          <t>BusinessDay Marcelle Ruth Cancer Centre partners UK's Royal Marsden to improve healthcare delivery in West Africa</t>
+          <t>Memorial Sloan Kettering Cancer Center Global Cancer Research and Training Program 2025 Update</t>
         </is>
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E282" s="5" t="inlineStr">
         <is>
-          <t>https://businessday.ng/news/article/marcelle-ruth-cancer-centre-royal-marsden-partner-to-elevate-west-africas-oncology-care/</t>
+          <t>https://www.mskcc.org/sites/default/files/node/118066/documents/gcrt_report_2026_6_01-29-98-44.pdf</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>University of Birmingham</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="B283" s="5" t="inlineStr">
         <is>
-          <t>University of Lagos (with Lagos University Teaching Hospital)</t>
+          <t>Obafemi Awolowo University Teaching Hospitals Complex (OAUTHC)</t>
         </is>
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
-          <t>Adesina Wahab UNILAG, University of Birmingham sign MoU on Transnational Education Engagement</t>
+          <t>Memorial Sloan Kettering Cancer Center Global Cancer Research and Training Program 2025 Update</t>
         </is>
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>29 January 2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E283" s="5" t="inlineStr">
         <is>
-          <t>https://www.vanguardngr.com/2026/01/unilag-university-of-birmingham-sign-mou-on-transnational-education-engagement/</t>
+          <t>https://www.mskcc.org/sites/default/files/node/118066/documents/gcrt_report_2026_6_01-29-98-44.pdf</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
         <is>
-          <t>University of Glasgow</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="B284" s="5" t="inlineStr">
         <is>
-          <t>Ahmadu Bello University</t>
+          <t>Obafemi Awolowo University Teaching Hospitals Complex (OAUTHC)</t>
         </is>
       </c>
       <c r="C284" s="5" t="inlineStr">
         <is>
-          <t>University of Glasgow School of Infection &amp; Immunity's Professor Harry de-Koning helps facilitate UofG-ABU MoU</t>
-        </is>
-      </c>
-      <c r="D284" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
+          <t>Memorial Sloan Kettering Cancer Center MSK's Global Cancer Research and Training (GCRT) Program</t>
+        </is>
+      </c>
+      <c r="D284" s="5" t="inlineStr"/>
       <c r="E284" s="5" t="inlineStr">
         <is>
-          <t>https://www.gla.ac.uk/schools/infectionimmunity/newsevents/headline_1265451_en.html</t>
+          <t>https://www.mskcc.org/hcp-education-training/international/global-cancer-disparities-initiatives</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>University of Maryland School of Medicine</t>
+          <t>St. Jude Children's Research Hospital</t>
         </is>
       </c>
       <c r="B285" s="5" t="inlineStr">
         <is>
-          <t>Lagos University Teaching Hospital (LUTH)</t>
+          <t>Abubakar Tafawa Balewa University Teaching Hospital (ATBUTH)</t>
         </is>
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>Lagos University Teaching Hospital Maryland LUTH</t>
+          <t>Leadership Bauchi Teaching Hospital Seeks Alliance To Strengthen Cancer Care</t>
         </is>
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="E285" s="5" t="inlineStr">
         <is>
-          <t>https://luth.gov.ng/news/maryland-luth</t>
+          <t>https://leadership.ng/bauchi-teaching-hospital-seeks-alliance-to-strengthen-cancer-care/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
         <is>
-          <t>University of Maryland School of Medicine</t>
+          <t>St. Jude Children's Research Hospital</t>
         </is>
       </c>
       <c r="B286" s="5" t="inlineStr">
         <is>
-          <t>Lagos University Teaching Hospital (LUTH)</t>
+          <t>The Dorcas Cancer Foundation (TDCF)</t>
         </is>
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>Lagos University Teaching Hospital University of Maryland School of Medicine Collaborates with Lagos University Teaching Hospital on Non-Communicable Diseases</t>
+          <t>Sunday Ehigiator TDCF, St. Jude Global Alliance, Partner on Improving Pediatric Cancer Outcomes in Nigeria, Others</t>
         </is>
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>August 2024</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="E286" s="5" t="inlineStr">
         <is>
-          <t>https://luth.gov.ng/news/maryland-luth</t>
+          <t>https://www.thisdaylive.com/2024/12/17/tdcf-st-jude-global-alliance-partner-on-improving-pediatric-cancer-outcomes-in-nigeria-others/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>University of Maryland School of Medicine</t>
+          <t>St. Jude Children's Research Hospital</t>
         </is>
       </c>
       <c r="B287" s="5" t="inlineStr">
         <is>
-          <t>Lagos University Teaching Hospital (LUTH)</t>
+          <t>The Dorcas Cancer Foundation (TDCF)</t>
         </is>
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>IHV Nigeria University of Maryland Dean of Medicine Visits LUTH</t>
+          <t>BusinessDay TDCF admitted into St Jude Global Alliance to improve pediatric cancer outcomes in Nigeria</t>
         </is>
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>August 2024</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="E287" s="5" t="inlineStr">
         <is>
-          <t>https://www.ihvnigeria.org/university-of-maryland-dean-of-medicine-visits-luth/</t>
+          <t>https://businessday.ng/life/article/tdcf-admitted-into-st-jude-global-alliance-to-improve-pediatric-cancer-outcomes-in-nigeria/</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>University of Virginia Health System</t>
+          <t>University of Illinois Chicago (UIC School of Public Health)</t>
         </is>
       </c>
       <c r="B288" s="5" t="inlineStr">
         <is>
-          <t>Federal Medical Centre Owo</t>
+          <t>Lagos State University (LASU)</t>
         </is>
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>UVA School of Medicine UVA Department of Nephrology Partners With Nigerian Federal Medical Center</t>
+          <t>UIC School of Public Health UIC and Lagos State University Sign Memorandum of Agreement</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E288" s="5" t="inlineStr">
         <is>
-          <t>https://news.med.virginia.edu/community/uva-department-of-nephrology-partners-with-nigerian-federal-medical-center/</t>
+          <t>https://publichealth.uic.edu/news-stories/uic-and-lagos-state-university-sign-memorandum-of-agreement/</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
         <is>
-          <t>Yale School of Medicine (Department of Psychiatry)</t>
+          <t>University of Maryland School of Medicine (Institute of Human Virology)</t>
         </is>
       </c>
       <c r="B289" s="5" t="inlineStr">
         <is>
-          <t>Imo State University Teaching Hospital</t>
+          <t>Institute of Human Virology Nigeria (IHVN)</t>
         </is>
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>Nigeria Health Watch Making Happiness Local: How a Project is Improving Access to Mental Healthcare in Imo State</t>
+          <t>University of Maryland School of Medicine University of Maryland Baltimore leadership helps IHV Nigeria launch campus in Abuja</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="E289" s="5" t="inlineStr">
         <is>
-          <t>https://nigeriahealthwatch.com/articles/torchlight/making-happiness-local-how-a-project-is-improving-access-to-mental-healthcare-in-imo-state/</t>
+          <t>https://ihv.umaryland.edu/news/2023/university-of-maryland-baltimore-leadership-helps-ihv-nigeria-launch-state-of-the-art-campus-in-public-healthcare-treatment-training-and-research-in-nigeria.html</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
         <is>
-          <t>Yale School of Medicine (Department of Psychiatry)</t>
+          <t>University of Maryland School of Medicine (Institute of Human Virology)</t>
         </is>
       </c>
       <c r="B290" s="5" t="inlineStr">
         <is>
-          <t>Imo State University Teaching Hospital</t>
+          <t>Institute of Human Virology Nigeria (IHVN)</t>
         </is>
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>Yale School of Medicine The HAPPINESS Project</t>
-        </is>
-      </c>
-      <c r="D290" s="5" t="inlineStr"/>
+          <t>US National Institutes of Health RePORTER: 5D43TW012280-05, Expanding the pool of Independent Investigators in Implementation Science (Institute of Human Virology Nigeria)</t>
+        </is>
+      </c>
+      <c r="D290" s="5" t="inlineStr">
+        <is>
+          <t>FY2026 (budget start 1 February 2026)</t>
+        </is>
+      </c>
       <c r="E290" s="5" t="inlineStr">
         <is>
-          <t>https://medicine.yale.edu/psychiatry/education/programs-and-initiatives/happiness</t>
+          <t>https://reporter.nih.gov/project-details/11251575</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="5" t="inlineStr">
         <is>
-          <t>Apollo Hospitals</t>
+          <t>University of Miami (Sylvester Comprehensive Cancer Center)</t>
         </is>
       </c>
       <c r="B291" s="5" t="inlineStr">
         <is>
-          <t>Duchess International Hospital (Reddington Hospital Group)</t>
+          <t>Ahmadu Bello University Teaching Hospital (ABUTH)</t>
         </is>
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>ThisDay Duchess International Hospital Has Put Lagos on World Healthcare Map, Says US Consul General</t>
+          <t>ClinicalTrials.gov Study Evaluating Safety, Tolerability, and Metabolism of Niraparib (NCT06412120)</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>11 November 2021</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E291" s="5" t="inlineStr">
         <is>
-          <t>https://www.thisdaylive.com/index.php/2021/11/11/duchess-international-hospital-has-put-lagos-on-world-healthcare-map-says-us-consul-general/</t>
+          <t>https://clinicaltrials.gov/study/NCT06412120</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
         <is>
-          <t>Apollo Hospitals</t>
+          <t>University of Miami (Sylvester Comprehensive Cancer Center)</t>
         </is>
       </c>
       <c r="B292" s="5" t="inlineStr">
         <is>
-          <t>Duchess International Hospital (Reddington Hospital Group)</t>
+          <t>Ahmadu Bello University Teaching Hospital (ABUTH)</t>
         </is>
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>Appolonia Adeyemi Duchess International Hospital debuts in Lagos, builds capacity</t>
+          <t>Ahmadu Bello University ABUTH to begin clinical trials on ovarian cancer next year</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="E292" s="5" t="inlineStr">
         <is>
-          <t>https://newtelegraphng.com/?p=192437</t>
+          <t>https://abu.edu.ng/abuth-to-begin-clinical-trials-on-ovarian-cancer-next-year/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>Apollo Hospitals</t>
+          <t>University of Miami (Sylvester Comprehensive Cancer Center)</t>
         </is>
       </c>
       <c r="B293" s="5" t="inlineStr">
         <is>
-          <t>State House Clinic</t>
+          <t>Ahmadu Bello University Teaching Hospital (ABUTH)</t>
         </is>
       </c>
       <c r="C293" s="5" t="inlineStr">
         <is>
-          <t>Blueprint State House Clinic, Indian hospital collaborate to assist heart, kidney, cancer patients</t>
+          <t>US National Library of Medicine NCT06412120: Niraparib as Maintenance Following Front-Line Treatment for Ovarian Cancer in Women of African Ancestry</t>
         </is>
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>2022-07-29</t>
+          <t>5 August 2026</t>
         </is>
       </c>
       <c r="E293" s="5" t="inlineStr">
         <is>
-          <t>https://blueprint.ng/state-house-clinic-indian-hospital-collaborate-to-assist-heart-kidney-cancer-patients/</t>
+          <t>https://clinicaltrials.gov/study/NCT06412120</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
         <is>
-          <t>Apollo Hospitals</t>
+          <t>University of Virginia Health System</t>
         </is>
       </c>
       <c r="B294" s="5" t="inlineStr">
         <is>
-          <t>State House Clinic</t>
+          <t>Federal Medical Centre Umuahia</t>
         </is>
       </c>
       <c r="C294" s="5" t="inlineStr">
         <is>
-          <t>ThisDay Medical Tourism: Indian Hospital to Train Nigerian Doctors on Cancer Treatment</t>
+          <t>UVA School of Medicine UVA Partners With Federal Medical Center in Nigeria to Elevate Global Kidney Care</t>
         </is>
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E294" s="5" t="inlineStr">
         <is>
-          <t>https://www.thisdaylive.com/2024/03/05/medical-tourism-indian-hospital-to-train-nigerian-doctors-on-cancer-treatment/</t>
+          <t>https://news.med.virginia.edu/community/uva-nigeria-elevating-global-kidney-care/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
         <is>
-          <t>Memorial Hospitals Group</t>
+          <t>Vanderbilt University Medical Center (Vanderbilt Institute for Global Health)</t>
         </is>
       </c>
       <c r="B295" s="5" t="inlineStr">
         <is>
-          <t>Kasi Healthcare</t>
+          <t>Aminu Kano Teaching Hospital and Bayero University Kano</t>
         </is>
       </c>
       <c r="C295" s="5" t="inlineStr">
         <is>
-          <t>Temitayo Ayetoto-Oladehinde Nigeria partners Turkey to tap $8.5trn healthcare market</t>
-        </is>
-      </c>
-      <c r="D295" s="5" t="inlineStr">
-        <is>
-          <t>2024-09-27</t>
-        </is>
-      </c>
+          <t>Fogarty International Center Vanderbilt-Nigeria Building Research Capacity in HIV and NCDs (V-BRCH)</t>
+        </is>
+      </c>
+      <c r="D295" s="5" t="inlineStr"/>
       <c r="E295" s="5" t="inlineStr">
         <is>
-          <t>https://businessday.ng/news/article/nigeria-partners-turkey-to-tap-8-5trn-healthcare-market/</t>
+          <t>https://fic.nih.gov/Grants/Search/Pages/hiv-research-training-d43tw011544.aspx</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
         <is>
-          <t>Peking University People's Hospital (named variously in press as People's University Hospital, Beijing)</t>
+          <t>Vanderbilt University Medical Center (Vanderbilt Institute for Global Health)</t>
         </is>
       </c>
       <c r="B296" s="5" t="inlineStr">
         <is>
-          <t>University of Abuja Teaching Hospital</t>
+          <t>Aminu Kano Teaching Hospital and Bayero University Kano</t>
         </is>
       </c>
       <c r="C296" s="5" t="inlineStr">
         <is>
-          <t>Within Nigeria Nigeria signs letter of intent with China to improve health sector</t>
-        </is>
-      </c>
-      <c r="D296" s="5" t="inlineStr">
-        <is>
-          <t>2022-08-20</t>
-        </is>
-      </c>
+          <t>Vanderbilt Institute for Global Health V-BRCH</t>
+        </is>
+      </c>
+      <c r="D296" s="5" t="inlineStr"/>
       <c r="E296" s="5" t="inlineStr">
         <is>
-          <t>https://www.withinnigeria.com/broadnews/2022/08/20/nigeria-signs-letter-of-intent-with-china-to-improve-health-sector/</t>
+          <t>https://www.vumc.org/global-health/v-brch</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
         <is>
+          <t>Vanderbilt University Medical Center (Vanderbilt Institute for Global Health)</t>
+        </is>
+      </c>
+      <c r="B297" s="5" t="inlineStr">
+        <is>
+          <t>Aminu Kano Teaching Hospital and Bayero University Kano</t>
+        </is>
+      </c>
+      <c r="C297" s="5" t="inlineStr">
+        <is>
+          <t>US National Institutes of Health RePORTER: 5D43TW011544-07, Vanderbilt-Nigeria Building Research Capacity in HIV and Non-communicable Diseases (V-BRCH)</t>
+        </is>
+      </c>
+      <c r="D297" s="5" t="inlineStr">
+        <is>
+          <t>FY2026 (budget start 1 January 2026)</t>
+        </is>
+      </c>
+      <c r="E297" s="5" t="inlineStr">
+        <is>
+          <t>https://reporter.nih.gov/project-details/11378551</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="5" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University (VCU Massey Comprehensive Cancer Center)</t>
+        </is>
+      </c>
+      <c r="B298" s="5" t="inlineStr">
+        <is>
+          <t>National Hospital Abuja</t>
+        </is>
+      </c>
+      <c r="C298" s="5" t="inlineStr">
+        <is>
+          <t>Anthonia Obokoh National Hospital signs MoU with U.S. cancer center to boost research, clinical trials in Nigeria</t>
+        </is>
+      </c>
+      <c r="D298" s="5" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="E298" s="5" t="inlineStr">
+        <is>
+          <t>https://nairametrics.com/2025/07/01/national-hospital-signs-mou-with-u-s-cancer-center-to-boost-research-clinical-trials-in-nigeria/</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="5" t="inlineStr">
+        <is>
+          <t>Evercare Group (owned at its 2021 launch by the TPG-managed Evercare Health Fund)</t>
+        </is>
+      </c>
+      <c r="B299" s="5" t="inlineStr">
+        <is>
+          <t>Evercare Hospital Lekki</t>
+        </is>
+      </c>
+      <c r="C299" s="5" t="inlineStr">
+        <is>
+          <t>Esther Oluku Evercare, MedEI, Commence Advanced Cochlear Implant Surgery in Nigeria</t>
+        </is>
+      </c>
+      <c r="D299" s="5" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="E299" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thisdaylive.com/2024/10/10/evercare-medei-commence-advanced-cochlear-implant-surgery-in-nigeria/</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="5" t="inlineStr">
+        <is>
+          <t>Evercare Group (owned at its 2021 launch by the TPG-managed Evercare Health Fund)</t>
+        </is>
+      </c>
+      <c r="B300" s="5" t="inlineStr">
+        <is>
+          <t>Evercare Hospital Lekki</t>
+        </is>
+      </c>
+      <c r="C300" s="5" t="inlineStr">
+        <is>
+          <t>TPG Evercare Group set to deliver accessible, quality healthcare in Nigeria</t>
+        </is>
+      </c>
+      <c r="D300" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E300" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tpg.com/news-and-insights/evercare-group-set-deliver-accessible-quality-healthcare-nigeria</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="5" t="inlineStr">
+        <is>
+          <t>Evercare Group (owned at its 2021 launch by the TPG-managed Evercare Health Fund)</t>
+        </is>
+      </c>
+      <c r="B301" s="5" t="inlineStr">
+        <is>
+          <t>Evercare Hospital Lekki</t>
+        </is>
+      </c>
+      <c r="C301" s="5" t="inlineStr">
+        <is>
+          <t>TPG Evercare Group set to deliver accessible, quality healthcare in Nigeria through a new world-class multispecialty hospital</t>
+        </is>
+      </c>
+      <c r="D301" s="5" t="inlineStr">
+        <is>
+          <t>26 February 2021</t>
+        </is>
+      </c>
+      <c r="E301" s="5" t="inlineStr">
+        <is>
+          <t>https://www.tpg.com/news-and-insights/evercare-group-set-deliver-accessible-quality-healthcare-nigeria</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="5" t="inlineStr">
+        <is>
+          <t>King's College Hospital NHS Foundation Trust</t>
+        </is>
+      </c>
+      <c r="B302" s="5" t="inlineStr">
+        <is>
+          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+        </is>
+      </c>
+      <c r="C302" s="5" t="inlineStr">
+        <is>
+          <t>Afreximbank King's College Hospital, London (KCH) affirmed as Clinical Partner</t>
+        </is>
+      </c>
+      <c r="D302" s="5" t="inlineStr">
+        <is>
+          <t>2021-06-03</t>
+        </is>
+      </c>
+      <c r="E302" s="5" t="inlineStr">
+        <is>
+          <t>https://www.amce.net/?p=10738</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="5" t="inlineStr">
+        <is>
+          <t>King's College Hospital NHS Foundation Trust</t>
+        </is>
+      </c>
+      <c r="B303" s="5" t="inlineStr">
+        <is>
+          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+        </is>
+      </c>
+      <c r="C303" s="5" t="inlineStr">
+        <is>
+          <t>Nnaemeka Onyekachi Afreximbank, BOI sign $75 million financing support for local manufacturers in Nigerian healthcare sector (reports AMCE commissioning)</t>
+        </is>
+      </c>
+      <c r="D303" s="5" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="E303" s="5" t="inlineStr">
+        <is>
+          <t>https://nairametrics.com/2025/06/05/afreximbank-boi-sign-75-million-financing-support-for-local-manufacturers-in-nigerian-healthcare-sector/</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="5" t="inlineStr">
+        <is>
+          <t>King's College Hospital NHS Foundation Trust</t>
+        </is>
+      </c>
+      <c r="B304" s="5" t="inlineStr">
+        <is>
+          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+        </is>
+      </c>
+      <c r="C304" s="5" t="inlineStr">
+        <is>
+          <t>Brand Spur African Medical Centre Of Excellence Opens In Abuja As Nigeria Targets $2.2bn Health Sector Overhaul</t>
+        </is>
+      </c>
+      <c r="D304" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E304" s="5" t="inlineStr">
+        <is>
+          <t>https://brandspurng.com/2026/09/19/african-medical-centre-of-excellence-opens-in-abuja-as-nigeria-targets-2-2bn-health-sector-overhaul/</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="5" t="inlineStr">
+        <is>
+          <t>King's College London</t>
+        </is>
+      </c>
+      <c r="B305" s="5" t="inlineStr">
+        <is>
+          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+        </is>
+      </c>
+      <c r="C305" s="5" t="inlineStr">
+        <is>
+          <t>King's College London New partnership to deliver medical excellence in Nigeria</t>
+        </is>
+      </c>
+      <c r="D305" s="5" t="inlineStr">
+        <is>
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="E305" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/news/new-partnership-to-deliver-medical-excellence-in-nigeria</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="5" t="inlineStr">
+        <is>
+          <t>King's College London</t>
+        </is>
+      </c>
+      <c r="B306" s="5" t="inlineStr">
+        <is>
+          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+        </is>
+      </c>
+      <c r="C306" s="5" t="inlineStr">
+        <is>
+          <t>Nnaemeka Onyekachi Afreximbank, BOI sign $75 million financing support for local manufacturers in Nigerian healthcare sector (reports KCL terms of agreement)</t>
+        </is>
+      </c>
+      <c r="D306" s="5" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="E306" s="5" t="inlineStr">
+        <is>
+          <t>https://nairametrics.com/2025/06/05/afreximbank-boi-sign-75-million-financing-support-for-local-manufacturers-in-nigerian-healthcare-sector/</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="5" t="inlineStr">
+        <is>
+          <t>Liverpool School of Tropical Medicine</t>
+        </is>
+      </c>
+      <c r="B307" s="5" t="inlineStr">
+        <is>
+          <t>National Postgraduate Medical College of Nigeria (with Wellbeing Foundation Africa)</t>
+        </is>
+      </c>
+      <c r="C307" s="5" t="inlineStr">
+        <is>
+          <t>Liverpool School of Tropical Medicine LSTM and Wellbeing Foundation Africa launch Advanced Training for Resident Doctors in Nigeria</t>
+        </is>
+      </c>
+      <c r="D307" s="5" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="E307" s="5" t="inlineStr">
+        <is>
+          <t>https://lstmed.ac.uk/news/liverpool-school-of-tropical-medicine-and-wellbeing-foundation-africa-launch-advanced-training-for-resident-doctors-in-nigeria/</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="5" t="inlineStr">
+        <is>
+          <t>Liverpool School of Tropical Medicine</t>
+        </is>
+      </c>
+      <c r="B308" s="5" t="inlineStr">
+        <is>
+          <t>National Postgraduate Medical College of Nigeria (with Wellbeing Foundation Africa)</t>
+        </is>
+      </c>
+      <c r="C308" s="5" t="inlineStr">
+        <is>
+          <t>Wellbeing Foundation Africa AOSS Training Expands to Port Harcourt and Gombe</t>
+        </is>
+      </c>
+      <c r="D308" s="5" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="E308" s="5" t="inlineStr">
+        <is>
+          <t>https://wbfafrica.org/aoss-training-expands-to-port-harcourt-and-gombe-ghwp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="5" t="inlineStr">
+        <is>
+          <t>Liverpool School of Tropical Medicine</t>
+        </is>
+      </c>
+      <c r="B309" s="5" t="inlineStr">
+        <is>
+          <t>National Postgraduate Medical College of Nigeria (with Wellbeing Foundation Africa)</t>
+        </is>
+      </c>
+      <c r="C309" s="5" t="inlineStr">
+        <is>
+          <t>Wellbeing Foundation Africa Liverpool School of Tropical Medicine, Wellbeing Foundation Africa, and Global Health Workforce Partnership</t>
+        </is>
+      </c>
+      <c r="D309" s="5" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="E309" s="5" t="inlineStr">
+        <is>
+          <t>https://wbfafrica.org/liverpool-school-of-tropical-medicine-wellbeing-foundation-africa-and-global-health-workforce-partnership/</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="5" t="inlineStr">
+        <is>
+          <t>Manipal Hospitals</t>
+        </is>
+      </c>
+      <c r="B310" s="5" t="inlineStr">
+        <is>
+          <t>Afe Babalola University Multi-System Hospital</t>
+        </is>
+      </c>
+      <c r="C310" s="5" t="inlineStr">
+        <is>
+          <t>Folasade Akpan ABUAD multi-system hospital records 50 successful kidney transplants</t>
+        </is>
+      </c>
+      <c r="D310" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E310" s="5" t="inlineStr">
+        <is>
+          <t>https://nannews.ng/abuad-multi-system-hospital-records-50-successful-kidney-transplants/</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="5" t="inlineStr">
+        <is>
+          <t>The Christie NHS Foundation Trust</t>
+        </is>
+      </c>
+      <c r="B311" s="5" t="inlineStr">
+        <is>
+          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+        </is>
+      </c>
+      <c r="C311" s="5" t="inlineStr">
+        <is>
+          <t>The Christie NHS Foundation Trust The Christie International hosts African Medical Centre of Excellence visit</t>
+        </is>
+      </c>
+      <c r="D311" s="5" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="E311" s="5" t="inlineStr">
+        <is>
+          <t>https://christie.nhs.uk/about-us/news-at-the-christie/latest-news-stories/the-christie-international-hosts-african-medical-centre-of-excellence-visit</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="5" t="inlineStr">
+        <is>
+          <t>The Christie NHS Foundation Trust</t>
+        </is>
+      </c>
+      <c r="B312" s="5" t="inlineStr">
+        <is>
+          <t>African Medical Centre of Excellence (AMCE), developed by Afreximbank</t>
+        </is>
+      </c>
+      <c r="C312" s="5" t="inlineStr">
+        <is>
+          <t>The Christie NHS Foundation Trust The Christie supporting a new African Medical Centre of Excellence project</t>
+        </is>
+      </c>
+      <c r="D312" s="5" t="inlineStr"/>
+      <c r="E312" s="5" t="inlineStr">
+        <is>
+          <t>https://christie.nhs.uk/about-us/about-the-christie/the-christie-international/partnerships-experience/the-christie-supporting-a-new-african-medical-centre-of-excellence-project</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="5" t="inlineStr">
+        <is>
+          <t>The Royal Marsden NHS Foundation Trust</t>
+        </is>
+      </c>
+      <c r="B313" s="5" t="inlineStr">
+        <is>
+          <t>Marcelle Ruth Cancer Centre &amp; Specialist Hospital</t>
+        </is>
+      </c>
+      <c r="C313" s="5" t="inlineStr">
+        <is>
+          <t>BusinessDay Marcelle Ruth Cancer Centre partners UK's Royal Marsden to improve healthcare delivery in West Africa</t>
+        </is>
+      </c>
+      <c r="D313" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E313" s="5" t="inlineStr">
+        <is>
+          <t>https://businessday.ng/news/article/marcelle-ruth-cancer-centre-royal-marsden-partner-to-elevate-west-africas-oncology-care/</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="5" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+      <c r="B314" s="5" t="inlineStr">
+        <is>
+          <t>University of Lagos (with Lagos University Teaching Hospital)</t>
+        </is>
+      </c>
+      <c r="C314" s="5" t="inlineStr">
+        <is>
+          <t>Adesina Wahab UNILAG, University of Birmingham sign MoU on Transnational Education Engagement</t>
+        </is>
+      </c>
+      <c r="D314" s="5" t="inlineStr">
+        <is>
+          <t>29 January 2026</t>
+        </is>
+      </c>
+      <c r="E314" s="5" t="inlineStr">
+        <is>
+          <t>https://www.vanguardngr.com/2026/01/unilag-university-of-birmingham-sign-mou-on-transnational-education-engagement/</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="5" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="B315" s="5" t="inlineStr">
+        <is>
+          <t>Ahmadu Bello University</t>
+        </is>
+      </c>
+      <c r="C315" s="5" t="inlineStr">
+        <is>
+          <t>University of Glasgow School of Infection &amp; Immunity's Professor Harry de-Koning helps facilitate UofG-ABU MoU</t>
+        </is>
+      </c>
+      <c r="D315" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E315" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gla.ac.uk/schools/infectionimmunity/newsevents/headline_1265451_en.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="5" t="inlineStr">
+        <is>
+          <t>University of Maryland School of Medicine</t>
+        </is>
+      </c>
+      <c r="B316" s="5" t="inlineStr">
+        <is>
+          <t>Lagos University Teaching Hospital (LUTH)</t>
+        </is>
+      </c>
+      <c r="C316" s="5" t="inlineStr">
+        <is>
+          <t>Lagos University Teaching Hospital Maryland LUTH</t>
+        </is>
+      </c>
+      <c r="D316" s="5" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="E316" s="5" t="inlineStr">
+        <is>
+          <t>https://luth.gov.ng/news/maryland-luth</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="5" t="inlineStr">
+        <is>
+          <t>University of Maryland School of Medicine</t>
+        </is>
+      </c>
+      <c r="B317" s="5" t="inlineStr">
+        <is>
+          <t>Lagos University Teaching Hospital (LUTH)</t>
+        </is>
+      </c>
+      <c r="C317" s="5" t="inlineStr">
+        <is>
+          <t>Lagos University Teaching Hospital University of Maryland School of Medicine Collaborates with Lagos University Teaching Hospital on Non-Communicable Diseases</t>
+        </is>
+      </c>
+      <c r="D317" s="5" t="inlineStr">
+        <is>
+          <t>August 2024</t>
+        </is>
+      </c>
+      <c r="E317" s="5" t="inlineStr">
+        <is>
+          <t>https://luth.gov.ng/news/maryland-luth</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="5" t="inlineStr">
+        <is>
+          <t>University of Maryland School of Medicine</t>
+        </is>
+      </c>
+      <c r="B318" s="5" t="inlineStr">
+        <is>
+          <t>Lagos University Teaching Hospital (LUTH)</t>
+        </is>
+      </c>
+      <c r="C318" s="5" t="inlineStr">
+        <is>
+          <t>IHV Nigeria University of Maryland Dean of Medicine Visits LUTH</t>
+        </is>
+      </c>
+      <c r="D318" s="5" t="inlineStr">
+        <is>
+          <t>August 2024</t>
+        </is>
+      </c>
+      <c r="E318" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ihvnigeria.org/university-of-maryland-dean-of-medicine-visits-luth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="5" t="inlineStr">
+        <is>
+          <t>University of Virginia Health System</t>
+        </is>
+      </c>
+      <c r="B319" s="5" t="inlineStr">
+        <is>
+          <t>Federal Medical Centre Owo</t>
+        </is>
+      </c>
+      <c r="C319" s="5" t="inlineStr">
+        <is>
+          <t>UVA School of Medicine UVA Department of Nephrology Partners With Nigerian Federal Medical Center</t>
+        </is>
+      </c>
+      <c r="D319" s="5" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="E319" s="5" t="inlineStr">
+        <is>
+          <t>https://news.med.virginia.edu/community/uva-department-of-nephrology-partners-with-nigerian-federal-medical-center/</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="5" t="inlineStr">
+        <is>
+          <t>Yale School of Medicine (Department of Psychiatry)</t>
+        </is>
+      </c>
+      <c r="B320" s="5" t="inlineStr">
+        <is>
+          <t>Imo State University Teaching Hospital</t>
+        </is>
+      </c>
+      <c r="C320" s="5" t="inlineStr">
+        <is>
+          <t>Nigeria Health Watch Making Happiness Local: How a Project is Improving Access to Mental Healthcare in Imo State</t>
+        </is>
+      </c>
+      <c r="D320" s="5" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="E320" s="5" t="inlineStr">
+        <is>
+          <t>https://nigeriahealthwatch.com/articles/torchlight/making-happiness-local-how-a-project-is-improving-access-to-mental-healthcare-in-imo-state/</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="5" t="inlineStr">
+        <is>
+          <t>Yale School of Medicine (Department of Psychiatry)</t>
+        </is>
+      </c>
+      <c r="B321" s="5" t="inlineStr">
+        <is>
+          <t>Imo State University Teaching Hospital</t>
+        </is>
+      </c>
+      <c r="C321" s="5" t="inlineStr">
+        <is>
+          <t>Yale School of Medicine The HAPPINESS Project</t>
+        </is>
+      </c>
+      <c r="D321" s="5" t="inlineStr"/>
+      <c r="E321" s="5" t="inlineStr">
+        <is>
+          <t>https://medicine.yale.edu/psychiatry/education/programs-and-initiatives/happiness</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="5" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals</t>
+        </is>
+      </c>
+      <c r="B322" s="5" t="inlineStr">
+        <is>
+          <t>Duchess International Hospital (Reddington Hospital Group)</t>
+        </is>
+      </c>
+      <c r="C322" s="5" t="inlineStr">
+        <is>
+          <t>ThisDay Duchess International Hospital Has Put Lagos on World Healthcare Map, Says US Consul General</t>
+        </is>
+      </c>
+      <c r="D322" s="5" t="inlineStr">
+        <is>
+          <t>11 November 2021</t>
+        </is>
+      </c>
+      <c r="E322" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thisdaylive.com/index.php/2021/11/11/duchess-international-hospital-has-put-lagos-on-world-healthcare-map-says-us-consul-general/</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="5" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals</t>
+        </is>
+      </c>
+      <c r="B323" s="5" t="inlineStr">
+        <is>
+          <t>Duchess International Hospital (Reddington Hospital Group)</t>
+        </is>
+      </c>
+      <c r="C323" s="5" t="inlineStr">
+        <is>
+          <t>Appolonia Adeyemi Duchess International Hospital debuts in Lagos, builds capacity</t>
+        </is>
+      </c>
+      <c r="D323" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E323" s="5" t="inlineStr">
+        <is>
+          <t>https://newtelegraphng.com/?p=192437</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="5" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals</t>
+        </is>
+      </c>
+      <c r="B324" s="5" t="inlineStr">
+        <is>
+          <t>State House Clinic</t>
+        </is>
+      </c>
+      <c r="C324" s="5" t="inlineStr">
+        <is>
+          <t>Blueprint State House Clinic, Indian hospital collaborate to assist heart, kidney, cancer patients</t>
+        </is>
+      </c>
+      <c r="D324" s="5" t="inlineStr">
+        <is>
+          <t>2022-07-29</t>
+        </is>
+      </c>
+      <c r="E324" s="5" t="inlineStr">
+        <is>
+          <t>https://blueprint.ng/state-house-clinic-indian-hospital-collaborate-to-assist-heart-kidney-cancer-patients/</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="5" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals</t>
+        </is>
+      </c>
+      <c r="B325" s="5" t="inlineStr">
+        <is>
+          <t>State House Clinic</t>
+        </is>
+      </c>
+      <c r="C325" s="5" t="inlineStr">
+        <is>
+          <t>ThisDay Medical Tourism: Indian Hospital to Train Nigerian Doctors on Cancer Treatment</t>
+        </is>
+      </c>
+      <c r="D325" s="5" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="E325" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thisdaylive.com/2024/03/05/medical-tourism-indian-hospital-to-train-nigerian-doctors-on-cancer-treatment/</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="5" t="inlineStr">
+        <is>
+          <t>Memorial Hospitals Group</t>
+        </is>
+      </c>
+      <c r="B326" s="5" t="inlineStr">
+        <is>
+          <t>Kasi Healthcare</t>
+        </is>
+      </c>
+      <c r="C326" s="5" t="inlineStr">
+        <is>
+          <t>Temitayo Ayetoto-Oladehinde Nigeria partners Turkey to tap $8.5trn healthcare market</t>
+        </is>
+      </c>
+      <c r="D326" s="5" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="E326" s="5" t="inlineStr">
+        <is>
+          <t>https://businessday.ng/news/article/nigeria-partners-turkey-to-tap-8-5trn-healthcare-market/</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="5" t="inlineStr">
+        <is>
           <t>Peking University People's Hospital (named variously in press as People's University Hospital, Beijing)</t>
         </is>
       </c>
-      <c r="B297" s="5" t="inlineStr">
+      <c r="B327" s="5" t="inlineStr">
         <is>
           <t>University of Abuja Teaching Hospital</t>
         </is>
       </c>
-      <c r="C297" s="5" t="inlineStr">
+      <c r="C327" s="5" t="inlineStr">
+        <is>
+          <t>Within Nigeria Nigeria signs letter of intent with China to improve health sector</t>
+        </is>
+      </c>
+      <c r="D327" s="5" t="inlineStr">
+        <is>
+          <t>2022-08-20</t>
+        </is>
+      </c>
+      <c r="E327" s="5" t="inlineStr">
+        <is>
+          <t>https://www.withinnigeria.com/broadnews/2022/08/20/nigeria-signs-letter-of-intent-with-china-to-improve-health-sector/</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="5" t="inlineStr">
+        <is>
+          <t>Peking University People's Hospital (named variously in press as People's University Hospital, Beijing)</t>
+        </is>
+      </c>
+      <c r="B328" s="5" t="inlineStr">
+        <is>
+          <t>University of Abuja Teaching Hospital</t>
+        </is>
+      </c>
+      <c r="C328" s="5" t="inlineStr">
         <is>
           <t>University of Abuja Teaching Hospital Nigeria, China signs letter of intent to improve health sector</t>
         </is>
       </c>
-      <c r="D297" s="5" t="inlineStr">
+      <c r="D328" s="5" t="inlineStr">
         <is>
           <t>2022-08</t>
         </is>
       </c>
-      <c r="E297" s="5" t="inlineStr">
+      <c r="E328" s="5" t="inlineStr">
         <is>
           <t>https://uathospital.ng/nigeria-china-signs-letter-of-intent-to-improve-health-sector/</t>
         </is>
@@ -17811,6 +19513,37 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E295" r:id="rId294"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E296" r:id="rId295"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E328" r:id="rId327"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Partnerships_Tracker.xlsx
+++ b/output/Partnerships_Tracker.xlsx
@@ -231,8 +231,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tracker" displayName="Tracker" ref="A1:L165" headerRowCount="1">
-  <autoFilter ref="A1:L165"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tracker" displayName="Tracker" ref="A1:L188" headerRowCount="1">
+  <autoFilter ref="A1:L188"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Status"/>
     <tableColumn id="2" name="Country"/>
@@ -558,7 +558,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scope: partnerships that are active, or ended or last active within the past five years. Last checked 2026-10-21.</t>
+          <t>Scope: partnerships that are active, or ended or last active within the past five years. Last checked 2026-10-30.</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF(Tracker!$A$2:$A$165,A5)</f>
+        <f>COUNTIF(Tracker!$A$2:$A$188,A5)</f>
         <v/>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Tracker!$A$2:$A$165,A6)</f>
+        <f>COUNTIF(Tracker!$A$2:$A$188,A6)</f>
         <v/>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Tracker!$A$2:$A$165,A7)</f>
+        <f>COUNTIF(Tracker!$A$2:$A$188,A7)</f>
         <v/>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -670,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L165"/>
+  <dimension ref="A1:L188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10222,6 +10222,1336 @@
       <c r="L165" s="14" t="inlineStr">
         <is>
           <t>Within Nigeria, 2022-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B166" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C166" s="13" t="inlineStr">
+        <is>
+          <t>Cleveland Clinic</t>
+        </is>
+      </c>
+      <c r="D166" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E166" s="12" t="inlineStr">
+        <is>
+          <t>Vall d'Hebron University Hospital (Advanced Clinical Simulation Centre)</t>
+        </is>
+      </c>
+      <c r="F166" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G166" s="12" t="inlineStr">
+        <is>
+          <t>Vall d'Hebron and Cleveland Clinic signed an agreement in February 2025 for educator development and courses in clinical simulation, shared resources and joint research on health education. The collaboration was renewed in 2025 and Vall d'Hebron instructors teach Cleveland Clinic's SEVA ventilation course.</t>
+        </is>
+      </c>
+      <c r="H166" s="12" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="I166" s="12" t="inlineStr"/>
+      <c r="J166" s="12" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="K166" s="12" t="inlineStr">
+        <is>
+          <t>Vall d'Hebron news item dated 07/02/2025 announces the agreement; Vall d'Hebron's 2025 report says the Advanced Clinical Simulation Centre signed 20 agreements in 2025, including the renewal of its collaboration with Cleveland Clinic.</t>
+        </is>
+      </c>
+      <c r="L166" s="14" t="inlineStr">
+        <is>
+          <t>Vall d'Hebron, 2025-02-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B167" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C167" s="13" t="inlineStr">
+        <is>
+          <t>George Washington University (School of Medicine and Health Sciences)</t>
+        </is>
+      </c>
+      <c r="D167" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E167" s="12" t="inlineStr">
+        <is>
+          <t>Universidad Autonoma de Madrid (Faculty of Medicine)</t>
+        </is>
+      </c>
+      <c r="F167" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G167" s="12" t="inlineStr">
+        <is>
+          <t>George Washington University's medical school and the Universidad Autonoma de Madrid run a reciprocal clinical rotation program under a framework agreement. Each year the Madrid faculty funds three of its students to spend a month on clinical rotations at George Washington.</t>
+        </is>
+      </c>
+      <c r="H167" s="12" t="inlineStr">
+        <is>
+          <t>2018-06</t>
+        </is>
+      </c>
+      <c r="I167" s="12" t="inlineStr"/>
+      <c r="J167" s="12" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K167" s="12" t="inlineStr">
+        <is>
+          <t>UAM's Faculty of Medicine published its 2026-2027 call for three grants for one month clinical rotations at George Washington University in July or August 2027. Applications ran from 13 to 18 October 2026 and the provisional admitted list is out. The specific agreement for the International Clinical Rotation Program between GW's SMHS and UAM was approved by UAM's governing council on 15 June 2018.</t>
+        </is>
+      </c>
+      <c r="L167" s="14" t="inlineStr">
+        <is>
+          <t>Universidad Autonoma de Madrid, 2026-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B168" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C168" s="13" t="inlineStr">
+        <is>
+          <t>Harvard Medical School (Harvard University)</t>
+        </is>
+      </c>
+      <c r="D168" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E168" s="12" t="inlineStr">
+        <is>
+          <t>Universidad Complutense de Madrid (Faculty of Medicine; Hospital Clinico San Carlos, Hospital 12 de Octubre, Hospital Gregorio Maranon)</t>
+        </is>
+      </c>
+      <c r="F168" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G168" s="12" t="inlineStr">
+        <is>
+          <t>Under the long standing agreement between Complutense University and Harvard, Harvard medical students take clinical electives at Complutense's teaching hospitals in Madrid. Complutense fifth year medical students spend a month in the Harvard Medical School Exchange Clerkship Program on scholarships from the Fundacion Fernandez-Cruz.</t>
+        </is>
+      </c>
+      <c r="H168" s="12" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="I168" s="12" t="inlineStr"/>
+      <c r="J168" s="12" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="K168" s="12" t="inlineStr">
+        <is>
+          <t>Complutense's Faculty of Medicine posted an elective description for the 2025-26 HMS to Complutense clinical rotation, created 28 October 2025, covering Hospital Clinico San Carlos, Hospital 12 de Octubre and Gregorio Maranon. Complutense reported on 30 January 2020 that seven medical students would spend a month at Harvard Medical School under this agreement, which is nearly three decades old (so dating from about 1991; the start year is approximate). The Real Colegio Complutense at Harvard has been affiliated with Harvard since 1990. The 2022-23 scholarship call offered 7 to 9 places in the HMS Exchange Clerkship Program.</t>
+        </is>
+      </c>
+      <c r="L168" s="14" t="inlineStr">
+        <is>
+          <t>Universidad Complutense de Madrid, 2025-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B169" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C169" s="13" t="inlineStr">
+        <is>
+          <t>Johns Hopkins University (Bloomberg School of Public Health)</t>
+        </is>
+      </c>
+      <c r="D169" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E169" s="12" t="inlineStr">
+        <is>
+          <t>Universitat Pompeu Fabra (JHU-UPF Public Policy Center), with the Agencia de Salut Publica de Barcelona</t>
+        </is>
+      </c>
+      <c r="F169" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G169" s="12" t="inlineStr">
+        <is>
+          <t>Johns Hopkins and Universitat Pompeu Fabra have run a joint public policy centre in Barcelona since 2013, with a health and well-being research line. With the Barcelona Public Health Agency they have also run, since 2004, the yearly Hopkins Fall Institute in Health Policy and Management, which Bloomberg School faculty teach.</t>
+        </is>
+      </c>
+      <c r="H169" s="12" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="I169" s="12" t="inlineStr"/>
+      <c r="J169" s="12" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="K169" s="12" t="inlineStr">
+        <is>
+          <t>UPF's repository holds the JHU-UPF Public Policy Center Annual Report 2024 to 2025, deposited in November 2025, which lists health and well-being among five research areas and mentions joint programs including the Fall Institute in Health Policy and Management. The Fall Institute began in 2004 (its 20th edition was in 2023), sponsored by the Barcelona Public Health Agency and the Bloomberg School in collaboration with UPF. A Bloomberg School page lists the November 2025 edition at UPF Barcelona School of Management. The Bloomberg School and UPF pages could not be fetched (HTTP 403), so the details come from search snippets.</t>
+        </is>
+      </c>
+      <c r="L169" s="14" t="inlineStr">
+        <is>
+          <t>Universitat Pompeu Fabra repository, 2025-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B170" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C170" s="13" t="inlineStr">
+        <is>
+          <t>MD Anderson Cancer Center</t>
+        </is>
+      </c>
+      <c r="D170" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E170" s="12" t="inlineStr">
+        <is>
+          <t>MD Anderson Cancer Center Madrid (operated by Grupo Hospiten)</t>
+        </is>
+      </c>
+      <c r="F170" s="12" t="inlineStr">
+        <is>
+          <t>Clinical affiliation</t>
+        </is>
+      </c>
+      <c r="G170" s="12" t="inlineStr">
+        <is>
+          <t>MD Anderson Cancer Center Madrid opened in 2000 as the first international affiliate of MD Anderson in Houston and still carries its name. Grupo Hospiten owns and runs the hospital, and Hospiten says Houston's protocols and standards are applied to care in Madrid.</t>
+        </is>
+      </c>
+      <c r="H170" s="12" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="I170" s="12" t="inlineStr"/>
+      <c r="J170" s="12" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K170" s="12" t="inlineStr">
+        <is>
+          <t>A Hospiten page of 18 September 2026 on the Newsweek and Statista ranking says MD Anderson Cancer Center Madrid has the backing of MD Anderson Cancer Center in Houston and is its only affiliate outside the United States. Forbes Spain ranked it among the three best oncology hospitals in Spain in December 2025. Hospiten's release of 10 January 2013 reported buying a further 39.98 percent of the shares; Hospiten later reported holding 99.97 percent, with MD Anderson Houston keeping 0.03 percent. In an MD Anderson oral history, former president John Mendelsohn describes MD Anderson Espana in Madrid as one of the sister institutions he created. Madrid does not appear on recent MD Anderson Sister Institution Network lists, so the tie is a branded affiliation, not a GAP sister institution.</t>
+        </is>
+      </c>
+      <c r="L170" s="14" t="inlineStr">
+        <is>
+          <t>Hospiten, 2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B171" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C171" s="13" t="inlineStr">
+        <is>
+          <t>Mount Sinai Health System (Icahn School of Medicine, Mount Sinai Fuster Heart Hospital)</t>
+        </is>
+      </c>
+      <c r="D171" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E171" s="12" t="inlineStr">
+        <is>
+          <t>Centro Nacional de Investigaciones Cardiovasculares Carlos III (CNIC)</t>
+        </is>
+      </c>
+      <c r="F171" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G171" s="12" t="inlineStr">
+        <is>
+          <t>Mount Sinai and Spain's national cardiovascular research centre CNIC have a long running research partnership with researcher exchanges, shared cardiac imaging work and jointly led clinical trials. Valentín Fuster is general director of CNIC and president of Mount Sinai Fuster Heart Hospital.</t>
+        </is>
+      </c>
+      <c r="H171" s="12" t="inlineStr"/>
+      <c r="I171" s="12" t="inlineStr"/>
+      <c r="J171" s="12" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="K171" s="12" t="inlineStr">
+        <is>
+          <t>A Mount Sinai release of 30 August 2025 presents the REBOOT trial and quotes Fuster that it joins earlier landmark trials led by CNIC and Mount Sinai, SECURE and DapaTAVI. A Mount Sinai release of 30 September 2024 reports BioImage results from the Mount Sinai and CNIC collaboration. A 2015 CNIC article describes the partnership program set up when Fuster took charge of CNIC while leading Mount Sinai's heart institute, starting with shared MRI imaging. No signing date for the original agreement was found.</t>
+        </is>
+      </c>
+      <c r="L171" s="14" t="inlineStr">
+        <is>
+          <t>EurekAlert, 2025-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B172" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C172" s="13" t="inlineStr">
+        <is>
+          <t>Penn State College of Medicine and Penn State Health (Beat Childhood Cancer Research Consortium)</t>
+        </is>
+      </c>
+      <c r="D172" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E172" s="12" t="inlineStr">
+        <is>
+          <t>Hospital Sant Joan de Déu Barcelona (Pediatric Cancer Center Barcelona)</t>
+        </is>
+      </c>
+      <c r="F172" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G172" s="12" t="inlineStr">
+        <is>
+          <t>SJD's Pediatric Cancer Center Barcelona joined the Beat Childhood Cancer Research Consortium, headquartered at Penn State College of Medicine, in November 2025, the first member outside North America. SJD acts as European sponsor for consortium trials, starting with BCC018 in high risk neuroblastoma.</t>
+        </is>
+      </c>
+      <c r="H172" s="12" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="I172" s="12" t="inlineStr"/>
+      <c r="J172" s="12" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="K172" s="12" t="inlineStr">
+        <is>
+          <t>SJD announcement and Penn State Health News of November 2025 (consortium of more than 55 children's hospitals and research institutions; borderline as a consortium, like the Cancer Core Europe record). SJD news item dated 24 November 2025.</t>
+        </is>
+      </c>
+      <c r="L172" s="14" t="inlineStr">
+        <is>
+          <t>SJD Barcelona Children's Hospital, 2025-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B173" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C173" s="13" t="inlineStr">
+        <is>
+          <t>University of Illinois Chicago (College of Applied Health Sciences)</t>
+        </is>
+      </c>
+      <c r="D173" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E173" s="12" t="inlineStr">
+        <is>
+          <t>TecnoCampus School of Health Sciences (Universitat Pompeu Fabra)</t>
+        </is>
+      </c>
+      <c r="F173" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G173" s="12" t="inlineStr">
+        <is>
+          <t>UIC's College of Applied Health Sciences and the TecnoCampus School of Health Sciences signed a letter of intent in October 2025 to set up an educational collaboration. It covers faculty and student exchanges, visiting professors and joint research in kinesiology, nutrition and rehabilitation sciences.</t>
+        </is>
+      </c>
+      <c r="H173" s="12" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="I173" s="12" t="inlineStr"/>
+      <c r="J173" s="12" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="K173" s="12" t="inlineStr">
+        <is>
+          <t>A UIC College of Applied Health Sciences news story of 20 October 2025 reports that Dean Carlos Crespo and TecnoCampus general director Josep Lluis Checa signed the letter of intent on 6 October 2025 in Barcelona. UIC is the University of Illinois's academic health enterprise and includes a medical school, but this tie runs through the allied health college.</t>
+        </is>
+      </c>
+      <c r="L173" s="14" t="inlineStr">
+        <is>
+          <t>University of Illinois Chicago, College of Applied Health Sciences, 2025-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B174" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C174" s="13" t="inlineStr">
+        <is>
+          <t>University of Kansas Medical Center</t>
+        </is>
+      </c>
+      <c r="D174" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E174" s="12" t="inlineStr">
+        <is>
+          <t>Universitat Internacional de Catalunya (UIC Barcelona) Faculty of Medicine and Health Sciences</t>
+        </is>
+      </c>
+      <c r="F174" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G174" s="12" t="inlineStr">
+        <is>
+          <t>The University of Kansas Medical Center is one of UIC Barcelona's North American exchange partners for medicine. KUMC sends medical, nursing and health professions students to Barcelona for clinical rotations.</t>
+        </is>
+      </c>
+      <c r="H174" s="12" t="inlineStr"/>
+      <c r="I174" s="12" t="inlineStr"/>
+      <c r="J174" s="12" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="K174" s="12" t="inlineStr">
+        <is>
+          <t>UIC Barcelona's medicine brochures in English and Spanish, created 16 February 2026, list the University of Kansas Medical Center among three North American exchange agreements. The January 2024 edition lists it as well. KUMC's Office of International Programs lists UIC Barcelona as a Spain rotation site for M1 and M4 medical students, nursing and health professions students, two students per cycle. The same page also lists M4 rotations at the University of Navarra in Pamplona and Madrid and a summer program at the Universidad de Santiago de Compostela.</t>
+        </is>
+      </c>
+      <c r="L174" s="14" t="inlineStr">
+        <is>
+          <t>UIC Barcelona, 2026-02-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B175" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C175" s="13" t="inlineStr">
+        <is>
+          <t>ABC Medical Center (Centro Médico ABC)</t>
+        </is>
+      </c>
+      <c r="D175" s="12" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E175" s="12" t="inlineStr">
+        <is>
+          <t>Hospital Sant Joan de Déu Barcelona (SJD Barcelona Children's Hospital)</t>
+        </is>
+      </c>
+      <c r="F175" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G175" s="12" t="inlineStr">
+        <is>
+          <t>SJD Barcelona Children's Hospital and ABC Medical Center in Mexico City signed a collaboration agreement in August 2025 for joint training of health professionals, pediatric oncology research and second opinions on highly complex pediatric cases.</t>
+        </is>
+      </c>
+      <c r="H175" s="12" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="I175" s="12" t="inlineStr"/>
+      <c r="J175" s="12" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="K175" s="12" t="inlineStr">
+        <is>
+          <t>SJD announced the agreement on 29 August 2025.</t>
+        </is>
+      </c>
+      <c r="L175" s="14" t="inlineStr">
+        <is>
+          <t>SJD Barcelona Children's Hospital, 2025-08-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B176" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C176" s="13" t="inlineStr">
+        <is>
+          <t>Aier Eye Hospital Group</t>
+        </is>
+      </c>
+      <c r="D176" s="12" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E176" s="12" t="inlineStr">
+        <is>
+          <t>Clínica Baviera</t>
+        </is>
+      </c>
+      <c r="F176" s="12" t="inlineStr">
+        <is>
+          <t>Ownership or management</t>
+        </is>
+      </c>
+      <c r="G176" s="12" t="inlineStr">
+        <is>
+          <t>Chinese eye hospital group Aier took control of Clínica Baviera, the Madrid listed ophthalmology clinic chain, through a 2017 takeover bid. Aier remains the majority shareholder with about 73 to 75 percent after selling part of its stake in April 2025 (reported figures vary).</t>
+        </is>
+      </c>
+      <c r="H176" s="12" t="inlineStr">
+        <is>
+          <t>2017-08</t>
+        </is>
+      </c>
+      <c r="I176" s="12" t="inlineStr"/>
+      <c r="J176" s="12" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="K176" s="12" t="inlineStr">
+        <is>
+          <t>Alimarket reported in 2017 that Aier Eye Hospital took control of Clínica Baviera with 86.8% after its bid. Alantra reported in April 2025 that Aier, the majority shareholder, and the founders' vehicle placed 8% of the shares, leaving Aier with about 74.8%. Later reports through Clínica Baviera's first-half 2026 results of 29 July 2026 give Aier between 73 and 75 percent.</t>
+        </is>
+      </c>
+      <c r="L176" s="14" t="inlineStr">
+        <is>
+          <t>Alimarket, 2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B177" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C177" s="13" t="inlineStr">
+        <is>
+          <t>Bupa</t>
+        </is>
+      </c>
+      <c r="D177" s="12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E177" s="12" t="inlineStr">
+        <is>
+          <t>Sanitas (Sanitas hospitals)</t>
+        </is>
+      </c>
+      <c r="F177" s="12" t="inlineStr">
+        <is>
+          <t>Ownership or management</t>
+        </is>
+      </c>
+      <c r="G177" s="12" t="inlineStr">
+        <is>
+          <t>British healthcare group Bupa owns Sanitas, which runs private hospitals in Spain including Hospital Universitario Sanitas La Moraleja, La Zarzuela, CIMA in Barcelona and the new Blua Sanitas Valdebebas, alongside its health insurance and aged care businesses. A public private partnership hospital contract held by Sanitas ended in 2024.</t>
+        </is>
+      </c>
+      <c r="H177" s="12" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="I177" s="12" t="inlineStr"/>
+      <c r="J177" s="12" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="K177" s="12" t="inlineStr">
+        <is>
+          <t>Bupa's full year 2025 results of 5 March 2026 report strong customer growth in its Spanish hospitals business, the opening of Hospital Blua Sanitas Valdebebas, and the end in 2024 of a PPP contract in that business.</t>
+        </is>
+      </c>
+      <c r="L177" s="14" t="inlineStr">
+        <is>
+          <t>Bupa, 2026-03-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B178" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C178" s="13" t="inlineStr">
+        <is>
+          <t>Burjeel Cancer Institute (Burjeel Holdings)</t>
+        </is>
+      </c>
+      <c r="D178" s="12" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E178" s="12" t="inlineStr">
+        <is>
+          <t>Hospital Sant Joan de Déu Barcelona (SJD Barcelona Children's Hospital)</t>
+        </is>
+      </c>
+      <c r="F178" s="12" t="inlineStr">
+        <is>
+          <t>Clinical affiliation</t>
+        </is>
+      </c>
+      <c r="G178" s="12" t="inlineStr">
+        <is>
+          <t>SJD Barcelona Children's Hospital and the Burjeel Cancer Institute in Abu Dhabi signed a memorandum of understanding in June 2025 on pediatric oncology and rare diseases. It covers joint management of complex cases, remote appointments and second opinions with SJD specialists, and expert visits.</t>
+        </is>
+      </c>
+      <c r="H178" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="I178" s="12" t="inlineStr"/>
+      <c r="J178" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="K178" s="12" t="inlineStr">
+        <is>
+          <t>SJD announced the memorandum on 9 June 2025.</t>
+        </is>
+      </c>
+      <c r="L178" s="14" t="inlineStr">
+        <is>
+          <t>SJD Barcelona Children's Hospital, 2025-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B179" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C179" s="13" t="inlineStr">
+        <is>
+          <t>Cancer Core Europe (Gustave Roussy, DKFZ and NCT Heidelberg, Netherlands Cancer Institute, Karolinska Institutet, Cancer Research UK Cambridge Centre, Istituto Nazionale dei Tumori Milan)</t>
+        </is>
+      </c>
+      <c r="D179" s="12" t="inlineStr">
+        <is>
+          <t>Multiple (France, Germany, Netherlands, Sweden, United Kingdom, Italy)</t>
+        </is>
+      </c>
+      <c r="E179" s="12" t="inlineStr">
+        <is>
+          <t>Vall d'Hebron Institute of Oncology (VHIO)</t>
+        </is>
+      </c>
+      <c r="F179" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G179" s="12" t="inlineStr">
+        <is>
+          <t>VHIO is a founding member of Cancer Core Europe, a standing consortium of seven European comprehensive cancer centres that runs joint translational research, clinical trial and training programmes. VHIO director Josep Tabernero has chaired the consortium since 2023.</t>
+        </is>
+      </c>
+      <c r="H179" s="12" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="I179" s="12" t="inlineStr"/>
+      <c r="J179" s="12" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="K179" s="12" t="inlineStr">
+        <is>
+          <t>VHIO announced on 18 October 2023 that Josep Tabernero took the chair of Cancer Core Europe. Karolinska Institutet's page for the consortium's 10th annual meeting in Stockholm on 23 and 24 March 2026 lists all seven members, including VHIO, and VHIO speakers.</t>
+        </is>
+      </c>
+      <c r="L179" s="14" t="inlineStr">
+        <is>
+          <t>Vall d'Hebron Institute of Oncology, 2023-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B180" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C180" s="13" t="inlineStr">
+        <is>
+          <t>Clariane (formerly Korian)</t>
+        </is>
+      </c>
+      <c r="D180" s="12" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E180" s="12" t="inlineStr">
+        <is>
+          <t>Clariane España (Ita Salud Mental, Grupo 5, Iterias)</t>
+        </is>
+      </c>
+      <c r="F180" s="12" t="inlineStr">
+        <is>
+          <t>Ownership or management</t>
+        </is>
+      </c>
+      <c r="G180" s="12" t="inlineStr">
+        <is>
+          <t>French care group Clariane owns Ita Salud Mental, bought in 2021, and Grupo 5, bought in 2023, giving it what Clariane calls the largest network of mental health facilities in the Iberian Peninsula with outpatient and inpatient psychiatric care, as well as the Seniors nursing homes. It opened the new Iterias psychotherapy brand in Barcelona in October 2025.</t>
+        </is>
+      </c>
+      <c r="H180" s="12" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I180" s="12" t="inlineStr"/>
+      <c r="J180" s="12" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="K180" s="12" t="inlineStr">
+        <is>
+          <t>Korian announced on 11 January 2023 that it had closed the Grupo 5 acquisition, adding to Ita Salud acquired in 2021. Clariane launched Iterias in Spain on 21 October 2025, and its Spain page reports EUR 267 million of Spanish revenue and 164 facilities as of 31 December 2025.</t>
+        </is>
+      </c>
+      <c r="L180" s="14" t="inlineStr">
+        <is>
+          <t>Business Wire, 2023-01-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B181" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C181" s="13" t="inlineStr">
+        <is>
+          <t>Fresenius Helios (Helios Health)</t>
+        </is>
+      </c>
+      <c r="D181" s="12" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E181" s="12" t="inlineStr">
+        <is>
+          <t>Quirónsalud</t>
+        </is>
+      </c>
+      <c r="F181" s="12" t="inlineStr">
+        <is>
+          <t>Ownership or management</t>
+        </is>
+      </c>
+      <c r="G181" s="12" t="inlineStr">
+        <is>
+          <t>Fresenius Helios, the hospital arm of the German Fresenius group, has owned Quirónsalud, the largest private hospital group in Spain, since early 2017. Quirónsalud lists 57 hospitals in Spain on its website.</t>
+        </is>
+      </c>
+      <c r="H181" s="12" t="inlineStr">
+        <is>
+          <t>2017-01</t>
+        </is>
+      </c>
+      <c r="I181" s="12" t="inlineStr"/>
+      <c r="J181" s="12" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="K181" s="12" t="inlineStr">
+        <is>
+          <t>Quirónsalud announced the integration with Helios on 5 September 2016. Fresenius reported on 25 February 2026 that Helios Spain grew revenue 7% to EUR 5,429 million in 2025 and had the strongest performance in the group.</t>
+        </is>
+      </c>
+      <c r="L181" s="14" t="inlineStr">
+        <is>
+          <t>Quirónsalud, 2016-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B182" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C182" s="13" t="inlineStr">
+        <is>
+          <t>GenesisCare</t>
+        </is>
+      </c>
+      <c r="D182" s="12" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E182" s="12" t="inlineStr">
+        <is>
+          <t>GenesisCare España (IMOncology and Oncosur radiotherapy centres)</t>
+        </is>
+      </c>
+      <c r="F182" s="12" t="inlineStr">
+        <is>
+          <t>Ownership or management</t>
+        </is>
+      </c>
+      <c r="G182" s="12" t="inlineStr">
+        <is>
+          <t>Australian cancer care provider GenesisCare entered Spain in 2016 by buying IMOncology and Oncosur and ran 18 oncology and radiotherapy centres and units, several inside Vithas and other private hospitals. In July 2026 it agreed to sell the Spanish business to Vithas; the sale awaits approval by the competition authority (CNMC), so the ownership tie continues.</t>
+        </is>
+      </c>
+      <c r="H182" s="12" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I182" s="12" t="inlineStr"/>
+      <c r="J182" s="12" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="K182" s="12" t="inlineStr">
+        <is>
+          <t>Alimarket reported on 22 July 2026 that Vithas closed the purchase of GenesisCare's Spanish business, with 18 centres and EUR 39.1 million revenue in 2025, subject to CNMC authorisation; no clearance was found by October 2026.</t>
+        </is>
+      </c>
+      <c r="L182" s="14" t="inlineStr">
+        <is>
+          <t>Alimarket, 2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B183" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C183" s="13" t="inlineStr">
+        <is>
+          <t>Grupo Médico Joya (Hospitales Joya)</t>
+        </is>
+      </c>
+      <c r="D183" s="12" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E183" s="12" t="inlineStr">
+        <is>
+          <t>HM Hospitales</t>
+        </is>
+      </c>
+      <c r="F183" s="12" t="inlineStr">
+        <is>
+          <t>Clinical affiliation</t>
+        </is>
+      </c>
+      <c r="G183" s="12" t="inlineStr">
+        <is>
+          <t>HM Hospitales and Mexican private hospital group Hospitales Joya signed a strategic framework agreement in September 2026 to support continuity of care for patients moving between Spain and Mexico. It also covers reciprocal rotations, fellowships and staff exchanges, links with HM's CIOCC, CIEC and CINAC centres, and sharing of clinical and management practice.</t>
+        </is>
+      </c>
+      <c r="H183" s="12" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I183" s="12" t="inlineStr"/>
+      <c r="J183" s="12" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K183" s="12" t="inlineStr">
+        <is>
+          <t>Alimarket reported on 11 September 2026 that the agreement was signed the previous Thursday at the Mexican Embassy in Spain by the chairs and chief executives of both groups.</t>
+        </is>
+      </c>
+      <c r="L183" s="14" t="inlineStr">
+        <is>
+          <t>Alimarket, 2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B184" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C184" s="13" t="inlineStr">
+        <is>
+          <t>Sun Yat-sen University Cancer Center</t>
+        </is>
+      </c>
+      <c r="D184" s="12" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E184" s="12" t="inlineStr">
+        <is>
+          <t>Hospital Sant Joan de Déu Barcelona (SJD Barcelona Children's Hospital)</t>
+        </is>
+      </c>
+      <c r="F184" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G184" s="12" t="inlineStr">
+        <is>
+          <t>SJD Barcelona Children's Hospital and Sun Yat-sen University Cancer Center in Guangzhou signed a strategic agreement in pediatric oncology in 2025, including a cross border virtual consultation system and joint work on cell immunotherapy and rare tumour guidelines. The two co-organised the China Pediatric Oncology Frontier Forum in November 2025.</t>
+        </is>
+      </c>
+      <c r="H184" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="I184" s="12" t="inlineStr"/>
+      <c r="J184" s="12" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="K184" s="12" t="inlineStr">
+        <is>
+          <t>SJD announced the agreement on 2 June 2025 and reported on 12 December 2025 that it co-organised the 2025 China Pediatric Oncology Frontier Forum hosted by the cancer center in Guangzhou in late November 2025.</t>
+        </is>
+      </c>
+      <c r="L184" s="14" t="inlineStr">
+        <is>
+          <t>SJD Barcelona Children's Hospital, 2025-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B185" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C185" s="13" t="inlineStr">
+        <is>
+          <t>Vivalto Santé</t>
+        </is>
+      </c>
+      <c r="D185" s="12" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E185" s="12" t="inlineStr">
+        <is>
+          <t>Ribera (Ribera Salud group)</t>
+        </is>
+      </c>
+      <c r="F185" s="12" t="inlineStr">
+        <is>
+          <t>Ownership or management</t>
+        </is>
+      </c>
+      <c r="G185" s="12" t="inlineStr">
+        <is>
+          <t>French private hospital group Vivalto Santé bought Ribera, which runs public concession and private hospitals in Spain, from Centene in November 2022 and is its main shareholder. Ribera signed to buy the HCB Hospitales group in Benidorm and Dénia in February 2026 and completed the purchase in October 2026, after the competition authority cleared it in September.</t>
+        </is>
+      </c>
+      <c r="H185" s="12" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="I185" s="12" t="inlineStr"/>
+      <c r="J185" s="12" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K185" s="12" t="inlineStr">
+        <is>
+          <t>Centene announced completion of the sale of Ribera Salud and its other Spanish and central European businesses to Vivalto Santé on 17 November 2022. Ribera's release of 18 February 2026 on the HCB acquisition names Vivalto Santé as its main shareholder; Alimarket reported on 1 October 2026 that the CNMC cleared the deal on 21 September 2026. economia3 reported on 6 October 2026 that Ribera had completed the acquisition.</t>
+        </is>
+      </c>
+      <c r="L185" s="14" t="inlineStr">
+        <is>
+          <t>Becker's Healthcare, 2022-11-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B186" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C186" s="13" t="inlineStr">
+        <is>
+          <t>Johns Hopkins Proton Therapy Center (Johns Hopkins Medicine)</t>
+        </is>
+      </c>
+      <c r="D186" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E186" s="12" t="inlineStr">
+        <is>
+          <t>Clínica Universidad de Navarra (Cancer Center) and Facultad de Medicina, Universidad de Navarra</t>
+        </is>
+      </c>
+      <c r="F186" s="12" t="inlineStr">
+        <is>
+          <t>Training and education</t>
+        </is>
+      </c>
+      <c r="G186" s="12" t="inlineStr">
+        <is>
+          <t>The Clínica Universidad de Navarra signed a collaboration agreement with the Johns Hopkins Proton Therapy Center in Washington in October 2023 to promote training and research in proton therapy for professionals in Spain's national health system.</t>
+        </is>
+      </c>
+      <c r="H186" s="12" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="I186" s="12" t="inlineStr"/>
+      <c r="J186" s="12" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="K186" s="12" t="inlineStr">
+        <is>
+          <t>CUN Cancer Center news item of 9 October 2023 announces the agreement; no later dated activity with Johns Hopkins found (CUN's 2025 and 2026 proton therapy courses do not name Johns Hopkins). Rule: latest evidence 2021 to September 2024 means Unclear.</t>
+        </is>
+      </c>
+      <c r="L186" s="14" t="inlineStr">
+        <is>
+          <t>Cancer Center Clínica Universidad de Navarra, 2023-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="15" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="B187" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C187" s="13" t="inlineStr">
+        <is>
+          <t>Hospital de Amor (Barretos Cancer Hospital)</t>
+        </is>
+      </c>
+      <c r="D187" s="12" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="E187" s="12" t="inlineStr">
+        <is>
+          <t>Hospital Sant Joan de Déu Barcelona (SJD Barcelona Children's Hospital)</t>
+        </is>
+      </c>
+      <c r="F187" s="12" t="inlineStr">
+        <is>
+          <t>Research collaboration</t>
+        </is>
+      </c>
+      <c r="G187" s="12" t="inlineStr">
+        <is>
+          <t>SJD Barcelona Children's Hospital and Hospital de Amor in Barretos, Brazil, signed an agreement in 2021 to share knowledge in pediatric oncology protocols, training and research. No later activity was found.</t>
+        </is>
+      </c>
+      <c r="H187" s="12" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="I187" s="12" t="inlineStr"/>
+      <c r="J187" s="12" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="K187" s="12" t="inlineStr">
+        <is>
+          <t>SJD announced the agreement on 13 July 2021; no later public evidence of activity was found.</t>
+        </is>
+      </c>
+      <c r="L187" s="14" t="inlineStr">
+        <is>
+          <t>SJD Barcelona Children's Hospital, 2021-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="16" t="inlineStr">
+        <is>
+          <t>Ended</t>
+        </is>
+      </c>
+      <c r="B188" s="12" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C188" s="13" t="inlineStr">
+        <is>
+          <t>Fresenius Helios (Helios Health)</t>
+        </is>
+      </c>
+      <c r="D188" s="12" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E188" s="12" t="inlineStr">
+        <is>
+          <t>Eugin Group (fertility clinics)</t>
+        </is>
+      </c>
+      <c r="F188" s="12" t="inlineStr">
+        <is>
+          <t>Ownership or management</t>
+        </is>
+      </c>
+      <c r="G188" s="12" t="inlineStr">
+        <is>
+          <t>Fresenius Helios bought the Barcelona based Eugin fertility clinic group from NMC Health's administrators in a deal signed in December 2020 and sold it to IVI RMA and GED Capital in January 2024. Helios kept the fertility units inside Quirónsalud hospitals.</t>
+        </is>
+      </c>
+      <c r="H188" s="12" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="I188" s="12" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="J188" s="12" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="K188" s="12" t="inlineStr">
+        <is>
+          <t>Fresenius announced the Eugin acquisition on 21 December 2020 and announced completion of the divestment to IVI RMA and GED Capital on 31 January 2024.</t>
+        </is>
+      </c>
+      <c r="L188" s="14" t="inlineStr">
+        <is>
+          <t>Fresenius, 2020-12-21</t>
         </is>
       </c>
     </row>
@@ -10391,10 +11721,33 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L163" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L164" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L188" r:id="rId187"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId165"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId188"/>
   </tableParts>
 </worksheet>
 </file>
@@ -10405,7 +11758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E328"/>
+  <dimension ref="A1:E382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -19212,6 +20565,1444 @@
       <c r="E328" s="5" t="inlineStr">
         <is>
           <t>https://uathospital.ng/nigeria-china-signs-letter-of-intent-to-improve-health-sector/</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Clinic</t>
+        </is>
+      </c>
+      <c r="B329" s="5" t="inlineStr">
+        <is>
+          <t>Vall d'Hebron University Hospital (Advanced Clinical Simulation Centre)</t>
+        </is>
+      </c>
+      <c r="C329" s="5" t="inlineStr">
+        <is>
+          <t>Vall d'Hebron Vall d'Hebron and Cleveland Clinic sign an agreement to strengthen educational collaboration in the field of simulation</t>
+        </is>
+      </c>
+      <c r="D329" s="5" t="inlineStr">
+        <is>
+          <t>2025-02-07</t>
+        </is>
+      </c>
+      <c r="E329" s="5" t="inlineStr">
+        <is>
+          <t>https://www.vallhebron.com/en/news/news/vall-dhebron-and-cleveland-clinic-sign-agreement-strengthen-educational-collaboration-field-simulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="5" t="inlineStr">
+        <is>
+          <t>Cleveland Clinic</t>
+        </is>
+      </c>
+      <c r="B330" s="5" t="inlineStr">
+        <is>
+          <t>Vall d'Hebron University Hospital (Advanced Clinical Simulation Centre)</t>
+        </is>
+      </c>
+      <c r="C330" s="5" t="inlineStr">
+        <is>
+          <t>Vall d'Hebron Report 2025</t>
+        </is>
+      </c>
+      <c r="D330" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E330" s="5" t="inlineStr">
+        <is>
+          <t>https://hospital.vallhebron.com/en/about-us/corporate-documentation/report-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="5" t="inlineStr">
+        <is>
+          <t>George Washington University (School of Medicine and Health Sciences)</t>
+        </is>
+      </c>
+      <c r="B331" s="5" t="inlineStr">
+        <is>
+          <t>Universidad Autonoma de Madrid (Faculty of Medicine)</t>
+        </is>
+      </c>
+      <c r="C331" s="5" t="inlineStr">
+        <is>
+          <t>Universidad Autonoma de Madrid, Facultad de Medicina Convocatoria de ayudas 2026-2027 para practicas clinicas en George Washington University</t>
+        </is>
+      </c>
+      <c r="D331" s="5" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="E331" s="5" t="inlineStr">
+        <is>
+          <t>https://www.uam.es/medicina/estudios/practicas-externas/convocatoria-george-washington-university</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="5" t="inlineStr">
+        <is>
+          <t>Harvard Medical School (Harvard University)</t>
+        </is>
+      </c>
+      <c r="B332" s="5" t="inlineStr">
+        <is>
+          <t>Universidad Complutense de Madrid (Faculty of Medicine; Hospital Clinico San Carlos, Hospital 12 de Octubre, Hospital Gregorio Maranon)</t>
+        </is>
+      </c>
+      <c r="C332" s="5" t="inlineStr">
+        <is>
+          <t>Universidad Complutense de Madrid, Facultad de Medicina Clinical rotation at Complutense Medical School (CMS) 2025-26: elective description</t>
+        </is>
+      </c>
+      <c r="D332" s="5" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="E332" s="5" t="inlineStr">
+        <is>
+          <t>https://medicina.ucm.es/file/elective-description-clinical-rotations-hms-cms-2025-2026-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="5" t="inlineStr">
+        <is>
+          <t>Harvard Medical School (Harvard University)</t>
+        </is>
+      </c>
+      <c r="B333" s="5" t="inlineStr">
+        <is>
+          <t>Universidad Complutense de Madrid (Faculty of Medicine; Hospital Clinico San Carlos, Hospital 12 de Octubre, Hospital Gregorio Maranon)</t>
+        </is>
+      </c>
+      <c r="C333" s="5" t="inlineStr">
+        <is>
+          <t>Alberto Martin Siete estudiantes de Medicina realizaran una estancia de un mes en Harvard</t>
+        </is>
+      </c>
+      <c r="D333" s="5" t="inlineStr">
+        <is>
+          <t>2020-01-30</t>
+        </is>
+      </c>
+      <c r="E333" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ucm.es/tribunacomplutense/264/art3995.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="5" t="inlineStr">
+        <is>
+          <t>Harvard Medical School (Harvard University)</t>
+        </is>
+      </c>
+      <c r="B334" s="5" t="inlineStr">
+        <is>
+          <t>Universidad Complutense de Madrid (Faculty of Medicine; Hospital Clinico San Carlos, Hospital 12 de Octubre, Hospital Gregorio Maranon)</t>
+        </is>
+      </c>
+      <c r="C334" s="5" t="inlineStr">
+        <is>
+          <t>Universidad Complutense de Madrid, Facultad de Medicina Convocatoria Becas Harvard Medical School 2022-2023</t>
+        </is>
+      </c>
+      <c r="D334" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E334" s="5" t="inlineStr">
+        <is>
+          <t>https://medicina.ucm.es/data/cont/media/www/805/Convocatoria%20Harvard%202022%20-%2023%20EV-1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="5" t="inlineStr">
+        <is>
+          <t>Johns Hopkins University (Bloomberg School of Public Health)</t>
+        </is>
+      </c>
+      <c r="B335" s="5" t="inlineStr">
+        <is>
+          <t>Universitat Pompeu Fabra (JHU-UPF Public Policy Center), with the Agencia de Salut Publica de Barcelona</t>
+        </is>
+      </c>
+      <c r="C335" s="5" t="inlineStr">
+        <is>
+          <t>JHU-UPF Public Policy Center Annual report: academic year 2024-2025: critical knowledge for decision-making</t>
+        </is>
+      </c>
+      <c r="D335" s="5" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="E335" s="5" t="inlineStr">
+        <is>
+          <t>https://repositori.upf.edu/items/3552909c-eb4b-47bd-91c3-47699ba09b59/full</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="5" t="inlineStr">
+        <is>
+          <t>Johns Hopkins University (Bloomberg School of Public Health)</t>
+        </is>
+      </c>
+      <c r="B336" s="5" t="inlineStr">
+        <is>
+          <t>Universitat Pompeu Fabra (JHU-UPF Public Policy Center), with the Agencia de Salut Publica de Barcelona</t>
+        </is>
+      </c>
+      <c r="C336" s="5" t="inlineStr">
+        <is>
+          <t>JHU-UPF Public Policy Center Hopkins Fall Institute</t>
+        </is>
+      </c>
+      <c r="D336" s="5" t="inlineStr"/>
+      <c r="E336" s="5" t="inlineStr">
+        <is>
+          <t>https://www.upf.edu/web/jhu-ppc/hopkins-fall-institute</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="5" t="inlineStr">
+        <is>
+          <t>Johns Hopkins University (Bloomberg School of Public Health)</t>
+        </is>
+      </c>
+      <c r="B337" s="5" t="inlineStr">
+        <is>
+          <t>Universitat Pompeu Fabra (JHU-UPF Public Policy Center), with the Agencia de Salut Publica de Barcelona</t>
+        </is>
+      </c>
+      <c r="C337" s="5" t="inlineStr">
+        <is>
+          <t>Johns Hopkins Bloomberg School of Public Health Fall Institute in Health Policy and Management</t>
+        </is>
+      </c>
+      <c r="D337" s="5" t="inlineStr"/>
+      <c r="E337" s="5" t="inlineStr">
+        <is>
+          <t>https://publichealth.jhu.edu/academics/fall-institute-in-health-policy-and-management</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="5" t="inlineStr">
+        <is>
+          <t>MD Anderson Cancer Center</t>
+        </is>
+      </c>
+      <c r="B338" s="5" t="inlineStr">
+        <is>
+          <t>MD Anderson Cancer Center Madrid (operated by Grupo Hospiten)</t>
+        </is>
+      </c>
+      <c r="C338" s="5" t="inlineStr">
+        <is>
+          <t>Hospiten MD Anderson Cancer Center Madrid - Hospiten, recognised among the world's leading cancer hospitals by Newsweek and Statista</t>
+        </is>
+      </c>
+      <c r="D338" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E338" s="5" t="inlineStr">
+        <is>
+          <t>https://hospiten.com/en/news/md-anderson-cancer-center-madrid-hospiten-reconocido-los-mejores-hospitales-oncologicos</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="5" t="inlineStr">
+        <is>
+          <t>MD Anderson Cancer Center</t>
+        </is>
+      </c>
+      <c r="B339" s="5" t="inlineStr">
+        <is>
+          <t>MD Anderson Cancer Center Madrid (operated by Grupo Hospiten)</t>
+        </is>
+      </c>
+      <c r="C339" s="5" t="inlineStr">
+        <is>
+          <t>Hospiten MD Anderson Cancer Center Madrid Hospiten, recognized by Forbes among the three best oncology hospitals in Spain</t>
+        </is>
+      </c>
+      <c r="D339" s="5" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="E339" s="5" t="inlineStr">
+        <is>
+          <t>https://hospiten.com/en/news/md-anderson-cancer-center-madrid-hospiten-recognized-by-forbes</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="5" t="inlineStr">
+        <is>
+          <t>MD Anderson Cancer Center</t>
+        </is>
+      </c>
+      <c r="B340" s="5" t="inlineStr">
+        <is>
+          <t>MD Anderson Cancer Center Madrid (operated by Grupo Hospiten)</t>
+        </is>
+      </c>
+      <c r="C340" s="5" t="inlineStr">
+        <is>
+          <t>Hospiten Grupo Hospiten adquiere el 39,98% de las acciones de MD Anderson Cancer Center Madrid</t>
+        </is>
+      </c>
+      <c r="D340" s="5" t="inlineStr">
+        <is>
+          <t>2013-01-10</t>
+        </is>
+      </c>
+      <c r="E340" s="5" t="inlineStr">
+        <is>
+          <t>https://hospiten.com/noticias/grupo-hospiten-compra-a-cartera-industrial-rea-su-participacion-en-el-md-anderson-cancer-center-madrid-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="5" t="inlineStr">
+        <is>
+          <t>MD Anderson Cancer Center</t>
+        </is>
+      </c>
+      <c r="B341" s="5" t="inlineStr">
+        <is>
+          <t>MD Anderson Cancer Center Madrid (operated by Grupo Hospiten)</t>
+        </is>
+      </c>
+      <c r="C341" s="5" t="inlineStr">
+        <is>
+          <t>MD Anderson Cancer Center Chapter 22: Sister Institutions (John Mendelsohn oral history)</t>
+        </is>
+      </c>
+      <c r="D341" s="5" t="inlineStr"/>
+      <c r="E341" s="5" t="inlineStr">
+        <is>
+          <t>https://openworks.mdanderson.org/mchv_interviewchapters/1438/</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="5" t="inlineStr">
+        <is>
+          <t>Mount Sinai Health System (Icahn School of Medicine, Mount Sinai Fuster Heart Hospital)</t>
+        </is>
+      </c>
+      <c r="B342" s="5" t="inlineStr">
+        <is>
+          <t>Centro Nacional de Investigaciones Cardiovasculares Carlos III (CNIC)</t>
+        </is>
+      </c>
+      <c r="C342" s="5" t="inlineStr">
+        <is>
+          <t>Mount Sinai Health System Beta blockers, the standard treatment after a heart attack, may offer no benefit for heart attack patients and women can have worse outcomes</t>
+        </is>
+      </c>
+      <c r="D342" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="E342" s="5" t="inlineStr">
+        <is>
+          <t>https://www.eurekalert.org/news-releases/1096364</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="5" t="inlineStr">
+        <is>
+          <t>Mount Sinai Health System (Icahn School of Medicine, Mount Sinai Fuster Heart Hospital)</t>
+        </is>
+      </c>
+      <c r="B343" s="5" t="inlineStr">
+        <is>
+          <t>Centro Nacional de Investigaciones Cardiovasculares Carlos III (CNIC)</t>
+        </is>
+      </c>
+      <c r="C343" s="5" t="inlineStr">
+        <is>
+          <t>Mount Sinai Health System Presence of subclinical atherosclerosis is marker of mortality and its progression increases risk of death</t>
+        </is>
+      </c>
+      <c r="D343" s="5" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="E343" s="5" t="inlineStr">
+        <is>
+          <t>https://www.eurekalert.org/news-releases/1059621</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="5" t="inlineStr">
+        <is>
+          <t>Mount Sinai Health System (Icahn School of Medicine, Mount Sinai Fuster Heart Hospital)</t>
+        </is>
+      </c>
+      <c r="B344" s="5" t="inlineStr">
+        <is>
+          <t>Centro Nacional de Investigaciones Cardiovasculares Carlos III (CNIC)</t>
+        </is>
+      </c>
+      <c r="C344" s="5" t="inlineStr">
+        <is>
+          <t>CNIC Shared learning between two giants of cardiovascular research</t>
+        </is>
+      </c>
+      <c r="D344" s="5" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="E344" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cnic.es/en/node/821</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="5" t="inlineStr">
+        <is>
+          <t>Penn State College of Medicine and Penn State Health (Beat Childhood Cancer Research Consortium)</t>
+        </is>
+      </c>
+      <c r="B345" s="5" t="inlineStr">
+        <is>
+          <t>Hospital Sant Joan de Déu Barcelona (Pediatric Cancer Center Barcelona)</t>
+        </is>
+      </c>
+      <c r="C345" s="5" t="inlineStr">
+        <is>
+          <t>SJD Barcelona Children's Hospital The SJD Barcelona Children's Hospital will be the first member of the Beat Childhood Cancer Consortium based outside of North America</t>
+        </is>
+      </c>
+      <c r="D345" s="5" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="E345" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sjdhospitalbarcelona.org/en/news/sjd-barcelona-childrens-hospital-will-be-first-member-beat-childhood-cancer-consortium-based-outside-north-america</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="5" t="inlineStr">
+        <is>
+          <t>Penn State College of Medicine and Penn State Health (Beat Childhood Cancer Research Consortium)</t>
+        </is>
+      </c>
+      <c r="B346" s="5" t="inlineStr">
+        <is>
+          <t>Hospital Sant Joan de Déu Barcelona (Pediatric Cancer Center Barcelona)</t>
+        </is>
+      </c>
+      <c r="C346" s="5" t="inlineStr">
+        <is>
+          <t>Penn State Health News Penn State's Beat Childhood Cancer Research Consortium welcomes SJD Pediatric Cancer Center Barcelona</t>
+        </is>
+      </c>
+      <c r="D346" s="5" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="E346" s="5" t="inlineStr">
+        <is>
+          <t>https://pennstatehealthnews.org/2025/11/penn-states-beat-childhood-cancer-research-consortium-welcomes-sjd-pediatric-cancer-center-barcelona/</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="5" t="inlineStr">
+        <is>
+          <t>University of Illinois Chicago (College of Applied Health Sciences)</t>
+        </is>
+      </c>
+      <c r="B347" s="5" t="inlineStr">
+        <is>
+          <t>TecnoCampus School of Health Sciences (Universitat Pompeu Fabra)</t>
+        </is>
+      </c>
+      <c r="C347" s="5" t="inlineStr">
+        <is>
+          <t>Emily Parenti-Lopez AHS dean formalizes international collaboration between UIC and Spanish university</t>
+        </is>
+      </c>
+      <c r="D347" s="5" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="E347" s="5" t="inlineStr">
+        <is>
+          <t>https://ahs.uic.edu/news-stories/ahs-dean-formalizes-international-collaboration-between-uic-and-spanish-university</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="5" t="inlineStr">
+        <is>
+          <t>University of Kansas Medical Center</t>
+        </is>
+      </c>
+      <c r="B348" s="5" t="inlineStr">
+        <is>
+          <t>Universitat Internacional de Catalunya (UIC Barcelona) Faculty of Medicine and Health Sciences</t>
+        </is>
+      </c>
+      <c r="C348" s="5" t="inlineStr">
+        <is>
+          <t>Universitat Internacional de Catalunya Medicine degree brochure (English)</t>
+        </is>
+      </c>
+      <c r="D348" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="E348" s="5" t="inlineStr">
+        <is>
+          <t>https://www.uic.es/sites/default/files/folleto-medicina-eng.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="5" t="inlineStr">
+        <is>
+          <t>University of Kansas Medical Center</t>
+        </is>
+      </c>
+      <c r="B349" s="5" t="inlineStr">
+        <is>
+          <t>Universitat Internacional de Catalunya (UIC Barcelona) Faculty of Medicine and Health Sciences</t>
+        </is>
+      </c>
+      <c r="C349" s="5" t="inlineStr">
+        <is>
+          <t>University of Kansas Medical Center, Office of International Programs International Educational Experiences: Spain</t>
+        </is>
+      </c>
+      <c r="D349" s="5" t="inlineStr"/>
+      <c r="E349" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kumc.edu/academic-and-student-affairs/departments/office-of-international-programs/outbound-programs/international-educational-experiences/program-locations/spain.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="5" t="inlineStr">
+        <is>
+          <t>ABC Medical Center (Centro Médico ABC)</t>
+        </is>
+      </c>
+      <c r="B350" s="5" t="inlineStr">
+        <is>
+          <t>Hospital Sant Joan de Déu Barcelona (SJD Barcelona Children's Hospital)</t>
+        </is>
+      </c>
+      <c r="C350" s="5" t="inlineStr">
+        <is>
+          <t>Hospital Sant Joan de Déu Barcelona The SJD Barcelona Children's Hospital and the ABC Medical Center in Mexico collaborate to advance pediatric oncology</t>
+        </is>
+      </c>
+      <c r="D350" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="E350" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sjdhospitalbarcelona.org/en/news/sjd-barcelona-childrens-hospital-abc-medical-center-mexico-collaborate-advance-pediatric-oncology</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="5" t="inlineStr">
+        <is>
+          <t>Aier Eye Hospital Group</t>
+        </is>
+      </c>
+      <c r="B351" s="5" t="inlineStr">
+        <is>
+          <t>Clínica Baviera</t>
+        </is>
+      </c>
+      <c r="C351" s="5" t="inlineStr">
+        <is>
+          <t>Alimarket Sanidad La china Aier Eye Hospital toma el control de Clínica Baviera</t>
+        </is>
+      </c>
+      <c r="D351" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="E351" s="5" t="inlineStr">
+        <is>
+          <t>https://www.alimarket.es/sanidad/noticia/239028/la-china-aier-eye-hospital-toma-el-control-de-clinica-baviera</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="5" t="inlineStr">
+        <is>
+          <t>Aier Eye Hospital Group</t>
+        </is>
+      </c>
+      <c r="B352" s="5" t="inlineStr">
+        <is>
+          <t>Clínica Baviera</t>
+        </is>
+      </c>
+      <c r="C352" s="5" t="inlineStr">
+        <is>
+          <t>Alantra Alantra Acts as Global Coordinator in the c.EUR42.4mn Placement of Clinica Baviera's Shares</t>
+        </is>
+      </c>
+      <c r="D352" s="5" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="E352" s="5" t="inlineStr">
+        <is>
+          <t>https://www.alantra.com/ib-transaction/clinica-baviera-accelerated-bookbuilding/</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="5" t="inlineStr">
+        <is>
+          <t>Aier Eye Hospital Group</t>
+        </is>
+      </c>
+      <c r="B353" s="5" t="inlineStr">
+        <is>
+          <t>Clínica Baviera</t>
+        </is>
+      </c>
+      <c r="C353" s="5" t="inlineStr">
+        <is>
+          <t>elEconomista Los dueños de Clínica Baviera venden un 8% de la compañía por 42,4 millones</t>
+        </is>
+      </c>
+      <c r="D353" s="5" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="E353" s="5" t="inlineStr">
+        <is>
+          <t>https://www.eleconomista.es/salud-bienestar/noticias/13301420/04/25/los-duenos-de-clinica-baviera-venden-un-8-de-la-compania-por-424-millones.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="5" t="inlineStr">
+        <is>
+          <t>Aier Eye Hospital Group</t>
+        </is>
+      </c>
+      <c r="B354" s="5" t="inlineStr">
+        <is>
+          <t>Clínica Baviera</t>
+        </is>
+      </c>
+      <c r="C354" s="5" t="inlineStr">
+        <is>
+          <t>Clínica Baviera Aier Eye Hospital (shareholder page)</t>
+        </is>
+      </c>
+      <c r="D354" s="5" t="inlineStr"/>
+      <c r="E354" s="5" t="inlineStr">
+        <is>
+          <t>https://grupobaviera.es/accionistas-inversores/en/aier-eye-hospital/</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="5" t="inlineStr">
+        <is>
+          <t>Bupa</t>
+        </is>
+      </c>
+      <c r="B355" s="5" t="inlineStr">
+        <is>
+          <t>Sanitas (Sanitas hospitals)</t>
+        </is>
+      </c>
+      <c r="C355" s="5" t="inlineStr">
+        <is>
+          <t>Bupa Bupa Group full year financial results 2025</t>
+        </is>
+      </c>
+      <c r="D355" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="E355" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bupa.com/news-and-press/press-releases/2026/bupa-group-full-year-financial-results-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="5" t="inlineStr">
+        <is>
+          <t>Bupa</t>
+        </is>
+      </c>
+      <c r="B356" s="5" t="inlineStr">
+        <is>
+          <t>Sanitas (Sanitas hospitals)</t>
+        </is>
+      </c>
+      <c r="C356" s="5" t="inlineStr">
+        <is>
+          <t>Bupa Results announcement and financial statement FY2025</t>
+        </is>
+      </c>
+      <c r="D356" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="E356" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bupa.com/~/media/files/b/bupa-v5/documents/financials/results-centre/2025/bupa-group-results-and-financial-statement-fy2025.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="5" t="inlineStr">
+        <is>
+          <t>Bupa</t>
+        </is>
+      </c>
+      <c r="B357" s="5" t="inlineStr">
+        <is>
+          <t>Sanitas (Sanitas hospitals)</t>
+        </is>
+      </c>
+      <c r="C357" s="5" t="inlineStr">
+        <is>
+          <t>Sanitas Sanitas 2026 executive summary</t>
+        </is>
+      </c>
+      <c r="D357" s="5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E357" s="5" t="inlineStr">
+        <is>
+          <t>https://informeanual.sanitas.es/wp-content/uploads/2026/07/Sanitas_2026_resumen-ejecutivo_EN.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="5" t="inlineStr">
+        <is>
+          <t>Burjeel Cancer Institute (Burjeel Holdings)</t>
+        </is>
+      </c>
+      <c r="B358" s="5" t="inlineStr">
+        <is>
+          <t>Hospital Sant Joan de Déu Barcelona (SJD Barcelona Children's Hospital)</t>
+        </is>
+      </c>
+      <c r="C358" s="5" t="inlineStr">
+        <is>
+          <t>Hospital Sant Joan de Déu Barcelona New international partnership between the SJD Barcelona Children's Hospital and the Burjeel Cancer Institute</t>
+        </is>
+      </c>
+      <c r="D358" s="5" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E358" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sjdhospitalbarcelona.org/en/news/new-international-partnership-between-sjd-barcelona-childrens-hospital-burjeel-cancer-institute</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="5" t="inlineStr">
+        <is>
+          <t>Cancer Core Europe (Gustave Roussy, DKFZ and NCT Heidelberg, Netherlands Cancer Institute, Karolinska Institutet, Cancer Research UK Cambridge Centre, Istituto Nazionale dei Tumori Milan)</t>
+        </is>
+      </c>
+      <c r="B359" s="5" t="inlineStr">
+        <is>
+          <t>Vall d'Hebron Institute of Oncology (VHIO)</t>
+        </is>
+      </c>
+      <c r="C359" s="5" t="inlineStr">
+        <is>
+          <t>VHIO Dr. Josep Tabernero, director of VHIO, chairman of the European consortium Cancer Core Europe</t>
+        </is>
+      </c>
+      <c r="D359" s="5" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="E359" s="5" t="inlineStr">
+        <is>
+          <t>https://vhio.net/2023/10/18/dr-josep-tabernero-director-of-vhio-assumes-the-presidency-of-the-european-project-cancer-core-europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="5" t="inlineStr">
+        <is>
+          <t>Cancer Core Europe (Gustave Roussy, DKFZ and NCT Heidelberg, Netherlands Cancer Institute, Karolinska Institutet, Cancer Research UK Cambridge Centre, Istituto Nazionale dei Tumori Milan)</t>
+        </is>
+      </c>
+      <c r="B360" s="5" t="inlineStr">
+        <is>
+          <t>Vall d'Hebron Institute of Oncology (VHIO)</t>
+        </is>
+      </c>
+      <c r="C360" s="5" t="inlineStr">
+        <is>
+          <t>Karolinska Institutet About Cancer Core Europe (CCE Annual Meeting and Karolinska CCC Days 2026)</t>
+        </is>
+      </c>
+      <c r="D360" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="E360" s="5" t="inlineStr">
+        <is>
+          <t>https://ki.se/en/cancer-research-ki/collaborations/cce-annual-meeting-karolinska-ccc-days-2026/about-cancer-core-europe</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="5" t="inlineStr">
+        <is>
+          <t>Clariane (formerly Korian)</t>
+        </is>
+      </c>
+      <c r="B361" s="5" t="inlineStr">
+        <is>
+          <t>Clariane España (Ita Salud Mental, Grupo 5, Iterias)</t>
+        </is>
+      </c>
+      <c r="C361" s="5" t="inlineStr">
+        <is>
+          <t>Korian Korian Closes the Acquisition of Grupo 5 Reinforcing Korian Position in Mental Health in Spain</t>
+        </is>
+      </c>
+      <c r="D361" s="5" t="inlineStr">
+        <is>
+          <t>2023-01-11</t>
+        </is>
+      </c>
+      <c r="E361" s="5" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20230111005688/en/Korian-Closes-the-Acquisition-of-Grupo-5-Reinforcing-Korian-Position-in-Mental-Health-in-Spain</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="5" t="inlineStr">
+        <is>
+          <t>Clariane (formerly Korian)</t>
+        </is>
+      </c>
+      <c r="B362" s="5" t="inlineStr">
+        <is>
+          <t>Clariane España (Ita Salud Mental, Grupo 5, Iterias)</t>
+        </is>
+      </c>
+      <c r="C362" s="5" t="inlineStr">
+        <is>
+          <t>Clariane Clariane launches Iterias in Spain, a new brand dedicated to psychotherapy for all</t>
+        </is>
+      </c>
+      <c r="D362" s="5" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="E362" s="5" t="inlineStr">
+        <is>
+          <t>https://www.clariane.com/en/press-room/press-releases/clariane-launches-iterias-in-spain-a-new-brand-dedicated-to-psychotherapy</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="5" t="inlineStr">
+        <is>
+          <t>Clariane (formerly Korian)</t>
+        </is>
+      </c>
+      <c r="B363" s="5" t="inlineStr">
+        <is>
+          <t>Clariane España (Ita Salud Mental, Grupo 5, Iterias)</t>
+        </is>
+      </c>
+      <c r="C363" s="5" t="inlineStr">
+        <is>
+          <t>Clariane Clariane in Spain</t>
+        </is>
+      </c>
+      <c r="D363" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E363" s="5" t="inlineStr">
+        <is>
+          <t>https://clariane.com/en/our-locations/clariane-in-spain</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="5" t="inlineStr">
+        <is>
+          <t>Fresenius Helios (Helios Health)</t>
+        </is>
+      </c>
+      <c r="B364" s="5" t="inlineStr">
+        <is>
+          <t>Quirónsalud</t>
+        </is>
+      </c>
+      <c r="C364" s="5" t="inlineStr">
+        <is>
+          <t>Quirónsalud Quirónsalud y Helios crean un grupo sanitario hispano-alemán, el mayor de Europa y uno de los mayores del mundo</t>
+        </is>
+      </c>
+      <c r="D364" s="5" t="inlineStr">
+        <is>
+          <t>2016-09-05</t>
+        </is>
+      </c>
+      <c r="E364" s="5" t="inlineStr">
+        <is>
+          <t>https://www.quironsalud.com/en/communication/news/quironsalud-helios-crean-grupo-sanitario-hispano-alem-25d03</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="5" t="inlineStr">
+        <is>
+          <t>Fresenius Helios (Helios Health)</t>
+        </is>
+      </c>
+      <c r="B365" s="5" t="inlineStr">
+        <is>
+          <t>Quirónsalud</t>
+        </is>
+      </c>
+      <c r="C365" s="5" t="inlineStr">
+        <is>
+          <t>Fresenius SE &amp; Co. KGaA #FutureFresenius: REJUVENATE in action (Q4 and FY 2025 results)</t>
+        </is>
+      </c>
+      <c r="D365" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E365" s="5" t="inlineStr">
+        <is>
+          <t>https://www.fresenius.com/press-release-q4-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="5" t="inlineStr">
+        <is>
+          <t>Fresenius Helios (Helios Health)</t>
+        </is>
+      </c>
+      <c r="B366" s="5" t="inlineStr">
+        <is>
+          <t>Quirónsalud</t>
+        </is>
+      </c>
+      <c r="C366" s="5" t="inlineStr">
+        <is>
+          <t>Fresenius SE &amp; Co. KGaA Fresenius Press Release Q4 and FY 2025</t>
+        </is>
+      </c>
+      <c r="D366" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E366" s="5" t="inlineStr">
+        <is>
+          <t>https://www.fresenius.com/sites/default/files/2026-02/20260225_fse_presserelease_q4_2025.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="5" t="inlineStr">
+        <is>
+          <t>Fresenius Helios (Helios Health)</t>
+        </is>
+      </c>
+      <c r="B367" s="5" t="inlineStr">
+        <is>
+          <t>Quirónsalud</t>
+        </is>
+      </c>
+      <c r="C367" s="5" t="inlineStr">
+        <is>
+          <t>Quirónsalud Quirónsalud corporate site</t>
+        </is>
+      </c>
+      <c r="D367" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E367" s="5" t="inlineStr">
+        <is>
+          <t>https://www.quironsalud.com/en</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="5" t="inlineStr">
+        <is>
+          <t>GenesisCare</t>
+        </is>
+      </c>
+      <c r="B368" s="5" t="inlineStr">
+        <is>
+          <t>GenesisCare España (IMOncology and Oncosur radiotherapy centres)</t>
+        </is>
+      </c>
+      <c r="C368" s="5" t="inlineStr">
+        <is>
+          <t>Alimarket Sanidad El grupo australiano GenesisCare entra en España con la compra del 100% de IMOncology</t>
+        </is>
+      </c>
+      <c r="D368" s="5" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E368" s="5" t="inlineStr">
+        <is>
+          <t>https://www.alimarket.es/noticia/214426/el-grupo-australiano-genesiscare-entra-en-espana-con-la-compra-del-100--de--imoncology</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="5" t="inlineStr">
+        <is>
+          <t>GenesisCare</t>
+        </is>
+      </c>
+      <c r="B369" s="5" t="inlineStr">
+        <is>
+          <t>GenesisCare España (IMOncology and Oncosur radiotherapy centres)</t>
+        </is>
+      </c>
+      <c r="C369" s="5" t="inlineStr">
+        <is>
+          <t>Eva de Frutos Vithas cierra la compra de GenesisCare España</t>
+        </is>
+      </c>
+      <c r="D369" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E369" s="5" t="inlineStr">
+        <is>
+          <t>https://www.alimarket.es/sanidad/noticia/429416/vithas-cierra-la-compra-de-genesiscare-espana</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="5" t="inlineStr">
+        <is>
+          <t>GenesisCare</t>
+        </is>
+      </c>
+      <c r="B370" s="5" t="inlineStr">
+        <is>
+          <t>GenesisCare España (IMOncology and Oncosur radiotherapy centres)</t>
+        </is>
+      </c>
+      <c r="C370" s="5" t="inlineStr">
+        <is>
+          <t>El Español Invertia Vithas adquiere GenesisCare para reforzar su red asistencial oncológica</t>
+        </is>
+      </c>
+      <c r="D370" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E370" s="5" t="inlineStr">
+        <is>
+          <t>https://www.elespanol.com/invertia/observatorios/sanidad/20260721/vithas-adquiere-genesiscare-reforzar-red-asistencial-oncologica-nuevos-centros-hospitalarios/1003744328844_0.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="5" t="inlineStr">
+        <is>
+          <t>Grupo Médico Joya (Hospitales Joya)</t>
+        </is>
+      </c>
+      <c r="B371" s="5" t="inlineStr">
+        <is>
+          <t>HM Hospitales</t>
+        </is>
+      </c>
+      <c r="C371" s="5" t="inlineStr">
+        <is>
+          <t>Alimarket Sanidad HM Hospitales y Grupo Médico Joya sellan una alianza estratégica para impulsar la continuidad asistencial entre España y México</t>
+        </is>
+      </c>
+      <c r="D371" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E371" s="5" t="inlineStr">
+        <is>
+          <t>https://www.alimarket.es/sanidad/noticia/430873/hm-hospitales-y-grupo-medico-joya-sellan-una-alianza-estrategica-para-impulsar-la-continuidad-asistencial-entre-espana-y-mexico</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="5" t="inlineStr">
+        <is>
+          <t>Sun Yat-sen University Cancer Center</t>
+        </is>
+      </c>
+      <c r="B372" s="5" t="inlineStr">
+        <is>
+          <t>Hospital Sant Joan de Déu Barcelona (SJD Barcelona Children's Hospital)</t>
+        </is>
+      </c>
+      <c r="C372" s="5" t="inlineStr">
+        <is>
+          <t>Hospital Sant Joan de Déu Barcelona The SJD Barcelona Children's Hospital signs an agreement with the Sun Yat-sen University Cancer Center to help further research in pediatric oncology</t>
+        </is>
+      </c>
+      <c r="D372" s="5" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="E372" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sjdhospitalbarcelona.org/en/news/sjd-barcelona-childrens-hospital-signs-agreement-sun-yat-sen-university-cancer-center-help-further-research-pediatric-oncology</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="5" t="inlineStr">
+        <is>
+          <t>Sun Yat-sen University Cancer Center</t>
+        </is>
+      </c>
+      <c r="B373" s="5" t="inlineStr">
+        <is>
+          <t>Hospital Sant Joan de Déu Barcelona (SJD Barcelona Children's Hospital)</t>
+        </is>
+      </c>
+      <c r="C373" s="5" t="inlineStr">
+        <is>
+          <t>Hospital Sant Joan de Déu Barcelona SJD Barcelona Children's Hospital experts were invited to the 2025 China Pediatric Oncology Frontier Forum</t>
+        </is>
+      </c>
+      <c r="D373" s="5" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="E373" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sjdhospitalbarcelona.org/en/news/sjd-barcelona-childrens-hospital-experts-were-invited-2025-china-pediatric-oncology-frontier-forum</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="5" t="inlineStr">
+        <is>
+          <t>Vivalto Santé</t>
+        </is>
+      </c>
+      <c r="B374" s="5" t="inlineStr">
+        <is>
+          <t>Ribera (Ribera Salud group)</t>
+        </is>
+      </c>
+      <c r="C374" s="5" t="inlineStr">
+        <is>
+          <t>Becker's Payer Issues Centene completes sale of Spanish, central European businesses</t>
+        </is>
+      </c>
+      <c r="D374" s="5" t="inlineStr">
+        <is>
+          <t>2022-11-17</t>
+        </is>
+      </c>
+      <c r="E374" s="5" t="inlineStr">
+        <is>
+          <t>https://www.beckerspayer.com/m-and-a/centene-completes-sale-of-spanish-central-european-businesses.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="5" t="inlineStr">
+        <is>
+          <t>Vivalto Santé</t>
+        </is>
+      </c>
+      <c r="B375" s="5" t="inlineStr">
+        <is>
+          <t>Ribera (Ribera Salud group)</t>
+        </is>
+      </c>
+      <c r="C375" s="5" t="inlineStr">
+        <is>
+          <t>Vivalto Santé Vivalto Santé entame un fort développement en Europe</t>
+        </is>
+      </c>
+      <c r="D375" s="5" t="inlineStr">
+        <is>
+          <t>2022-11-17</t>
+        </is>
+      </c>
+      <c r="E375" s="5" t="inlineStr">
+        <is>
+          <t>https://www.vivalto-sante.com/wp-content/uploads/2022/11/2022-11-17-Vivalto-Sante-entame-un-fort-developpement-en-europe.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="5" t="inlineStr">
+        <is>
+          <t>Vivalto Santé</t>
+        </is>
+      </c>
+      <c r="B376" s="5" t="inlineStr">
+        <is>
+          <t>Ribera (Ribera Salud group)</t>
+        </is>
+      </c>
+      <c r="C376" s="5" t="inlineStr">
+        <is>
+          <t>Ribera Health Group Ribera signs the acquisition of the HCB Hospitals group and reinforces its growth in the Valencian Community</t>
+        </is>
+      </c>
+      <c r="D376" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="E376" s="5" t="inlineStr">
+        <is>
+          <t>https://www.riberasalud.com/en/ribera-firma-la-adquisicion-del-grupo-hcb-hospitales-y-refuerza-su-crecimiento-en-la-comunidad-valenciana/</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="5" t="inlineStr">
+        <is>
+          <t>Vivalto Santé</t>
+        </is>
+      </c>
+      <c r="B377" s="5" t="inlineStr">
+        <is>
+          <t>Ribera (Ribera Salud group)</t>
+        </is>
+      </c>
+      <c r="C377" s="5" t="inlineStr">
+        <is>
+          <t>Alimarket Sanidad La CNMC autoriza en primera fase y con compromisos la adquisición del Grupo HCB Hospitales por parte de Grupo Ribera</t>
+        </is>
+      </c>
+      <c r="D377" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E377" s="5" t="inlineStr">
+        <is>
+          <t>https://www.alimarket.es/sanidad/noticia/431931/la-cnmc-autoriza-en-primera-fase-y-con-compromisos-la-adquisicion-del-grupo-hcb-hospitales-por-parte-de-grupo-ribera</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="5" t="inlineStr">
+        <is>
+          <t>Vivalto Santé</t>
+        </is>
+      </c>
+      <c r="B378" s="5" t="inlineStr">
+        <is>
+          <t>Ribera (Ribera Salud group)</t>
+        </is>
+      </c>
+      <c r="C378" s="5" t="inlineStr">
+        <is>
+          <t>economia3 Ribera culmina la compra de HCB y refuerza su red sanitaria valenciana</t>
+        </is>
+      </c>
+      <c r="D378" s="5" t="inlineStr">
+        <is>
+          <t>6 October 2026</t>
+        </is>
+      </c>
+      <c r="E378" s="5" t="inlineStr">
+        <is>
+          <t>https://economia3.com/2026/10/06/762373-ribera-culmina-la-compra-de-hcb-y-refuerza-su-red-sanitaria-valenciana/</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="5" t="inlineStr">
+        <is>
+          <t>Johns Hopkins Proton Therapy Center (Johns Hopkins Medicine)</t>
+        </is>
+      </c>
+      <c r="B379" s="5" t="inlineStr">
+        <is>
+          <t>Clínica Universidad de Navarra (Cancer Center) and Facultad de Medicina, Universidad de Navarra</t>
+        </is>
+      </c>
+      <c r="C379" s="5" t="inlineStr">
+        <is>
+          <t>Clínica Universidad de Navarra La Clínica Universidad de Navarra y Johns Hopkins se alían para impulsar la formación en protonterapia en España</t>
+        </is>
+      </c>
+      <c r="D379" s="5" t="inlineStr">
+        <is>
+          <t>2023-10-09</t>
+        </is>
+      </c>
+      <c r="E379" s="5" t="inlineStr">
+        <is>
+          <t>https://cancercenter.cun.es/noticias/clinica-universidad-navarra-johns-hopkins-alian-impulsar-formacion-protonterapia-espana</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="5" t="inlineStr">
+        <is>
+          <t>Hospital de Amor (Barretos Cancer Hospital)</t>
+        </is>
+      </c>
+      <c r="B380" s="5" t="inlineStr">
+        <is>
+          <t>Hospital Sant Joan de Déu Barcelona (SJD Barcelona Children's Hospital)</t>
+        </is>
+      </c>
+      <c r="C380" s="5" t="inlineStr">
+        <is>
+          <t>Hospital Sant Joan de Déu Barcelona SJD Barcelona Children's Hospital and the Brazilian cancer hospital in Barretos sign a collaboration agreement</t>
+        </is>
+      </c>
+      <c r="D380" s="5" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="E380" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sjdhospitalbarcelona.org/en/news/sjd-barcelona-childrens-hospital-brazilian-cancer-hospital-barretos-sign-collaboration-agreement</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="5" t="inlineStr">
+        <is>
+          <t>Fresenius Helios (Helios Health)</t>
+        </is>
+      </c>
+      <c r="B381" s="5" t="inlineStr">
+        <is>
+          <t>Eugin Group (fertility clinics)</t>
+        </is>
+      </c>
+      <c r="C381" s="5" t="inlineStr">
+        <is>
+          <t>Fresenius SE &amp; Co. KGaA Fresenius Helios acquires Eugin Group</t>
+        </is>
+      </c>
+      <c r="D381" s="5" t="inlineStr">
+        <is>
+          <t>2020-12-21</t>
+        </is>
+      </c>
+      <c r="E381" s="5" t="inlineStr">
+        <is>
+          <t>https://www.fresenius.com/sites/default/files/2021-11/FSE_Helios_Acquisition_Eugin_e.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="5" t="inlineStr">
+        <is>
+          <t>Fresenius Helios (Helios Health)</t>
+        </is>
+      </c>
+      <c r="B382" s="5" t="inlineStr">
+        <is>
+          <t>Eugin Group (fertility clinics)</t>
+        </is>
+      </c>
+      <c r="C382" s="5" t="inlineStr">
+        <is>
+          <t>Fresenius SE &amp; Co. KGaA Fresenius successfully completes divestment of fertility services group Eugin</t>
+        </is>
+      </c>
+      <c r="D382" s="5" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="E382" s="5" t="inlineStr">
+        <is>
+          <t>https://www.fresenius.com/sites/default/files/2024-01/20240131_FSE_Press_Release_ClosingEugin.pdf</t>
         </is>
       </c>
     </row>
@@ -19544,6 +22335,60 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E326" r:id="rId325"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E327" r:id="rId326"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E382" r:id="rId381"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
